--- a/dados/base/bpo.xlsx
+++ b/dados/base/bpo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11136" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11137" uniqueCount="254">
   <si>
     <t>CodCliente</t>
   </si>
@@ -733,6 +733,10 @@
     <t>Comentário Padrão   Previsão para conclusão dia 14/09/2026 - Data Comentário: 11/09/2026 16:03</t>
   </si>
   <si>
+    <t>Aguardando Liberação do Fiscal   
+Aguardando e-mail do fiscal. - Data Comentário: 14/09/2026 15:15</t>
+  </si>
+  <si>
     <t>Comentário Padrão   Previsão para conclusão dia 11/09/2026 - Data Comentário: 11/09/2026 16:41</t>
   </si>
   <si>
@@ -1272,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -1334,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -1402,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -1470,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -1538,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -1606,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -1674,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="AF8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -1742,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -1804,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="AF10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -1866,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -1928,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="AF12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -1990,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="AF13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:33">
@@ -2052,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="AF14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -2114,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="AF15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -2176,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="AF16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -2238,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="AF17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -2300,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="AF18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:32">
@@ -2362,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="AF19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:32">
@@ -2424,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="AF20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:32">
@@ -2486,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="AF21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:32">
@@ -2548,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="AF22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -2610,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="AF23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:32">
@@ -2672,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="AF24" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="1:32">
@@ -2734,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:32">
@@ -2796,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:32">
@@ -2858,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="1:32">
@@ -2920,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="AF28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:32">
@@ -2982,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="AF29" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:32">
@@ -3044,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="AF30" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:32">
@@ -3106,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="AF31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:32">
@@ -3168,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="AF32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" spans="1:32">
@@ -3230,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="AF33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" spans="1:32">
@@ -3292,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="AF34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:32">
@@ -3354,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="AF35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:32">
@@ -3416,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="AF36" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" spans="1:32">
@@ -3478,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="AF37" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:32">
@@ -3540,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="AF38" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:32">
@@ -3602,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="AF39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:32">
@@ -3664,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="AF40" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41" spans="1:32">
@@ -3726,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="AF41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:32">
@@ -3788,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="AF42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:32">
@@ -3850,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="AF43" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:32">
@@ -3912,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="AF44" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:32">
@@ -3974,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="AF45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="1:32">
@@ -4036,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="AF46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:32">
@@ -4098,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AF47" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48" spans="1:32">
@@ -4160,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AF48" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:32">
@@ -4222,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="AF49" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:32">
@@ -4284,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="AF50" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:32">
@@ -4346,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="AF51" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="52" spans="1:32">
@@ -4408,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="AF52" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:32">
@@ -4470,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="AF53" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="1:32">
@@ -4532,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AF54" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:32">
@@ -4594,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="AF55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" spans="1:32">
@@ -4656,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="AF56" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57" spans="1:32">
@@ -4718,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="AF57" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="58" spans="1:32">
@@ -4780,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="AF58" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59" spans="1:32">
@@ -4842,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="AF59" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60" spans="1:32">
@@ -4904,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="AF60" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" spans="1:32">
@@ -4966,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="AF61" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62" spans="1:32">
@@ -5028,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="AF62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="63" spans="1:32">
@@ -5090,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="AF63" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="64" spans="1:32">
@@ -5152,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="AF64" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="65" spans="1:32">
@@ -5214,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="AF65" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="66" spans="1:32">
@@ -5276,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AF66" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="67" spans="1:32">
@@ -5338,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="AF67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="68" spans="1:32">
@@ -5400,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="AF68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="69" spans="1:32">
@@ -5462,7 +5466,7 @@
         <v>0</v>
       </c>
       <c r="AF69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="70" spans="1:32">
@@ -5524,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="AF70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="71" spans="1:32">
@@ -5586,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="AF71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="72" spans="1:32">
@@ -5648,7 +5652,7 @@
         <v>0</v>
       </c>
       <c r="AF72" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="1:32">
@@ -5710,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="AF73" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="74" spans="1:32">
@@ -5772,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="AF74" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:32">
@@ -5834,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="AF75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="1:32">
@@ -5896,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="AF76" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" spans="1:32">
@@ -5958,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="AF77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:32">
@@ -6020,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="AF78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:32">
@@ -6082,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="AF79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:32">
@@ -6144,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="AF80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:32">
@@ -6206,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="AF81" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:32">
@@ -6268,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="AF82" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="1:32">
@@ -6330,7 +6334,7 @@
         <v>0</v>
       </c>
       <c r="AF83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="84" spans="1:32">
@@ -6392,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="AF84" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:32">
@@ -6454,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="AF85" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:32">
@@ -6516,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="AF86" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="87" spans="1:32">
@@ -6578,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="AF87" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="88" spans="1:32">
@@ -6640,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="AF88" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="89" spans="1:32">
@@ -6702,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="AF89" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" spans="1:32">
@@ -6764,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="AF90" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="1:32">
@@ -6826,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="AF91" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" spans="1:32">
@@ -6888,7 +6892,7 @@
         <v>0</v>
       </c>
       <c r="AF92" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" spans="1:32">
@@ -6950,7 +6954,7 @@
         <v>0</v>
       </c>
       <c r="AF93" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="94" spans="1:32">
@@ -7012,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="AF94" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95" spans="1:32">
@@ -7074,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="AF95" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="96" spans="1:32">
@@ -7136,7 +7140,7 @@
         <v>0</v>
       </c>
       <c r="AF96" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="97" spans="1:32">
@@ -7198,7 +7202,7 @@
         <v>0</v>
       </c>
       <c r="AF97" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="98" spans="1:32">
@@ -7260,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="AF98" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="99" spans="1:32">
@@ -7322,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="AF99" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="1:32">
@@ -7384,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="AF100" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="101" spans="1:32">
@@ -7446,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="AF101" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="102" spans="1:32">
@@ -7508,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="AF102" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="103" spans="1:32">
@@ -7570,7 +7574,7 @@
         <v>0</v>
       </c>
       <c r="AF103" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="1:32">
@@ -7632,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="AF104" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="105" spans="1:32">
@@ -7694,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="AF105" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" spans="1:32">
@@ -7756,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="AF106" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="107" spans="1:32">
@@ -7818,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="AF107" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="108" spans="1:32">
@@ -7880,7 +7884,7 @@
         <v>0</v>
       </c>
       <c r="AF108" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="109" spans="1:32">
@@ -7942,7 +7946,7 @@
         <v>0</v>
       </c>
       <c r="AF109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="110" spans="1:32">
@@ -8004,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="AF110" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="111" spans="1:32">
@@ -8066,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="AF111" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="112" spans="1:32">
@@ -8128,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="AF112" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="113" spans="1:32">
@@ -8190,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="AF113" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114" spans="1:32">
@@ -8252,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="AF114" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="115" spans="1:32">
@@ -8314,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="AF115" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:32">
@@ -8376,7 +8380,7 @@
         <v>0</v>
       </c>
       <c r="AF116" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="117" spans="1:32">
@@ -8438,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="AF117" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="118" spans="1:32">
@@ -8500,7 +8504,7 @@
         <v>0</v>
       </c>
       <c r="AF118" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="119" spans="1:32">
@@ -8562,7 +8566,7 @@
         <v>0</v>
       </c>
       <c r="AF119" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:32">
@@ -8624,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="AF120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:32">
@@ -8686,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="AF121" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" spans="1:32">
@@ -8748,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="AF122" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123" spans="1:32">
@@ -8810,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="AF123" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="124" spans="1:32">
@@ -8872,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="AF124" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="125" spans="1:32">
@@ -8934,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="AF125" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="126" spans="1:32">
@@ -8996,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="AF126" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="127" spans="1:32">
@@ -9058,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="AF127" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="128" spans="1:32">
@@ -9120,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="AF128" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" spans="1:32">
@@ -9182,7 +9186,7 @@
         <v>0</v>
       </c>
       <c r="AF129" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="130" spans="1:32">
@@ -9244,7 +9248,7 @@
         <v>0</v>
       </c>
       <c r="AF130" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="131" spans="1:32">
@@ -9306,7 +9310,7 @@
         <v>0</v>
       </c>
       <c r="AF131" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="132" spans="1:32">
@@ -9368,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="AF132" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133" spans="1:32">
@@ -9430,7 +9434,7 @@
         <v>0</v>
       </c>
       <c r="AF133" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="134" spans="1:32">
@@ -9492,7 +9496,7 @@
         <v>0</v>
       </c>
       <c r="AF134" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="135" spans="1:32">
@@ -9554,7 +9558,7 @@
         <v>0</v>
       </c>
       <c r="AF135" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="136" spans="1:32">
@@ -9616,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="AF136" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="137" spans="1:32">
@@ -9678,7 +9682,7 @@
         <v>0</v>
       </c>
       <c r="AF137" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="138" spans="1:32">
@@ -9740,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="AF138" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="139" spans="1:32">
@@ -9802,7 +9806,7 @@
         <v>0</v>
       </c>
       <c r="AF139" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="140" spans="1:32">
@@ -9864,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="AF140" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="141" spans="1:32">
@@ -9926,7 +9930,7 @@
         <v>0</v>
       </c>
       <c r="AF141" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="142" spans="1:32">
@@ -9988,7 +9992,7 @@
         <v>0</v>
       </c>
       <c r="AF142" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="143" spans="1:32">
@@ -10050,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="AF143" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144" spans="1:32">
@@ -10112,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="AF144" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="145" spans="1:32">
@@ -10174,7 +10178,7 @@
         <v>0</v>
       </c>
       <c r="AF145" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146" spans="1:32">
@@ -10236,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="AF146" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="147" spans="1:32">
@@ -10298,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="AF147" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="148" spans="1:32">
@@ -10356,11 +10360,14 @@
       <c r="U148" t="s">
         <v>235</v>
       </c>
+      <c r="V148" t="s">
+        <v>239</v>
+      </c>
       <c r="Z148">
         <v>0</v>
       </c>
       <c r="AF148" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:32">
@@ -10422,7 +10429,7 @@
         <v>0</v>
       </c>
       <c r="AF149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:32">
@@ -10484,7 +10491,7 @@
         <v>0</v>
       </c>
       <c r="AF150" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="151" spans="1:32">
@@ -10546,7 +10553,7 @@
         <v>0</v>
       </c>
       <c r="AF151" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="152" spans="1:32">
@@ -10608,7 +10615,7 @@
         <v>0</v>
       </c>
       <c r="AF152" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="153" spans="1:32">
@@ -10670,7 +10677,7 @@
         <v>0</v>
       </c>
       <c r="AF153" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="154" spans="1:32">
@@ -10732,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="AF154" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="155" spans="1:32">
@@ -10794,7 +10801,7 @@
         <v>0</v>
       </c>
       <c r="AF155" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="156" spans="1:32">
@@ -10856,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="AF156" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="157" spans="1:32">
@@ -10918,7 +10925,7 @@
         <v>0</v>
       </c>
       <c r="AF157" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="158" spans="1:32">
@@ -10980,7 +10987,7 @@
         <v>0</v>
       </c>
       <c r="AF158" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="159" spans="1:32">
@@ -11042,7 +11049,7 @@
         <v>0</v>
       </c>
       <c r="AF159" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="160" spans="1:32">
@@ -11104,7 +11111,7 @@
         <v>0</v>
       </c>
       <c r="AF160" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="161" spans="1:32">
@@ -11166,7 +11173,7 @@
         <v>0</v>
       </c>
       <c r="AF161" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="162" spans="1:32">
@@ -11228,7 +11235,7 @@
         <v>0</v>
       </c>
       <c r="AF162" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="163" spans="1:32">
@@ -11290,7 +11297,7 @@
         <v>0</v>
       </c>
       <c r="AF163" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="164" spans="1:32">
@@ -11352,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="AF164" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="165" spans="1:32">
@@ -11414,7 +11421,7 @@
         <v>0</v>
       </c>
       <c r="AF165" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="166" spans="1:32">
@@ -11476,7 +11483,7 @@
         <v>0</v>
       </c>
       <c r="AF166" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="167" spans="1:32">
@@ -11538,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="AF167" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="168" spans="1:32">
@@ -11600,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="AF168" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="169" spans="1:32">
@@ -11662,7 +11669,7 @@
         <v>0</v>
       </c>
       <c r="AF169" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="170" spans="1:32">
@@ -11724,7 +11731,7 @@
         <v>0</v>
       </c>
       <c r="AF170" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="171" spans="1:32">
@@ -11786,7 +11793,7 @@
         <v>0</v>
       </c>
       <c r="AF171" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="172" spans="1:32">
@@ -11848,7 +11855,7 @@
         <v>0</v>
       </c>
       <c r="AF172" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="173" spans="1:32">
@@ -11910,7 +11917,7 @@
         <v>0</v>
       </c>
       <c r="AF173" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="174" spans="1:32">
@@ -11972,7 +11979,7 @@
         <v>0</v>
       </c>
       <c r="AF174" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="175" spans="1:32">
@@ -12034,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="AF175" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="176" spans="1:32">
@@ -12096,7 +12103,7 @@
         <v>0</v>
       </c>
       <c r="AF176" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="177" spans="1:32">
@@ -12158,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="AF177" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="178" spans="1:32">
@@ -12220,7 +12227,7 @@
         <v>0</v>
       </c>
       <c r="AF178" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="179" spans="1:32">
@@ -12282,7 +12289,7 @@
         <v>0</v>
       </c>
       <c r="AF179" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="180" spans="1:32">
@@ -12344,7 +12351,7 @@
         <v>0</v>
       </c>
       <c r="AF180" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="181" spans="1:32">
@@ -12406,7 +12413,7 @@
         <v>0</v>
       </c>
       <c r="AF181" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="182" spans="1:32">
@@ -12468,7 +12475,7 @@
         <v>0</v>
       </c>
       <c r="AF182" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="183" spans="1:32">
@@ -12530,7 +12537,7 @@
         <v>0</v>
       </c>
       <c r="AF183" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="184" spans="1:32">
@@ -12592,7 +12599,7 @@
         <v>0</v>
       </c>
       <c r="AF184" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="185" spans="1:32">
@@ -12654,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="AF185" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="186" spans="1:32">
@@ -12716,7 +12723,7 @@
         <v>0</v>
       </c>
       <c r="AF186" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="187" spans="1:32">
@@ -12778,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="AF187" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="188" spans="1:32">
@@ -12840,7 +12847,7 @@
         <v>0</v>
       </c>
       <c r="AF188" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="189" spans="1:32">
@@ -12902,7 +12909,7 @@
         <v>0</v>
       </c>
       <c r="AF189" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="190" spans="1:32">
@@ -12964,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="AF190" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="191" spans="1:32">
@@ -13026,7 +13033,7 @@
         <v>0</v>
       </c>
       <c r="AF191" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="192" spans="1:32">
@@ -13088,7 +13095,7 @@
         <v>0</v>
       </c>
       <c r="AF192" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="193" spans="1:32">
@@ -13150,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="AF193" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="194" spans="1:32">
@@ -13212,7 +13219,7 @@
         <v>0</v>
       </c>
       <c r="AF194" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="195" spans="1:32">
@@ -13274,7 +13281,7 @@
         <v>0</v>
       </c>
       <c r="AF195" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="196" spans="1:32">
@@ -13336,7 +13343,7 @@
         <v>0</v>
       </c>
       <c r="AF196" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="197" spans="1:32">
@@ -13398,7 +13405,7 @@
         <v>0</v>
       </c>
       <c r="AF197" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="198" spans="1:32">
@@ -13460,7 +13467,7 @@
         <v>0</v>
       </c>
       <c r="AF198" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="199" spans="1:32">
@@ -13522,7 +13529,7 @@
         <v>0</v>
       </c>
       <c r="AF199" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="200" spans="1:32">
@@ -13584,7 +13591,7 @@
         <v>0</v>
       </c>
       <c r="AF200" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="201" spans="1:32">
@@ -13646,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="AF201" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="202" spans="1:32">
@@ -13708,7 +13715,7 @@
         <v>0</v>
       </c>
       <c r="AF202" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="203" spans="1:32">
@@ -13770,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AF203" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="204" spans="1:32">
@@ -13832,7 +13839,7 @@
         <v>0</v>
       </c>
       <c r="AF204" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="205" spans="1:32">
@@ -13894,7 +13901,7 @@
         <v>0</v>
       </c>
       <c r="AF205" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="206" spans="1:32">
@@ -13956,7 +13963,7 @@
         <v>0</v>
       </c>
       <c r="AF206" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="207" spans="1:32">
@@ -14018,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AF207" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="208" spans="1:32">
@@ -14080,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="AF208" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="209" spans="1:32">
@@ -14142,7 +14149,7 @@
         <v>0</v>
       </c>
       <c r="AF209" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="210" spans="1:32">
@@ -14204,7 +14211,7 @@
         <v>0</v>
       </c>
       <c r="AF210" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="211" spans="1:32">
@@ -14266,7 +14273,7 @@
         <v>0</v>
       </c>
       <c r="AF211" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="212" spans="1:32">
@@ -14328,7 +14335,7 @@
         <v>0</v>
       </c>
       <c r="AF212" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="213" spans="1:32">
@@ -14390,7 +14397,7 @@
         <v>0</v>
       </c>
       <c r="AF213" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="214" spans="1:32">
@@ -14452,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="AF214" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="215" spans="1:32">
@@ -14514,7 +14521,7 @@
         <v>0</v>
       </c>
       <c r="AF215" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="216" spans="1:32">
@@ -14576,7 +14583,7 @@
         <v>0</v>
       </c>
       <c r="AF216" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="217" spans="1:32">
@@ -14638,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AF217" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="218" spans="1:32">
@@ -14700,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="AF218" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="219" spans="1:32">
@@ -14762,7 +14769,7 @@
         <v>0</v>
       </c>
       <c r="AF219" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="220" spans="1:32">
@@ -14824,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="AF220" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="221" spans="1:32">
@@ -14886,7 +14893,7 @@
         <v>0</v>
       </c>
       <c r="AF221" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="222" spans="1:32">
@@ -14948,7 +14955,7 @@
         <v>0</v>
       </c>
       <c r="AF222" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="223" spans="1:32">
@@ -15010,7 +15017,7 @@
         <v>0</v>
       </c>
       <c r="AF223" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="224" spans="1:32">
@@ -15072,7 +15079,7 @@
         <v>0</v>
       </c>
       <c r="AF224" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="225" spans="1:32">
@@ -15134,7 +15141,7 @@
         <v>0</v>
       </c>
       <c r="AF225" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="226" spans="1:32">
@@ -15196,7 +15203,7 @@
         <v>0</v>
       </c>
       <c r="AF226" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="227" spans="1:32">
@@ -15258,7 +15265,7 @@
         <v>0</v>
       </c>
       <c r="AF227" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="228" spans="1:32">
@@ -15320,7 +15327,7 @@
         <v>0</v>
       </c>
       <c r="AF228" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="229" spans="1:32">
@@ -15382,7 +15389,7 @@
         <v>0</v>
       </c>
       <c r="AF229" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="230" spans="1:32">
@@ -15444,7 +15451,7 @@
         <v>0</v>
       </c>
       <c r="AF230" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="231" spans="1:32">
@@ -15506,7 +15513,7 @@
         <v>0</v>
       </c>
       <c r="AF231" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="232" spans="1:32">
@@ -15568,7 +15575,7 @@
         <v>0</v>
       </c>
       <c r="AF232" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="233" spans="1:32">
@@ -15630,7 +15637,7 @@
         <v>0</v>
       </c>
       <c r="AF233" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="234" spans="1:32">
@@ -15692,7 +15699,7 @@
         <v>0</v>
       </c>
       <c r="AF234" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="235" spans="1:32">
@@ -15754,7 +15761,7 @@
         <v>0</v>
       </c>
       <c r="AF235" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="236" spans="1:32">
@@ -15816,7 +15823,7 @@
         <v>0</v>
       </c>
       <c r="AF236" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="237" spans="1:32">
@@ -15878,7 +15885,7 @@
         <v>0</v>
       </c>
       <c r="AF237" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="238" spans="1:32">
@@ -15940,7 +15947,7 @@
         <v>0</v>
       </c>
       <c r="AF238" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="239" spans="1:32">
@@ -16002,7 +16009,7 @@
         <v>0</v>
       </c>
       <c r="AF239" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="240" spans="1:32">
@@ -16064,7 +16071,7 @@
         <v>0</v>
       </c>
       <c r="AF240" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="241" spans="1:32">
@@ -16126,7 +16133,7 @@
         <v>0</v>
       </c>
       <c r="AF241" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="242" spans="1:32">
@@ -16188,7 +16195,7 @@
         <v>0</v>
       </c>
       <c r="AF242" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="243" spans="1:32">
@@ -16250,7 +16257,7 @@
         <v>0</v>
       </c>
       <c r="AF243" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="244" spans="1:32">
@@ -16312,7 +16319,7 @@
         <v>0</v>
       </c>
       <c r="AF244" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="245" spans="1:32">
@@ -16374,7 +16381,7 @@
         <v>0</v>
       </c>
       <c r="AF245" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="246" spans="1:32">
@@ -16436,7 +16443,7 @@
         <v>0</v>
       </c>
       <c r="AF246" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="247" spans="1:32">
@@ -16498,7 +16505,7 @@
         <v>0</v>
       </c>
       <c r="AF247" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="248" spans="1:32">
@@ -16560,7 +16567,7 @@
         <v>0</v>
       </c>
       <c r="AF248" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="249" spans="1:32">
@@ -16622,7 +16629,7 @@
         <v>0</v>
       </c>
       <c r="AF249" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="250" spans="1:32">
@@ -16684,7 +16691,7 @@
         <v>0</v>
       </c>
       <c r="AF250" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="251" spans="1:32">
@@ -16746,7 +16753,7 @@
         <v>0</v>
       </c>
       <c r="AF251" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="252" spans="1:32">
@@ -16808,7 +16815,7 @@
         <v>0</v>
       </c>
       <c r="AF252" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="253" spans="1:32">
@@ -16870,7 +16877,7 @@
         <v>0</v>
       </c>
       <c r="AF253" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" spans="1:32">
@@ -16932,7 +16939,7 @@
         <v>0</v>
       </c>
       <c r="AF254" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="255" spans="1:32">
@@ -16994,7 +17001,7 @@
         <v>0</v>
       </c>
       <c r="AF255" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="256" spans="1:32">
@@ -17056,7 +17063,7 @@
         <v>0</v>
       </c>
       <c r="AF256" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="257" spans="1:32">
@@ -17118,7 +17125,7 @@
         <v>0</v>
       </c>
       <c r="AF257" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="258" spans="1:32">
@@ -17180,7 +17187,7 @@
         <v>0</v>
       </c>
       <c r="AF258" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="259" spans="1:32">
@@ -17242,7 +17249,7 @@
         <v>0</v>
       </c>
       <c r="AF259" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="260" spans="1:32">
@@ -17304,7 +17311,7 @@
         <v>0</v>
       </c>
       <c r="AF260" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="261" spans="1:32">
@@ -17366,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="AF261" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="262" spans="1:32">
@@ -17428,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="AF262" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="263" spans="1:32">
@@ -17490,7 +17497,7 @@
         <v>0</v>
       </c>
       <c r="AF263" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="264" spans="1:32">
@@ -17552,7 +17559,7 @@
         <v>0</v>
       </c>
       <c r="AF264" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="265" spans="1:32">
@@ -17614,7 +17621,7 @@
         <v>0</v>
       </c>
       <c r="AF265" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="266" spans="1:32">
@@ -17676,7 +17683,7 @@
         <v>0</v>
       </c>
       <c r="AF266" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="267" spans="1:32">
@@ -17738,7 +17745,7 @@
         <v>0</v>
       </c>
       <c r="AF267" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="268" spans="1:32">
@@ -17800,7 +17807,7 @@
         <v>0</v>
       </c>
       <c r="AF268" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="269" spans="1:32">
@@ -17862,7 +17869,7 @@
         <v>0</v>
       </c>
       <c r="AF269" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="270" spans="1:32">
@@ -17924,7 +17931,7 @@
         <v>0</v>
       </c>
       <c r="AF270" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="271" spans="1:32">
@@ -17986,7 +17993,7 @@
         <v>0</v>
       </c>
       <c r="AF271" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="272" spans="1:32">
@@ -18048,7 +18055,7 @@
         <v>0</v>
       </c>
       <c r="AF272" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="273" spans="1:32">
@@ -18110,7 +18117,7 @@
         <v>0</v>
       </c>
       <c r="AF273" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="274" spans="1:32">
@@ -18172,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="AF274" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="275" spans="1:32">
@@ -18234,7 +18241,7 @@
         <v>0</v>
       </c>
       <c r="AF275" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="276" spans="1:32">
@@ -18296,7 +18303,7 @@
         <v>0</v>
       </c>
       <c r="AF276" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="277" spans="1:32">
@@ -18358,7 +18365,7 @@
         <v>0</v>
       </c>
       <c r="AF277" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="278" spans="1:32">
@@ -18420,7 +18427,7 @@
         <v>0</v>
       </c>
       <c r="AF278" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="279" spans="1:32">
@@ -18482,7 +18489,7 @@
         <v>0</v>
       </c>
       <c r="AF279" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="280" spans="1:32">
@@ -18544,7 +18551,7 @@
         <v>0</v>
       </c>
       <c r="AF280" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="281" spans="1:32">
@@ -18606,7 +18613,7 @@
         <v>0</v>
       </c>
       <c r="AF281" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="282" spans="1:32">
@@ -18668,7 +18675,7 @@
         <v>0</v>
       </c>
       <c r="AF282" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="283" spans="1:32">
@@ -18730,7 +18737,7 @@
         <v>0</v>
       </c>
       <c r="AF283" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="284" spans="1:32">
@@ -18792,7 +18799,7 @@
         <v>0</v>
       </c>
       <c r="AF284" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="285" spans="1:32">
@@ -18854,7 +18861,7 @@
         <v>0</v>
       </c>
       <c r="AF285" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="286" spans="1:32">
@@ -18916,7 +18923,7 @@
         <v>0</v>
       </c>
       <c r="AF286" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="287" spans="1:32">
@@ -18978,7 +18985,7 @@
         <v>0</v>
       </c>
       <c r="AF287" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="288" spans="1:32">
@@ -19040,7 +19047,7 @@
         <v>0</v>
       </c>
       <c r="AF288" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="289" spans="1:32">
@@ -19102,7 +19109,7 @@
         <v>0</v>
       </c>
       <c r="AF289" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="290" spans="1:32">
@@ -19164,7 +19171,7 @@
         <v>0</v>
       </c>
       <c r="AF290" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="291" spans="1:32">
@@ -19226,7 +19233,7 @@
         <v>0</v>
       </c>
       <c r="AF291" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="292" spans="1:32">
@@ -19288,7 +19295,7 @@
         <v>0</v>
       </c>
       <c r="AF292" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="293" spans="1:32">
@@ -19350,7 +19357,7 @@
         <v>0</v>
       </c>
       <c r="AF293" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="294" spans="1:32">
@@ -19412,7 +19419,7 @@
         <v>0</v>
       </c>
       <c r="AF294" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="295" spans="1:32">
@@ -19474,7 +19481,7 @@
         <v>0</v>
       </c>
       <c r="AF295" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="296" spans="1:32">
@@ -19536,7 +19543,7 @@
         <v>0</v>
       </c>
       <c r="AF296" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="297" spans="1:32">
@@ -19598,7 +19605,7 @@
         <v>0</v>
       </c>
       <c r="AF297" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="298" spans="1:32">
@@ -19660,7 +19667,7 @@
         <v>0</v>
       </c>
       <c r="AF298" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="299" spans="1:32">
@@ -19722,7 +19729,7 @@
         <v>0</v>
       </c>
       <c r="AF299" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="300" spans="1:32">
@@ -19784,7 +19791,7 @@
         <v>0</v>
       </c>
       <c r="AF300" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="301" spans="1:32">
@@ -19846,7 +19853,7 @@
         <v>0</v>
       </c>
       <c r="AF301" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="302" spans="1:32">
@@ -19908,7 +19915,7 @@
         <v>0</v>
       </c>
       <c r="AF302" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="303" spans="1:32">
@@ -19970,7 +19977,7 @@
         <v>0</v>
       </c>
       <c r="AF303" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="304" spans="1:32">
@@ -20032,7 +20039,7 @@
         <v>0</v>
       </c>
       <c r="AF304" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="305" spans="1:32">
@@ -20094,7 +20101,7 @@
         <v>0</v>
       </c>
       <c r="AF305" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="306" spans="1:32">
@@ -20156,7 +20163,7 @@
         <v>0</v>
       </c>
       <c r="AF306" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="307" spans="1:32">
@@ -20218,7 +20225,7 @@
         <v>0</v>
       </c>
       <c r="AF307" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="308" spans="1:32">
@@ -20280,7 +20287,7 @@
         <v>0</v>
       </c>
       <c r="AF308" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="309" spans="1:32">
@@ -20342,7 +20349,7 @@
         <v>0</v>
       </c>
       <c r="AF309" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="310" spans="1:32">
@@ -20404,7 +20411,7 @@
         <v>0</v>
       </c>
       <c r="AF310" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="311" spans="1:32">
@@ -20466,7 +20473,7 @@
         <v>0</v>
       </c>
       <c r="AF311" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="312" spans="1:32">
@@ -20528,7 +20535,7 @@
         <v>0</v>
       </c>
       <c r="AF312" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="313" spans="1:32">
@@ -20590,7 +20597,7 @@
         <v>0</v>
       </c>
       <c r="AF313" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="314" spans="1:32">
@@ -20652,7 +20659,7 @@
         <v>0</v>
       </c>
       <c r="AF314" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="315" spans="1:32">
@@ -20714,7 +20721,7 @@
         <v>0</v>
       </c>
       <c r="AF315" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="316" spans="1:32">
@@ -20776,7 +20783,7 @@
         <v>0</v>
       </c>
       <c r="AF316" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="317" spans="1:32">
@@ -20838,7 +20845,7 @@
         <v>0</v>
       </c>
       <c r="AF317" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="318" spans="1:32">
@@ -20900,7 +20907,7 @@
         <v>0</v>
       </c>
       <c r="AF318" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="319" spans="1:32">
@@ -20962,7 +20969,7 @@
         <v>0</v>
       </c>
       <c r="AF319" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="320" spans="1:32">
@@ -21024,7 +21031,7 @@
         <v>0</v>
       </c>
       <c r="AF320" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="321" spans="1:32">
@@ -21086,7 +21093,7 @@
         <v>0</v>
       </c>
       <c r="AF321" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="322" spans="1:32">
@@ -21148,7 +21155,7 @@
         <v>0</v>
       </c>
       <c r="AF322" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="323" spans="1:32">
@@ -21210,7 +21217,7 @@
         <v>0</v>
       </c>
       <c r="AF323" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="324" spans="1:32">
@@ -21272,7 +21279,7 @@
         <v>0</v>
       </c>
       <c r="AF324" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="325" spans="1:32">
@@ -21334,7 +21341,7 @@
         <v>0</v>
       </c>
       <c r="AF325" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="326" spans="1:32">
@@ -21396,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="AF326" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="327" spans="1:32">
@@ -21458,7 +21465,7 @@
         <v>0</v>
       </c>
       <c r="AF327" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="328" spans="1:32">
@@ -21520,7 +21527,7 @@
         <v>0</v>
       </c>
       <c r="AF328" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="329" spans="1:32">
@@ -21582,7 +21589,7 @@
         <v>0</v>
       </c>
       <c r="AF329" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="330" spans="1:32">
@@ -21644,7 +21651,7 @@
         <v>0</v>
       </c>
       <c r="AF330" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="331" spans="1:32">
@@ -21706,7 +21713,7 @@
         <v>0</v>
       </c>
       <c r="AF331" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="332" spans="1:32">
@@ -21768,7 +21775,7 @@
         <v>0</v>
       </c>
       <c r="AF332" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="333" spans="1:32">
@@ -21830,7 +21837,7 @@
         <v>0</v>
       </c>
       <c r="AF333" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="334" spans="1:32">
@@ -21892,7 +21899,7 @@
         <v>0</v>
       </c>
       <c r="AF334" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="335" spans="1:32">
@@ -21954,7 +21961,7 @@
         <v>0</v>
       </c>
       <c r="AF335" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="336" spans="1:32">
@@ -22016,7 +22023,7 @@
         <v>0</v>
       </c>
       <c r="AF336" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="337" spans="1:32">
@@ -22078,7 +22085,7 @@
         <v>0</v>
       </c>
       <c r="AF337" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="338" spans="1:32">
@@ -22140,7 +22147,7 @@
         <v>0</v>
       </c>
       <c r="AF338" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="339" spans="1:32">
@@ -22202,7 +22209,7 @@
         <v>0</v>
       </c>
       <c r="AF339" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="340" spans="1:32">
@@ -22264,7 +22271,7 @@
         <v>0</v>
       </c>
       <c r="AF340" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="341" spans="1:32">
@@ -22326,7 +22333,7 @@
         <v>0</v>
       </c>
       <c r="AF341" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="342" spans="1:32">
@@ -22388,7 +22395,7 @@
         <v>0</v>
       </c>
       <c r="AF342" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="343" spans="1:32">
@@ -22450,7 +22457,7 @@
         <v>0</v>
       </c>
       <c r="AF343" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="344" spans="1:32">
@@ -22512,7 +22519,7 @@
         <v>0</v>
       </c>
       <c r="AF344" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="345" spans="1:32">
@@ -22574,7 +22581,7 @@
         <v>0</v>
       </c>
       <c r="AF345" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="346" spans="1:32">
@@ -22636,7 +22643,7 @@
         <v>0</v>
       </c>
       <c r="AF346" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="347" spans="1:32">
@@ -22698,7 +22705,7 @@
         <v>0</v>
       </c>
       <c r="AF347" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="348" spans="1:32">
@@ -22760,7 +22767,7 @@
         <v>0</v>
       </c>
       <c r="AF348" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="349" spans="1:32">
@@ -22822,7 +22829,7 @@
         <v>0</v>
       </c>
       <c r="AF349" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="350" spans="1:32">
@@ -22884,7 +22891,7 @@
         <v>0</v>
       </c>
       <c r="AF350" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="351" spans="1:32">
@@ -22946,7 +22953,7 @@
         <v>0</v>
       </c>
       <c r="AF351" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="352" spans="1:32">
@@ -23008,7 +23015,7 @@
         <v>0</v>
       </c>
       <c r="AF352" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="353" spans="1:32">
@@ -23070,7 +23077,7 @@
         <v>0</v>
       </c>
       <c r="AF353" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="354" spans="1:32">
@@ -23132,7 +23139,7 @@
         <v>0</v>
       </c>
       <c r="AF354" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="355" spans="1:32">
@@ -23194,7 +23201,7 @@
         <v>0</v>
       </c>
       <c r="AF355" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="356" spans="1:32">
@@ -23256,7 +23263,7 @@
         <v>0</v>
       </c>
       <c r="AF356" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="357" spans="1:32">
@@ -23318,7 +23325,7 @@
         <v>0</v>
       </c>
       <c r="AF357" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="358" spans="1:32">
@@ -23380,7 +23387,7 @@
         <v>0</v>
       </c>
       <c r="AF358" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="359" spans="1:32">
@@ -23442,7 +23449,7 @@
         <v>0</v>
       </c>
       <c r="AF359" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="360" spans="1:32">
@@ -23504,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="AF360" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="361" spans="1:32">
@@ -23566,7 +23573,7 @@
         <v>0</v>
       </c>
       <c r="AF361" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="362" spans="1:32">
@@ -23628,7 +23635,7 @@
         <v>0</v>
       </c>
       <c r="AF362" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="363" spans="1:32">
@@ -23690,7 +23697,7 @@
         <v>0</v>
       </c>
       <c r="AF363" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="364" spans="1:32">
@@ -23752,7 +23759,7 @@
         <v>0</v>
       </c>
       <c r="AF364" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="365" spans="1:32">
@@ -23814,7 +23821,7 @@
         <v>0</v>
       </c>
       <c r="AF365" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="366" spans="1:32">
@@ -23876,7 +23883,7 @@
         <v>0</v>
       </c>
       <c r="AF366" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="367" spans="1:32">
@@ -23938,7 +23945,7 @@
         <v>0</v>
       </c>
       <c r="AF367" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="368" spans="1:32">
@@ -24000,7 +24007,7 @@
         <v>0</v>
       </c>
       <c r="AF368" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="369" spans="1:32">
@@ -24062,7 +24069,7 @@
         <v>0</v>
       </c>
       <c r="AF369" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="370" spans="1:32">
@@ -24124,7 +24131,7 @@
         <v>0</v>
       </c>
       <c r="AF370" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="371" spans="1:32">
@@ -24186,7 +24193,7 @@
         <v>0</v>
       </c>
       <c r="AF371" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="372" spans="1:32">
@@ -24248,7 +24255,7 @@
         <v>0</v>
       </c>
       <c r="AF372" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="373" spans="1:32">
@@ -24310,7 +24317,7 @@
         <v>0</v>
       </c>
       <c r="AF373" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="374" spans="1:32">
@@ -24372,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="AF374" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="375" spans="1:32">
@@ -24434,7 +24441,7 @@
         <v>0</v>
       </c>
       <c r="AF375" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="376" spans="1:32">
@@ -24496,7 +24503,7 @@
         <v>0</v>
       </c>
       <c r="AF376" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="377" spans="1:32">
@@ -24558,7 +24565,7 @@
         <v>0</v>
       </c>
       <c r="AF377" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="378" spans="1:32">
@@ -24620,7 +24627,7 @@
         <v>0</v>
       </c>
       <c r="AF378" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="379" spans="1:32">
@@ -24682,7 +24689,7 @@
         <v>0</v>
       </c>
       <c r="AF379" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="380" spans="1:32">
@@ -24744,7 +24751,7 @@
         <v>0</v>
       </c>
       <c r="AF380" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="381" spans="1:32">
@@ -24806,7 +24813,7 @@
         <v>0</v>
       </c>
       <c r="AF381" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="382" spans="1:32">
@@ -24868,7 +24875,7 @@
         <v>0</v>
       </c>
       <c r="AF382" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="383" spans="1:32">
@@ -24930,7 +24937,7 @@
         <v>0</v>
       </c>
       <c r="AF383" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="384" spans="1:32">
@@ -24992,7 +24999,7 @@
         <v>0</v>
       </c>
       <c r="AF384" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="385" spans="1:32">
@@ -25054,7 +25061,7 @@
         <v>0</v>
       </c>
       <c r="AF385" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="386" spans="1:32">
@@ -25116,7 +25123,7 @@
         <v>0</v>
       </c>
       <c r="AF386" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="387" spans="1:32">
@@ -25178,7 +25185,7 @@
         <v>0</v>
       </c>
       <c r="AF387" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="388" spans="1:32">
@@ -25240,7 +25247,7 @@
         <v>0</v>
       </c>
       <c r="AF388" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="389" spans="1:32">
@@ -25302,7 +25309,7 @@
         <v>0</v>
       </c>
       <c r="AF389" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="390" spans="1:32">
@@ -25364,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="AF390" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="391" spans="1:32">
@@ -25426,7 +25433,7 @@
         <v>0</v>
       </c>
       <c r="AF391" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="392" spans="1:32">
@@ -25488,7 +25495,7 @@
         <v>0</v>
       </c>
       <c r="AF392" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="393" spans="1:32">
@@ -25550,7 +25557,7 @@
         <v>0</v>
       </c>
       <c r="AF393" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="394" spans="1:32">
@@ -25612,7 +25619,7 @@
         <v>0</v>
       </c>
       <c r="AF394" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="395" spans="1:32">
@@ -25674,7 +25681,7 @@
         <v>0</v>
       </c>
       <c r="AF395" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="396" spans="1:32">
@@ -25736,7 +25743,7 @@
         <v>0</v>
       </c>
       <c r="AF396" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="397" spans="1:32">
@@ -25798,7 +25805,7 @@
         <v>0</v>
       </c>
       <c r="AF397" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="398" spans="1:32">
@@ -25860,7 +25867,7 @@
         <v>0</v>
       </c>
       <c r="AF398" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="399" spans="1:32">
@@ -25922,7 +25929,7 @@
         <v>0</v>
       </c>
       <c r="AF399" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="400" spans="1:32">
@@ -25984,7 +25991,7 @@
         <v>0</v>
       </c>
       <c r="AF400" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="401" spans="1:32">
@@ -26046,7 +26053,7 @@
         <v>0</v>
       </c>
       <c r="AF401" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="402" spans="1:32">
@@ -26108,7 +26115,7 @@
         <v>0</v>
       </c>
       <c r="AF402" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="403" spans="1:32">
@@ -26170,7 +26177,7 @@
         <v>0</v>
       </c>
       <c r="AF403" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="404" spans="1:32">
@@ -26232,7 +26239,7 @@
         <v>0</v>
       </c>
       <c r="AF404" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="405" spans="1:32">
@@ -26294,7 +26301,7 @@
         <v>0</v>
       </c>
       <c r="AF405" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="406" spans="1:32">
@@ -26356,7 +26363,7 @@
         <v>0</v>
       </c>
       <c r="AF406" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="407" spans="1:32">
@@ -26418,7 +26425,7 @@
         <v>0</v>
       </c>
       <c r="AF407" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="408" spans="1:32">
@@ -26480,7 +26487,7 @@
         <v>0</v>
       </c>
       <c r="AF408" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="409" spans="1:32">
@@ -26542,7 +26549,7 @@
         <v>0</v>
       </c>
       <c r="AF409" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="410" spans="1:32">
@@ -26604,7 +26611,7 @@
         <v>0</v>
       </c>
       <c r="AF410" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="411" spans="1:32">
@@ -26666,7 +26673,7 @@
         <v>0</v>
       </c>
       <c r="AF411" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="412" spans="1:32">
@@ -26728,7 +26735,7 @@
         <v>0</v>
       </c>
       <c r="AF412" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="413" spans="1:32">
@@ -26790,7 +26797,7 @@
         <v>0</v>
       </c>
       <c r="AF413" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="414" spans="1:32">
@@ -26852,7 +26859,7 @@
         <v>0</v>
       </c>
       <c r="AF414" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="415" spans="1:32">
@@ -26914,7 +26921,7 @@
         <v>0</v>
       </c>
       <c r="AF415" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="416" spans="1:32">
@@ -26976,7 +26983,7 @@
         <v>0</v>
       </c>
       <c r="AF416" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="417" spans="1:32">
@@ -27038,7 +27045,7 @@
         <v>0</v>
       </c>
       <c r="AF417" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="418" spans="1:32">
@@ -27100,7 +27107,7 @@
         <v>0</v>
       </c>
       <c r="AF418" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="419" spans="1:32">
@@ -27162,7 +27169,7 @@
         <v>0</v>
       </c>
       <c r="AF419" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="420" spans="1:32">
@@ -27224,7 +27231,7 @@
         <v>0</v>
       </c>
       <c r="AF420" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="421" spans="1:32">
@@ -27286,7 +27293,7 @@
         <v>0</v>
       </c>
       <c r="AF421" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="422" spans="1:32">
@@ -27348,7 +27355,7 @@
         <v>0</v>
       </c>
       <c r="AF422" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="423" spans="1:32">
@@ -27410,7 +27417,7 @@
         <v>0</v>
       </c>
       <c r="AF423" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="424" spans="1:32">
@@ -27472,7 +27479,7 @@
         <v>0</v>
       </c>
       <c r="AF424" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="425" spans="1:32">
@@ -27534,7 +27541,7 @@
         <v>0</v>
       </c>
       <c r="AF425" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="426" spans="1:32">
@@ -27596,7 +27603,7 @@
         <v>0</v>
       </c>
       <c r="AF426" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="427" spans="1:32">
@@ -27658,7 +27665,7 @@
         <v>0</v>
       </c>
       <c r="AF427" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="428" spans="1:32">
@@ -27720,7 +27727,7 @@
         <v>0</v>
       </c>
       <c r="AF428" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="429" spans="1:32">
@@ -27782,7 +27789,7 @@
         <v>0</v>
       </c>
       <c r="AF429" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="430" spans="1:32">
@@ -27844,7 +27851,7 @@
         <v>0</v>
       </c>
       <c r="AF430" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="431" spans="1:32">
@@ -27906,7 +27913,7 @@
         <v>0</v>
       </c>
       <c r="AF431" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="432" spans="1:32">
@@ -27968,7 +27975,7 @@
         <v>0</v>
       </c>
       <c r="AF432" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="433" spans="1:32">
@@ -28030,7 +28037,7 @@
         <v>0</v>
       </c>
       <c r="AF433" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="434" spans="1:32">
@@ -28092,7 +28099,7 @@
         <v>0</v>
       </c>
       <c r="AF434" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="435" spans="1:32">
@@ -28154,7 +28161,7 @@
         <v>0</v>
       </c>
       <c r="AF435" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="436" spans="1:32">
@@ -28216,7 +28223,7 @@
         <v>0</v>
       </c>
       <c r="AF436" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="437" spans="1:32">
@@ -28278,7 +28285,7 @@
         <v>0</v>
       </c>
       <c r="AF437" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="438" spans="1:32">
@@ -28340,7 +28347,7 @@
         <v>0</v>
       </c>
       <c r="AF438" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="439" spans="1:32">
@@ -28402,7 +28409,7 @@
         <v>0</v>
       </c>
       <c r="AF439" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="440" spans="1:32">
@@ -28464,7 +28471,7 @@
         <v>0</v>
       </c>
       <c r="AF440" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="441" spans="1:32">
@@ -28526,7 +28533,7 @@
         <v>0</v>
       </c>
       <c r="AF441" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="442" spans="1:32">
@@ -28588,7 +28595,7 @@
         <v>0</v>
       </c>
       <c r="AF442" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="443" spans="1:32">
@@ -28650,7 +28657,7 @@
         <v>0</v>
       </c>
       <c r="AF443" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="444" spans="1:32">
@@ -28712,7 +28719,7 @@
         <v>0</v>
       </c>
       <c r="AF444" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="445" spans="1:32">
@@ -28774,7 +28781,7 @@
         <v>0</v>
       </c>
       <c r="AF445" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="446" spans="1:32">
@@ -28836,7 +28843,7 @@
         <v>0</v>
       </c>
       <c r="AF446" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="447" spans="1:32">
@@ -28898,7 +28905,7 @@
         <v>0</v>
       </c>
       <c r="AF447" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="448" spans="1:32">
@@ -28960,7 +28967,7 @@
         <v>0</v>
       </c>
       <c r="AF448" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="449" spans="1:32">
@@ -29022,7 +29029,7 @@
         <v>0</v>
       </c>
       <c r="AF449" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="450" spans="1:32">
@@ -29084,7 +29091,7 @@
         <v>0</v>
       </c>
       <c r="AF450" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="451" spans="1:32">
@@ -29146,7 +29153,7 @@
         <v>0</v>
       </c>
       <c r="AF451" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="452" spans="1:32">
@@ -29208,7 +29215,7 @@
         <v>0</v>
       </c>
       <c r="AF452" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="453" spans="1:32">
@@ -29270,7 +29277,7 @@
         <v>0</v>
       </c>
       <c r="AF453" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="454" spans="1:32">
@@ -29332,7 +29339,7 @@
         <v>0</v>
       </c>
       <c r="AF454" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="455" spans="1:32">
@@ -29394,7 +29401,7 @@
         <v>0</v>
       </c>
       <c r="AF455" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="456" spans="1:32">
@@ -29456,7 +29463,7 @@
         <v>0</v>
       </c>
       <c r="AF456" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="457" spans="1:32">
@@ -29518,7 +29525,7 @@
         <v>0</v>
       </c>
       <c r="AF457" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="458" spans="1:32">
@@ -29580,7 +29587,7 @@
         <v>0</v>
       </c>
       <c r="AF458" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="459" spans="1:32">
@@ -29642,7 +29649,7 @@
         <v>0</v>
       </c>
       <c r="AF459" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="460" spans="1:32">
@@ -29704,7 +29711,7 @@
         <v>0</v>
       </c>
       <c r="AF460" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="461" spans="1:32">
@@ -29766,7 +29773,7 @@
         <v>0</v>
       </c>
       <c r="AF461" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="462" spans="1:32">
@@ -29828,7 +29835,7 @@
         <v>0</v>
       </c>
       <c r="AF462" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="463" spans="1:32">
@@ -29890,7 +29897,7 @@
         <v>0</v>
       </c>
       <c r="AF463" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="464" spans="1:32">
@@ -29952,7 +29959,7 @@
         <v>0</v>
       </c>
       <c r="AF464" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="465" spans="1:32">
@@ -30014,7 +30021,7 @@
         <v>0</v>
       </c>
       <c r="AF465" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="466" spans="1:32">
@@ -30076,7 +30083,7 @@
         <v>0</v>
       </c>
       <c r="AF466" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="467" spans="1:32">
@@ -30138,7 +30145,7 @@
         <v>0</v>
       </c>
       <c r="AF467" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="468" spans="1:32">
@@ -30206,7 +30213,7 @@
         <v>220</v>
       </c>
       <c r="AF468" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="469" spans="1:32">
@@ -30274,7 +30281,7 @@
         <v>220</v>
       </c>
       <c r="AF469" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="470" spans="1:32">
@@ -30342,7 +30349,7 @@
         <v>220</v>
       </c>
       <c r="AF470" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="471" spans="1:32">
@@ -30410,7 +30417,7 @@
         <v>220</v>
       </c>
       <c r="AF471" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="472" spans="1:32">
@@ -30478,7 +30485,7 @@
         <v>220</v>
       </c>
       <c r="AF472" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="473" spans="1:32">
@@ -30546,7 +30553,7 @@
         <v>220</v>
       </c>
       <c r="AF473" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="474" spans="1:32">
@@ -30614,7 +30621,7 @@
         <v>220</v>
       </c>
       <c r="AF474" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="475" spans="1:32">
@@ -30682,7 +30689,7 @@
         <v>220</v>
       </c>
       <c r="AF475" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="476" spans="1:32">
@@ -30750,7 +30757,7 @@
         <v>220</v>
       </c>
       <c r="AF476" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="477" spans="1:32">
@@ -30818,7 +30825,7 @@
         <v>220</v>
       </c>
       <c r="AF477" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="478" spans="1:32">
@@ -30886,7 +30893,7 @@
         <v>220</v>
       </c>
       <c r="AF478" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="479" spans="1:32">
@@ -30954,7 +30961,7 @@
         <v>220</v>
       </c>
       <c r="AF479" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="480" spans="1:32">
@@ -31022,7 +31029,7 @@
         <v>220</v>
       </c>
       <c r="AF480" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="481" spans="1:32">
@@ -31090,7 +31097,7 @@
         <v>220</v>
       </c>
       <c r="AF481" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="482" spans="1:32">
@@ -31155,10 +31162,10 @@
         <v>0</v>
       </c>
       <c r="AA482" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF482" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="483" spans="1:32">
@@ -31223,10 +31230,10 @@
         <v>0</v>
       </c>
       <c r="AA483" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF483" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="484" spans="1:32">
@@ -31291,10 +31298,10 @@
         <v>0</v>
       </c>
       <c r="AA484" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF484" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="485" spans="1:32">
@@ -31359,10 +31366,10 @@
         <v>0</v>
       </c>
       <c r="AA485" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF485" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="486" spans="1:32">
@@ -31427,10 +31434,10 @@
         <v>0</v>
       </c>
       <c r="AA486" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF486" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="487" spans="1:32">
@@ -31495,10 +31502,10 @@
         <v>0</v>
       </c>
       <c r="AA487" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF487" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="488" spans="1:32">
@@ -31563,10 +31570,10 @@
         <v>0</v>
       </c>
       <c r="AA488" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF488" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="489" spans="1:32">
@@ -31631,10 +31638,10 @@
         <v>0</v>
       </c>
       <c r="AA489" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF489" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="490" spans="1:32">
@@ -31699,10 +31706,10 @@
         <v>0</v>
       </c>
       <c r="AA490" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF490" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="491" spans="1:32">
@@ -31770,7 +31777,7 @@
         <v>216</v>
       </c>
       <c r="AF491" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="492" spans="1:32">
@@ -31838,7 +31845,7 @@
         <v>216</v>
       </c>
       <c r="AF492" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="493" spans="1:32">
@@ -31906,7 +31913,7 @@
         <v>216</v>
       </c>
       <c r="AF493" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="494" spans="1:32">
@@ -31974,7 +31981,7 @@
         <v>216</v>
       </c>
       <c r="AF494" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="495" spans="1:32">
@@ -32042,7 +32049,7 @@
         <v>216</v>
       </c>
       <c r="AF495" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="496" spans="1:32">
@@ -32110,7 +32117,7 @@
         <v>216</v>
       </c>
       <c r="AF496" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="497" spans="1:32">
@@ -32178,7 +32185,7 @@
         <v>216</v>
       </c>
       <c r="AF497" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="498" spans="1:32">
@@ -32246,7 +32253,7 @@
         <v>216</v>
       </c>
       <c r="AF498" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="499" spans="1:32">
@@ -32314,7 +32321,7 @@
         <v>216</v>
       </c>
       <c r="AF499" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="500" spans="1:32">
@@ -32382,7 +32389,7 @@
         <v>216</v>
       </c>
       <c r="AF500" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="501" spans="1:32">
@@ -32450,7 +32457,7 @@
         <v>216</v>
       </c>
       <c r="AF501" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="502" spans="1:32">
@@ -32515,10 +32522,10 @@
         <v>0</v>
       </c>
       <c r="AA502" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF502" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="503" spans="1:32">
@@ -32583,10 +32590,10 @@
         <v>0</v>
       </c>
       <c r="AA503" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF503" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="504" spans="1:32">
@@ -32651,7 +32658,7 @@
         <v>235</v>
       </c>
       <c r="V504" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Z504">
         <v>0</v>
@@ -32660,7 +32667,7 @@
         <v>216</v>
       </c>
       <c r="AF504" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="505" spans="1:32">
@@ -32728,7 +32735,7 @@
         <v>216</v>
       </c>
       <c r="AF505" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="506" spans="1:32">
@@ -32796,7 +32803,7 @@
         <v>216</v>
       </c>
       <c r="AF506" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="507" spans="1:32">
@@ -32864,7 +32871,7 @@
         <v>216</v>
       </c>
       <c r="AF507" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="508" spans="1:32">
@@ -32932,7 +32939,7 @@
         <v>216</v>
       </c>
       <c r="AF508" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="509" spans="1:32">
@@ -33000,7 +33007,7 @@
         <v>216</v>
       </c>
       <c r="AF509" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="510" spans="1:32">
@@ -33062,16 +33069,16 @@
         <v>236</v>
       </c>
       <c r="V510" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Z510">
         <v>0</v>
       </c>
       <c r="AA510" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF510" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="511" spans="1:32">
@@ -33133,16 +33140,16 @@
         <v>236</v>
       </c>
       <c r="V511" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Z511">
         <v>0</v>
       </c>
       <c r="AA511" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF511" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="512" spans="1:32">
@@ -33204,16 +33211,16 @@
         <v>236</v>
       </c>
       <c r="V512" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z512">
         <v>0</v>
       </c>
       <c r="AA512" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF512" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="513" spans="1:32">
@@ -33275,16 +33282,16 @@
         <v>236</v>
       </c>
       <c r="V513" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z513">
         <v>0</v>
       </c>
       <c r="AA513" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF513" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="514" spans="1:32">
@@ -33346,16 +33353,16 @@
         <v>236</v>
       </c>
       <c r="V514" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z514">
         <v>0</v>
       </c>
       <c r="AA514" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF514" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="515" spans="1:32">
@@ -33417,16 +33424,16 @@
         <v>236</v>
       </c>
       <c r="V515" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z515">
         <v>0</v>
       </c>
       <c r="AA515" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF515" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="516" spans="1:32">
@@ -33488,16 +33495,16 @@
         <v>236</v>
       </c>
       <c r="V516" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z516">
         <v>0</v>
       </c>
       <c r="AA516" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF516" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="517" spans="1:32">
@@ -33559,16 +33566,16 @@
         <v>236</v>
       </c>
       <c r="V517" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z517">
         <v>0</v>
       </c>
       <c r="AA517" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF517" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="518" spans="1:32">
@@ -33630,16 +33637,16 @@
         <v>236</v>
       </c>
       <c r="V518" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z518">
         <v>0</v>
       </c>
       <c r="AA518" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF518" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="519" spans="1:32">
@@ -33701,16 +33708,16 @@
         <v>236</v>
       </c>
       <c r="V519" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z519">
         <v>0</v>
       </c>
       <c r="AA519" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF519" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="520" spans="1:32">
@@ -33772,16 +33779,16 @@
         <v>236</v>
       </c>
       <c r="V520" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z520">
         <v>0</v>
       </c>
       <c r="AA520" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF520" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="521" spans="1:32">
@@ -33843,16 +33850,16 @@
         <v>236</v>
       </c>
       <c r="V521" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z521">
         <v>0</v>
       </c>
       <c r="AA521" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF521" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="522" spans="1:32">
@@ -33914,16 +33921,16 @@
         <v>236</v>
       </c>
       <c r="V522" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z522">
         <v>0</v>
       </c>
       <c r="AA522" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF522" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="523" spans="1:32">
@@ -33985,16 +33992,16 @@
         <v>236</v>
       </c>
       <c r="V523" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z523">
         <v>0</v>
       </c>
       <c r="AA523" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF523" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="524" spans="1:32">
@@ -34056,16 +34063,16 @@
         <v>236</v>
       </c>
       <c r="V524" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z524">
         <v>0</v>
       </c>
       <c r="AA524" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF524" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="525" spans="1:32">
@@ -34127,16 +34134,16 @@
         <v>236</v>
       </c>
       <c r="V525" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z525">
         <v>0</v>
       </c>
       <c r="AA525" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF525" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="526" spans="1:32">
@@ -34198,16 +34205,16 @@
         <v>236</v>
       </c>
       <c r="V526" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z526">
         <v>0</v>
       </c>
       <c r="AA526" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF526" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="527" spans="1:32">
@@ -34269,16 +34276,16 @@
         <v>236</v>
       </c>
       <c r="V527" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z527">
         <v>0</v>
       </c>
       <c r="AA527" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF527" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="528" spans="1:32">
@@ -34343,10 +34350,10 @@
         <v>0</v>
       </c>
       <c r="AA528" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF528" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="529" spans="1:32">
@@ -34411,10 +34418,10 @@
         <v>0</v>
       </c>
       <c r="AA529" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF529" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="530" spans="1:32">
@@ -34479,10 +34486,10 @@
         <v>0</v>
       </c>
       <c r="AA530" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF530" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="531" spans="1:32">
@@ -34547,10 +34554,10 @@
         <v>0</v>
       </c>
       <c r="AA531" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF531" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="532" spans="1:32">
@@ -34615,10 +34622,10 @@
         <v>0</v>
       </c>
       <c r="AA532" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF532" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="533" spans="1:32">
@@ -34683,10 +34690,10 @@
         <v>0</v>
       </c>
       <c r="AA533" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF533" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="534" spans="1:32">
@@ -34751,10 +34758,10 @@
         <v>0</v>
       </c>
       <c r="AA534" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF534" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="535" spans="1:32">
@@ -34819,10 +34826,10 @@
         <v>0</v>
       </c>
       <c r="AA535" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF535" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="536" spans="1:32">
@@ -34887,10 +34894,10 @@
         <v>0</v>
       </c>
       <c r="AA536" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF536" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="537" spans="1:32">
@@ -34955,10 +34962,10 @@
         <v>0</v>
       </c>
       <c r="AA537" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF537" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="538" spans="1:32">
@@ -35023,10 +35030,10 @@
         <v>0</v>
       </c>
       <c r="AA538" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF538" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="539" spans="1:32">
@@ -35091,10 +35098,10 @@
         <v>0</v>
       </c>
       <c r="AA539" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF539" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="540" spans="1:32">
@@ -35159,10 +35166,10 @@
         <v>0</v>
       </c>
       <c r="AA540" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF540" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="541" spans="1:32">
@@ -35227,10 +35234,10 @@
         <v>0</v>
       </c>
       <c r="AA541" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF541" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="542" spans="1:32">
@@ -35295,10 +35302,10 @@
         <v>0</v>
       </c>
       <c r="AA542" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF542" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="543" spans="1:32">
@@ -35363,10 +35370,10 @@
         <v>0</v>
       </c>
       <c r="AA543" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF543" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="544" spans="1:32">
@@ -35434,7 +35441,7 @@
         <v>222</v>
       </c>
       <c r="AF544" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="545" spans="1:32">
@@ -35499,10 +35506,10 @@
         <v>0</v>
       </c>
       <c r="AA545" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF545" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="546" spans="1:32">
@@ -35570,7 +35577,7 @@
         <v>222</v>
       </c>
       <c r="AF546" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="547" spans="1:32">
@@ -35635,10 +35642,10 @@
         <v>0</v>
       </c>
       <c r="AA547" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF547" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="548" spans="1:32">
@@ -35706,7 +35713,7 @@
         <v>222</v>
       </c>
       <c r="AF548" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="549" spans="1:32">
@@ -35771,10 +35778,10 @@
         <v>0</v>
       </c>
       <c r="AA549" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF549" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="550" spans="1:32">
@@ -35842,7 +35849,7 @@
         <v>222</v>
       </c>
       <c r="AF550" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="551" spans="1:32">
@@ -35910,7 +35917,7 @@
         <v>222</v>
       </c>
       <c r="AF551" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="552" spans="1:32">
@@ -35978,7 +35985,7 @@
         <v>222</v>
       </c>
       <c r="AF552" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="553" spans="1:32">
@@ -36043,10 +36050,10 @@
         <v>0</v>
       </c>
       <c r="AA553" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF553" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="554" spans="1:32">
@@ -36111,10 +36118,10 @@
         <v>0</v>
       </c>
       <c r="AA554" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF554" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="555" spans="1:32">
@@ -36182,7 +36189,7 @@
         <v>222</v>
       </c>
       <c r="AF555" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="556" spans="1:32">
@@ -36247,10 +36254,10 @@
         <v>0</v>
       </c>
       <c r="AA556" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF556" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="557" spans="1:32">
@@ -36318,7 +36325,7 @@
         <v>222</v>
       </c>
       <c r="AF557" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="558" spans="1:32">
@@ -36383,10 +36390,10 @@
         <v>0</v>
       </c>
       <c r="AA558" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF558" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="559" spans="1:32">
@@ -36451,10 +36458,10 @@
         <v>0</v>
       </c>
       <c r="AA559" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF559" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="560" spans="1:32">
@@ -36522,7 +36529,7 @@
         <v>222</v>
       </c>
       <c r="AF560" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="561" spans="1:32">
@@ -36587,10 +36594,10 @@
         <v>0</v>
       </c>
       <c r="AA561" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF561" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="562" spans="1:32">
@@ -36655,10 +36662,10 @@
         <v>0</v>
       </c>
       <c r="AA562" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF562" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="563" spans="1:32">
@@ -36723,10 +36730,10 @@
         <v>0</v>
       </c>
       <c r="AA563" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF563" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="564" spans="1:32">
@@ -36791,10 +36798,10 @@
         <v>0</v>
       </c>
       <c r="AA564" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF564" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="565" spans="1:32">
@@ -36859,10 +36866,10 @@
         <v>0</v>
       </c>
       <c r="AA565" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF565" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="566" spans="1:32">
@@ -36927,10 +36934,10 @@
         <v>0</v>
       </c>
       <c r="AA566" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF566" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="567" spans="1:32">
@@ -36995,10 +37002,10 @@
         <v>0</v>
       </c>
       <c r="AA567" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF567" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="568" spans="1:32">
@@ -37063,10 +37070,10 @@
         <v>0</v>
       </c>
       <c r="AA568" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF568" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="569" spans="1:32">
@@ -37131,10 +37138,10 @@
         <v>0</v>
       </c>
       <c r="AA569" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF569" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="570" spans="1:32">
@@ -37199,10 +37206,10 @@
         <v>0</v>
       </c>
       <c r="AA570" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF570" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="571" spans="1:32">
@@ -37267,10 +37274,10 @@
         <v>0</v>
       </c>
       <c r="AA571" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF571" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="572" spans="1:32">
@@ -37335,10 +37342,10 @@
         <v>0</v>
       </c>
       <c r="AA572" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF572" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="573" spans="1:32">
@@ -37403,10 +37410,10 @@
         <v>0</v>
       </c>
       <c r="AA573" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF573" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="574" spans="1:32">
@@ -37471,10 +37478,10 @@
         <v>0</v>
       </c>
       <c r="AA574" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF574" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="575" spans="1:32">
@@ -37539,10 +37546,10 @@
         <v>0</v>
       </c>
       <c r="AA575" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF575" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="576" spans="1:32">
@@ -37607,10 +37614,10 @@
         <v>0</v>
       </c>
       <c r="AA576" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF576" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="577" spans="1:32">
@@ -37675,16 +37682,16 @@
         <v>235</v>
       </c>
       <c r="V577" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z577">
         <v>0</v>
       </c>
       <c r="AA577" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF577" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="578" spans="1:32">
@@ -37749,16 +37756,16 @@
         <v>235</v>
       </c>
       <c r="V578" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z578">
         <v>0</v>
       </c>
       <c r="AA578" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF578" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="579" spans="1:32">
@@ -37823,10 +37830,10 @@
         <v>0</v>
       </c>
       <c r="AA579" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF579" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="580" spans="1:32">
@@ -37891,16 +37898,16 @@
         <v>235</v>
       </c>
       <c r="V580" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z580">
         <v>0</v>
       </c>
       <c r="AA580" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF580" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="581" spans="1:32">
@@ -37965,16 +37972,16 @@
         <v>235</v>
       </c>
       <c r="V581" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z581">
         <v>0</v>
       </c>
       <c r="AA581" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF581" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="582" spans="1:32">
@@ -38039,16 +38046,16 @@
         <v>235</v>
       </c>
       <c r="V582" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z582">
         <v>0</v>
       </c>
       <c r="AA582" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF582" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="583" spans="1:32">
@@ -38113,16 +38120,16 @@
         <v>235</v>
       </c>
       <c r="V583" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z583">
         <v>0</v>
       </c>
       <c r="AA583" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF583" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="584" spans="1:32">
@@ -38187,10 +38194,10 @@
         <v>0</v>
       </c>
       <c r="AA584" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF584" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="585" spans="1:32">
@@ -38255,10 +38262,10 @@
         <v>0</v>
       </c>
       <c r="AA585" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF585" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="586" spans="1:32">
@@ -38323,10 +38330,10 @@
         <v>0</v>
       </c>
       <c r="AA586" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF586" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="587" spans="1:32">
@@ -38391,16 +38398,16 @@
         <v>235</v>
       </c>
       <c r="V587" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z587">
         <v>0</v>
       </c>
       <c r="AA587" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF587" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="588" spans="1:32">
@@ -38465,10 +38472,10 @@
         <v>0</v>
       </c>
       <c r="AA588" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF588" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="589" spans="1:32">
@@ -38533,10 +38540,10 @@
         <v>0</v>
       </c>
       <c r="AA589" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF589" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="590" spans="1:32">
@@ -38601,10 +38608,10 @@
         <v>0</v>
       </c>
       <c r="AA590" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF590" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="591" spans="1:32">
@@ -38669,10 +38676,10 @@
         <v>0</v>
       </c>
       <c r="AA591" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF591" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="592" spans="1:32">
@@ -38737,10 +38744,10 @@
         <v>0</v>
       </c>
       <c r="AA592" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF592" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="593" spans="1:32">
@@ -38805,10 +38812,10 @@
         <v>0</v>
       </c>
       <c r="AA593" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF593" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="594" spans="1:32">
@@ -38873,10 +38880,10 @@
         <v>0</v>
       </c>
       <c r="AA594" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF594" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="595" spans="1:32">
@@ -38941,10 +38948,10 @@
         <v>0</v>
       </c>
       <c r="AA595" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF595" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="596" spans="1:32">
@@ -39009,10 +39016,10 @@
         <v>0</v>
       </c>
       <c r="AA596" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF596" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="597" spans="1:32">
@@ -39077,10 +39084,10 @@
         <v>0</v>
       </c>
       <c r="AA597" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF597" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="598" spans="1:32">
@@ -39145,10 +39152,10 @@
         <v>0</v>
       </c>
       <c r="AA598" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF598" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="599" spans="1:32">
@@ -39213,10 +39220,10 @@
         <v>0</v>
       </c>
       <c r="AA599" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF599" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="600" spans="1:32">
@@ -39281,10 +39288,10 @@
         <v>0</v>
       </c>
       <c r="AA600" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF600" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="601" spans="1:32">
@@ -39349,10 +39356,10 @@
         <v>0</v>
       </c>
       <c r="AA601" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF601" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="602" spans="1:32">
@@ -39417,10 +39424,10 @@
         <v>0</v>
       </c>
       <c r="AA602" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF602" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="603" spans="1:32">
@@ -39485,10 +39492,10 @@
         <v>0</v>
       </c>
       <c r="AA603" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF603" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="604" spans="1:32">
@@ -39553,10 +39560,10 @@
         <v>0</v>
       </c>
       <c r="AA604" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF604" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="605" spans="1:32">
@@ -39621,10 +39628,10 @@
         <v>0</v>
       </c>
       <c r="AA605" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF605" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="606" spans="1:32">
@@ -39689,10 +39696,10 @@
         <v>0</v>
       </c>
       <c r="AA606" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF606" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="607" spans="1:32">
@@ -39757,10 +39764,10 @@
         <v>0</v>
       </c>
       <c r="AA607" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF607" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="608" spans="1:32">
@@ -39825,10 +39832,10 @@
         <v>0</v>
       </c>
       <c r="AA608" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF608" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="609" spans="1:32">
@@ -39893,10 +39900,10 @@
         <v>0</v>
       </c>
       <c r="AA609" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF609" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="610" spans="1:32">
@@ -39961,10 +39968,10 @@
         <v>0</v>
       </c>
       <c r="AA610" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF610" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="611" spans="1:32">
@@ -40029,10 +40036,10 @@
         <v>0</v>
       </c>
       <c r="AA611" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF611" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="612" spans="1:32">
@@ -40097,10 +40104,10 @@
         <v>0</v>
       </c>
       <c r="AA612" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF612" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="613" spans="1:32">
@@ -40165,10 +40172,10 @@
         <v>0</v>
       </c>
       <c r="AA613" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF613" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="614" spans="1:32">
@@ -40233,10 +40240,10 @@
         <v>0</v>
       </c>
       <c r="AA614" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF614" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="615" spans="1:32">
@@ -40301,10 +40308,10 @@
         <v>0</v>
       </c>
       <c r="AA615" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF615" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="616" spans="1:32">
@@ -40369,10 +40376,10 @@
         <v>0</v>
       </c>
       <c r="AA616" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF616" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="617" spans="1:32">
@@ -40437,10 +40444,10 @@
         <v>0</v>
       </c>
       <c r="AA617" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF617" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="618" spans="1:32">
@@ -40505,10 +40512,10 @@
         <v>0</v>
       </c>
       <c r="AA618" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF618" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="619" spans="1:32">
@@ -40573,10 +40580,10 @@
         <v>0</v>
       </c>
       <c r="AA619" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF619" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="620" spans="1:32">
@@ -40641,10 +40648,10 @@
         <v>0</v>
       </c>
       <c r="AA620" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF620" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="621" spans="1:32">
@@ -40709,10 +40716,10 @@
         <v>0</v>
       </c>
       <c r="AA621" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF621" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="622" spans="1:32">
@@ -40777,10 +40784,10 @@
         <v>0</v>
       </c>
       <c r="AA622" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF622" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="623" spans="1:32">
@@ -40845,10 +40852,10 @@
         <v>0</v>
       </c>
       <c r="AA623" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF623" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="624" spans="1:32">
@@ -40913,10 +40920,10 @@
         <v>0</v>
       </c>
       <c r="AA624" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF624" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="625" spans="1:32">
@@ -40981,10 +40988,10 @@
         <v>0</v>
       </c>
       <c r="AA625" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF625" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="626" spans="1:32">
@@ -41049,10 +41056,10 @@
         <v>0</v>
       </c>
       <c r="AA626" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AF626" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="627" spans="1:32">
@@ -41117,10 +41124,10 @@
         <v>0</v>
       </c>
       <c r="AA627" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF627" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="628" spans="1:32">
@@ -41185,10 +41192,10 @@
         <v>0</v>
       </c>
       <c r="AA628" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF628" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="629" spans="1:32">
@@ -41253,10 +41260,10 @@
         <v>0</v>
       </c>
       <c r="AA629" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF629" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="630" spans="1:32">
@@ -41321,10 +41328,10 @@
         <v>0</v>
       </c>
       <c r="AA630" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF630" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="631" spans="1:32">
@@ -41389,10 +41396,10 @@
         <v>0</v>
       </c>
       <c r="AA631" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF631" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="632" spans="1:32">
@@ -41457,10 +41464,10 @@
         <v>0</v>
       </c>
       <c r="AA632" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF632" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="633" spans="1:32">
@@ -41525,10 +41532,10 @@
         <v>0</v>
       </c>
       <c r="AA633" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF633" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="634" spans="1:32">
@@ -41593,10 +41600,10 @@
         <v>0</v>
       </c>
       <c r="AA634" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF634" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="635" spans="1:32">
@@ -41661,10 +41668,10 @@
         <v>0</v>
       </c>
       <c r="AA635" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF635" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="636" spans="1:32">
@@ -41729,10 +41736,10 @@
         <v>0</v>
       </c>
       <c r="AA636" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF636" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="637" spans="1:32">
@@ -41797,10 +41804,10 @@
         <v>0</v>
       </c>
       <c r="AA637" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF637" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="638" spans="1:32">
@@ -41865,10 +41872,10 @@
         <v>0</v>
       </c>
       <c r="AA638" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF638" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="639" spans="1:32">
@@ -41936,7 +41943,7 @@
         <v>224</v>
       </c>
       <c r="AF639" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="640" spans="1:32">
@@ -42004,7 +42011,7 @@
         <v>224</v>
       </c>
       <c r="AF640" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="641" spans="1:32">
@@ -42072,7 +42079,7 @@
         <v>224</v>
       </c>
       <c r="AF641" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="642" spans="1:32">
@@ -42137,10 +42144,10 @@
         <v>0</v>
       </c>
       <c r="AA642" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF642" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="643" spans="1:32">
@@ -42205,10 +42212,10 @@
         <v>0</v>
       </c>
       <c r="AA643" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF643" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="644" spans="1:32">
@@ -42273,10 +42280,10 @@
         <v>0</v>
       </c>
       <c r="AA644" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF644" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="645" spans="1:32">
@@ -42341,10 +42348,10 @@
         <v>0</v>
       </c>
       <c r="AA645" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF645" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="646" spans="1:32">
@@ -42409,10 +42416,10 @@
         <v>0</v>
       </c>
       <c r="AA646" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF646" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="647" spans="1:32">
@@ -42477,10 +42484,10 @@
         <v>0</v>
       </c>
       <c r="AA647" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF647" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="648" spans="1:32">
@@ -42545,10 +42552,10 @@
         <v>0</v>
       </c>
       <c r="AA648" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF648" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="649" spans="1:32">
@@ -42613,10 +42620,10 @@
         <v>0</v>
       </c>
       <c r="AA649" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF649" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="650" spans="1:32">
@@ -42684,7 +42691,7 @@
         <v>225</v>
       </c>
       <c r="AF650" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="651" spans="1:32">
@@ -42752,7 +42759,7 @@
         <v>225</v>
       </c>
       <c r="AF651" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="652" spans="1:32">
@@ -42820,7 +42827,7 @@
         <v>225</v>
       </c>
       <c r="AF652" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="653" spans="1:32">
@@ -42888,7 +42895,7 @@
         <v>225</v>
       </c>
       <c r="AF653" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="654" spans="1:32">
@@ -42956,7 +42963,7 @@
         <v>225</v>
       </c>
       <c r="AF654" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="655" spans="1:32">
@@ -43024,7 +43031,7 @@
         <v>225</v>
       </c>
       <c r="AF655" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="656" spans="1:32">
@@ -43092,7 +43099,7 @@
         <v>225</v>
       </c>
       <c r="AF656" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="657" spans="1:32">
@@ -43160,7 +43167,7 @@
         <v>225</v>
       </c>
       <c r="AF657" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="658" spans="1:32">
@@ -43228,7 +43235,7 @@
         <v>225</v>
       </c>
       <c r="AF658" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="659" spans="1:32">
@@ -43296,7 +43303,7 @@
         <v>225</v>
       </c>
       <c r="AF659" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="660" spans="1:32">
@@ -43364,7 +43371,7 @@
         <v>225</v>
       </c>
       <c r="AF660" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="661" spans="1:32">
@@ -43432,7 +43439,7 @@
         <v>225</v>
       </c>
       <c r="AF661" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="662" spans="1:32">
@@ -43500,7 +43507,7 @@
         <v>225</v>
       </c>
       <c r="AF662" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="663" spans="1:32">
@@ -43568,7 +43575,7 @@
         <v>225</v>
       </c>
       <c r="AF663" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="664" spans="1:32">
@@ -43636,7 +43643,7 @@
         <v>225</v>
       </c>
       <c r="AF664" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="665" spans="1:32">
@@ -43704,7 +43711,7 @@
         <v>225</v>
       </c>
       <c r="AF665" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="666" spans="1:32">
@@ -43772,7 +43779,7 @@
         <v>225</v>
       </c>
       <c r="AF666" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="667" spans="1:32">
@@ -43840,7 +43847,7 @@
         <v>225</v>
       </c>
       <c r="AF667" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="668" spans="1:32">
@@ -43908,7 +43915,7 @@
         <v>225</v>
       </c>
       <c r="AF668" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="669" spans="1:32">
@@ -43976,7 +43983,7 @@
         <v>225</v>
       </c>
       <c r="AF669" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="670" spans="1:32">
@@ -44044,7 +44051,7 @@
         <v>225</v>
       </c>
       <c r="AF670" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="671" spans="1:32">
@@ -44112,7 +44119,7 @@
         <v>225</v>
       </c>
       <c r="AF671" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="672" spans="1:32">
@@ -44180,7 +44187,7 @@
         <v>225</v>
       </c>
       <c r="AF672" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="673" spans="1:32">
@@ -44248,7 +44255,7 @@
         <v>225</v>
       </c>
       <c r="AF673" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="674" spans="1:32">
@@ -44316,7 +44323,7 @@
         <v>225</v>
       </c>
       <c r="AF674" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="675" spans="1:32">
@@ -44384,7 +44391,7 @@
         <v>225</v>
       </c>
       <c r="AF675" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="676" spans="1:32">
@@ -44452,7 +44459,7 @@
         <v>225</v>
       </c>
       <c r="AF676" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="677" spans="1:32">
@@ -44520,7 +44527,7 @@
         <v>225</v>
       </c>
       <c r="AF677" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="678" spans="1:32">
@@ -44588,7 +44595,7 @@
         <v>225</v>
       </c>
       <c r="AF678" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="679" spans="1:32">
@@ -44656,7 +44663,7 @@
         <v>225</v>
       </c>
       <c r="AF679" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="680" spans="1:32">
@@ -44724,7 +44731,7 @@
         <v>225</v>
       </c>
       <c r="AF680" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="681" spans="1:32">
@@ -44792,7 +44799,7 @@
         <v>225</v>
       </c>
       <c r="AF681" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="682" spans="1:32">
@@ -44860,7 +44867,7 @@
         <v>225</v>
       </c>
       <c r="AF682" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="683" spans="1:32">
@@ -44928,7 +44935,7 @@
         <v>225</v>
       </c>
       <c r="AF683" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="684" spans="1:32">
@@ -44996,7 +45003,7 @@
         <v>225</v>
       </c>
       <c r="AF684" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="685" spans="1:32">
@@ -45064,7 +45071,7 @@
         <v>225</v>
       </c>
       <c r="AF685" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="686" spans="1:32">
@@ -45132,7 +45139,7 @@
         <v>225</v>
       </c>
       <c r="AF686" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="687" spans="1:32">
@@ -45200,7 +45207,7 @@
         <v>225</v>
       </c>
       <c r="AF687" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="688" spans="1:32">
@@ -45268,7 +45275,7 @@
         <v>225</v>
       </c>
       <c r="AF688" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="689" spans="1:32">
@@ -45336,7 +45343,7 @@
         <v>225</v>
       </c>
       <c r="AF689" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="690" spans="1:32">
@@ -45404,7 +45411,7 @@
         <v>225</v>
       </c>
       <c r="AF690" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="691" spans="1:32">
@@ -45472,7 +45479,7 @@
         <v>225</v>
       </c>
       <c r="AF691" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="692" spans="1:32">
@@ -45540,7 +45547,7 @@
         <v>225</v>
       </c>
       <c r="AF692" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="693" spans="1:32">
@@ -45608,7 +45615,7 @@
         <v>225</v>
       </c>
       <c r="AF693" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="694" spans="1:32">
@@ -45676,7 +45683,7 @@
         <v>225</v>
       </c>
       <c r="AF694" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="695" spans="1:32">
@@ -45744,7 +45751,7 @@
         <v>225</v>
       </c>
       <c r="AF695" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="696" spans="1:32">
@@ -45812,7 +45819,7 @@
         <v>225</v>
       </c>
       <c r="AF696" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="697" spans="1:32">
@@ -45880,7 +45887,7 @@
         <v>225</v>
       </c>
       <c r="AF697" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="698" spans="1:32">
@@ -45948,7 +45955,7 @@
         <v>225</v>
       </c>
       <c r="AF698" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="699" spans="1:32">
@@ -46016,7 +46023,7 @@
         <v>225</v>
       </c>
       <c r="AF699" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="700" spans="1:32">
@@ -46084,7 +46091,7 @@
         <v>225</v>
       </c>
       <c r="AF700" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="701" spans="1:32">
@@ -46152,7 +46159,7 @@
         <v>225</v>
       </c>
       <c r="AF701" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="702" spans="1:32">
@@ -46220,7 +46227,7 @@
         <v>225</v>
       </c>
       <c r="AF702" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="703" spans="1:32">
@@ -46288,7 +46295,7 @@
         <v>225</v>
       </c>
       <c r="AF703" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="704" spans="1:32">
@@ -46356,7 +46363,7 @@
         <v>225</v>
       </c>
       <c r="AF704" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="705" spans="1:32">
@@ -46424,7 +46431,7 @@
         <v>225</v>
       </c>
       <c r="AF705" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="706" spans="1:32">
@@ -46492,7 +46499,7 @@
         <v>225</v>
       </c>
       <c r="AF706" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="707" spans="1:32">
@@ -46560,7 +46567,7 @@
         <v>225</v>
       </c>
       <c r="AF707" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="708" spans="1:32">
@@ -46628,7 +46635,7 @@
         <v>225</v>
       </c>
       <c r="AF708" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="709" spans="1:32">
@@ -46696,7 +46703,7 @@
         <v>219</v>
       </c>
       <c r="AF709" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="710" spans="1:32">
@@ -46764,7 +46771,7 @@
         <v>225</v>
       </c>
       <c r="AF710" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="711" spans="1:32">
@@ -46832,7 +46839,7 @@
         <v>225</v>
       </c>
       <c r="AF711" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="712" spans="1:32">
@@ -46900,7 +46907,7 @@
         <v>225</v>
       </c>
       <c r="AF712" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="713" spans="1:32">
@@ -46968,7 +46975,7 @@
         <v>225</v>
       </c>
       <c r="AF713" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="714" spans="1:32">
@@ -47036,7 +47043,7 @@
         <v>225</v>
       </c>
       <c r="AF714" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="715" spans="1:32">
@@ -47104,7 +47111,7 @@
         <v>225</v>
       </c>
       <c r="AF715" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="716" spans="1:32">
@@ -47172,7 +47179,7 @@
         <v>225</v>
       </c>
       <c r="AF716" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="717" spans="1:32">
@@ -47240,7 +47247,7 @@
         <v>219</v>
       </c>
       <c r="AF717" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="718" spans="1:32">
@@ -47308,7 +47315,7 @@
         <v>219</v>
       </c>
       <c r="AF718" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="719" spans="1:32">
@@ -47376,7 +47383,7 @@
         <v>219</v>
       </c>
       <c r="AF719" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="720" spans="1:32">
@@ -47444,7 +47451,7 @@
         <v>219</v>
       </c>
       <c r="AF720" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="721" spans="1:32">
@@ -47512,7 +47519,7 @@
         <v>225</v>
       </c>
       <c r="AF721" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="722" spans="1:32">
@@ -47580,7 +47587,7 @@
         <v>225</v>
       </c>
       <c r="AF722" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="723" spans="1:32">
@@ -47648,7 +47655,7 @@
         <v>225</v>
       </c>
       <c r="AF723" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="724" spans="1:32">
@@ -47716,7 +47723,7 @@
         <v>219</v>
       </c>
       <c r="AF724" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="725" spans="1:32">
@@ -47784,7 +47791,7 @@
         <v>225</v>
       </c>
       <c r="AF725" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="726" spans="1:32">
@@ -47852,7 +47859,7 @@
         <v>225</v>
       </c>
       <c r="AF726" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="727" spans="1:32">
@@ -47920,7 +47927,7 @@
         <v>225</v>
       </c>
       <c r="AF727" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="728" spans="1:32">
@@ -47988,7 +47995,7 @@
         <v>225</v>
       </c>
       <c r="AF728" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="729" spans="1:32">
@@ -48056,7 +48063,7 @@
         <v>225</v>
       </c>
       <c r="AF729" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="730" spans="1:32">
@@ -48124,7 +48131,7 @@
         <v>225</v>
       </c>
       <c r="AF730" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="731" spans="1:32">
@@ -48192,7 +48199,7 @@
         <v>219</v>
       </c>
       <c r="AF731" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="732" spans="1:32">
@@ -48260,7 +48267,7 @@
         <v>219</v>
       </c>
       <c r="AF732" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="733" spans="1:32">
@@ -48328,7 +48335,7 @@
         <v>219</v>
       </c>
       <c r="AF733" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="734" spans="1:32">
@@ -48396,7 +48403,7 @@
         <v>219</v>
       </c>
       <c r="AF734" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="735" spans="1:32">
@@ -48464,7 +48471,7 @@
         <v>219</v>
       </c>
       <c r="AF735" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="736" spans="1:32">
@@ -48532,7 +48539,7 @@
         <v>219</v>
       </c>
       <c r="AF736" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="737" spans="1:32">
@@ -48597,7 +48604,7 @@
         <v>235</v>
       </c>
       <c r="V737" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z737">
         <v>0</v>
@@ -48606,7 +48613,7 @@
         <v>225</v>
       </c>
       <c r="AF737" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="738" spans="1:32">
@@ -48671,7 +48678,7 @@
         <v>235</v>
       </c>
       <c r="V738" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z738">
         <v>0</v>
@@ -48680,7 +48687,7 @@
         <v>225</v>
       </c>
       <c r="AF738" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="739" spans="1:32">
@@ -48745,7 +48752,7 @@
         <v>235</v>
       </c>
       <c r="V739" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z739">
         <v>0</v>
@@ -48754,7 +48761,7 @@
         <v>225</v>
       </c>
       <c r="AF739" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="740" spans="1:32">
@@ -48819,7 +48826,7 @@
         <v>235</v>
       </c>
       <c r="V740" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z740">
         <v>0</v>
@@ -48828,7 +48835,7 @@
         <v>225</v>
       </c>
       <c r="AF740" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="741" spans="1:32">
@@ -48893,7 +48900,7 @@
         <v>235</v>
       </c>
       <c r="V741" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z741">
         <v>0</v>
@@ -48902,7 +48909,7 @@
         <v>225</v>
       </c>
       <c r="AF741" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="742" spans="1:32">
@@ -48967,7 +48974,7 @@
         <v>235</v>
       </c>
       <c r="V742" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z742">
         <v>0</v>
@@ -48976,7 +48983,7 @@
         <v>225</v>
       </c>
       <c r="AF742" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="743" spans="1:32">
@@ -49041,7 +49048,7 @@
         <v>235</v>
       </c>
       <c r="V743" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z743">
         <v>0</v>
@@ -49050,7 +49057,7 @@
         <v>225</v>
       </c>
       <c r="AF743" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="744" spans="1:32">
@@ -49115,7 +49122,7 @@
         <v>235</v>
       </c>
       <c r="V744" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z744">
         <v>0</v>
@@ -49124,7 +49131,7 @@
         <v>225</v>
       </c>
       <c r="AF744" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="745" spans="1:32">
@@ -49189,7 +49196,7 @@
         <v>235</v>
       </c>
       <c r="V745" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z745">
         <v>0</v>
@@ -49198,7 +49205,7 @@
         <v>225</v>
       </c>
       <c r="AF745" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="746" spans="1:32">
@@ -49263,7 +49270,7 @@
         <v>235</v>
       </c>
       <c r="V746" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z746">
         <v>0</v>
@@ -49272,7 +49279,7 @@
         <v>225</v>
       </c>
       <c r="AF746" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="747" spans="1:32">
@@ -49337,7 +49344,7 @@
         <v>235</v>
       </c>
       <c r="V747" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z747">
         <v>0</v>
@@ -49346,7 +49353,7 @@
         <v>225</v>
       </c>
       <c r="AF747" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="748" spans="1:32">
@@ -49411,7 +49418,7 @@
         <v>235</v>
       </c>
       <c r="V748" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z748">
         <v>0</v>
@@ -49420,7 +49427,7 @@
         <v>225</v>
       </c>
       <c r="AF748" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="749" spans="1:32">
@@ -49485,7 +49492,7 @@
         <v>235</v>
       </c>
       <c r="V749" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z749">
         <v>0</v>
@@ -49494,7 +49501,7 @@
         <v>225</v>
       </c>
       <c r="AF749" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="750" spans="1:32">
@@ -49559,7 +49566,7 @@
         <v>235</v>
       </c>
       <c r="V750" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z750">
         <v>0</v>
@@ -49568,7 +49575,7 @@
         <v>225</v>
       </c>
       <c r="AF750" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="751" spans="1:32">
@@ -49633,7 +49640,7 @@
         <v>235</v>
       </c>
       <c r="V751" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z751">
         <v>0</v>
@@ -49642,7 +49649,7 @@
         <v>225</v>
       </c>
       <c r="AF751" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="752" spans="1:32">
@@ -49707,7 +49714,7 @@
         <v>235</v>
       </c>
       <c r="V752" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z752">
         <v>0</v>
@@ -49716,7 +49723,7 @@
         <v>225</v>
       </c>
       <c r="AF752" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="753" spans="1:32">
@@ -49784,7 +49791,7 @@
         <v>225</v>
       </c>
       <c r="AF753" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="754" spans="1:32">
@@ -49852,7 +49859,7 @@
         <v>225</v>
       </c>
       <c r="AF754" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="755" spans="1:32">
@@ -49920,7 +49927,7 @@
         <v>225</v>
       </c>
       <c r="AF755" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="756" spans="1:32">
@@ -49988,7 +49995,7 @@
         <v>225</v>
       </c>
       <c r="AF756" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="757" spans="1:32">
@@ -50056,7 +50063,7 @@
         <v>225</v>
       </c>
       <c r="AF757" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="758" spans="1:32">
@@ -50124,7 +50131,7 @@
         <v>225</v>
       </c>
       <c r="AF758" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="759" spans="1:32">
@@ -50192,7 +50199,7 @@
         <v>225</v>
       </c>
       <c r="AF759" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="760" spans="1:32">
@@ -50260,7 +50267,7 @@
         <v>225</v>
       </c>
       <c r="AF760" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="761" spans="1:32">
@@ -50322,16 +50329,16 @@
         <v>235</v>
       </c>
       <c r="V761" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z761">
         <v>0</v>
       </c>
       <c r="AA761" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF761" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="762" spans="1:32">
@@ -50393,16 +50400,16 @@
         <v>235</v>
       </c>
       <c r="V762" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z762">
         <v>0</v>
       </c>
       <c r="AA762" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF762" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="763" spans="1:32">
@@ -50464,16 +50471,16 @@
         <v>235</v>
       </c>
       <c r="V763" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z763">
         <v>0</v>
       </c>
       <c r="AA763" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF763" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="764" spans="1:32">
@@ -50535,16 +50542,16 @@
         <v>235</v>
       </c>
       <c r="V764" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z764">
         <v>0</v>
       </c>
       <c r="AA764" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF764" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="765" spans="1:32">
@@ -50606,16 +50613,16 @@
         <v>235</v>
       </c>
       <c r="V765" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z765">
         <v>0</v>
       </c>
       <c r="AA765" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF765" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="766" spans="1:32">
@@ -50677,16 +50684,16 @@
         <v>235</v>
       </c>
       <c r="V766" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z766">
         <v>0</v>
       </c>
       <c r="AA766" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF766" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="767" spans="1:32">
@@ -50748,16 +50755,16 @@
         <v>235</v>
       </c>
       <c r="V767" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z767">
         <v>0</v>
       </c>
       <c r="AA767" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF767" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="768" spans="1:32">
@@ -50819,16 +50826,16 @@
         <v>235</v>
       </c>
       <c r="V768" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z768">
         <v>0</v>
       </c>
       <c r="AA768" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF768" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="769" spans="1:32">
@@ -50890,16 +50897,16 @@
         <v>235</v>
       </c>
       <c r="V769" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z769">
         <v>0</v>
       </c>
       <c r="AA769" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF769" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="770" spans="1:32">
@@ -50961,16 +50968,16 @@
         <v>235</v>
       </c>
       <c r="V770" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z770">
         <v>0</v>
       </c>
       <c r="AA770" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF770" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="771" spans="1:32">
@@ -51032,16 +51039,16 @@
         <v>235</v>
       </c>
       <c r="V771" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z771">
         <v>0</v>
       </c>
       <c r="AA771" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF771" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="772" spans="1:32">
@@ -51106,10 +51113,10 @@
         <v>0</v>
       </c>
       <c r="AA772" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF772" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="773" spans="1:32">
@@ -51174,10 +51181,10 @@
         <v>0</v>
       </c>
       <c r="AA773" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF773" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="774" spans="1:32">
@@ -51242,10 +51249,10 @@
         <v>0</v>
       </c>
       <c r="AA774" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF774" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="775" spans="1:32">
@@ -51310,10 +51317,10 @@
         <v>0</v>
       </c>
       <c r="AA775" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF775" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="776" spans="1:32">
@@ -51378,10 +51385,10 @@
         <v>0</v>
       </c>
       <c r="AA776" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF776" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="777" spans="1:32">
@@ -51446,10 +51453,10 @@
         <v>0</v>
       </c>
       <c r="AA777" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF777" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="778" spans="1:32">
@@ -51514,10 +51521,10 @@
         <v>0</v>
       </c>
       <c r="AA778" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF778" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="779" spans="1:32">
@@ -51582,10 +51589,10 @@
         <v>0</v>
       </c>
       <c r="AA779" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF779" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="780" spans="1:32">
@@ -51650,10 +51657,10 @@
         <v>0</v>
       </c>
       <c r="AA780" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF780" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="781" spans="1:32">
@@ -51718,10 +51725,10 @@
         <v>0</v>
       </c>
       <c r="AA781" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF781" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="782" spans="1:32">
@@ -51786,10 +51793,10 @@
         <v>0</v>
       </c>
       <c r="AA782" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF782" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="783" spans="1:32">
@@ -51854,10 +51861,10 @@
         <v>0</v>
       </c>
       <c r="AA783" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF783" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="784" spans="1:32">
@@ -51922,10 +51929,10 @@
         <v>0</v>
       </c>
       <c r="AA784" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF784" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="785" spans="1:32">
@@ -51990,10 +51997,10 @@
         <v>0</v>
       </c>
       <c r="AA785" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF785" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="786" spans="1:32">
@@ -52058,10 +52065,10 @@
         <v>0</v>
       </c>
       <c r="AA786" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF786" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="787" spans="1:32">
@@ -52126,10 +52133,10 @@
         <v>0</v>
       </c>
       <c r="AA787" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF787" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="788" spans="1:32">
@@ -52197,7 +52204,7 @@
         <v>221</v>
       </c>
       <c r="AF788" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="789" spans="1:32">
@@ -52265,7 +52272,7 @@
         <v>221</v>
       </c>
       <c r="AF789" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="790" spans="1:32">
@@ -52333,7 +52340,7 @@
         <v>221</v>
       </c>
       <c r="AF790" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="791" spans="1:32">
@@ -52401,7 +52408,7 @@
         <v>221</v>
       </c>
       <c r="AF791" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="792" spans="1:32">
@@ -52469,7 +52476,7 @@
         <v>221</v>
       </c>
       <c r="AF792" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="793" spans="1:32">
@@ -52537,7 +52544,7 @@
         <v>221</v>
       </c>
       <c r="AF793" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="794" spans="1:32">
@@ -52605,7 +52612,7 @@
         <v>221</v>
       </c>
       <c r="AF794" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="795" spans="1:32">
@@ -52673,7 +52680,7 @@
         <v>221</v>
       </c>
       <c r="AF795" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="796" spans="1:32">
@@ -52741,7 +52748,7 @@
         <v>221</v>
       </c>
       <c r="AF796" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="797" spans="1:32">
@@ -52809,7 +52816,7 @@
         <v>221</v>
       </c>
       <c r="AF797" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="798" spans="1:32">
@@ -52877,7 +52884,7 @@
         <v>221</v>
       </c>
       <c r="AF798" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="799" spans="1:32">
@@ -52945,7 +52952,7 @@
         <v>221</v>
       </c>
       <c r="AF799" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="800" spans="1:32">
@@ -53013,7 +53020,7 @@
         <v>221</v>
       </c>
       <c r="AF800" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="801" spans="1:32">
@@ -53081,7 +53088,7 @@
         <v>221</v>
       </c>
       <c r="AF801" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="802" spans="1:32">
@@ -53149,7 +53156,7 @@
         <v>221</v>
       </c>
       <c r="AF802" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="803" spans="1:32">
@@ -53217,7 +53224,7 @@
         <v>221</v>
       </c>
       <c r="AF803" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="804" spans="1:32">
@@ -53285,7 +53292,7 @@
         <v>221</v>
       </c>
       <c r="AF804" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="805" spans="1:32">
@@ -53353,7 +53360,7 @@
         <v>221</v>
       </c>
       <c r="AF805" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="806" spans="1:32">
@@ -53421,7 +53428,7 @@
         <v>221</v>
       </c>
       <c r="AF806" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="807" spans="1:32">
@@ -53489,7 +53496,7 @@
         <v>221</v>
       </c>
       <c r="AF807" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="808" spans="1:32">
@@ -53557,7 +53564,7 @@
         <v>226</v>
       </c>
       <c r="AF808" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="809" spans="1:32">
@@ -53625,7 +53632,7 @@
         <v>226</v>
       </c>
       <c r="AF809" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="810" spans="1:32">
@@ -53693,7 +53700,7 @@
         <v>226</v>
       </c>
       <c r="AF810" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="811" spans="1:32">
@@ -53761,7 +53768,7 @@
         <v>226</v>
       </c>
       <c r="AF811" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="812" spans="1:32">
@@ -53829,7 +53836,7 @@
         <v>226</v>
       </c>
       <c r="AF812" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="813" spans="1:32">
@@ -53897,7 +53904,7 @@
         <v>226</v>
       </c>
       <c r="AF813" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="814" spans="1:32">
@@ -53965,7 +53972,7 @@
         <v>226</v>
       </c>
       <c r="AF814" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="815" spans="1:32">
@@ -54033,7 +54040,7 @@
         <v>226</v>
       </c>
       <c r="AF815" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="816" spans="1:32">
@@ -54101,7 +54108,7 @@
         <v>226</v>
       </c>
       <c r="AF816" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="817" spans="1:32">
@@ -54169,7 +54176,7 @@
         <v>226</v>
       </c>
       <c r="AF817" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="818" spans="1:32">
@@ -54237,7 +54244,7 @@
         <v>226</v>
       </c>
       <c r="AF818" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="819" spans="1:32">
@@ -54305,7 +54312,7 @@
         <v>226</v>
       </c>
       <c r="AF819" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="820" spans="1:32">
@@ -54373,7 +54380,7 @@
         <v>226</v>
       </c>
       <c r="AF820" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="821" spans="1:32">
@@ -54441,7 +54448,7 @@
         <v>226</v>
       </c>
       <c r="AF821" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/dados/base/bpo.xlsx
+++ b/dados/base/bpo.xlsx
@@ -1879,7 +1879,7 @@
         <v>46283</v>
       </c>
       <c r="M10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N10" t="s">
         <v>221</v>
@@ -1947,7 +1947,7 @@
         <v>46283</v>
       </c>
       <c r="M11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N11" t="s">
         <v>221</v>
@@ -2015,7 +2015,7 @@
         <v>46283</v>
       </c>
       <c r="M12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N12" t="s">
         <v>221</v>
@@ -4123,7 +4123,7 @@
         <v>46283</v>
       </c>
       <c r="M43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N43" t="s">
         <v>221</v>
@@ -4191,7 +4191,7 @@
         <v>46283</v>
       </c>
       <c r="M44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N44" t="s">
         <v>221</v>
@@ -4259,7 +4259,7 @@
         <v>46283</v>
       </c>
       <c r="M45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N45" t="s">
         <v>221</v>
@@ -5687,7 +5687,7 @@
         <v>46283</v>
       </c>
       <c r="M66" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N66" t="s">
         <v>221</v>

--- a/dados/base/bpo.xlsx
+++ b/dados/base/bpo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12224" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12227" uniqueCount="288">
   <si>
     <t>CodCliente</t>
   </si>
@@ -493,10 +493,10 @@
     <t>B.P.O. - DELTA</t>
   </si>
   <si>
-    <t>B.P.O. - GUARANI</t>
+    <t>ROSSI - CTB</t>
   </si>
   <si>
-    <t>ROSSI - CTB</t>
+    <t>B.P.O. - GUARANI</t>
   </si>
   <si>
     <t>B.P.O. - GUARANI EF</t>
@@ -5006,31 +5006,31 @@
     </row>
     <row r="56" spans="1:33">
       <c r="A56">
-        <v>4064</v>
+        <v>2371</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="C56" t="s">
         <v>141</v>
       </c>
       <c r="D56" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E56" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F56" t="s">
         <v>147</v>
       </c>
       <c r="G56">
-        <v>9312</v>
+        <v>3790</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J56" t="s">
         <v>175</v>
@@ -5045,10 +5045,10 @@
         <v>220</v>
       </c>
       <c r="O56">
-        <v>17841025</v>
+        <v>17540512</v>
       </c>
       <c r="P56" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="Q56" t="s">
         <v>236</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U56" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W56" t="s">
         <v>254</v>
@@ -5074,16 +5074,16 @@
     </row>
     <row r="57" spans="1:33">
       <c r="A57">
-        <v>4917</v>
+        <v>3366</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C57" t="s">
         <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E57" t="s">
         <v>147</v>
@@ -5092,13 +5092,13 @@
         <v>147</v>
       </c>
       <c r="G57">
-        <v>9312</v>
+        <v>3790</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="J57" t="s">
         <v>175</v>
@@ -5113,10 +5113,10 @@
         <v>220</v>
       </c>
       <c r="O57">
-        <v>17629841</v>
+        <v>17448656</v>
       </c>
       <c r="P57" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="Q57" t="s">
         <v>236</v>
@@ -5125,10 +5125,10 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W57" t="s">
         <v>254</v>
@@ -5142,16 +5142,16 @@
     </row>
     <row r="58" spans="1:33">
       <c r="A58">
-        <v>4917</v>
+        <v>2371</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C58" t="s">
         <v>141</v>
       </c>
       <c r="D58" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E58" t="s">
         <v>147</v>
@@ -5160,13 +5160,13 @@
         <v>147</v>
       </c>
       <c r="G58">
-        <v>9277</v>
+        <v>2152</v>
       </c>
       <c r="H58">
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J58" t="s">
         <v>176</v>
@@ -5181,10 +5181,10 @@
         <v>220</v>
       </c>
       <c r="O58">
-        <v>17629821</v>
+        <v>17540411</v>
       </c>
       <c r="P58" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q58" t="s">
         <v>236</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U58" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA58">
         <v>0</v>
@@ -5210,16 +5210,16 @@
     </row>
     <row r="59" spans="1:33">
       <c r="A59">
-        <v>2371</v>
+        <v>3366</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C59" t="s">
         <v>141</v>
       </c>
       <c r="D59" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E59" t="s">
         <v>147</v>
@@ -5228,16 +5228,16 @@
         <v>147</v>
       </c>
       <c r="G59">
-        <v>3790</v>
+        <v>2152</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L59" s="1">
         <v>46295</v>
@@ -5249,10 +5249,10 @@
         <v>220</v>
       </c>
       <c r="O59">
-        <v>17540512</v>
+        <v>17448596</v>
       </c>
       <c r="P59" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="Q59" t="s">
         <v>236</v>
@@ -5267,7 +5267,7 @@
         <v>244</v>
       </c>
       <c r="W59" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA59">
         <v>0</v>
@@ -5278,146 +5278,152 @@
     </row>
     <row r="60" spans="1:33">
       <c r="A60">
-        <v>3366</v>
+        <v>2804</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C60" t="s">
         <v>141</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E60" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F60" t="s">
         <v>147</v>
       </c>
       <c r="G60">
-        <v>3790</v>
+        <v>7040</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J60" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="L60" s="1">
-        <v>46295</v>
-      </c>
-      <c r="M60" t="s">
-        <v>211</v>
+        <v>46280</v>
       </c>
       <c r="N60" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O60">
-        <v>17448656</v>
+        <v>17326612</v>
       </c>
       <c r="P60" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="Q60" t="s">
-        <v>236</v>
+        <v>237</v>
+      </c>
+      <c r="R60" s="1">
+        <v>46280.72560332176</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T60" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U60" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W60" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AA60">
         <v>0</v>
       </c>
+      <c r="AB60" t="s">
+        <v>279</v>
+      </c>
       <c r="AG60" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="61" spans="1:33">
       <c r="A61">
-        <v>2371</v>
+        <v>2835</v>
       </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="C61" t="s">
         <v>141</v>
       </c>
       <c r="D61" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F61" t="s">
         <v>147</v>
       </c>
       <c r="G61">
-        <v>2152</v>
+        <v>7040</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J61" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="L61" s="1">
-        <v>46295</v>
-      </c>
-      <c r="M61" t="s">
-        <v>211</v>
+        <v>46280</v>
       </c>
       <c r="N61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O61">
-        <v>17540411</v>
+        <v>17089972</v>
       </c>
       <c r="P61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q61" t="s">
-        <v>236</v>
+        <v>237</v>
+      </c>
+      <c r="R61" s="1">
+        <v>46282.47436697916</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T61" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U61" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W61" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA61">
         <v>0</v>
       </c>
+      <c r="AB61" t="s">
+        <v>279</v>
+      </c>
       <c r="AG61" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:33">
       <c r="A62">
-        <v>3366</v>
+        <v>2837</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
         <v>141</v>
@@ -5426,72 +5432,75 @@
         <v>142</v>
       </c>
       <c r="E62" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F62" t="s">
         <v>147</v>
       </c>
       <c r="G62">
-        <v>2152</v>
+        <v>7040</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J62" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="L62" s="1">
-        <v>46295</v>
-      </c>
-      <c r="M62" t="s">
-        <v>211</v>
+        <v>46280</v>
       </c>
       <c r="N62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O62">
-        <v>17448596</v>
+        <v>17582284</v>
       </c>
       <c r="P62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q62" t="s">
-        <v>236</v>
+        <v>237</v>
+      </c>
+      <c r="R62" s="1">
+        <v>46282.4745590625</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T62" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U62" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W62" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA62">
         <v>0</v>
       </c>
+      <c r="AB62" t="s">
+        <v>279</v>
+      </c>
       <c r="AG62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="63" spans="1:33">
       <c r="A63">
-        <v>2804</v>
+        <v>2838</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
         <v>141</v>
       </c>
       <c r="D63" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E63" t="s">
         <v>148</v>
@@ -5518,7 +5527,7 @@
         <v>221</v>
       </c>
       <c r="O63">
-        <v>17326612</v>
+        <v>17389995</v>
       </c>
       <c r="P63" t="s">
         <v>227</v>
@@ -5527,7 +5536,7 @@
         <v>237</v>
       </c>
       <c r="R63" s="1">
-        <v>46280.72560332176</v>
+        <v>46282.4739224537</v>
       </c>
       <c r="S63">
         <v>15</v>
@@ -5553,19 +5562,19 @@
     </row>
     <row r="64" spans="1:33">
       <c r="A64">
-        <v>2835</v>
+        <v>2842</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
         <v>141</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E64" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F64" t="s">
         <v>147</v>
@@ -5589,7 +5598,7 @@
         <v>221</v>
       </c>
       <c r="O64">
-        <v>17089972</v>
+        <v>17161658</v>
       </c>
       <c r="P64" t="s">
         <v>227</v>
@@ -5598,7 +5607,7 @@
         <v>237</v>
       </c>
       <c r="R64" s="1">
-        <v>46282.47436697916</v>
+        <v>46282.47498869213</v>
       </c>
       <c r="S64">
         <v>15</v>
@@ -5624,10 +5633,10 @@
     </row>
     <row r="65" spans="1:33">
       <c r="A65">
-        <v>2837</v>
+        <v>3004</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
         <v>141</v>
@@ -5660,7 +5669,7 @@
         <v>221</v>
       </c>
       <c r="O65">
-        <v>17582284</v>
+        <v>17033285</v>
       </c>
       <c r="P65" t="s">
         <v>227</v>
@@ -5669,7 +5678,7 @@
         <v>237</v>
       </c>
       <c r="R65" s="1">
-        <v>46282.4745590625</v>
+        <v>46282.47512175926</v>
       </c>
       <c r="S65">
         <v>15</v>
@@ -5695,10 +5704,10 @@
     </row>
     <row r="66" spans="1:33">
       <c r="A66">
-        <v>2838</v>
+        <v>3005</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
         <v>141</v>
@@ -5731,7 +5740,7 @@
         <v>221</v>
       </c>
       <c r="O66">
-        <v>17389995</v>
+        <v>17263482</v>
       </c>
       <c r="P66" t="s">
         <v>227</v>
@@ -5740,7 +5749,7 @@
         <v>237</v>
       </c>
       <c r="R66" s="1">
-        <v>46282.4739224537</v>
+        <v>46282.47529371528</v>
       </c>
       <c r="S66">
         <v>15</v>
@@ -5766,19 +5775,19 @@
     </row>
     <row r="67" spans="1:33">
       <c r="A67">
-        <v>2842</v>
+        <v>3039</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
         <v>141</v>
       </c>
       <c r="D67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F67" t="s">
         <v>147</v>
@@ -5802,7 +5811,7 @@
         <v>221</v>
       </c>
       <c r="O67">
-        <v>17161658</v>
+        <v>17585738</v>
       </c>
       <c r="P67" t="s">
         <v>227</v>
@@ -5811,7 +5820,7 @@
         <v>237</v>
       </c>
       <c r="R67" s="1">
-        <v>46282.47498869213</v>
+        <v>46282.47544363426</v>
       </c>
       <c r="S67">
         <v>15</v>
@@ -5837,16 +5846,16 @@
     </row>
     <row r="68" spans="1:33">
       <c r="A68">
-        <v>3004</v>
+        <v>3053</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C68" t="s">
         <v>141</v>
       </c>
       <c r="D68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
         <v>148</v>
@@ -5873,7 +5882,7 @@
         <v>221</v>
       </c>
       <c r="O68">
-        <v>17033285</v>
+        <v>17194136</v>
       </c>
       <c r="P68" t="s">
         <v>227</v>
@@ -5882,7 +5891,7 @@
         <v>237</v>
       </c>
       <c r="R68" s="1">
-        <v>46282.47512175926</v>
+        <v>46282.47562407408</v>
       </c>
       <c r="S68">
         <v>15</v>
@@ -5908,10 +5917,10 @@
     </row>
     <row r="69" spans="1:33">
       <c r="A69">
-        <v>3005</v>
+        <v>3209</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
         <v>141</v>
@@ -5920,7 +5929,7 @@
         <v>142</v>
       </c>
       <c r="E69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F69" t="s">
         <v>147</v>
@@ -5944,7 +5953,7 @@
         <v>221</v>
       </c>
       <c r="O69">
-        <v>17263482</v>
+        <v>17135070</v>
       </c>
       <c r="P69" t="s">
         <v>227</v>
@@ -5953,7 +5962,7 @@
         <v>237</v>
       </c>
       <c r="R69" s="1">
-        <v>46282.47529371528</v>
+        <v>46282.4758247338</v>
       </c>
       <c r="S69">
         <v>15</v>
@@ -5979,10 +5988,10 @@
     </row>
     <row r="70" spans="1:33">
       <c r="A70">
-        <v>3039</v>
+        <v>3480</v>
       </c>
       <c r="B70" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C70" t="s">
         <v>141</v>
@@ -6015,7 +6024,7 @@
         <v>221</v>
       </c>
       <c r="O70">
-        <v>17585738</v>
+        <v>17821480</v>
       </c>
       <c r="P70" t="s">
         <v>227</v>
@@ -6024,7 +6033,7 @@
         <v>237</v>
       </c>
       <c r="R70" s="1">
-        <v>46282.47544363426</v>
+        <v>46282.47608140046</v>
       </c>
       <c r="S70">
         <v>15</v>
@@ -6050,16 +6059,16 @@
     </row>
     <row r="71" spans="1:33">
       <c r="A71">
-        <v>3053</v>
+        <v>3481</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C71" t="s">
         <v>141</v>
       </c>
       <c r="D71" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E71" t="s">
         <v>148</v>
@@ -6086,7 +6095,7 @@
         <v>221</v>
       </c>
       <c r="O71">
-        <v>17194136</v>
+        <v>17333186</v>
       </c>
       <c r="P71" t="s">
         <v>227</v>
@@ -6095,7 +6104,7 @@
         <v>237</v>
       </c>
       <c r="R71" s="1">
-        <v>46282.47562407408</v>
+        <v>46282.47626608796</v>
       </c>
       <c r="S71">
         <v>15</v>
@@ -6121,25 +6130,25 @@
     </row>
     <row r="72" spans="1:33">
       <c r="A72">
-        <v>3209</v>
+        <v>2804</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C72" t="s">
         <v>141</v>
       </c>
       <c r="D72" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E72" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F72" t="s">
         <v>147</v>
       </c>
       <c r="G72">
-        <v>7040</v>
+        <v>7041</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -6148,16 +6157,16 @@
         <v>158</v>
       </c>
       <c r="J72" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="L72" s="1">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="N72" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O72">
-        <v>17135070</v>
+        <v>17326621</v>
       </c>
       <c r="P72" t="s">
         <v>227</v>
@@ -6166,10 +6175,10 @@
         <v>237</v>
       </c>
       <c r="R72" s="1">
-        <v>46282.4758247338</v>
+        <v>46268.39249731482</v>
       </c>
       <c r="S72">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="T72" t="s">
         <v>241</v>
@@ -6177,14 +6186,11 @@
       <c r="U72" t="s">
         <v>243</v>
       </c>
-      <c r="W72" t="s">
-        <v>256</v>
-      </c>
       <c r="AA72">
         <v>0</v>
       </c>
       <c r="AB72" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
       <c r="AG72" t="s">
         <v>285</v>
@@ -6192,10 +6198,10 @@
     </row>
     <row r="73" spans="1:33">
       <c r="A73">
-        <v>3480</v>
+        <v>2835</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C73" t="s">
         <v>141</v>
@@ -6210,7 +6216,7 @@
         <v>147</v>
       </c>
       <c r="G73">
-        <v>7040</v>
+        <v>7041</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -6219,16 +6225,16 @@
         <v>158</v>
       </c>
       <c r="J73" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="L73" s="1">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="N73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O73">
-        <v>17821480</v>
+        <v>17089997</v>
       </c>
       <c r="P73" t="s">
         <v>227</v>
@@ -6237,10 +6243,10 @@
         <v>237</v>
       </c>
       <c r="R73" s="1">
-        <v>46282.47608140046</v>
+        <v>46268.39249833333</v>
       </c>
       <c r="S73">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="T73" t="s">
         <v>241</v>
@@ -6248,14 +6254,11 @@
       <c r="U73" t="s">
         <v>243</v>
       </c>
-      <c r="W73" t="s">
-        <v>256</v>
-      </c>
       <c r="AA73">
         <v>0</v>
       </c>
       <c r="AB73" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
       <c r="AG73" t="s">
         <v>285</v>
@@ -6263,10 +6266,10 @@
     </row>
     <row r="74" spans="1:33">
       <c r="A74">
-        <v>3481</v>
+        <v>2837</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C74" t="s">
         <v>141</v>
@@ -6281,7 +6284,7 @@
         <v>147</v>
       </c>
       <c r="G74">
-        <v>7040</v>
+        <v>7041</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -6290,16 +6293,16 @@
         <v>158</v>
       </c>
       <c r="J74" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="L74" s="1">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="N74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O74">
-        <v>17333186</v>
+        <v>17582293</v>
       </c>
       <c r="P74" t="s">
         <v>227</v>
@@ -6308,10 +6311,10 @@
         <v>237</v>
       </c>
       <c r="R74" s="1">
-        <v>46282.47626608796</v>
+        <v>46268.39249914352</v>
       </c>
       <c r="S74">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="T74" t="s">
         <v>241</v>
@@ -6319,14 +6322,11 @@
       <c r="U74" t="s">
         <v>243</v>
       </c>
-      <c r="W74" t="s">
-        <v>256</v>
-      </c>
       <c r="AA74">
         <v>0</v>
       </c>
       <c r="AB74" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
       <c r="AG74" t="s">
         <v>285</v>
@@ -6334,16 +6334,16 @@
     </row>
     <row r="75" spans="1:33">
       <c r="A75">
-        <v>2804</v>
+        <v>2838</v>
       </c>
       <c r="B75" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C75" t="s">
         <v>141</v>
       </c>
       <c r="D75" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E75" t="s">
         <v>148</v>
@@ -6370,7 +6370,7 @@
         <v>220</v>
       </c>
       <c r="O75">
-        <v>17326621</v>
+        <v>17390004</v>
       </c>
       <c r="P75" t="s">
         <v>227</v>
@@ -6379,7 +6379,7 @@
         <v>237</v>
       </c>
       <c r="R75" s="1">
-        <v>46268.39249731482</v>
+        <v>46268.39250015046</v>
       </c>
       <c r="S75">
         <v>29</v>
@@ -6402,19 +6402,19 @@
     </row>
     <row r="76" spans="1:33">
       <c r="A76">
-        <v>2835</v>
+        <v>2842</v>
       </c>
       <c r="B76" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C76" t="s">
         <v>141</v>
       </c>
       <c r="D76" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F76" t="s">
         <v>147</v>
@@ -6438,7 +6438,7 @@
         <v>220</v>
       </c>
       <c r="O76">
-        <v>17089997</v>
+        <v>17161680</v>
       </c>
       <c r="P76" t="s">
         <v>227</v>
@@ -6447,7 +6447,7 @@
         <v>237</v>
       </c>
       <c r="R76" s="1">
-        <v>46268.39249833333</v>
+        <v>46268.39250150463</v>
       </c>
       <c r="S76">
         <v>29</v>
@@ -6470,10 +6470,10 @@
     </row>
     <row r="77" spans="1:33">
       <c r="A77">
-        <v>2837</v>
+        <v>3004</v>
       </c>
       <c r="B77" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C77" t="s">
         <v>141</v>
@@ -6506,7 +6506,7 @@
         <v>220</v>
       </c>
       <c r="O77">
-        <v>17582293</v>
+        <v>17033305</v>
       </c>
       <c r="P77" t="s">
         <v>227</v>
@@ -6515,7 +6515,7 @@
         <v>237</v>
       </c>
       <c r="R77" s="1">
-        <v>46268.39249914352</v>
+        <v>46268.39250226852</v>
       </c>
       <c r="S77">
         <v>29</v>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="78" spans="1:33">
       <c r="A78">
-        <v>2838</v>
+        <v>3005</v>
       </c>
       <c r="B78" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C78" t="s">
         <v>141</v>
@@ -6574,7 +6574,7 @@
         <v>220</v>
       </c>
       <c r="O78">
-        <v>17390004</v>
+        <v>17263491</v>
       </c>
       <c r="P78" t="s">
         <v>227</v>
@@ -6583,7 +6583,7 @@
         <v>237</v>
       </c>
       <c r="R78" s="1">
-        <v>46268.39250015046</v>
+        <v>46268.39250332176</v>
       </c>
       <c r="S78">
         <v>29</v>
@@ -6606,19 +6606,19 @@
     </row>
     <row r="79" spans="1:33">
       <c r="A79">
-        <v>2842</v>
+        <v>3039</v>
       </c>
       <c r="B79" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C79" t="s">
         <v>141</v>
       </c>
       <c r="D79" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E79" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F79" t="s">
         <v>147</v>
@@ -6642,7 +6642,7 @@
         <v>220</v>
       </c>
       <c r="O79">
-        <v>17161680</v>
+        <v>17585747</v>
       </c>
       <c r="P79" t="s">
         <v>227</v>
@@ -6651,7 +6651,7 @@
         <v>237</v>
       </c>
       <c r="R79" s="1">
-        <v>46268.39250150463</v>
+        <v>46268.39250452547</v>
       </c>
       <c r="S79">
         <v>29</v>
@@ -6674,16 +6674,16 @@
     </row>
     <row r="80" spans="1:33">
       <c r="A80">
-        <v>3004</v>
+        <v>3053</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C80" t="s">
         <v>141</v>
       </c>
       <c r="D80" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E80" t="s">
         <v>148</v>
@@ -6710,7 +6710,7 @@
         <v>220</v>
       </c>
       <c r="O80">
-        <v>17033305</v>
+        <v>17194164</v>
       </c>
       <c r="P80" t="s">
         <v>227</v>
@@ -6719,7 +6719,7 @@
         <v>237</v>
       </c>
       <c r="R80" s="1">
-        <v>46268.39250226852</v>
+        <v>46268.39250524306</v>
       </c>
       <c r="S80">
         <v>29</v>
@@ -6742,10 +6742,10 @@
     </row>
     <row r="81" spans="1:33">
       <c r="A81">
-        <v>3005</v>
+        <v>3209</v>
       </c>
       <c r="B81" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C81" t="s">
         <v>141</v>
@@ -6754,7 +6754,7 @@
         <v>142</v>
       </c>
       <c r="E81" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F81" t="s">
         <v>147</v>
@@ -6778,7 +6778,7 @@
         <v>220</v>
       </c>
       <c r="O81">
-        <v>17263491</v>
+        <v>17135091</v>
       </c>
       <c r="P81" t="s">
         <v>227</v>
@@ -6787,7 +6787,7 @@
         <v>237</v>
       </c>
       <c r="R81" s="1">
-        <v>46268.39250332176</v>
+        <v>46268.39250652778</v>
       </c>
       <c r="S81">
         <v>29</v>
@@ -6810,10 +6810,10 @@
     </row>
     <row r="82" spans="1:33">
       <c r="A82">
-        <v>3039</v>
+        <v>3480</v>
       </c>
       <c r="B82" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C82" t="s">
         <v>141</v>
@@ -6846,7 +6846,7 @@
         <v>220</v>
       </c>
       <c r="O82">
-        <v>17585747</v>
+        <v>17821489</v>
       </c>
       <c r="P82" t="s">
         <v>227</v>
@@ -6855,7 +6855,7 @@
         <v>237</v>
       </c>
       <c r="R82" s="1">
-        <v>46268.39250452547</v>
+        <v>46268.39250747685</v>
       </c>
       <c r="S82">
         <v>29</v>
@@ -6878,16 +6878,16 @@
     </row>
     <row r="83" spans="1:33">
       <c r="A83">
-        <v>3053</v>
+        <v>3481</v>
       </c>
       <c r="B83" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C83" t="s">
         <v>141</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E83" t="s">
         <v>148</v>
@@ -6914,7 +6914,7 @@
         <v>220</v>
       </c>
       <c r="O83">
-        <v>17194164</v>
+        <v>17333195</v>
       </c>
       <c r="P83" t="s">
         <v>227</v>
@@ -6923,7 +6923,7 @@
         <v>237</v>
       </c>
       <c r="R83" s="1">
-        <v>46268.39250524306</v>
+        <v>46268.39250818287</v>
       </c>
       <c r="S83">
         <v>29</v>
@@ -6946,25 +6946,25 @@
     </row>
     <row r="84" spans="1:33">
       <c r="A84">
-        <v>3209</v>
+        <v>2804</v>
       </c>
       <c r="B84" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C84" t="s">
         <v>141</v>
       </c>
       <c r="D84" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E84" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F84" t="s">
         <v>147</v>
       </c>
       <c r="G84">
-        <v>7041</v>
+        <v>11289</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -6973,16 +6973,16 @@
         <v>158</v>
       </c>
       <c r="J84" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="L84" s="1">
-        <v>46266</v>
+        <v>46281</v>
       </c>
       <c r="N84" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O84">
-        <v>17135091</v>
+        <v>17326643</v>
       </c>
       <c r="P84" t="s">
         <v>227</v>
@@ -6991,10 +6991,10 @@
         <v>237</v>
       </c>
       <c r="R84" s="1">
-        <v>46268.39250652778</v>
+        <v>46280.7143515162</v>
       </c>
       <c r="S84">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="T84" t="s">
         <v>241</v>
@@ -7014,16 +7014,16 @@
     </row>
     <row r="85" spans="1:33">
       <c r="A85">
-        <v>3480</v>
+        <v>3053</v>
       </c>
       <c r="B85" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C85" t="s">
         <v>141</v>
       </c>
       <c r="D85" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E85" t="s">
         <v>148</v>
@@ -7032,7 +7032,7 @@
         <v>147</v>
       </c>
       <c r="G85">
-        <v>7041</v>
+        <v>11289</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -7041,16 +7041,16 @@
         <v>158</v>
       </c>
       <c r="J85" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="L85" s="1">
-        <v>46266</v>
+        <v>46281</v>
       </c>
       <c r="N85" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O85">
-        <v>17821489</v>
+        <v>17194213</v>
       </c>
       <c r="P85" t="s">
         <v>227</v>
@@ -7059,10 +7059,10 @@
         <v>237</v>
       </c>
       <c r="R85" s="1">
-        <v>46268.39250747685</v>
+        <v>46280.71435333334</v>
       </c>
       <c r="S85">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="T85" t="s">
         <v>241</v>
@@ -7082,16 +7082,16 @@
     </row>
     <row r="86" spans="1:33">
       <c r="A86">
-        <v>3481</v>
+        <v>2804</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C86" t="s">
         <v>141</v>
       </c>
       <c r="D86" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E86" t="s">
         <v>148</v>
@@ -7100,7 +7100,7 @@
         <v>147</v>
       </c>
       <c r="G86">
-        <v>7041</v>
+        <v>11288</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -7109,16 +7109,16 @@
         <v>158</v>
       </c>
       <c r="J86" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L86" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="N86" t="s">
         <v>220</v>
       </c>
       <c r="O86">
-        <v>17333195</v>
+        <v>17326632</v>
       </c>
       <c r="P86" t="s">
         <v>227</v>
@@ -7127,10 +7127,10 @@
         <v>237</v>
       </c>
       <c r="R86" s="1">
-        <v>46268.39250818287</v>
+        <v>46268.39323719907</v>
       </c>
       <c r="S86">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T86" t="s">
         <v>241</v>
@@ -7150,16 +7150,16 @@
     </row>
     <row r="87" spans="1:33">
       <c r="A87">
-        <v>2804</v>
+        <v>3053</v>
       </c>
       <c r="B87" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C87" t="s">
         <v>141</v>
       </c>
       <c r="D87" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E87" t="s">
         <v>148</v>
@@ -7168,7 +7168,7 @@
         <v>147</v>
       </c>
       <c r="G87">
-        <v>11289</v>
+        <v>11288</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -7177,16 +7177,16 @@
         <v>158</v>
       </c>
       <c r="J87" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="L87" s="1">
-        <v>46281</v>
+        <v>46267</v>
       </c>
       <c r="N87" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O87">
-        <v>17326643</v>
+        <v>17194186</v>
       </c>
       <c r="P87" t="s">
         <v>227</v>
@@ -7195,10 +7195,10 @@
         <v>237</v>
       </c>
       <c r="R87" s="1">
-        <v>46280.7143515162</v>
+        <v>46268.39323780093</v>
       </c>
       <c r="S87">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T87" t="s">
         <v>241</v>
@@ -7218,10 +7218,10 @@
     </row>
     <row r="88" spans="1:33">
       <c r="A88">
-        <v>3053</v>
+        <v>4064</v>
       </c>
       <c r="B88" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C88" t="s">
         <v>141</v>
@@ -7230,182 +7230,194 @@
         <v>143</v>
       </c>
       <c r="E88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F88" t="s">
         <v>147</v>
       </c>
       <c r="G88">
-        <v>11289</v>
+        <v>9312</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J88" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="L88" s="1">
-        <v>46281</v>
+        <v>46295</v>
+      </c>
+      <c r="M88" t="s">
+        <v>211</v>
       </c>
       <c r="N88" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O88">
-        <v>17194213</v>
+        <v>17841025</v>
       </c>
       <c r="P88" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q88" t="s">
         <v>237</v>
       </c>
       <c r="R88" s="1">
-        <v>46280.71435333334</v>
+        <v>46295.40172307871</v>
       </c>
       <c r="S88">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T88" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="U88" t="s">
         <v>243</v>
       </c>
+      <c r="W88" t="s">
+        <v>254</v>
+      </c>
       <c r="AA88">
         <v>0</v>
       </c>
       <c r="AB88" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="89" spans="1:33">
       <c r="A89">
-        <v>2804</v>
+        <v>4917</v>
       </c>
       <c r="B89" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C89" t="s">
         <v>141</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E89" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F89" t="s">
         <v>147</v>
       </c>
       <c r="G89">
-        <v>11288</v>
+        <v>9312</v>
       </c>
       <c r="H89">
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J89" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L89" s="1">
-        <v>46267</v>
+        <v>46295</v>
+      </c>
+      <c r="M89" t="s">
+        <v>211</v>
       </c>
       <c r="N89" t="s">
         <v>220</v>
       </c>
       <c r="O89">
-        <v>17326632</v>
+        <v>17629841</v>
       </c>
       <c r="P89" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q89" t="s">
         <v>237</v>
       </c>
       <c r="R89" s="1">
-        <v>46268.39323719907</v>
+        <v>46295.40172364583</v>
       </c>
       <c r="S89">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T89" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="U89" t="s">
         <v>243</v>
       </c>
+      <c r="W89" t="s">
+        <v>254</v>
+      </c>
       <c r="AA89">
         <v>0</v>
       </c>
       <c r="AB89" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="90" spans="1:33">
       <c r="A90">
-        <v>3053</v>
+        <v>4059</v>
       </c>
       <c r="B90" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C90" t="s">
         <v>141</v>
       </c>
       <c r="D90" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E90" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F90" t="s">
         <v>147</v>
       </c>
       <c r="G90">
-        <v>11288</v>
+        <v>9327</v>
       </c>
       <c r="H90">
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J90" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="L90" s="1">
-        <v>46267</v>
+        <v>46280</v>
       </c>
       <c r="N90" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O90">
-        <v>17194186</v>
+        <v>17311887</v>
       </c>
       <c r="P90" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q90" t="s">
         <v>237</v>
       </c>
       <c r="R90" s="1">
-        <v>46268.39323780093</v>
+        <v>46280.75157195602</v>
       </c>
       <c r="S90">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="T90" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="U90" t="s">
         <v>243</v>
@@ -7414,27 +7426,27 @@
         <v>0</v>
       </c>
       <c r="AB90" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="AG90" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="91" spans="1:33">
       <c r="A91">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="B91" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C91" t="s">
         <v>141</v>
       </c>
       <c r="D91" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E91" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F91" t="s">
         <v>147</v>
@@ -7446,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J91" t="s">
         <v>168</v>
@@ -7458,7 +7470,7 @@
         <v>221</v>
       </c>
       <c r="O91">
-        <v>17311887</v>
+        <v>17841036</v>
       </c>
       <c r="P91" t="s">
         <v>224</v>
@@ -7467,7 +7479,7 @@
         <v>237</v>
       </c>
       <c r="R91" s="1">
-        <v>46280.75157195602</v>
+        <v>46280.75190127315</v>
       </c>
       <c r="S91">
         <v>15</v>
@@ -7490,19 +7502,19 @@
     </row>
     <row r="92" spans="1:33">
       <c r="A92">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C92" t="s">
         <v>141</v>
       </c>
       <c r="D92" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E92" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F92" t="s">
         <v>147</v>
@@ -7514,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J92" t="s">
         <v>168</v>
@@ -7526,7 +7538,7 @@
         <v>221</v>
       </c>
       <c r="O92">
-        <v>17841036</v>
+        <v>17222004</v>
       </c>
       <c r="P92" t="s">
         <v>224</v>
@@ -7535,7 +7547,7 @@
         <v>237</v>
       </c>
       <c r="R92" s="1">
-        <v>46280.75190127315</v>
+        <v>46280.75219267361</v>
       </c>
       <c r="S92">
         <v>15</v>
@@ -7558,10 +7570,10 @@
     </row>
     <row r="93" spans="1:33">
       <c r="A93">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C93" t="s">
         <v>141</v>
@@ -7570,7 +7582,7 @@
         <v>142</v>
       </c>
       <c r="E93" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F93" t="s">
         <v>147</v>
@@ -7582,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J93" t="s">
         <v>168</v>
@@ -7594,7 +7606,7 @@
         <v>221</v>
       </c>
       <c r="O93">
-        <v>17222004</v>
+        <v>17424451</v>
       </c>
       <c r="P93" t="s">
         <v>224</v>
@@ -7603,7 +7615,7 @@
         <v>237</v>
       </c>
       <c r="R93" s="1">
-        <v>46280.75219267361</v>
+        <v>46280.75248533565</v>
       </c>
       <c r="S93">
         <v>15</v>
@@ -7626,10 +7638,10 @@
     </row>
     <row r="94" spans="1:33">
       <c r="A94">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C94" t="s">
         <v>141</v>
@@ -7638,7 +7650,7 @@
         <v>142</v>
       </c>
       <c r="E94" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F94" t="s">
         <v>147</v>
@@ -7650,7 +7662,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J94" t="s">
         <v>168</v>
@@ -7662,7 +7674,7 @@
         <v>221</v>
       </c>
       <c r="O94">
-        <v>17424451</v>
+        <v>17493444</v>
       </c>
       <c r="P94" t="s">
         <v>224</v>
@@ -7671,7 +7683,7 @@
         <v>237</v>
       </c>
       <c r="R94" s="1">
-        <v>46280.75248533565</v>
+        <v>46280.75296913194</v>
       </c>
       <c r="S94">
         <v>15</v>
@@ -7694,10 +7706,10 @@
     </row>
     <row r="95" spans="1:33">
       <c r="A95">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C95" t="s">
         <v>141</v>
@@ -7718,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J95" t="s">
         <v>168</v>
@@ -7730,7 +7742,7 @@
         <v>221</v>
       </c>
       <c r="O95">
-        <v>17493444</v>
+        <v>17424491</v>
       </c>
       <c r="P95" t="s">
         <v>224</v>
@@ -7739,7 +7751,7 @@
         <v>237</v>
       </c>
       <c r="R95" s="1">
-        <v>46280.75296913194</v>
+        <v>46280.75326030092</v>
       </c>
       <c r="S95">
         <v>15</v>
@@ -7762,10 +7774,10 @@
     </row>
     <row r="96" spans="1:33">
       <c r="A96">
-        <v>4068</v>
+        <v>4602</v>
       </c>
       <c r="B96" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C96" t="s">
         <v>141</v>
@@ -7786,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J96" t="s">
         <v>168</v>
@@ -7798,7 +7810,7 @@
         <v>221</v>
       </c>
       <c r="O96">
-        <v>17424491</v>
+        <v>17719860</v>
       </c>
       <c r="P96" t="s">
         <v>224</v>
@@ -7807,7 +7819,7 @@
         <v>237</v>
       </c>
       <c r="R96" s="1">
-        <v>46280.75326030092</v>
+        <v>46280.75372538195</v>
       </c>
       <c r="S96">
         <v>15</v>
@@ -7830,10 +7842,10 @@
     </row>
     <row r="97" spans="1:33">
       <c r="A97">
-        <v>4602</v>
+        <v>4815</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="C97" t="s">
         <v>141</v>
@@ -7854,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J97" t="s">
         <v>168</v>
@@ -7866,7 +7878,7 @@
         <v>221</v>
       </c>
       <c r="O97">
-        <v>17719860</v>
+        <v>17728390</v>
       </c>
       <c r="P97" t="s">
         <v>224</v>
@@ -7875,7 +7887,7 @@
         <v>237</v>
       </c>
       <c r="R97" s="1">
-        <v>46280.75372538195</v>
+        <v>46280.75461721064</v>
       </c>
       <c r="S97">
         <v>15</v>
@@ -7898,16 +7910,16 @@
     </row>
     <row r="98" spans="1:33">
       <c r="A98">
-        <v>4815</v>
+        <v>4917</v>
       </c>
       <c r="B98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C98" t="s">
         <v>141</v>
       </c>
       <c r="D98" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E98" t="s">
         <v>147</v>
@@ -7922,7 +7934,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J98" t="s">
         <v>168</v>
@@ -7934,7 +7946,7 @@
         <v>221</v>
       </c>
       <c r="O98">
-        <v>17728390</v>
+        <v>17629852</v>
       </c>
       <c r="P98" t="s">
         <v>224</v>
@@ -7943,7 +7955,7 @@
         <v>237</v>
       </c>
       <c r="R98" s="1">
-        <v>46280.75461721064</v>
+        <v>46280.75492121528</v>
       </c>
       <c r="S98">
         <v>15</v>
@@ -7966,16 +7978,16 @@
     </row>
     <row r="99" spans="1:33">
       <c r="A99">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B99" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C99" t="s">
         <v>141</v>
       </c>
       <c r="D99" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E99" t="s">
         <v>147</v>
@@ -7984,25 +7996,25 @@
         <v>147</v>
       </c>
       <c r="G99">
-        <v>9327</v>
+        <v>9328</v>
       </c>
       <c r="H99">
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J99" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="L99" s="1">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="N99" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O99">
-        <v>17629852</v>
+        <v>17311896</v>
       </c>
       <c r="P99" t="s">
         <v>224</v>
@@ -8011,10 +8023,10 @@
         <v>237</v>
       </c>
       <c r="R99" s="1">
-        <v>46280.75492121528</v>
+        <v>46266.71710929398</v>
       </c>
       <c r="S99">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="T99" t="s">
         <v>238</v>
@@ -8034,19 +8046,19 @@
     </row>
     <row r="100" spans="1:33">
       <c r="A100">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="B100" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C100" t="s">
         <v>141</v>
       </c>
       <c r="D100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E100" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F100" t="s">
         <v>147</v>
@@ -8058,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J100" t="s">
         <v>177</v>
@@ -8070,7 +8082,7 @@
         <v>220</v>
       </c>
       <c r="O100">
-        <v>17311896</v>
+        <v>17841045</v>
       </c>
       <c r="P100" t="s">
         <v>224</v>
@@ -8079,7 +8091,7 @@
         <v>237</v>
       </c>
       <c r="R100" s="1">
-        <v>46266.71710929398</v>
+        <v>46266.71760243056</v>
       </c>
       <c r="S100">
         <v>29</v>
@@ -8102,19 +8114,19 @@
     </row>
     <row r="101" spans="1:33">
       <c r="A101">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B101" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C101" t="s">
         <v>141</v>
       </c>
       <c r="D101" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E101" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F101" t="s">
         <v>147</v>
@@ -8126,7 +8138,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J101" t="s">
         <v>177</v>
@@ -8138,7 +8150,7 @@
         <v>220</v>
       </c>
       <c r="O101">
-        <v>17841045</v>
+        <v>17222030</v>
       </c>
       <c r="P101" t="s">
         <v>224</v>
@@ -8147,7 +8159,7 @@
         <v>237</v>
       </c>
       <c r="R101" s="1">
-        <v>46266.71760243056</v>
+        <v>46266.71793020833</v>
       </c>
       <c r="S101">
         <v>29</v>
@@ -8170,10 +8182,10 @@
     </row>
     <row r="102" spans="1:33">
       <c r="A102">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C102" t="s">
         <v>141</v>
@@ -8182,7 +8194,7 @@
         <v>142</v>
       </c>
       <c r="E102" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F102" t="s">
         <v>147</v>
@@ -8194,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J102" t="s">
         <v>177</v>
@@ -8206,7 +8218,7 @@
         <v>220</v>
       </c>
       <c r="O102">
-        <v>17222030</v>
+        <v>17424460</v>
       </c>
       <c r="P102" t="s">
         <v>224</v>
@@ -8215,7 +8227,7 @@
         <v>237</v>
       </c>
       <c r="R102" s="1">
-        <v>46266.71793020833</v>
+        <v>46266.71818136574</v>
       </c>
       <c r="S102">
         <v>29</v>
@@ -8238,10 +8250,10 @@
     </row>
     <row r="103" spans="1:33">
       <c r="A103">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C103" t="s">
         <v>141</v>
@@ -8250,7 +8262,7 @@
         <v>142</v>
       </c>
       <c r="E103" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F103" t="s">
         <v>147</v>
@@ -8262,7 +8274,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J103" t="s">
         <v>177</v>
@@ -8274,7 +8286,7 @@
         <v>220</v>
       </c>
       <c r="O103">
-        <v>17424460</v>
+        <v>17493453</v>
       </c>
       <c r="P103" t="s">
         <v>224</v>
@@ -8283,7 +8295,7 @@
         <v>237</v>
       </c>
       <c r="R103" s="1">
-        <v>46266.71818136574</v>
+        <v>46266.71859741898</v>
       </c>
       <c r="S103">
         <v>29</v>
@@ -8306,10 +8318,10 @@
     </row>
     <row r="104" spans="1:33">
       <c r="A104">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C104" t="s">
         <v>141</v>
@@ -8330,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J104" t="s">
         <v>177</v>
@@ -8342,7 +8354,7 @@
         <v>220</v>
       </c>
       <c r="O104">
-        <v>17493453</v>
+        <v>17424500</v>
       </c>
       <c r="P104" t="s">
         <v>224</v>
@@ -8351,7 +8363,7 @@
         <v>237</v>
       </c>
       <c r="R104" s="1">
-        <v>46266.71859741898</v>
+        <v>46266.71905170139</v>
       </c>
       <c r="S104">
         <v>29</v>
@@ -8374,10 +8386,10 @@
     </row>
     <row r="105" spans="1:33">
       <c r="A105">
-        <v>4068</v>
+        <v>4602</v>
       </c>
       <c r="B105" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C105" t="s">
         <v>141</v>
@@ -8398,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J105" t="s">
         <v>177</v>
@@ -8410,7 +8422,7 @@
         <v>220</v>
       </c>
       <c r="O105">
-        <v>17424500</v>
+        <v>17719869</v>
       </c>
       <c r="P105" t="s">
         <v>224</v>
@@ -8419,7 +8431,7 @@
         <v>237</v>
       </c>
       <c r="R105" s="1">
-        <v>46266.71905170139</v>
+        <v>46266.71958452546</v>
       </c>
       <c r="S105">
         <v>29</v>
@@ -8442,10 +8454,10 @@
     </row>
     <row r="106" spans="1:33">
       <c r="A106">
-        <v>4602</v>
+        <v>4815</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="C106" t="s">
         <v>141</v>
@@ -8466,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J106" t="s">
         <v>177</v>
@@ -8478,7 +8490,7 @@
         <v>220</v>
       </c>
       <c r="O106">
-        <v>17719869</v>
+        <v>17728399</v>
       </c>
       <c r="P106" t="s">
         <v>224</v>
@@ -8487,7 +8499,7 @@
         <v>237</v>
       </c>
       <c r="R106" s="1">
-        <v>46266.71958452546</v>
+        <v>46266.71982650463</v>
       </c>
       <c r="S106">
         <v>29</v>
@@ -8510,16 +8522,16 @@
     </row>
     <row r="107" spans="1:33">
       <c r="A107">
-        <v>4815</v>
+        <v>4917</v>
       </c>
       <c r="B107" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C107" t="s">
         <v>141</v>
       </c>
       <c r="D107" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E107" t="s">
         <v>147</v>
@@ -8534,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J107" t="s">
         <v>177</v>
@@ -8546,7 +8558,7 @@
         <v>220</v>
       </c>
       <c r="O107">
-        <v>17728399</v>
+        <v>17629861</v>
       </c>
       <c r="P107" t="s">
         <v>224</v>
@@ -8555,7 +8567,7 @@
         <v>237</v>
       </c>
       <c r="R107" s="1">
-        <v>46266.71982650463</v>
+        <v>46266.72010234954</v>
       </c>
       <c r="S107">
         <v>29</v>
@@ -8578,16 +8590,16 @@
     </row>
     <row r="108" spans="1:33">
       <c r="A108">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B108" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C108" t="s">
         <v>141</v>
       </c>
       <c r="D108" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E108" t="s">
         <v>147</v>
@@ -8596,25 +8608,25 @@
         <v>147</v>
       </c>
       <c r="G108">
-        <v>9328</v>
+        <v>9588</v>
       </c>
       <c r="H108">
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J108" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="L108" s="1">
-        <v>46266</v>
+        <v>46281</v>
       </c>
       <c r="N108" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O108">
-        <v>17629861</v>
+        <v>17311917</v>
       </c>
       <c r="P108" t="s">
         <v>224</v>
@@ -8623,10 +8635,10 @@
         <v>237</v>
       </c>
       <c r="R108" s="1">
-        <v>46266.72010234954</v>
+        <v>46281.61917107639</v>
       </c>
       <c r="S108">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="T108" t="s">
         <v>238</v>
@@ -8638,10 +8650,10 @@
         <v>0</v>
       </c>
       <c r="AB108" t="s">
-        <v>279</v>
+        <v>224</v>
       </c>
       <c r="AG108" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="109" spans="1:33">
@@ -8664,13 +8676,13 @@
         <v>147</v>
       </c>
       <c r="G109">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H109">
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J109" t="s">
         <v>169</v>
@@ -8678,11 +8690,14 @@
       <c r="L109" s="1">
         <v>46281</v>
       </c>
+      <c r="M109" t="s">
+        <v>212</v>
+      </c>
       <c r="N109" t="s">
         <v>221</v>
       </c>
       <c r="O109">
-        <v>17311917</v>
+        <v>17311927</v>
       </c>
       <c r="P109" t="s">
         <v>224</v>
@@ -8691,7 +8706,7 @@
         <v>237</v>
       </c>
       <c r="R109" s="1">
-        <v>46281.61917107639</v>
+        <v>46286.74416417824</v>
       </c>
       <c r="S109">
         <v>14</v>
@@ -8702,6 +8717,9 @@
       <c r="U109" t="s">
         <v>243</v>
       </c>
+      <c r="W109" t="s">
+        <v>257</v>
+      </c>
       <c r="AA109">
         <v>0</v>
       </c>
@@ -8714,10 +8732,10 @@
     </row>
     <row r="110" spans="1:33">
       <c r="A110">
-        <v>4059</v>
+        <v>4061</v>
       </c>
       <c r="B110" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C110" t="s">
         <v>141</v>
@@ -8726,19 +8744,19 @@
         <v>144</v>
       </c>
       <c r="E110" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F110" t="s">
         <v>147</v>
       </c>
       <c r="G110">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H110">
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J110" t="s">
         <v>169</v>
@@ -8746,14 +8764,11 @@
       <c r="L110" s="1">
         <v>46281</v>
       </c>
-      <c r="M110" t="s">
-        <v>212</v>
-      </c>
       <c r="N110" t="s">
         <v>221</v>
       </c>
       <c r="O110">
-        <v>17311927</v>
+        <v>17311967</v>
       </c>
       <c r="P110" t="s">
         <v>224</v>
@@ -8762,7 +8777,7 @@
         <v>237</v>
       </c>
       <c r="R110" s="1">
-        <v>46286.74416417824</v>
+        <v>46281.61917159722</v>
       </c>
       <c r="S110">
         <v>14</v>
@@ -8772,9 +8787,6 @@
       </c>
       <c r="U110" t="s">
         <v>243</v>
-      </c>
-      <c r="W110" t="s">
-        <v>257</v>
       </c>
       <c r="AA110">
         <v>0</v>
@@ -8806,13 +8818,13 @@
         <v>147</v>
       </c>
       <c r="G111">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H111">
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J111" t="s">
         <v>169</v>
@@ -8820,11 +8832,14 @@
       <c r="L111" s="1">
         <v>46281</v>
       </c>
+      <c r="M111" t="s">
+        <v>212</v>
+      </c>
       <c r="N111" t="s">
         <v>221</v>
       </c>
       <c r="O111">
-        <v>17311967</v>
+        <v>17311977</v>
       </c>
       <c r="P111" t="s">
         <v>224</v>
@@ -8833,7 +8848,7 @@
         <v>237</v>
       </c>
       <c r="R111" s="1">
-        <v>46281.61917159722</v>
+        <v>46286.74416459491</v>
       </c>
       <c r="S111">
         <v>14</v>
@@ -8844,6 +8859,9 @@
       <c r="U111" t="s">
         <v>243</v>
       </c>
+      <c r="W111" t="s">
+        <v>258</v>
+      </c>
       <c r="AA111">
         <v>0</v>
       </c>
@@ -8856,10 +8874,10 @@
     </row>
     <row r="112" spans="1:33">
       <c r="A112">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B112" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C112" t="s">
         <v>141</v>
@@ -8868,19 +8886,19 @@
         <v>144</v>
       </c>
       <c r="E112" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F112" t="s">
         <v>147</v>
       </c>
       <c r="G112">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H112">
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J112" t="s">
         <v>169</v>
@@ -8888,14 +8906,11 @@
       <c r="L112" s="1">
         <v>46281</v>
       </c>
-      <c r="M112" t="s">
-        <v>212</v>
-      </c>
       <c r="N112" t="s">
         <v>221</v>
       </c>
       <c r="O112">
-        <v>17311977</v>
+        <v>17756707</v>
       </c>
       <c r="P112" t="s">
         <v>224</v>
@@ -8904,7 +8919,7 @@
         <v>237</v>
       </c>
       <c r="R112" s="1">
-        <v>46286.74416459491</v>
+        <v>46281.61917203703</v>
       </c>
       <c r="S112">
         <v>14</v>
@@ -8914,9 +8929,6 @@
       </c>
       <c r="U112" t="s">
         <v>243</v>
-      </c>
-      <c r="W112" t="s">
-        <v>258</v>
       </c>
       <c r="AA112">
         <v>0</v>
@@ -8948,13 +8960,13 @@
         <v>147</v>
       </c>
       <c r="G113">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J113" t="s">
         <v>169</v>
@@ -8962,11 +8974,14 @@
       <c r="L113" s="1">
         <v>46281</v>
       </c>
+      <c r="M113" t="s">
+        <v>212</v>
+      </c>
       <c r="N113" t="s">
         <v>221</v>
       </c>
       <c r="O113">
-        <v>17756707</v>
+        <v>17756717</v>
       </c>
       <c r="P113" t="s">
         <v>224</v>
@@ -8975,7 +8990,7 @@
         <v>237</v>
       </c>
       <c r="R113" s="1">
-        <v>46281.61917203703</v>
+        <v>46286.74416505787</v>
       </c>
       <c r="S113">
         <v>14</v>
@@ -8986,6 +9001,9 @@
       <c r="U113" t="s">
         <v>243</v>
       </c>
+      <c r="W113" t="s">
+        <v>258</v>
+      </c>
       <c r="AA113">
         <v>0</v>
       </c>
@@ -8998,10 +9016,10 @@
     </row>
     <row r="114" spans="1:33">
       <c r="A114">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B114" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C114" t="s">
         <v>141</v>
@@ -9010,19 +9028,19 @@
         <v>144</v>
       </c>
       <c r="E114" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F114" t="s">
         <v>147</v>
       </c>
       <c r="G114">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J114" t="s">
         <v>169</v>
@@ -9030,14 +9048,11 @@
       <c r="L114" s="1">
         <v>46281</v>
       </c>
-      <c r="M114" t="s">
-        <v>212</v>
-      </c>
       <c r="N114" t="s">
         <v>221</v>
       </c>
       <c r="O114">
-        <v>17756717</v>
+        <v>17221886</v>
       </c>
       <c r="P114" t="s">
         <v>224</v>
@@ -9046,7 +9061,7 @@
         <v>237</v>
       </c>
       <c r="R114" s="1">
-        <v>46286.74416505787</v>
+        <v>46281.6191725</v>
       </c>
       <c r="S114">
         <v>14</v>
@@ -9056,9 +9071,6 @@
       </c>
       <c r="U114" t="s">
         <v>243</v>
-      </c>
-      <c r="W114" t="s">
-        <v>258</v>
       </c>
       <c r="AA114">
         <v>0</v>
@@ -9090,13 +9102,13 @@
         <v>147</v>
       </c>
       <c r="G115">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J115" t="s">
         <v>169</v>
@@ -9104,11 +9116,14 @@
       <c r="L115" s="1">
         <v>46281</v>
       </c>
+      <c r="M115" t="s">
+        <v>212</v>
+      </c>
       <c r="N115" t="s">
         <v>221</v>
       </c>
       <c r="O115">
-        <v>17221886</v>
+        <v>17221914</v>
       </c>
       <c r="P115" t="s">
         <v>224</v>
@@ -9117,7 +9132,7 @@
         <v>237</v>
       </c>
       <c r="R115" s="1">
-        <v>46281.6191725</v>
+        <v>46286.74416604167</v>
       </c>
       <c r="S115">
         <v>14</v>
@@ -9128,6 +9143,9 @@
       <c r="U115" t="s">
         <v>243</v>
       </c>
+      <c r="W115" t="s">
+        <v>258</v>
+      </c>
       <c r="AA115">
         <v>0</v>
       </c>
@@ -9140,10 +9158,10 @@
     </row>
     <row r="116" spans="1:33">
       <c r="A116">
-        <v>4063</v>
+        <v>4535</v>
       </c>
       <c r="B116" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C116" t="s">
         <v>141</v>
@@ -9152,19 +9170,19 @@
         <v>144</v>
       </c>
       <c r="E116" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F116" t="s">
         <v>147</v>
       </c>
       <c r="G116">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H116">
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J116" t="s">
         <v>169</v>
@@ -9172,14 +9190,11 @@
       <c r="L116" s="1">
         <v>46281</v>
       </c>
-      <c r="M116" t="s">
-        <v>212</v>
-      </c>
       <c r="N116" t="s">
         <v>221</v>
       </c>
       <c r="O116">
-        <v>17221914</v>
+        <v>17260697</v>
       </c>
       <c r="P116" t="s">
         <v>224</v>
@@ -9188,7 +9203,7 @@
         <v>237</v>
       </c>
       <c r="R116" s="1">
-        <v>46286.74416604167</v>
+        <v>46281.61917288195</v>
       </c>
       <c r="S116">
         <v>14</v>
@@ -9198,9 +9213,6 @@
       </c>
       <c r="U116" t="s">
         <v>243</v>
-      </c>
-      <c r="W116" t="s">
-        <v>258</v>
       </c>
       <c r="AA116">
         <v>0</v>
@@ -9232,13 +9244,13 @@
         <v>147</v>
       </c>
       <c r="G117">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H117">
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J117" t="s">
         <v>169</v>
@@ -9246,11 +9258,14 @@
       <c r="L117" s="1">
         <v>46281</v>
       </c>
+      <c r="M117" t="s">
+        <v>212</v>
+      </c>
       <c r="N117" t="s">
         <v>221</v>
       </c>
       <c r="O117">
-        <v>17260697</v>
+        <v>17260707</v>
       </c>
       <c r="P117" t="s">
         <v>224</v>
@@ -9259,7 +9274,7 @@
         <v>237</v>
       </c>
       <c r="R117" s="1">
-        <v>46281.61917288195</v>
+        <v>46286.74416644676</v>
       </c>
       <c r="S117">
         <v>14</v>
@@ -9270,6 +9285,9 @@
       <c r="U117" t="s">
         <v>243</v>
       </c>
+      <c r="W117" t="s">
+        <v>258</v>
+      </c>
       <c r="AA117">
         <v>0</v>
       </c>
@@ -9282,16 +9300,16 @@
     </row>
     <row r="118" spans="1:33">
       <c r="A118">
-        <v>4535</v>
+        <v>4815</v>
       </c>
       <c r="B118" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="C118" t="s">
         <v>141</v>
       </c>
       <c r="D118" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E118" t="s">
         <v>147</v>
@@ -9300,13 +9318,13 @@
         <v>147</v>
       </c>
       <c r="G118">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H118">
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J118" t="s">
         <v>169</v>
@@ -9314,14 +9332,11 @@
       <c r="L118" s="1">
         <v>46281</v>
       </c>
-      <c r="M118" t="s">
-        <v>212</v>
-      </c>
       <c r="N118" t="s">
         <v>221</v>
       </c>
       <c r="O118">
-        <v>17260707</v>
+        <v>17728410</v>
       </c>
       <c r="P118" t="s">
         <v>224</v>
@@ -9330,7 +9345,7 @@
         <v>237</v>
       </c>
       <c r="R118" s="1">
-        <v>46286.74416644676</v>
+        <v>46281.61917341435</v>
       </c>
       <c r="S118">
         <v>14</v>
@@ -9340,9 +9355,6 @@
       </c>
       <c r="U118" t="s">
         <v>243</v>
-      </c>
-      <c r="W118" t="s">
-        <v>258</v>
       </c>
       <c r="AA118">
         <v>0</v>
@@ -9374,13 +9386,13 @@
         <v>147</v>
       </c>
       <c r="G119">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H119">
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J119" t="s">
         <v>169</v>
@@ -9388,11 +9400,14 @@
       <c r="L119" s="1">
         <v>46281</v>
       </c>
+      <c r="M119" t="s">
+        <v>212</v>
+      </c>
       <c r="N119" t="s">
         <v>221</v>
       </c>
       <c r="O119">
-        <v>17728410</v>
+        <v>17728420</v>
       </c>
       <c r="P119" t="s">
         <v>224</v>
@@ -9401,7 +9416,7 @@
         <v>237</v>
       </c>
       <c r="R119" s="1">
-        <v>46281.61917341435</v>
+        <v>46286.74416686343</v>
       </c>
       <c r="S119">
         <v>14</v>
@@ -9412,6 +9427,9 @@
       <c r="U119" t="s">
         <v>243</v>
       </c>
+      <c r="W119" t="s">
+        <v>258</v>
+      </c>
       <c r="AA119">
         <v>0</v>
       </c>
@@ -9424,16 +9442,16 @@
     </row>
     <row r="120" spans="1:33">
       <c r="A120">
-        <v>4815</v>
+        <v>4059</v>
       </c>
       <c r="B120" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C120" t="s">
         <v>141</v>
       </c>
       <c r="D120" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E120" t="s">
         <v>147</v>
@@ -9442,28 +9460,25 @@
         <v>147</v>
       </c>
       <c r="G120">
-        <v>9600</v>
+        <v>11293</v>
       </c>
       <c r="H120">
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J120" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="L120" s="1">
-        <v>46281</v>
-      </c>
-      <c r="M120" t="s">
-        <v>212</v>
+        <v>46267</v>
       </c>
       <c r="N120" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O120">
-        <v>17728420</v>
+        <v>17311936</v>
       </c>
       <c r="P120" t="s">
         <v>224</v>
@@ -9472,10 +9487,10 @@
         <v>237</v>
       </c>
       <c r="R120" s="1">
-        <v>46286.74416686343</v>
+        <v>46267.65902924768</v>
       </c>
       <c r="S120">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T120" t="s">
         <v>238</v>
@@ -9483,9 +9498,6 @@
       <c r="U120" t="s">
         <v>243</v>
       </c>
-      <c r="W120" t="s">
-        <v>258</v>
-      </c>
       <c r="AA120">
         <v>0</v>
       </c>
@@ -9498,10 +9510,10 @@
     </row>
     <row r="121" spans="1:33">
       <c r="A121">
-        <v>4059</v>
+        <v>4061</v>
       </c>
       <c r="B121" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C121" t="s">
         <v>141</v>
@@ -9510,7 +9522,7 @@
         <v>144</v>
       </c>
       <c r="E121" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F121" t="s">
         <v>147</v>
@@ -9522,7 +9534,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J121" t="s">
         <v>178</v>
@@ -9534,7 +9546,7 @@
         <v>220</v>
       </c>
       <c r="O121">
-        <v>17311936</v>
+        <v>17311986</v>
       </c>
       <c r="P121" t="s">
         <v>224</v>
@@ -9543,7 +9555,7 @@
         <v>237</v>
       </c>
       <c r="R121" s="1">
-        <v>46267.65902924768</v>
+        <v>46267.65903065972</v>
       </c>
       <c r="S121">
         <v>28</v>
@@ -9566,10 +9578,10 @@
     </row>
     <row r="122" spans="1:33">
       <c r="A122">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B122" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C122" t="s">
         <v>141</v>
@@ -9578,7 +9590,7 @@
         <v>144</v>
       </c>
       <c r="E122" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F122" t="s">
         <v>147</v>
@@ -9590,7 +9602,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J122" t="s">
         <v>178</v>
@@ -9602,7 +9614,7 @@
         <v>220</v>
       </c>
       <c r="O122">
-        <v>17311986</v>
+        <v>17756726</v>
       </c>
       <c r="P122" t="s">
         <v>224</v>
@@ -9611,7 +9623,7 @@
         <v>237</v>
       </c>
       <c r="R122" s="1">
-        <v>46267.65903065972</v>
+        <v>46267.65903172454</v>
       </c>
       <c r="S122">
         <v>28</v>
@@ -9634,10 +9646,10 @@
     </row>
     <row r="123" spans="1:33">
       <c r="A123">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B123" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C123" t="s">
         <v>141</v>
@@ -9646,7 +9658,7 @@
         <v>144</v>
       </c>
       <c r="E123" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F123" t="s">
         <v>147</v>
@@ -9658,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J123" t="s">
         <v>178</v>
@@ -9670,7 +9682,7 @@
         <v>220</v>
       </c>
       <c r="O123">
-        <v>17756726</v>
+        <v>17221940</v>
       </c>
       <c r="P123" t="s">
         <v>224</v>
@@ -9679,7 +9691,7 @@
         <v>237</v>
       </c>
       <c r="R123" s="1">
-        <v>46267.65903172454</v>
+        <v>46267.65903244213</v>
       </c>
       <c r="S123">
         <v>28</v>
@@ -9702,10 +9714,10 @@
     </row>
     <row r="124" spans="1:33">
       <c r="A124">
-        <v>4063</v>
+        <v>4535</v>
       </c>
       <c r="B124" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C124" t="s">
         <v>141</v>
@@ -9714,7 +9726,7 @@
         <v>144</v>
       </c>
       <c r="E124" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F124" t="s">
         <v>147</v>
@@ -9726,7 +9738,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J124" t="s">
         <v>178</v>
@@ -9738,7 +9750,7 @@
         <v>220</v>
       </c>
       <c r="O124">
-        <v>17221940</v>
+        <v>17260716</v>
       </c>
       <c r="P124" t="s">
         <v>224</v>
@@ -9747,7 +9759,7 @@
         <v>237</v>
       </c>
       <c r="R124" s="1">
-        <v>46267.65903244213</v>
+        <v>46267.65903319445</v>
       </c>
       <c r="S124">
         <v>28</v>
@@ -9770,16 +9782,16 @@
     </row>
     <row r="125" spans="1:33">
       <c r="A125">
-        <v>4535</v>
+        <v>4815</v>
       </c>
       <c r="B125" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="C125" t="s">
         <v>141</v>
       </c>
       <c r="D125" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E125" t="s">
         <v>147</v>
@@ -9794,7 +9806,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J125" t="s">
         <v>178</v>
@@ -9806,7 +9818,7 @@
         <v>220</v>
       </c>
       <c r="O125">
-        <v>17260716</v>
+        <v>17728429</v>
       </c>
       <c r="P125" t="s">
         <v>224</v>
@@ -9815,7 +9827,7 @@
         <v>237</v>
       </c>
       <c r="R125" s="1">
-        <v>46267.65903319445</v>
+        <v>46267.65903408565</v>
       </c>
       <c r="S125">
         <v>28</v>
@@ -9838,16 +9850,16 @@
     </row>
     <row r="126" spans="1:33">
       <c r="A126">
-        <v>4815</v>
+        <v>4059</v>
       </c>
       <c r="B126" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C126" t="s">
         <v>141</v>
       </c>
       <c r="D126" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E126" t="s">
         <v>147</v>
@@ -9856,25 +9868,25 @@
         <v>147</v>
       </c>
       <c r="G126">
-        <v>11293</v>
+        <v>9570</v>
       </c>
       <c r="H126">
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J126" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L126" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="N126" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O126">
-        <v>17728429</v>
+        <v>17311907</v>
       </c>
       <c r="P126" t="s">
         <v>224</v>
@@ -9883,10 +9895,10 @@
         <v>237</v>
       </c>
       <c r="R126" s="1">
-        <v>46267.65903408565</v>
+        <v>46266.65725641204</v>
       </c>
       <c r="S126">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T126" t="s">
         <v>238</v>
@@ -9901,15 +9913,15 @@
         <v>224</v>
       </c>
       <c r="AG126" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="127" spans="1:33">
       <c r="A127">
-        <v>4059</v>
+        <v>4061</v>
       </c>
       <c r="B127" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C127" t="s">
         <v>141</v>
@@ -9918,7 +9930,7 @@
         <v>144</v>
       </c>
       <c r="E127" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F127" t="s">
         <v>147</v>
@@ -9930,7 +9942,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J127" t="s">
         <v>179</v>
@@ -9942,7 +9954,7 @@
         <v>221</v>
       </c>
       <c r="O127">
-        <v>17311907</v>
+        <v>17311957</v>
       </c>
       <c r="P127" t="s">
         <v>224</v>
@@ -9951,7 +9963,7 @@
         <v>237</v>
       </c>
       <c r="R127" s="1">
-        <v>46266.65725641204</v>
+        <v>46266.65725738426</v>
       </c>
       <c r="S127">
         <v>29</v>
@@ -9974,10 +9986,10 @@
     </row>
     <row r="128" spans="1:33">
       <c r="A128">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B128" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C128" t="s">
         <v>141</v>
@@ -9986,7 +9998,7 @@
         <v>144</v>
       </c>
       <c r="E128" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F128" t="s">
         <v>147</v>
@@ -9998,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J128" t="s">
         <v>179</v>
@@ -10010,7 +10022,7 @@
         <v>221</v>
       </c>
       <c r="O128">
-        <v>17311957</v>
+        <v>17756697</v>
       </c>
       <c r="P128" t="s">
         <v>224</v>
@@ -10019,7 +10031,7 @@
         <v>237</v>
       </c>
       <c r="R128" s="1">
-        <v>46266.65725738426</v>
+        <v>46266.65725806713</v>
       </c>
       <c r="S128">
         <v>29</v>
@@ -10042,10 +10054,10 @@
     </row>
     <row r="129" spans="1:33">
       <c r="A129">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B129" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C129" t="s">
         <v>141</v>
@@ -10054,7 +10066,7 @@
         <v>144</v>
       </c>
       <c r="E129" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F129" t="s">
         <v>147</v>
@@ -10066,7 +10078,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J129" t="s">
         <v>179</v>
@@ -10078,7 +10090,7 @@
         <v>221</v>
       </c>
       <c r="O129">
-        <v>17756697</v>
+        <v>17221863</v>
       </c>
       <c r="P129" t="s">
         <v>224</v>
@@ -10087,7 +10099,7 @@
         <v>237</v>
       </c>
       <c r="R129" s="1">
-        <v>46266.65725806713</v>
+        <v>46266.65725861111</v>
       </c>
       <c r="S129">
         <v>29</v>
@@ -10110,10 +10122,10 @@
     </row>
     <row r="130" spans="1:33">
       <c r="A130">
-        <v>4063</v>
+        <v>4535</v>
       </c>
       <c r="B130" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C130" t="s">
         <v>141</v>
@@ -10122,7 +10134,7 @@
         <v>144</v>
       </c>
       <c r="E130" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F130" t="s">
         <v>147</v>
@@ -10134,7 +10146,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J130" t="s">
         <v>179</v>
@@ -10146,7 +10158,7 @@
         <v>221</v>
       </c>
       <c r="O130">
-        <v>17221863</v>
+        <v>17260687</v>
       </c>
       <c r="P130" t="s">
         <v>224</v>
@@ -10155,7 +10167,7 @@
         <v>237</v>
       </c>
       <c r="R130" s="1">
-        <v>46266.65725861111</v>
+        <v>46266.65725960648</v>
       </c>
       <c r="S130">
         <v>29</v>
@@ -10178,16 +10190,16 @@
     </row>
     <row r="131" spans="1:33">
       <c r="A131">
-        <v>4535</v>
+        <v>4917</v>
       </c>
       <c r="B131" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="C131" t="s">
         <v>141</v>
       </c>
       <c r="D131" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E131" t="s">
         <v>147</v>
@@ -10196,25 +10208,28 @@
         <v>147</v>
       </c>
       <c r="G131">
-        <v>9570</v>
+        <v>9277</v>
       </c>
       <c r="H131">
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J131" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L131" s="1">
-        <v>46266</v>
+        <v>46295</v>
+      </c>
+      <c r="M131" t="s">
+        <v>211</v>
       </c>
       <c r="N131" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O131">
-        <v>17260687</v>
+        <v>17629821</v>
       </c>
       <c r="P131" t="s">
         <v>224</v>
@@ -10223,16 +10238,19 @@
         <v>237</v>
       </c>
       <c r="R131" s="1">
-        <v>46266.65725960648</v>
+        <v>46295.40261266204</v>
       </c>
       <c r="S131">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="T131" t="s">
         <v>238</v>
       </c>
       <c r="U131" t="s">
         <v>243</v>
+      </c>
+      <c r="W131" t="s">
+        <v>254</v>
       </c>
       <c r="AA131">
         <v>0</v>
@@ -55060,7 +55078,7 @@
         <v>2143</v>
       </c>
       <c r="I765" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J765" t="s">
         <v>201</v>
@@ -55134,7 +55152,7 @@
         <v>2143</v>
       </c>
       <c r="I766" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J766" t="s">
         <v>201</v>
@@ -55208,7 +55226,7 @@
         <v>2143</v>
       </c>
       <c r="I767" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J767" t="s">
         <v>202</v>
@@ -55282,7 +55300,7 @@
         <v>2143</v>
       </c>
       <c r="I768" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J768" t="s">
         <v>203</v>
@@ -55356,7 +55374,7 @@
         <v>2143</v>
       </c>
       <c r="I769" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J769" t="s">
         <v>204</v>
@@ -55430,7 +55448,7 @@
         <v>2143</v>
       </c>
       <c r="I770" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J770" t="s">
         <v>205</v>
@@ -55504,7 +55522,7 @@
         <v>2143</v>
       </c>
       <c r="I771" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J771" t="s">
         <v>205</v>
@@ -55578,7 +55596,7 @@
         <v>2143</v>
       </c>
       <c r="I772" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J772" t="s">
         <v>206</v>
@@ -55652,7 +55670,7 @@
         <v>2143</v>
       </c>
       <c r="I773" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J773" t="s">
         <v>190</v>
@@ -55726,7 +55744,7 @@
         <v>2143</v>
       </c>
       <c r="I774" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J774" t="s">
         <v>190</v>
@@ -55800,7 +55818,7 @@
         <v>0</v>
       </c>
       <c r="I775" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J775" t="s">
         <v>172</v>
@@ -55874,7 +55892,7 @@
         <v>0</v>
       </c>
       <c r="I776" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J776" t="s">
         <v>172</v>
@@ -55948,7 +55966,7 @@
         <v>0</v>
       </c>
       <c r="I777" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J777" t="s">
         <v>207</v>
@@ -56022,7 +56040,7 @@
         <v>0</v>
       </c>
       <c r="I778" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J778" t="s">
         <v>207</v>
@@ -56096,7 +56114,7 @@
         <v>0</v>
       </c>
       <c r="I779" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J779" t="s">
         <v>167</v>
@@ -56170,7 +56188,7 @@
         <v>0</v>
       </c>
       <c r="I780" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J780" t="s">
         <v>167</v>
@@ -56244,7 +56262,7 @@
         <v>0</v>
       </c>
       <c r="I781" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J781" t="s">
         <v>170</v>
@@ -56315,7 +56333,7 @@
         <v>0</v>
       </c>
       <c r="I782" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J782" t="s">
         <v>181</v>
@@ -56389,7 +56407,7 @@
         <v>0</v>
       </c>
       <c r="I783" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J783" t="s">
         <v>181</v>
@@ -56463,7 +56481,7 @@
         <v>0</v>
       </c>
       <c r="I784" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J784" t="s">
         <v>199</v>
@@ -56531,7 +56549,7 @@
         <v>0</v>
       </c>
       <c r="I785" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J785" t="s">
         <v>199</v>
@@ -56599,7 +56617,7 @@
         <v>0</v>
       </c>
       <c r="I786" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J786" t="s">
         <v>199</v>
@@ -56667,7 +56685,7 @@
         <v>0</v>
       </c>
       <c r="I787" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J787" t="s">
         <v>199</v>
@@ -56735,7 +56753,7 @@
         <v>0</v>
       </c>
       <c r="I788" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J788" t="s">
         <v>199</v>
@@ -56803,7 +56821,7 @@
         <v>0</v>
       </c>
       <c r="I789" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J789" t="s">
         <v>199</v>
@@ -56871,7 +56889,7 @@
         <v>0</v>
       </c>
       <c r="I790" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J790" t="s">
         <v>188</v>
@@ -56939,7 +56957,7 @@
         <v>0</v>
       </c>
       <c r="I791" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J791" t="s">
         <v>188</v>
@@ -57007,7 +57025,7 @@
         <v>0</v>
       </c>
       <c r="I792" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J792" t="s">
         <v>188</v>
@@ -57075,7 +57093,7 @@
         <v>0</v>
       </c>
       <c r="I793" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J793" t="s">
         <v>188</v>
@@ -57143,7 +57161,7 @@
         <v>0</v>
       </c>
       <c r="I794" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J794" t="s">
         <v>188</v>
@@ -57211,7 +57229,7 @@
         <v>0</v>
       </c>
       <c r="I795" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J795" t="s">
         <v>188</v>
@@ -57279,7 +57297,7 @@
         <v>0</v>
       </c>
       <c r="I796" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J796" t="s">
         <v>188</v>
@@ -57347,7 +57365,7 @@
         <v>0</v>
       </c>
       <c r="I797" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J797" t="s">
         <v>188</v>
@@ -57415,7 +57433,7 @@
         <v>0</v>
       </c>
       <c r="I798" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J798" t="s">
         <v>188</v>
@@ -57483,7 +57501,7 @@
         <v>0</v>
       </c>
       <c r="I799" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J799" t="s">
         <v>188</v>
@@ -57551,7 +57569,7 @@
         <v>0</v>
       </c>
       <c r="I800" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J800" t="s">
         <v>188</v>
@@ -57619,7 +57637,7 @@
         <v>0</v>
       </c>
       <c r="I801" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J801" t="s">
         <v>188</v>
@@ -57687,7 +57705,7 @@
         <v>0</v>
       </c>
       <c r="I802" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J802" t="s">
         <v>188</v>
@@ -57755,7 +57773,7 @@
         <v>0</v>
       </c>
       <c r="I803" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J803" t="s">
         <v>188</v>
@@ -57823,7 +57841,7 @@
         <v>0</v>
       </c>
       <c r="I804" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J804" t="s">
         <v>188</v>
@@ -57891,7 +57909,7 @@
         <v>2143</v>
       </c>
       <c r="I805" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J805" t="s">
         <v>200</v>

--- a/dados/base/bpo.xlsx
+++ b/dados/base/bpo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12227" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12228" uniqueCount="288">
   <si>
     <t>CodCliente</t>
   </si>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>BENEDITO FRANCISCO BABOSA EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>GBA FOOD SERVICE LTDA</t>
   </si>
   <si>
     <t>LOTERICA ARCADAS LTDA</t>
@@ -263,6 +260,9 @@
   </si>
   <si>
     <t xml:space="preserve">GBA IMÓVEIS LTDA </t>
+  </si>
+  <si>
+    <t>GBA FOOD SERVICE LTDA</t>
   </si>
   <si>
     <t>B. A. BARBOSA SUPERMERCADO LTDA (FILIAL 02)</t>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="3" spans="1:34">
       <c r="A3">
-        <v>4815</v>
+        <v>4917</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -1411,7 +1411,7 @@
         <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
         <v>147</v>
@@ -1441,7 +1441,7 @@
         <v>220</v>
       </c>
       <c r="O3">
-        <v>17728378</v>
+        <v>17629831</v>
       </c>
       <c r="P3" t="s">
         <v>224</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="4" spans="1:34">
       <c r="A4">
-        <v>4917</v>
+        <v>2371</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
@@ -1479,7 +1479,7 @@
         <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>147</v>
@@ -1488,57 +1488,57 @@
         <v>147</v>
       </c>
       <c r="G4">
-        <v>9309</v>
+        <v>7038</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L4" s="1">
-        <v>46290</v>
+        <v>46280</v>
       </c>
       <c r="M4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O4">
-        <v>17629831</v>
+        <v>17540583</v>
       </c>
       <c r="P4" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="Q4" t="s">
         <v>235</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AG4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5">
-        <v>2371</v>
+        <v>3366</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
@@ -1547,7 +1547,7 @@
         <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
         <v>147</v>
@@ -1577,7 +1577,7 @@
         <v>221</v>
       </c>
       <c r="O5">
-        <v>17540583</v>
+        <v>17448677</v>
       </c>
       <c r="P5" t="s">
         <v>147</v>
@@ -1606,16 +1606,16 @@
     </row>
     <row r="6" spans="1:34">
       <c r="A6">
-        <v>3366</v>
+        <v>2371</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
         <v>147</v>
@@ -1624,7 +1624,7 @@
         <v>147</v>
       </c>
       <c r="G6">
-        <v>7038</v>
+        <v>11290</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1633,10 +1633,10 @@
         <v>154</v>
       </c>
       <c r="J6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L6" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M6" t="s">
         <v>210</v>
@@ -1645,7 +1645,7 @@
         <v>221</v>
       </c>
       <c r="O6">
-        <v>17448677</v>
+        <v>17540614</v>
       </c>
       <c r="P6" t="s">
         <v>147</v>
@@ -1654,7 +1654,7 @@
         <v>235</v>
       </c>
       <c r="S6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T6" t="s">
         <v>239</v>
@@ -1669,15 +1669,15 @@
         <v>0</v>
       </c>
       <c r="AG6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:34">
       <c r="A7">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>141</v>
@@ -1713,7 +1713,7 @@
         <v>221</v>
       </c>
       <c r="O7">
-        <v>17540614</v>
+        <v>17503158</v>
       </c>
       <c r="P7" t="s">
         <v>147</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="8" spans="1:34">
       <c r="A8">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
@@ -1781,7 +1781,7 @@
         <v>221</v>
       </c>
       <c r="O8">
-        <v>17503158</v>
+        <v>17503208</v>
       </c>
       <c r="P8" t="s">
         <v>147</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="9" spans="1:34">
       <c r="A9">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="B9" t="s">
         <v>40</v>
@@ -1849,7 +1849,7 @@
         <v>221</v>
       </c>
       <c r="O9">
-        <v>17503208</v>
+        <v>17412526</v>
       </c>
       <c r="P9" t="s">
         <v>147</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="10" spans="1:34">
       <c r="A10">
-        <v>2374</v>
+        <v>2395</v>
       </c>
       <c r="B10" t="s">
         <v>41</v>
@@ -1917,7 +1917,7 @@
         <v>221</v>
       </c>
       <c r="O10">
-        <v>17412526</v>
+        <v>17798753</v>
       </c>
       <c r="P10" t="s">
         <v>147</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="11" spans="1:34">
       <c r="A11">
-        <v>2395</v>
+        <v>2426</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1985,7 +1985,7 @@
         <v>221</v>
       </c>
       <c r="O11">
-        <v>17798753</v>
+        <v>17671185</v>
       </c>
       <c r="P11" t="s">
         <v>147</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="12" spans="1:34">
       <c r="A12">
-        <v>2426</v>
+        <v>2994</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
@@ -2053,7 +2053,7 @@
         <v>221</v>
       </c>
       <c r="O12">
-        <v>17671185</v>
+        <v>17269394</v>
       </c>
       <c r="P12" t="s">
         <v>147</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="13" spans="1:34">
       <c r="A13">
-        <v>2994</v>
+        <v>3278</v>
       </c>
       <c r="B13" t="s">
         <v>44</v>
@@ -2121,7 +2121,7 @@
         <v>221</v>
       </c>
       <c r="O13">
-        <v>17269394</v>
+        <v>17595355</v>
       </c>
       <c r="P13" t="s">
         <v>147</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="14" spans="1:34">
       <c r="A14">
-        <v>3278</v>
+        <v>3279</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
@@ -2189,7 +2189,7 @@
         <v>221</v>
       </c>
       <c r="O14">
-        <v>17595355</v>
+        <v>17277245</v>
       </c>
       <c r="P14" t="s">
         <v>147</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="15" spans="1:34">
       <c r="A15">
-        <v>3279</v>
+        <v>3497</v>
       </c>
       <c r="B15" t="s">
         <v>46</v>
@@ -2257,7 +2257,7 @@
         <v>221</v>
       </c>
       <c r="O15">
-        <v>17277245</v>
+        <v>17304750</v>
       </c>
       <c r="P15" t="s">
         <v>147</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="16" spans="1:34">
       <c r="A16">
-        <v>3497</v>
+        <v>3862</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
@@ -2325,7 +2325,7 @@
         <v>221</v>
       </c>
       <c r="O16">
-        <v>17304750</v>
+        <v>17870262</v>
       </c>
       <c r="P16" t="s">
         <v>147</v>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="17" spans="1:33">
       <c r="A17">
-        <v>3862</v>
+        <v>4423</v>
       </c>
       <c r="B17" t="s">
         <v>48</v>
@@ -2393,7 +2393,7 @@
         <v>221</v>
       </c>
       <c r="O17">
-        <v>17870262</v>
+        <v>17166469</v>
       </c>
       <c r="P17" t="s">
         <v>147</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="18" spans="1:33">
       <c r="A18">
-        <v>4423</v>
+        <v>4424</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
@@ -2461,7 +2461,7 @@
         <v>221</v>
       </c>
       <c r="O18">
-        <v>17166469</v>
+        <v>17524207</v>
       </c>
       <c r="P18" t="s">
         <v>147</v>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="19" spans="1:33">
       <c r="A19">
-        <v>4424</v>
+        <v>4633</v>
       </c>
       <c r="B19" t="s">
         <v>50</v>
@@ -2529,7 +2529,7 @@
         <v>221</v>
       </c>
       <c r="O19">
-        <v>17524207</v>
+        <v>17683019</v>
       </c>
       <c r="P19" t="s">
         <v>147</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="20" spans="1:33">
       <c r="A20">
-        <v>4633</v>
+        <v>4990</v>
       </c>
       <c r="B20" t="s">
         <v>51</v>
@@ -2597,7 +2597,7 @@
         <v>221</v>
       </c>
       <c r="O20">
-        <v>17683019</v>
+        <v>17061863</v>
       </c>
       <c r="P20" t="s">
         <v>147</v>
@@ -2626,7 +2626,7 @@
     </row>
     <row r="21" spans="1:33">
       <c r="A21">
-        <v>4990</v>
+        <v>5070</v>
       </c>
       <c r="B21" t="s">
         <v>52</v>
@@ -2665,7 +2665,7 @@
         <v>221</v>
       </c>
       <c r="O21">
-        <v>17061863</v>
+        <v>17374654</v>
       </c>
       <c r="P21" t="s">
         <v>147</v>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="22" spans="1:33">
       <c r="A22">
-        <v>5070</v>
+        <v>3216</v>
       </c>
       <c r="B22" t="s">
         <v>53</v>
@@ -2703,52 +2703,52 @@
         <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F22" t="s">
         <v>147</v>
       </c>
       <c r="G22">
-        <v>11290</v>
+        <v>6803</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L22" s="1">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="M22" t="s">
         <v>210</v>
       </c>
       <c r="N22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O22">
-        <v>17374654</v>
+        <v>17758819</v>
       </c>
       <c r="P22" t="s">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c r="Q22" t="s">
         <v>235</v>
       </c>
       <c r="S22">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W22" t="s">
         <v>246</v>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="23" spans="1:33">
       <c r="A23">
-        <v>3216</v>
+        <v>3218</v>
       </c>
       <c r="B23" t="s">
         <v>54</v>
@@ -2801,7 +2801,7 @@
         <v>220</v>
       </c>
       <c r="O23">
-        <v>17758819</v>
+        <v>17135394</v>
       </c>
       <c r="P23" t="s">
         <v>225</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="24" spans="1:33">
       <c r="A24">
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="B24" t="s">
         <v>55</v>
@@ -2869,7 +2869,7 @@
         <v>220</v>
       </c>
       <c r="O24">
-        <v>17135394</v>
+        <v>17726270</v>
       </c>
       <c r="P24" t="s">
         <v>225</v>
@@ -2898,10 +2898,10 @@
     </row>
     <row r="25" spans="1:33">
       <c r="A25">
-        <v>3220</v>
+        <v>3216</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
         <v>141</v>
@@ -2916,7 +2916,7 @@
         <v>147</v>
       </c>
       <c r="G25">
-        <v>6803</v>
+        <v>6131</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2925,10 +2925,10 @@
         <v>155</v>
       </c>
       <c r="J25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L25" s="1">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="M25" t="s">
         <v>210</v>
@@ -2937,7 +2937,7 @@
         <v>220</v>
       </c>
       <c r="O25">
-        <v>17726270</v>
+        <v>17758775</v>
       </c>
       <c r="P25" t="s">
         <v>225</v>
@@ -2946,7 +2946,7 @@
         <v>235</v>
       </c>
       <c r="S25">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T25" t="s">
         <v>240</v>
@@ -2955,21 +2955,21 @@
         <v>243</v>
       </c>
       <c r="W25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AG25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:33">
       <c r="A26">
-        <v>3216</v>
+        <v>3666</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
         <v>141</v>
@@ -3005,7 +3005,7 @@
         <v>220</v>
       </c>
       <c r="O26">
-        <v>17758775</v>
+        <v>17722618</v>
       </c>
       <c r="P26" t="s">
         <v>225</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="27" spans="1:33">
       <c r="A27">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="B27" t="s">
         <v>57</v>
@@ -3073,7 +3073,7 @@
         <v>220</v>
       </c>
       <c r="O27">
-        <v>17722618</v>
+        <v>17314162</v>
       </c>
       <c r="P27" t="s">
         <v>225</v>
@@ -3102,7 +3102,7 @@
     </row>
     <row r="28" spans="1:33">
       <c r="A28">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="B28" t="s">
         <v>58</v>
@@ -3141,7 +3141,7 @@
         <v>220</v>
       </c>
       <c r="O28">
-        <v>17314162</v>
+        <v>17314317</v>
       </c>
       <c r="P28" t="s">
         <v>225</v>
@@ -3170,7 +3170,7 @@
     </row>
     <row r="29" spans="1:33">
       <c r="A29">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="B29" t="s">
         <v>59</v>
@@ -3209,7 +3209,7 @@
         <v>220</v>
       </c>
       <c r="O29">
-        <v>17314317</v>
+        <v>17772375</v>
       </c>
       <c r="P29" t="s">
         <v>225</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="30" spans="1:33">
       <c r="A30">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="B30" t="s">
         <v>60</v>
@@ -3277,7 +3277,7 @@
         <v>220</v>
       </c>
       <c r="O30">
-        <v>17772375</v>
+        <v>17035326</v>
       </c>
       <c r="P30" t="s">
         <v>225</v>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="31" spans="1:33">
       <c r="A31">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="B31" t="s">
         <v>61</v>
@@ -3345,7 +3345,7 @@
         <v>220</v>
       </c>
       <c r="O31">
-        <v>17035326</v>
+        <v>17772510</v>
       </c>
       <c r="P31" t="s">
         <v>225</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="32" spans="1:33">
       <c r="A32">
-        <v>3671</v>
+        <v>4614</v>
       </c>
       <c r="B32" t="s">
         <v>62</v>
@@ -3413,7 +3413,7 @@
         <v>220</v>
       </c>
       <c r="O32">
-        <v>17772510</v>
+        <v>17880107</v>
       </c>
       <c r="P32" t="s">
         <v>225</v>
@@ -3442,10 +3442,10 @@
     </row>
     <row r="33" spans="1:33">
       <c r="A33">
-        <v>4614</v>
+        <v>3216</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
         <v>141</v>
@@ -3460,37 +3460,37 @@
         <v>147</v>
       </c>
       <c r="G33">
-        <v>6131</v>
+        <v>7042</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J33" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L33" s="1">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="M33" t="s">
         <v>210</v>
       </c>
       <c r="N33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O33">
-        <v>17880107</v>
+        <v>17758840</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q33" t="s">
         <v>235</v>
       </c>
       <c r="S33">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T33" t="s">
         <v>240</v>
@@ -3499,27 +3499,27 @@
         <v>243</v>
       </c>
       <c r="W33" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AG33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" spans="1:33">
       <c r="A34">
-        <v>3216</v>
+        <v>3219</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
         <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
         <v>148</v>
@@ -3549,7 +3549,7 @@
         <v>221</v>
       </c>
       <c r="O34">
-        <v>17758840</v>
+        <v>17515452</v>
       </c>
       <c r="P34" t="s">
         <v>226</v>
@@ -3578,16 +3578,16 @@
     </row>
     <row r="35" spans="1:33">
       <c r="A35">
-        <v>3219</v>
+        <v>3667</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
         <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
         <v>148</v>
@@ -3617,7 +3617,7 @@
         <v>221</v>
       </c>
       <c r="O35">
-        <v>17515452</v>
+        <v>17314228</v>
       </c>
       <c r="P35" t="s">
         <v>226</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="36" spans="1:33">
       <c r="A36">
-        <v>3667</v>
+        <v>3669</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
         <v>141</v>
@@ -3685,7 +3685,7 @@
         <v>221</v>
       </c>
       <c r="O36">
-        <v>17314228</v>
+        <v>17772421</v>
       </c>
       <c r="P36" t="s">
         <v>226</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="37" spans="1:33">
       <c r="A37">
-        <v>3669</v>
+        <v>2804</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
         <v>141</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
         <v>148</v>
@@ -3732,57 +3732,57 @@
         <v>147</v>
       </c>
       <c r="G37">
-        <v>7042</v>
+        <v>11796</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J37" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L37" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="M37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O37">
-        <v>17772421</v>
+        <v>18165575</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q37" t="s">
         <v>235</v>
       </c>
       <c r="S37">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T37" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="U37" t="s">
         <v>243</v>
       </c>
       <c r="W37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA37">
         <v>0</v>
       </c>
       <c r="AG37" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="1:33">
       <c r="A38">
-        <v>2804</v>
+        <v>3053</v>
       </c>
       <c r="B38" t="s">
         <v>65</v>
@@ -3791,7 +3791,7 @@
         <v>141</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E38" t="s">
         <v>148</v>
@@ -3815,13 +3815,13 @@
         <v>46281</v>
       </c>
       <c r="M38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N38" t="s">
         <v>220</v>
       </c>
       <c r="O38">
-        <v>18165575</v>
+        <v>18165653</v>
       </c>
       <c r="P38" t="s">
         <v>227</v>
@@ -3839,7 +3839,7 @@
         <v>243</v>
       </c>
       <c r="W38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA38">
         <v>0</v>
@@ -3853,7 +3853,7 @@
         <v>3053</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
         <v>141</v>
@@ -3868,7 +3868,7 @@
         <v>147</v>
       </c>
       <c r="G39">
-        <v>11796</v>
+        <v>5770</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -3877,19 +3877,19 @@
         <v>157</v>
       </c>
       <c r="J39" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L39" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="M39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N39" t="s">
         <v>220</v>
       </c>
       <c r="O39">
-        <v>18165653</v>
+        <v>17194085</v>
       </c>
       <c r="P39" t="s">
         <v>227</v>
@@ -3898,7 +3898,7 @@
         <v>235</v>
       </c>
       <c r="S39">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T39" t="s">
         <v>241</v>
@@ -3907,27 +3907,27 @@
         <v>243</v>
       </c>
       <c r="W39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA39">
         <v>0</v>
       </c>
       <c r="AG39" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="40" spans="1:33">
       <c r="A40">
-        <v>3053</v>
+        <v>2804</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
         <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -3936,7 +3936,7 @@
         <v>147</v>
       </c>
       <c r="G40">
-        <v>5770</v>
+        <v>11799</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -3945,10 +3945,10 @@
         <v>157</v>
       </c>
       <c r="J40" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="L40" s="1">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="M40" t="s">
         <v>209</v>
@@ -3957,7 +3957,7 @@
         <v>220</v>
       </c>
       <c r="O40">
-        <v>17194085</v>
+        <v>18165585</v>
       </c>
       <c r="P40" t="s">
         <v>227</v>
@@ -3966,7 +3966,7 @@
         <v>235</v>
       </c>
       <c r="S40">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T40" t="s">
         <v>241</v>
@@ -3975,7 +3975,7 @@
         <v>243</v>
       </c>
       <c r="W40" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA40">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="41" spans="1:33">
       <c r="A41">
-        <v>2804</v>
+        <v>3053</v>
       </c>
       <c r="B41" t="s">
         <v>65</v>
@@ -3995,7 +3995,7 @@
         <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E41" t="s">
         <v>148</v>
@@ -4025,7 +4025,7 @@
         <v>220</v>
       </c>
       <c r="O41">
-        <v>18165585</v>
+        <v>18165663</v>
       </c>
       <c r="P41" t="s">
         <v>227</v>
@@ -4054,16 +4054,16 @@
     </row>
     <row r="42" spans="1:33">
       <c r="A42">
-        <v>3053</v>
+        <v>2804</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
         <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
         <v>148</v>
@@ -4072,7 +4072,7 @@
         <v>147</v>
       </c>
       <c r="G42">
-        <v>11799</v>
+        <v>5652</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -4081,10 +4081,10 @@
         <v>157</v>
       </c>
       <c r="J42" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L42" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="M42" t="s">
         <v>209</v>
@@ -4093,7 +4093,7 @@
         <v>220</v>
       </c>
       <c r="O42">
-        <v>18165663</v>
+        <v>17326571</v>
       </c>
       <c r="P42" t="s">
         <v>227</v>
@@ -4102,7 +4102,7 @@
         <v>235</v>
       </c>
       <c r="S42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" t="s">
         <v>241</v>
@@ -4111,13 +4111,13 @@
         <v>243</v>
       </c>
       <c r="W42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA42">
         <v>0</v>
       </c>
       <c r="AG42" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:33">
@@ -4125,7 +4125,7 @@
         <v>2804</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
         <v>141</v>
@@ -4140,37 +4140,37 @@
         <v>147</v>
       </c>
       <c r="G43">
-        <v>5652</v>
+        <v>3889</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L43" s="1">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="M43" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N43" t="s">
         <v>220</v>
       </c>
       <c r="O43">
-        <v>17326571</v>
+        <v>17326521</v>
       </c>
       <c r="P43" t="s">
         <v>227</v>
       </c>
       <c r="Q43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="S43">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T43" t="s">
         <v>241</v>
@@ -4179,27 +4179,27 @@
         <v>243</v>
       </c>
       <c r="W43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA43">
         <v>0</v>
       </c>
       <c r="AG43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:33">
       <c r="A44">
-        <v>2804</v>
+        <v>2835</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
         <v>141</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E44" t="s">
         <v>148</v>
@@ -4229,7 +4229,7 @@
         <v>220</v>
       </c>
       <c r="O44">
-        <v>17326521</v>
+        <v>17089790</v>
       </c>
       <c r="P44" t="s">
         <v>227</v>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="45" spans="1:33">
       <c r="A45">
-        <v>2835</v>
+        <v>2837</v>
       </c>
       <c r="B45" t="s">
         <v>67</v>
@@ -4297,7 +4297,7 @@
         <v>220</v>
       </c>
       <c r="O45">
-        <v>17089790</v>
+        <v>17582223</v>
       </c>
       <c r="P45" t="s">
         <v>227</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="46" spans="1:33">
       <c r="A46">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="B46" t="s">
         <v>68</v>
@@ -4365,7 +4365,7 @@
         <v>220</v>
       </c>
       <c r="O46">
-        <v>17582223</v>
+        <v>17389934</v>
       </c>
       <c r="P46" t="s">
         <v>227</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="47" spans="1:33">
       <c r="A47">
-        <v>2838</v>
+        <v>2842</v>
       </c>
       <c r="B47" t="s">
         <v>69</v>
@@ -4403,10 +4403,10 @@
         <v>141</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F47" t="s">
         <v>147</v>
@@ -4433,7 +4433,7 @@
         <v>220</v>
       </c>
       <c r="O47">
-        <v>17389934</v>
+        <v>17161497</v>
       </c>
       <c r="P47" t="s">
         <v>227</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="48" spans="1:33">
       <c r="A48">
-        <v>2842</v>
+        <v>3004</v>
       </c>
       <c r="B48" t="s">
         <v>70</v>
@@ -4471,10 +4471,10 @@
         <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" t="s">
         <v>147</v>
@@ -4501,7 +4501,7 @@
         <v>220</v>
       </c>
       <c r="O48">
-        <v>17161497</v>
+        <v>17033150</v>
       </c>
       <c r="P48" t="s">
         <v>227</v>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="49" spans="1:33">
       <c r="A49">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="B49" t="s">
         <v>71</v>
@@ -4569,7 +4569,7 @@
         <v>220</v>
       </c>
       <c r="O49">
-        <v>17033150</v>
+        <v>17263421</v>
       </c>
       <c r="P49" t="s">
         <v>227</v>
@@ -4598,7 +4598,7 @@
     </row>
     <row r="50" spans="1:33">
       <c r="A50">
-        <v>3005</v>
+        <v>3039</v>
       </c>
       <c r="B50" t="s">
         <v>72</v>
@@ -4637,7 +4637,7 @@
         <v>220</v>
       </c>
       <c r="O50">
-        <v>17263421</v>
+        <v>17585676</v>
       </c>
       <c r="P50" t="s">
         <v>227</v>
@@ -4666,16 +4666,16 @@
     </row>
     <row r="51" spans="1:33">
       <c r="A51">
-        <v>3039</v>
+        <v>3053</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s">
         <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E51" t="s">
         <v>148</v>
@@ -4705,7 +4705,7 @@
         <v>220</v>
       </c>
       <c r="O51">
-        <v>17585676</v>
+        <v>17193943</v>
       </c>
       <c r="P51" t="s">
         <v>227</v>
@@ -4734,19 +4734,19 @@
     </row>
     <row r="52" spans="1:33">
       <c r="A52">
-        <v>3053</v>
+        <v>3209</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C52" t="s">
         <v>141</v>
       </c>
       <c r="D52" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E52" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F52" t="s">
         <v>147</v>
@@ -4773,7 +4773,7 @@
         <v>220</v>
       </c>
       <c r="O52">
-        <v>17193943</v>
+        <v>17134936</v>
       </c>
       <c r="P52" t="s">
         <v>227</v>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="53" spans="1:33">
       <c r="A53">
-        <v>3209</v>
+        <v>3480</v>
       </c>
       <c r="B53" t="s">
         <v>74</v>
@@ -4814,7 +4814,7 @@
         <v>142</v>
       </c>
       <c r="E53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F53" t="s">
         <v>147</v>
@@ -4841,7 +4841,7 @@
         <v>220</v>
       </c>
       <c r="O53">
-        <v>17134936</v>
+        <v>17821419</v>
       </c>
       <c r="P53" t="s">
         <v>227</v>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="54" spans="1:33">
       <c r="A54">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="B54" t="s">
         <v>75</v>
@@ -4909,7 +4909,7 @@
         <v>220</v>
       </c>
       <c r="O54">
-        <v>17821419</v>
+        <v>17333125</v>
       </c>
       <c r="P54" t="s">
         <v>227</v>
@@ -4938,31 +4938,31 @@
     </row>
     <row r="55" spans="1:33">
       <c r="A55">
-        <v>3481</v>
+        <v>2371</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="C55" t="s">
         <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F55" t="s">
         <v>147</v>
       </c>
       <c r="G55">
-        <v>3889</v>
+        <v>3790</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J55" t="s">
         <v>175</v>
@@ -4977,10 +4977,10 @@
         <v>220</v>
       </c>
       <c r="O55">
-        <v>17333125</v>
+        <v>17540512</v>
       </c>
       <c r="P55" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="Q55" t="s">
         <v>236</v>
@@ -4989,10 +4989,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="U55" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="W55" t="s">
         <v>254</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="56" spans="1:33">
       <c r="A56">
-        <v>2371</v>
+        <v>3366</v>
       </c>
       <c r="B56" t="s">
         <v>37</v>
@@ -5015,7 +5015,7 @@
         <v>141</v>
       </c>
       <c r="D56" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E56" t="s">
         <v>147</v>
@@ -5045,7 +5045,7 @@
         <v>220</v>
       </c>
       <c r="O56">
-        <v>17540512</v>
+        <v>17448656</v>
       </c>
       <c r="P56" t="s">
         <v>147</v>
@@ -5074,16 +5074,16 @@
     </row>
     <row r="57" spans="1:33">
       <c r="A57">
-        <v>3366</v>
+        <v>2371</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C57" t="s">
         <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E57" t="s">
         <v>147</v>
@@ -5092,16 +5092,16 @@
         <v>147</v>
       </c>
       <c r="G57">
-        <v>3790</v>
+        <v>2152</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J57" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L57" s="1">
         <v>46295</v>
@@ -5113,10 +5113,10 @@
         <v>220</v>
       </c>
       <c r="O57">
-        <v>17448656</v>
+        <v>17540411</v>
       </c>
       <c r="P57" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="Q57" t="s">
         <v>236</v>
@@ -5131,7 +5131,7 @@
         <v>244</v>
       </c>
       <c r="W57" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA57">
         <v>0</v>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="58" spans="1:33">
       <c r="A58">
-        <v>2371</v>
+        <v>3366</v>
       </c>
       <c r="B58" t="s">
         <v>37</v>
@@ -5151,7 +5151,7 @@
         <v>141</v>
       </c>
       <c r="D58" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E58" t="s">
         <v>147</v>
@@ -5181,7 +5181,7 @@
         <v>220</v>
       </c>
       <c r="O58">
-        <v>17540411</v>
+        <v>17448596</v>
       </c>
       <c r="P58" t="s">
         <v>228</v>
@@ -5210,84 +5210,87 @@
     </row>
     <row r="59" spans="1:33">
       <c r="A59">
-        <v>3366</v>
+        <v>2804</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C59" t="s">
         <v>141</v>
       </c>
       <c r="D59" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E59" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F59" t="s">
         <v>147</v>
       </c>
       <c r="G59">
-        <v>2152</v>
+        <v>7040</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J59" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="L59" s="1">
-        <v>46295</v>
-      </c>
-      <c r="M59" t="s">
-        <v>211</v>
+        <v>46280</v>
       </c>
       <c r="N59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O59">
-        <v>17448596</v>
+        <v>17326612</v>
       </c>
       <c r="P59" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q59" t="s">
-        <v>236</v>
+        <v>237</v>
+      </c>
+      <c r="R59" s="1">
+        <v>46280.72560332176</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T59" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U59" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="W59" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA59">
         <v>0</v>
       </c>
+      <c r="AB59" t="s">
+        <v>279</v>
+      </c>
       <c r="AG59" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" spans="1:33">
       <c r="A60">
-        <v>2804</v>
+        <v>2835</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
         <v>141</v>
       </c>
       <c r="D60" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E60" t="s">
         <v>148</v>
@@ -5314,7 +5317,7 @@
         <v>221</v>
       </c>
       <c r="O60">
-        <v>17326612</v>
+        <v>17089972</v>
       </c>
       <c r="P60" t="s">
         <v>227</v>
@@ -5323,7 +5326,7 @@
         <v>237</v>
       </c>
       <c r="R60" s="1">
-        <v>46280.72560332176</v>
+        <v>46282.47436697916</v>
       </c>
       <c r="S60">
         <v>15</v>
@@ -5349,7 +5352,7 @@
     </row>
     <row r="61" spans="1:33">
       <c r="A61">
-        <v>2835</v>
+        <v>2837</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
@@ -5385,7 +5388,7 @@
         <v>221</v>
       </c>
       <c r="O61">
-        <v>17089972</v>
+        <v>17582284</v>
       </c>
       <c r="P61" t="s">
         <v>227</v>
@@ -5394,7 +5397,7 @@
         <v>237</v>
       </c>
       <c r="R61" s="1">
-        <v>46282.47436697916</v>
+        <v>46282.4745590625</v>
       </c>
       <c r="S61">
         <v>15</v>
@@ -5420,7 +5423,7 @@
     </row>
     <row r="62" spans="1:33">
       <c r="A62">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="B62" t="s">
         <v>68</v>
@@ -5456,7 +5459,7 @@
         <v>221</v>
       </c>
       <c r="O62">
-        <v>17582284</v>
+        <v>17389995</v>
       </c>
       <c r="P62" t="s">
         <v>227</v>
@@ -5465,7 +5468,7 @@
         <v>237</v>
       </c>
       <c r="R62" s="1">
-        <v>46282.4745590625</v>
+        <v>46282.4739224537</v>
       </c>
       <c r="S62">
         <v>15</v>
@@ -5491,7 +5494,7 @@
     </row>
     <row r="63" spans="1:33">
       <c r="A63">
-        <v>2838</v>
+        <v>2842</v>
       </c>
       <c r="B63" t="s">
         <v>69</v>
@@ -5500,10 +5503,10 @@
         <v>141</v>
       </c>
       <c r="D63" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E63" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F63" t="s">
         <v>147</v>
@@ -5527,7 +5530,7 @@
         <v>221</v>
       </c>
       <c r="O63">
-        <v>17389995</v>
+        <v>17161658</v>
       </c>
       <c r="P63" t="s">
         <v>227</v>
@@ -5536,7 +5539,7 @@
         <v>237</v>
       </c>
       <c r="R63" s="1">
-        <v>46282.4739224537</v>
+        <v>46282.47498869213</v>
       </c>
       <c r="S63">
         <v>15</v>
@@ -5562,7 +5565,7 @@
     </row>
     <row r="64" spans="1:33">
       <c r="A64">
-        <v>2842</v>
+        <v>3004</v>
       </c>
       <c r="B64" t="s">
         <v>70</v>
@@ -5571,10 +5574,10 @@
         <v>141</v>
       </c>
       <c r="D64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F64" t="s">
         <v>147</v>
@@ -5598,7 +5601,7 @@
         <v>221</v>
       </c>
       <c r="O64">
-        <v>17161658</v>
+        <v>17033285</v>
       </c>
       <c r="P64" t="s">
         <v>227</v>
@@ -5607,7 +5610,7 @@
         <v>237</v>
       </c>
       <c r="R64" s="1">
-        <v>46282.47498869213</v>
+        <v>46282.47512175926</v>
       </c>
       <c r="S64">
         <v>15</v>
@@ -5633,7 +5636,7 @@
     </row>
     <row r="65" spans="1:33">
       <c r="A65">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="B65" t="s">
         <v>71</v>
@@ -5669,7 +5672,7 @@
         <v>221</v>
       </c>
       <c r="O65">
-        <v>17033285</v>
+        <v>17263482</v>
       </c>
       <c r="P65" t="s">
         <v>227</v>
@@ -5678,7 +5681,7 @@
         <v>237</v>
       </c>
       <c r="R65" s="1">
-        <v>46282.47512175926</v>
+        <v>46282.47529371528</v>
       </c>
       <c r="S65">
         <v>15</v>
@@ -5704,7 +5707,7 @@
     </row>
     <row r="66" spans="1:33">
       <c r="A66">
-        <v>3005</v>
+        <v>3039</v>
       </c>
       <c r="B66" t="s">
         <v>72</v>
@@ -5740,7 +5743,7 @@
         <v>221</v>
       </c>
       <c r="O66">
-        <v>17263482</v>
+        <v>17585738</v>
       </c>
       <c r="P66" t="s">
         <v>227</v>
@@ -5749,7 +5752,7 @@
         <v>237</v>
       </c>
       <c r="R66" s="1">
-        <v>46282.47529371528</v>
+        <v>46282.47544363426</v>
       </c>
       <c r="S66">
         <v>15</v>
@@ -5775,16 +5778,16 @@
     </row>
     <row r="67" spans="1:33">
       <c r="A67">
-        <v>3039</v>
+        <v>3053</v>
       </c>
       <c r="B67" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C67" t="s">
         <v>141</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E67" t="s">
         <v>148</v>
@@ -5811,7 +5814,7 @@
         <v>221</v>
       </c>
       <c r="O67">
-        <v>17585738</v>
+        <v>17194136</v>
       </c>
       <c r="P67" t="s">
         <v>227</v>
@@ -5820,7 +5823,7 @@
         <v>237</v>
       </c>
       <c r="R67" s="1">
-        <v>46282.47544363426</v>
+        <v>46282.47562407408</v>
       </c>
       <c r="S67">
         <v>15</v>
@@ -5846,19 +5849,19 @@
     </row>
     <row r="68" spans="1:33">
       <c r="A68">
-        <v>3053</v>
+        <v>3209</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
         <v>141</v>
       </c>
       <c r="D68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E68" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F68" t="s">
         <v>147</v>
@@ -5882,7 +5885,7 @@
         <v>221</v>
       </c>
       <c r="O68">
-        <v>17194136</v>
+        <v>17135070</v>
       </c>
       <c r="P68" t="s">
         <v>227</v>
@@ -5891,7 +5894,7 @@
         <v>237</v>
       </c>
       <c r="R68" s="1">
-        <v>46282.47562407408</v>
+        <v>46282.4758247338</v>
       </c>
       <c r="S68">
         <v>15</v>
@@ -5917,7 +5920,7 @@
     </row>
     <row r="69" spans="1:33">
       <c r="A69">
-        <v>3209</v>
+        <v>3480</v>
       </c>
       <c r="B69" t="s">
         <v>74</v>
@@ -5929,7 +5932,7 @@
         <v>142</v>
       </c>
       <c r="E69" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F69" t="s">
         <v>147</v>
@@ -5953,7 +5956,7 @@
         <v>221</v>
       </c>
       <c r="O69">
-        <v>17135070</v>
+        <v>17821480</v>
       </c>
       <c r="P69" t="s">
         <v>227</v>
@@ -5962,7 +5965,7 @@
         <v>237</v>
       </c>
       <c r="R69" s="1">
-        <v>46282.4758247338</v>
+        <v>46282.47608140046</v>
       </c>
       <c r="S69">
         <v>15</v>
@@ -5988,7 +5991,7 @@
     </row>
     <row r="70" spans="1:33">
       <c r="A70">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="B70" t="s">
         <v>75</v>
@@ -6024,7 +6027,7 @@
         <v>221</v>
       </c>
       <c r="O70">
-        <v>17821480</v>
+        <v>17333186</v>
       </c>
       <c r="P70" t="s">
         <v>227</v>
@@ -6033,7 +6036,7 @@
         <v>237</v>
       </c>
       <c r="R70" s="1">
-        <v>46282.47608140046</v>
+        <v>46282.47626608796</v>
       </c>
       <c r="S70">
         <v>15</v>
@@ -6059,16 +6062,16 @@
     </row>
     <row r="71" spans="1:33">
       <c r="A71">
-        <v>3481</v>
+        <v>2804</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C71" t="s">
         <v>141</v>
       </c>
       <c r="D71" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E71" t="s">
         <v>148</v>
@@ -6077,7 +6080,7 @@
         <v>147</v>
       </c>
       <c r="G71">
-        <v>7040</v>
+        <v>7041</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -6086,16 +6089,16 @@
         <v>158</v>
       </c>
       <c r="J71" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="L71" s="1">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="N71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O71">
-        <v>17333186</v>
+        <v>17326621</v>
       </c>
       <c r="P71" t="s">
         <v>227</v>
@@ -6104,10 +6107,10 @@
         <v>237</v>
       </c>
       <c r="R71" s="1">
-        <v>46282.47626608796</v>
+        <v>46268.39249731482</v>
       </c>
       <c r="S71">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="T71" t="s">
         <v>241</v>
@@ -6115,14 +6118,11 @@
       <c r="U71" t="s">
         <v>243</v>
       </c>
-      <c r="W71" t="s">
-        <v>256</v>
-      </c>
       <c r="AA71">
         <v>0</v>
       </c>
       <c r="AB71" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
       <c r="AG71" t="s">
         <v>285</v>
@@ -6130,16 +6130,16 @@
     </row>
     <row r="72" spans="1:33">
       <c r="A72">
-        <v>2804</v>
+        <v>2835</v>
       </c>
       <c r="B72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C72" t="s">
         <v>141</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E72" t="s">
         <v>148</v>
@@ -6166,7 +6166,7 @@
         <v>220</v>
       </c>
       <c r="O72">
-        <v>17326621</v>
+        <v>17089997</v>
       </c>
       <c r="P72" t="s">
         <v>227</v>
@@ -6175,7 +6175,7 @@
         <v>237</v>
       </c>
       <c r="R72" s="1">
-        <v>46268.39249731482</v>
+        <v>46268.39249833333</v>
       </c>
       <c r="S72">
         <v>29</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="73" spans="1:33">
       <c r="A73">
-        <v>2835</v>
+        <v>2837</v>
       </c>
       <c r="B73" t="s">
         <v>67</v>
@@ -6234,7 +6234,7 @@
         <v>220</v>
       </c>
       <c r="O73">
-        <v>17089997</v>
+        <v>17582293</v>
       </c>
       <c r="P73" t="s">
         <v>227</v>
@@ -6243,7 +6243,7 @@
         <v>237</v>
       </c>
       <c r="R73" s="1">
-        <v>46268.39249833333</v>
+        <v>46268.39249914352</v>
       </c>
       <c r="S73">
         <v>29</v>
@@ -6266,7 +6266,7 @@
     </row>
     <row r="74" spans="1:33">
       <c r="A74">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="B74" t="s">
         <v>68</v>
@@ -6302,7 +6302,7 @@
         <v>220</v>
       </c>
       <c r="O74">
-        <v>17582293</v>
+        <v>17390004</v>
       </c>
       <c r="P74" t="s">
         <v>227</v>
@@ -6311,7 +6311,7 @@
         <v>237</v>
       </c>
       <c r="R74" s="1">
-        <v>46268.39249914352</v>
+        <v>46268.39250015046</v>
       </c>
       <c r="S74">
         <v>29</v>
@@ -6334,7 +6334,7 @@
     </row>
     <row r="75" spans="1:33">
       <c r="A75">
-        <v>2838</v>
+        <v>2842</v>
       </c>
       <c r="B75" t="s">
         <v>69</v>
@@ -6343,10 +6343,10 @@
         <v>141</v>
       </c>
       <c r="D75" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E75" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F75" t="s">
         <v>147</v>
@@ -6370,7 +6370,7 @@
         <v>220</v>
       </c>
       <c r="O75">
-        <v>17390004</v>
+        <v>17161680</v>
       </c>
       <c r="P75" t="s">
         <v>227</v>
@@ -6379,7 +6379,7 @@
         <v>237</v>
       </c>
       <c r="R75" s="1">
-        <v>46268.39250015046</v>
+        <v>46268.39250150463</v>
       </c>
       <c r="S75">
         <v>29</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="76" spans="1:33">
       <c r="A76">
-        <v>2842</v>
+        <v>3004</v>
       </c>
       <c r="B76" t="s">
         <v>70</v>
@@ -6411,10 +6411,10 @@
         <v>141</v>
       </c>
       <c r="D76" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E76" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F76" t="s">
         <v>147</v>
@@ -6438,7 +6438,7 @@
         <v>220</v>
       </c>
       <c r="O76">
-        <v>17161680</v>
+        <v>17033305</v>
       </c>
       <c r="P76" t="s">
         <v>227</v>
@@ -6447,7 +6447,7 @@
         <v>237</v>
       </c>
       <c r="R76" s="1">
-        <v>46268.39250150463</v>
+        <v>46268.39250226852</v>
       </c>
       <c r="S76">
         <v>29</v>
@@ -6470,7 +6470,7 @@
     </row>
     <row r="77" spans="1:33">
       <c r="A77">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="B77" t="s">
         <v>71</v>
@@ -6506,7 +6506,7 @@
         <v>220</v>
       </c>
       <c r="O77">
-        <v>17033305</v>
+        <v>17263491</v>
       </c>
       <c r="P77" t="s">
         <v>227</v>
@@ -6515,7 +6515,7 @@
         <v>237</v>
       </c>
       <c r="R77" s="1">
-        <v>46268.39250226852</v>
+        <v>46268.39250332176</v>
       </c>
       <c r="S77">
         <v>29</v>
@@ -6538,7 +6538,7 @@
     </row>
     <row r="78" spans="1:33">
       <c r="A78">
-        <v>3005</v>
+        <v>3039</v>
       </c>
       <c r="B78" t="s">
         <v>72</v>
@@ -6574,7 +6574,7 @@
         <v>220</v>
       </c>
       <c r="O78">
-        <v>17263491</v>
+        <v>17585747</v>
       </c>
       <c r="P78" t="s">
         <v>227</v>
@@ -6583,7 +6583,7 @@
         <v>237</v>
       </c>
       <c r="R78" s="1">
-        <v>46268.39250332176</v>
+        <v>46268.39250452547</v>
       </c>
       <c r="S78">
         <v>29</v>
@@ -6606,16 +6606,16 @@
     </row>
     <row r="79" spans="1:33">
       <c r="A79">
-        <v>3039</v>
+        <v>3053</v>
       </c>
       <c r="B79" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C79" t="s">
         <v>141</v>
       </c>
       <c r="D79" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E79" t="s">
         <v>148</v>
@@ -6642,7 +6642,7 @@
         <v>220</v>
       </c>
       <c r="O79">
-        <v>17585747</v>
+        <v>17194164</v>
       </c>
       <c r="P79" t="s">
         <v>227</v>
@@ -6651,7 +6651,7 @@
         <v>237</v>
       </c>
       <c r="R79" s="1">
-        <v>46268.39250452547</v>
+        <v>46268.39250524306</v>
       </c>
       <c r="S79">
         <v>29</v>
@@ -6674,19 +6674,19 @@
     </row>
     <row r="80" spans="1:33">
       <c r="A80">
-        <v>3053</v>
+        <v>3209</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C80" t="s">
         <v>141</v>
       </c>
       <c r="D80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E80" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F80" t="s">
         <v>147</v>
@@ -6710,7 +6710,7 @@
         <v>220</v>
       </c>
       <c r="O80">
-        <v>17194164</v>
+        <v>17135091</v>
       </c>
       <c r="P80" t="s">
         <v>227</v>
@@ -6719,7 +6719,7 @@
         <v>237</v>
       </c>
       <c r="R80" s="1">
-        <v>46268.39250524306</v>
+        <v>46268.39250652778</v>
       </c>
       <c r="S80">
         <v>29</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="81" spans="1:33">
       <c r="A81">
-        <v>3209</v>
+        <v>3480</v>
       </c>
       <c r="B81" t="s">
         <v>74</v>
@@ -6754,7 +6754,7 @@
         <v>142</v>
       </c>
       <c r="E81" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F81" t="s">
         <v>147</v>
@@ -6778,7 +6778,7 @@
         <v>220</v>
       </c>
       <c r="O81">
-        <v>17135091</v>
+        <v>17821489</v>
       </c>
       <c r="P81" t="s">
         <v>227</v>
@@ -6787,7 +6787,7 @@
         <v>237</v>
       </c>
       <c r="R81" s="1">
-        <v>46268.39250652778</v>
+        <v>46268.39250747685</v>
       </c>
       <c r="S81">
         <v>29</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="82" spans="1:33">
       <c r="A82">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="B82" t="s">
         <v>75</v>
@@ -6846,7 +6846,7 @@
         <v>220</v>
       </c>
       <c r="O82">
-        <v>17821489</v>
+        <v>17333195</v>
       </c>
       <c r="P82" t="s">
         <v>227</v>
@@ -6855,7 +6855,7 @@
         <v>237</v>
       </c>
       <c r="R82" s="1">
-        <v>46268.39250747685</v>
+        <v>46268.39250818287</v>
       </c>
       <c r="S82">
         <v>29</v>
@@ -6878,16 +6878,16 @@
     </row>
     <row r="83" spans="1:33">
       <c r="A83">
-        <v>3481</v>
+        <v>2804</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C83" t="s">
         <v>141</v>
       </c>
       <c r="D83" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E83" t="s">
         <v>148</v>
@@ -6896,7 +6896,7 @@
         <v>147</v>
       </c>
       <c r="G83">
-        <v>7041</v>
+        <v>11289</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -6905,16 +6905,16 @@
         <v>158</v>
       </c>
       <c r="J83" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="L83" s="1">
-        <v>46266</v>
+        <v>46281</v>
       </c>
       <c r="N83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O83">
-        <v>17333195</v>
+        <v>17326643</v>
       </c>
       <c r="P83" t="s">
         <v>227</v>
@@ -6923,10 +6923,10 @@
         <v>237</v>
       </c>
       <c r="R83" s="1">
-        <v>46268.39250818287</v>
+        <v>46280.7143515162</v>
       </c>
       <c r="S83">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="T83" t="s">
         <v>241</v>
@@ -6946,7 +6946,7 @@
     </row>
     <row r="84" spans="1:33">
       <c r="A84">
-        <v>2804</v>
+        <v>3053</v>
       </c>
       <c r="B84" t="s">
         <v>65</v>
@@ -6955,7 +6955,7 @@
         <v>141</v>
       </c>
       <c r="D84" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E84" t="s">
         <v>148</v>
@@ -6982,7 +6982,7 @@
         <v>221</v>
       </c>
       <c r="O84">
-        <v>17326643</v>
+        <v>17194213</v>
       </c>
       <c r="P84" t="s">
         <v>227</v>
@@ -6991,7 +6991,7 @@
         <v>237</v>
       </c>
       <c r="R84" s="1">
-        <v>46280.7143515162</v>
+        <v>46280.71435333334</v>
       </c>
       <c r="S84">
         <v>14</v>
@@ -7014,16 +7014,16 @@
     </row>
     <row r="85" spans="1:33">
       <c r="A85">
-        <v>3053</v>
+        <v>2804</v>
       </c>
       <c r="B85" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C85" t="s">
         <v>141</v>
       </c>
       <c r="D85" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E85" t="s">
         <v>148</v>
@@ -7032,7 +7032,7 @@
         <v>147</v>
       </c>
       <c r="G85">
-        <v>11289</v>
+        <v>11288</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -7041,16 +7041,16 @@
         <v>158</v>
       </c>
       <c r="J85" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="L85" s="1">
-        <v>46281</v>
+        <v>46267</v>
       </c>
       <c r="N85" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O85">
-        <v>17194213</v>
+        <v>17326632</v>
       </c>
       <c r="P85" t="s">
         <v>227</v>
@@ -7059,10 +7059,10 @@
         <v>237</v>
       </c>
       <c r="R85" s="1">
-        <v>46280.71435333334</v>
+        <v>46268.39323719907</v>
       </c>
       <c r="S85">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T85" t="s">
         <v>241</v>
@@ -7082,7 +7082,7 @@
     </row>
     <row r="86" spans="1:33">
       <c r="A86">
-        <v>2804</v>
+        <v>3053</v>
       </c>
       <c r="B86" t="s">
         <v>65</v>
@@ -7091,7 +7091,7 @@
         <v>141</v>
       </c>
       <c r="D86" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E86" t="s">
         <v>148</v>
@@ -7118,7 +7118,7 @@
         <v>220</v>
       </c>
       <c r="O86">
-        <v>17326632</v>
+        <v>17194186</v>
       </c>
       <c r="P86" t="s">
         <v>227</v>
@@ -7127,7 +7127,7 @@
         <v>237</v>
       </c>
       <c r="R86" s="1">
-        <v>46268.39323719907</v>
+        <v>46268.39323780093</v>
       </c>
       <c r="S86">
         <v>28</v>
@@ -7150,10 +7150,10 @@
     </row>
     <row r="87" spans="1:33">
       <c r="A87">
-        <v>3053</v>
+        <v>4064</v>
       </c>
       <c r="B87" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C87" t="s">
         <v>141</v>
@@ -7162,66 +7162,72 @@
         <v>143</v>
       </c>
       <c r="E87" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F87" t="s">
         <v>147</v>
       </c>
       <c r="G87">
-        <v>11288</v>
+        <v>9312</v>
       </c>
       <c r="H87">
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J87" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L87" s="1">
-        <v>46267</v>
+        <v>46295</v>
+      </c>
+      <c r="M87" t="s">
+        <v>211</v>
       </c>
       <c r="N87" t="s">
         <v>220</v>
       </c>
       <c r="O87">
-        <v>17194186</v>
+        <v>17841025</v>
       </c>
       <c r="P87" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q87" t="s">
         <v>237</v>
       </c>
       <c r="R87" s="1">
-        <v>46268.39323780093</v>
+        <v>46295.40172307871</v>
       </c>
       <c r="S87">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T87" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="U87" t="s">
         <v>243</v>
       </c>
+      <c r="W87" t="s">
+        <v>254</v>
+      </c>
       <c r="AA87">
         <v>0</v>
       </c>
       <c r="AB87" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG87" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="88" spans="1:33">
       <c r="A88">
-        <v>4064</v>
+        <v>4917</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C88" t="s">
         <v>141</v>
@@ -7230,7 +7236,7 @@
         <v>143</v>
       </c>
       <c r="E88" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F88" t="s">
         <v>147</v>
@@ -7257,7 +7263,7 @@
         <v>220</v>
       </c>
       <c r="O88">
-        <v>17841025</v>
+        <v>17629841</v>
       </c>
       <c r="P88" t="s">
         <v>224</v>
@@ -7266,7 +7272,7 @@
         <v>237</v>
       </c>
       <c r="R88" s="1">
-        <v>46295.40172307871</v>
+        <v>46295.40172364583</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -7292,16 +7298,16 @@
     </row>
     <row r="89" spans="1:33">
       <c r="A89">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C89" t="s">
         <v>141</v>
       </c>
       <c r="D89" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E89" t="s">
         <v>147</v>
@@ -7310,7 +7316,7 @@
         <v>147</v>
       </c>
       <c r="G89">
-        <v>9312</v>
+        <v>9327</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -7319,19 +7325,16 @@
         <v>160</v>
       </c>
       <c r="J89" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="L89" s="1">
-        <v>46295</v>
-      </c>
-      <c r="M89" t="s">
-        <v>211</v>
+        <v>46280</v>
       </c>
       <c r="N89" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O89">
-        <v>17629841</v>
+        <v>17311887</v>
       </c>
       <c r="P89" t="s">
         <v>224</v>
@@ -7340,10 +7343,10 @@
         <v>237</v>
       </c>
       <c r="R89" s="1">
-        <v>46295.40172364583</v>
+        <v>46280.75157195602</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T89" t="s">
         <v>238</v>
@@ -7351,14 +7354,11 @@
       <c r="U89" t="s">
         <v>243</v>
       </c>
-      <c r="W89" t="s">
-        <v>254</v>
-      </c>
       <c r="AA89">
         <v>0</v>
       </c>
       <c r="AB89" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
       <c r="AG89" t="s">
         <v>286</v>
@@ -7366,19 +7366,19 @@
     </row>
     <row r="90" spans="1:33">
       <c r="A90">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C90" t="s">
         <v>141</v>
       </c>
       <c r="D90" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E90" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F90" t="s">
         <v>147</v>
@@ -7402,7 +7402,7 @@
         <v>221</v>
       </c>
       <c r="O90">
-        <v>17311887</v>
+        <v>17841036</v>
       </c>
       <c r="P90" t="s">
         <v>224</v>
@@ -7411,7 +7411,7 @@
         <v>237</v>
       </c>
       <c r="R90" s="1">
-        <v>46280.75157195602</v>
+        <v>46280.75190127315</v>
       </c>
       <c r="S90">
         <v>15</v>
@@ -7434,19 +7434,19 @@
     </row>
     <row r="91" spans="1:33">
       <c r="A91">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B91" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
         <v>141</v>
       </c>
       <c r="D91" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E91" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F91" t="s">
         <v>147</v>
@@ -7470,7 +7470,7 @@
         <v>221</v>
       </c>
       <c r="O91">
-        <v>17841036</v>
+        <v>17222004</v>
       </c>
       <c r="P91" t="s">
         <v>224</v>
@@ -7479,7 +7479,7 @@
         <v>237</v>
       </c>
       <c r="R91" s="1">
-        <v>46280.75190127315</v>
+        <v>46280.75219267361</v>
       </c>
       <c r="S91">
         <v>15</v>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="92" spans="1:33">
       <c r="A92">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="C92" t="s">
         <v>141</v>
@@ -7514,7 +7514,7 @@
         <v>142</v>
       </c>
       <c r="E92" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F92" t="s">
         <v>147</v>
@@ -7538,7 +7538,7 @@
         <v>221</v>
       </c>
       <c r="O92">
-        <v>17222004</v>
+        <v>17424451</v>
       </c>
       <c r="P92" t="s">
         <v>224</v>
@@ -7547,7 +7547,7 @@
         <v>237</v>
       </c>
       <c r="R92" s="1">
-        <v>46280.75219267361</v>
+        <v>46280.75248533565</v>
       </c>
       <c r="S92">
         <v>15</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="93" spans="1:33">
       <c r="A93">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B93" t="s">
         <v>79</v>
@@ -7582,7 +7582,7 @@
         <v>142</v>
       </c>
       <c r="E93" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F93" t="s">
         <v>147</v>
@@ -7606,7 +7606,7 @@
         <v>221</v>
       </c>
       <c r="O93">
-        <v>17424451</v>
+        <v>17493444</v>
       </c>
       <c r="P93" t="s">
         <v>224</v>
@@ -7615,7 +7615,7 @@
         <v>237</v>
       </c>
       <c r="R93" s="1">
-        <v>46280.75248533565</v>
+        <v>46280.75296913194</v>
       </c>
       <c r="S93">
         <v>15</v>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="94" spans="1:33">
       <c r="A94">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="B94" t="s">
         <v>80</v>
@@ -7674,7 +7674,7 @@
         <v>221</v>
       </c>
       <c r="O94">
-        <v>17493444</v>
+        <v>17424491</v>
       </c>
       <c r="P94" t="s">
         <v>224</v>
@@ -7683,7 +7683,7 @@
         <v>237</v>
       </c>
       <c r="R94" s="1">
-        <v>46280.75296913194</v>
+        <v>46280.75326030092</v>
       </c>
       <c r="S94">
         <v>15</v>
@@ -7706,7 +7706,7 @@
     </row>
     <row r="95" spans="1:33">
       <c r="A95">
-        <v>4068</v>
+        <v>4602</v>
       </c>
       <c r="B95" t="s">
         <v>81</v>
@@ -7742,7 +7742,7 @@
         <v>221</v>
       </c>
       <c r="O95">
-        <v>17424491</v>
+        <v>17719860</v>
       </c>
       <c r="P95" t="s">
         <v>224</v>
@@ -7751,7 +7751,7 @@
         <v>237</v>
       </c>
       <c r="R95" s="1">
-        <v>46280.75326030092</v>
+        <v>46280.75372538195</v>
       </c>
       <c r="S95">
         <v>15</v>
@@ -7774,7 +7774,7 @@
     </row>
     <row r="96" spans="1:33">
       <c r="A96">
-        <v>4602</v>
+        <v>4815</v>
       </c>
       <c r="B96" t="s">
         <v>82</v>
@@ -7810,7 +7810,7 @@
         <v>221</v>
       </c>
       <c r="O96">
-        <v>17719860</v>
+        <v>17728390</v>
       </c>
       <c r="P96" t="s">
         <v>224</v>
@@ -7819,7 +7819,7 @@
         <v>237</v>
       </c>
       <c r="R96" s="1">
-        <v>46280.75372538195</v>
+        <v>46280.75461721064</v>
       </c>
       <c r="S96">
         <v>15</v>
@@ -7842,7 +7842,7 @@
     </row>
     <row r="97" spans="1:33">
       <c r="A97">
-        <v>4815</v>
+        <v>4917</v>
       </c>
       <c r="B97" t="s">
         <v>35</v>
@@ -7851,7 +7851,7 @@
         <v>141</v>
       </c>
       <c r="D97" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E97" t="s">
         <v>147</v>
@@ -7878,7 +7878,7 @@
         <v>221</v>
       </c>
       <c r="O97">
-        <v>17728390</v>
+        <v>17629852</v>
       </c>
       <c r="P97" t="s">
         <v>224</v>
@@ -7887,7 +7887,7 @@
         <v>237</v>
       </c>
       <c r="R97" s="1">
-        <v>46280.75461721064</v>
+        <v>46280.75492121528</v>
       </c>
       <c r="S97">
         <v>15</v>
@@ -7910,16 +7910,16 @@
     </row>
     <row r="98" spans="1:33">
       <c r="A98">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B98" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C98" t="s">
         <v>141</v>
       </c>
       <c r="D98" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E98" t="s">
         <v>147</v>
@@ -7928,7 +7928,7 @@
         <v>147</v>
       </c>
       <c r="G98">
-        <v>9327</v>
+        <v>9328</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -7937,16 +7937,16 @@
         <v>160</v>
       </c>
       <c r="J98" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="L98" s="1">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="N98" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O98">
-        <v>17629852</v>
+        <v>17311896</v>
       </c>
       <c r="P98" t="s">
         <v>224</v>
@@ -7955,10 +7955,10 @@
         <v>237</v>
       </c>
       <c r="R98" s="1">
-        <v>46280.75492121528</v>
+        <v>46266.71710929398</v>
       </c>
       <c r="S98">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="T98" t="s">
         <v>238</v>
@@ -7978,19 +7978,19 @@
     </row>
     <row r="99" spans="1:33">
       <c r="A99">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C99" t="s">
         <v>141</v>
       </c>
       <c r="D99" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E99" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F99" t="s">
         <v>147</v>
@@ -8014,7 +8014,7 @@
         <v>220</v>
       </c>
       <c r="O99">
-        <v>17311896</v>
+        <v>17841045</v>
       </c>
       <c r="P99" t="s">
         <v>224</v>
@@ -8023,7 +8023,7 @@
         <v>237</v>
       </c>
       <c r="R99" s="1">
-        <v>46266.71710929398</v>
+        <v>46266.71760243056</v>
       </c>
       <c r="S99">
         <v>29</v>
@@ -8046,19 +8046,19 @@
     </row>
     <row r="100" spans="1:33">
       <c r="A100">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C100" t="s">
         <v>141</v>
       </c>
       <c r="D100" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E100" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F100" t="s">
         <v>147</v>
@@ -8082,7 +8082,7 @@
         <v>220</v>
       </c>
       <c r="O100">
-        <v>17841045</v>
+        <v>17222030</v>
       </c>
       <c r="P100" t="s">
         <v>224</v>
@@ -8091,7 +8091,7 @@
         <v>237</v>
       </c>
       <c r="R100" s="1">
-        <v>46266.71760243056</v>
+        <v>46266.71793020833</v>
       </c>
       <c r="S100">
         <v>29</v>
@@ -8114,10 +8114,10 @@
     </row>
     <row r="101" spans="1:33">
       <c r="A101">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="C101" t="s">
         <v>141</v>
@@ -8126,7 +8126,7 @@
         <v>142</v>
       </c>
       <c r="E101" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F101" t="s">
         <v>147</v>
@@ -8150,7 +8150,7 @@
         <v>220</v>
       </c>
       <c r="O101">
-        <v>17222030</v>
+        <v>17424460</v>
       </c>
       <c r="P101" t="s">
         <v>224</v>
@@ -8159,7 +8159,7 @@
         <v>237</v>
       </c>
       <c r="R101" s="1">
-        <v>46266.71793020833</v>
+        <v>46266.71818136574</v>
       </c>
       <c r="S101">
         <v>29</v>
@@ -8182,7 +8182,7 @@
     </row>
     <row r="102" spans="1:33">
       <c r="A102">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B102" t="s">
         <v>79</v>
@@ -8194,7 +8194,7 @@
         <v>142</v>
       </c>
       <c r="E102" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F102" t="s">
         <v>147</v>
@@ -8218,7 +8218,7 @@
         <v>220</v>
       </c>
       <c r="O102">
-        <v>17424460</v>
+        <v>17493453</v>
       </c>
       <c r="P102" t="s">
         <v>224</v>
@@ -8227,7 +8227,7 @@
         <v>237</v>
       </c>
       <c r="R102" s="1">
-        <v>46266.71818136574</v>
+        <v>46266.71859741898</v>
       </c>
       <c r="S102">
         <v>29</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="103" spans="1:33">
       <c r="A103">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="B103" t="s">
         <v>80</v>
@@ -8286,7 +8286,7 @@
         <v>220</v>
       </c>
       <c r="O103">
-        <v>17493453</v>
+        <v>17424500</v>
       </c>
       <c r="P103" t="s">
         <v>224</v>
@@ -8295,7 +8295,7 @@
         <v>237</v>
       </c>
       <c r="R103" s="1">
-        <v>46266.71859741898</v>
+        <v>46266.71905170139</v>
       </c>
       <c r="S103">
         <v>29</v>
@@ -8318,7 +8318,7 @@
     </row>
     <row r="104" spans="1:33">
       <c r="A104">
-        <v>4068</v>
+        <v>4602</v>
       </c>
       <c r="B104" t="s">
         <v>81</v>
@@ -8354,7 +8354,7 @@
         <v>220</v>
       </c>
       <c r="O104">
-        <v>17424500</v>
+        <v>17719869</v>
       </c>
       <c r="P104" t="s">
         <v>224</v>
@@ -8363,7 +8363,7 @@
         <v>237</v>
       </c>
       <c r="R104" s="1">
-        <v>46266.71905170139</v>
+        <v>46266.71958452546</v>
       </c>
       <c r="S104">
         <v>29</v>
@@ -8386,7 +8386,7 @@
     </row>
     <row r="105" spans="1:33">
       <c r="A105">
-        <v>4602</v>
+        <v>4815</v>
       </c>
       <c r="B105" t="s">
         <v>82</v>
@@ -8422,7 +8422,7 @@
         <v>220</v>
       </c>
       <c r="O105">
-        <v>17719869</v>
+        <v>17728399</v>
       </c>
       <c r="P105" t="s">
         <v>224</v>
@@ -8431,7 +8431,7 @@
         <v>237</v>
       </c>
       <c r="R105" s="1">
-        <v>46266.71958452546</v>
+        <v>46266.71982650463</v>
       </c>
       <c r="S105">
         <v>29</v>
@@ -8454,7 +8454,7 @@
     </row>
     <row r="106" spans="1:33">
       <c r="A106">
-        <v>4815</v>
+        <v>4917</v>
       </c>
       <c r="B106" t="s">
         <v>35</v>
@@ -8463,7 +8463,7 @@
         <v>141</v>
       </c>
       <c r="D106" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E106" t="s">
         <v>147</v>
@@ -8490,7 +8490,7 @@
         <v>220</v>
       </c>
       <c r="O106">
-        <v>17728399</v>
+        <v>17629861</v>
       </c>
       <c r="P106" t="s">
         <v>224</v>
@@ -8499,7 +8499,7 @@
         <v>237</v>
       </c>
       <c r="R106" s="1">
-        <v>46266.71982650463</v>
+        <v>46266.72010234954</v>
       </c>
       <c r="S106">
         <v>29</v>
@@ -8522,16 +8522,16 @@
     </row>
     <row r="107" spans="1:33">
       <c r="A107">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B107" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C107" t="s">
         <v>141</v>
       </c>
       <c r="D107" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E107" t="s">
         <v>147</v>
@@ -8540,7 +8540,7 @@
         <v>147</v>
       </c>
       <c r="G107">
-        <v>9328</v>
+        <v>9588</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>160</v>
       </c>
       <c r="J107" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="L107" s="1">
-        <v>46266</v>
+        <v>46281</v>
       </c>
       <c r="N107" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O107">
-        <v>17629861</v>
+        <v>17311917</v>
       </c>
       <c r="P107" t="s">
         <v>224</v>
@@ -8567,10 +8567,10 @@
         <v>237</v>
       </c>
       <c r="R107" s="1">
-        <v>46266.72010234954</v>
+        <v>46281.61917107639</v>
       </c>
       <c r="S107">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="T107" t="s">
         <v>238</v>
@@ -8582,10 +8582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="s">
-        <v>279</v>
+        <v>224</v>
       </c>
       <c r="AG107" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="108" spans="1:33">
@@ -8593,7 +8593,7 @@
         <v>4059</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C108" t="s">
         <v>141</v>
@@ -8608,7 +8608,7 @@
         <v>147</v>
       </c>
       <c r="G108">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -8622,11 +8622,14 @@
       <c r="L108" s="1">
         <v>46281</v>
       </c>
+      <c r="M108" t="s">
+        <v>212</v>
+      </c>
       <c r="N108" t="s">
         <v>221</v>
       </c>
       <c r="O108">
-        <v>17311917</v>
+        <v>17311927</v>
       </c>
       <c r="P108" t="s">
         <v>224</v>
@@ -8635,7 +8638,7 @@
         <v>237</v>
       </c>
       <c r="R108" s="1">
-        <v>46281.61917107639</v>
+        <v>46286.74416417824</v>
       </c>
       <c r="S108">
         <v>14</v>
@@ -8646,6 +8649,9 @@
       <c r="U108" t="s">
         <v>243</v>
       </c>
+      <c r="W108" t="s">
+        <v>257</v>
+      </c>
       <c r="AA108">
         <v>0</v>
       </c>
@@ -8658,10 +8664,10 @@
     </row>
     <row r="109" spans="1:33">
       <c r="A109">
-        <v>4059</v>
+        <v>4061</v>
       </c>
       <c r="B109" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C109" t="s">
         <v>141</v>
@@ -8670,13 +8676,13 @@
         <v>144</v>
       </c>
       <c r="E109" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F109" t="s">
         <v>147</v>
       </c>
       <c r="G109">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -8690,14 +8696,11 @@
       <c r="L109" s="1">
         <v>46281</v>
       </c>
-      <c r="M109" t="s">
-        <v>212</v>
-      </c>
       <c r="N109" t="s">
         <v>221</v>
       </c>
       <c r="O109">
-        <v>17311927</v>
+        <v>17311967</v>
       </c>
       <c r="P109" t="s">
         <v>224</v>
@@ -8706,7 +8709,7 @@
         <v>237</v>
       </c>
       <c r="R109" s="1">
-        <v>46286.74416417824</v>
+        <v>46281.61917159722</v>
       </c>
       <c r="S109">
         <v>14</v>
@@ -8716,9 +8719,6 @@
       </c>
       <c r="U109" t="s">
         <v>243</v>
-      </c>
-      <c r="W109" t="s">
-        <v>257</v>
       </c>
       <c r="AA109">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>147</v>
       </c>
       <c r="G110">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -8764,11 +8764,14 @@
       <c r="L110" s="1">
         <v>46281</v>
       </c>
+      <c r="M110" t="s">
+        <v>212</v>
+      </c>
       <c r="N110" t="s">
         <v>221</v>
       </c>
       <c r="O110">
-        <v>17311967</v>
+        <v>17311977</v>
       </c>
       <c r="P110" t="s">
         <v>224</v>
@@ -8777,7 +8780,7 @@
         <v>237</v>
       </c>
       <c r="R110" s="1">
-        <v>46281.61917159722</v>
+        <v>46286.74416459491</v>
       </c>
       <c r="S110">
         <v>14</v>
@@ -8788,6 +8791,9 @@
       <c r="U110" t="s">
         <v>243</v>
       </c>
+      <c r="W110" t="s">
+        <v>258</v>
+      </c>
       <c r="AA110">
         <v>0</v>
       </c>
@@ -8800,10 +8806,10 @@
     </row>
     <row r="111" spans="1:33">
       <c r="A111">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B111" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C111" t="s">
         <v>141</v>
@@ -8812,13 +8818,13 @@
         <v>144</v>
       </c>
       <c r="E111" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F111" t="s">
         <v>147</v>
       </c>
       <c r="G111">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -8832,14 +8838,11 @@
       <c r="L111" s="1">
         <v>46281</v>
       </c>
-      <c r="M111" t="s">
-        <v>212</v>
-      </c>
       <c r="N111" t="s">
         <v>221</v>
       </c>
       <c r="O111">
-        <v>17311977</v>
+        <v>17756707</v>
       </c>
       <c r="P111" t="s">
         <v>224</v>
@@ -8848,7 +8851,7 @@
         <v>237</v>
       </c>
       <c r="R111" s="1">
-        <v>46286.74416459491</v>
+        <v>46281.61917203703</v>
       </c>
       <c r="S111">
         <v>14</v>
@@ -8858,9 +8861,6 @@
       </c>
       <c r="U111" t="s">
         <v>243</v>
-      </c>
-      <c r="W111" t="s">
-        <v>258</v>
       </c>
       <c r="AA111">
         <v>0</v>
@@ -8892,7 +8892,7 @@
         <v>147</v>
       </c>
       <c r="G112">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -8906,11 +8906,14 @@
       <c r="L112" s="1">
         <v>46281</v>
       </c>
+      <c r="M112" t="s">
+        <v>212</v>
+      </c>
       <c r="N112" t="s">
         <v>221</v>
       </c>
       <c r="O112">
-        <v>17756707</v>
+        <v>17756717</v>
       </c>
       <c r="P112" t="s">
         <v>224</v>
@@ -8919,7 +8922,7 @@
         <v>237</v>
       </c>
       <c r="R112" s="1">
-        <v>46281.61917203703</v>
+        <v>46286.74416505787</v>
       </c>
       <c r="S112">
         <v>14</v>
@@ -8930,6 +8933,9 @@
       <c r="U112" t="s">
         <v>243</v>
       </c>
+      <c r="W112" t="s">
+        <v>258</v>
+      </c>
       <c r="AA112">
         <v>0</v>
       </c>
@@ -8942,10 +8948,10 @@
     </row>
     <row r="113" spans="1:33">
       <c r="A113">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B113" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C113" t="s">
         <v>141</v>
@@ -8954,13 +8960,13 @@
         <v>144</v>
       </c>
       <c r="E113" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F113" t="s">
         <v>147</v>
       </c>
       <c r="G113">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -8974,14 +8980,11 @@
       <c r="L113" s="1">
         <v>46281</v>
       </c>
-      <c r="M113" t="s">
-        <v>212</v>
-      </c>
       <c r="N113" t="s">
         <v>221</v>
       </c>
       <c r="O113">
-        <v>17756717</v>
+        <v>17221886</v>
       </c>
       <c r="P113" t="s">
         <v>224</v>
@@ -8990,7 +8993,7 @@
         <v>237</v>
       </c>
       <c r="R113" s="1">
-        <v>46286.74416505787</v>
+        <v>46281.6191725</v>
       </c>
       <c r="S113">
         <v>14</v>
@@ -9000,9 +9003,6 @@
       </c>
       <c r="U113" t="s">
         <v>243</v>
-      </c>
-      <c r="W113" t="s">
-        <v>258</v>
       </c>
       <c r="AA113">
         <v>0</v>
@@ -9034,7 +9034,7 @@
         <v>147</v>
       </c>
       <c r="G114">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -9048,11 +9048,14 @@
       <c r="L114" s="1">
         <v>46281</v>
       </c>
+      <c r="M114" t="s">
+        <v>212</v>
+      </c>
       <c r="N114" t="s">
         <v>221</v>
       </c>
       <c r="O114">
-        <v>17221886</v>
+        <v>17221914</v>
       </c>
       <c r="P114" t="s">
         <v>224</v>
@@ -9061,7 +9064,7 @@
         <v>237</v>
       </c>
       <c r="R114" s="1">
-        <v>46281.6191725</v>
+        <v>46286.74416604167</v>
       </c>
       <c r="S114">
         <v>14</v>
@@ -9072,6 +9075,9 @@
       <c r="U114" t="s">
         <v>243</v>
       </c>
+      <c r="W114" t="s">
+        <v>258</v>
+      </c>
       <c r="AA114">
         <v>0</v>
       </c>
@@ -9084,10 +9090,10 @@
     </row>
     <row r="115" spans="1:33">
       <c r="A115">
-        <v>4063</v>
+        <v>4535</v>
       </c>
       <c r="B115" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C115" t="s">
         <v>141</v>
@@ -9096,13 +9102,13 @@
         <v>144</v>
       </c>
       <c r="E115" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F115" t="s">
         <v>147</v>
       </c>
       <c r="G115">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -9116,14 +9122,11 @@
       <c r="L115" s="1">
         <v>46281</v>
       </c>
-      <c r="M115" t="s">
-        <v>212</v>
-      </c>
       <c r="N115" t="s">
         <v>221</v>
       </c>
       <c r="O115">
-        <v>17221914</v>
+        <v>17260697</v>
       </c>
       <c r="P115" t="s">
         <v>224</v>
@@ -9132,7 +9135,7 @@
         <v>237</v>
       </c>
       <c r="R115" s="1">
-        <v>46286.74416604167</v>
+        <v>46281.61917288195</v>
       </c>
       <c r="S115">
         <v>14</v>
@@ -9142,9 +9145,6 @@
       </c>
       <c r="U115" t="s">
         <v>243</v>
-      </c>
-      <c r="W115" t="s">
-        <v>258</v>
       </c>
       <c r="AA115">
         <v>0</v>
@@ -9176,7 +9176,7 @@
         <v>147</v>
       </c>
       <c r="G116">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -9190,11 +9190,14 @@
       <c r="L116" s="1">
         <v>46281</v>
       </c>
+      <c r="M116" t="s">
+        <v>212</v>
+      </c>
       <c r="N116" t="s">
         <v>221</v>
       </c>
       <c r="O116">
-        <v>17260697</v>
+        <v>17260707</v>
       </c>
       <c r="P116" t="s">
         <v>224</v>
@@ -9203,7 +9206,7 @@
         <v>237</v>
       </c>
       <c r="R116" s="1">
-        <v>46281.61917288195</v>
+        <v>46286.74416644676</v>
       </c>
       <c r="S116">
         <v>14</v>
@@ -9214,6 +9217,9 @@
       <c r="U116" t="s">
         <v>243</v>
       </c>
+      <c r="W116" t="s">
+        <v>258</v>
+      </c>
       <c r="AA116">
         <v>0</v>
       </c>
@@ -9226,16 +9232,16 @@
     </row>
     <row r="117" spans="1:33">
       <c r="A117">
-        <v>4535</v>
+        <v>4815</v>
       </c>
       <c r="B117" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C117" t="s">
         <v>141</v>
       </c>
       <c r="D117" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E117" t="s">
         <v>147</v>
@@ -9244,7 +9250,7 @@
         <v>147</v>
       </c>
       <c r="G117">
-        <v>9600</v>
+        <v>9588</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -9258,14 +9264,11 @@
       <c r="L117" s="1">
         <v>46281</v>
       </c>
-      <c r="M117" t="s">
-        <v>212</v>
-      </c>
       <c r="N117" t="s">
         <v>221</v>
       </c>
       <c r="O117">
-        <v>17260707</v>
+        <v>17728410</v>
       </c>
       <c r="P117" t="s">
         <v>224</v>
@@ -9274,7 +9277,7 @@
         <v>237</v>
       </c>
       <c r="R117" s="1">
-        <v>46286.74416644676</v>
+        <v>46281.61917341435</v>
       </c>
       <c r="S117">
         <v>14</v>
@@ -9284,9 +9287,6 @@
       </c>
       <c r="U117" t="s">
         <v>243</v>
-      </c>
-      <c r="W117" t="s">
-        <v>258</v>
       </c>
       <c r="AA117">
         <v>0</v>
@@ -9303,7 +9303,7 @@
         <v>4815</v>
       </c>
       <c r="B118" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C118" t="s">
         <v>141</v>
@@ -9318,7 +9318,7 @@
         <v>147</v>
       </c>
       <c r="G118">
-        <v>9588</v>
+        <v>9600</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -9332,11 +9332,14 @@
       <c r="L118" s="1">
         <v>46281</v>
       </c>
+      <c r="M118" t="s">
+        <v>212</v>
+      </c>
       <c r="N118" t="s">
         <v>221</v>
       </c>
       <c r="O118">
-        <v>17728410</v>
+        <v>17728420</v>
       </c>
       <c r="P118" t="s">
         <v>224</v>
@@ -9345,7 +9348,7 @@
         <v>237</v>
       </c>
       <c r="R118" s="1">
-        <v>46281.61917341435</v>
+        <v>46286.74416686343</v>
       </c>
       <c r="S118">
         <v>14</v>
@@ -9356,6 +9359,9 @@
       <c r="U118" t="s">
         <v>243</v>
       </c>
+      <c r="W118" t="s">
+        <v>258</v>
+      </c>
       <c r="AA118">
         <v>0</v>
       </c>
@@ -9368,16 +9374,16 @@
     </row>
     <row r="119" spans="1:33">
       <c r="A119">
-        <v>4815</v>
+        <v>4059</v>
       </c>
       <c r="B119" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C119" t="s">
         <v>141</v>
       </c>
       <c r="D119" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E119" t="s">
         <v>147</v>
@@ -9386,7 +9392,7 @@
         <v>147</v>
       </c>
       <c r="G119">
-        <v>9600</v>
+        <v>11293</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -9395,19 +9401,16 @@
         <v>160</v>
       </c>
       <c r="J119" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="L119" s="1">
-        <v>46281</v>
-      </c>
-      <c r="M119" t="s">
-        <v>212</v>
+        <v>46267</v>
       </c>
       <c r="N119" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O119">
-        <v>17728420</v>
+        <v>17311936</v>
       </c>
       <c r="P119" t="s">
         <v>224</v>
@@ -9416,10 +9419,10 @@
         <v>237</v>
       </c>
       <c r="R119" s="1">
-        <v>46286.74416686343</v>
+        <v>46267.65902924768</v>
       </c>
       <c r="S119">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T119" t="s">
         <v>238</v>
@@ -9427,9 +9430,6 @@
       <c r="U119" t="s">
         <v>243</v>
       </c>
-      <c r="W119" t="s">
-        <v>258</v>
-      </c>
       <c r="AA119">
         <v>0</v>
       </c>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="120" spans="1:33">
       <c r="A120">
-        <v>4059</v>
+        <v>4061</v>
       </c>
       <c r="B120" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C120" t="s">
         <v>141</v>
@@ -9454,7 +9454,7 @@
         <v>144</v>
       </c>
       <c r="E120" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F120" t="s">
         <v>147</v>
@@ -9478,7 +9478,7 @@
         <v>220</v>
       </c>
       <c r="O120">
-        <v>17311936</v>
+        <v>17311986</v>
       </c>
       <c r="P120" t="s">
         <v>224</v>
@@ -9487,7 +9487,7 @@
         <v>237</v>
       </c>
       <c r="R120" s="1">
-        <v>46267.65902924768</v>
+        <v>46267.65903065972</v>
       </c>
       <c r="S120">
         <v>28</v>
@@ -9510,10 +9510,10 @@
     </row>
     <row r="121" spans="1:33">
       <c r="A121">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B121" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C121" t="s">
         <v>141</v>
@@ -9522,7 +9522,7 @@
         <v>144</v>
       </c>
       <c r="E121" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F121" t="s">
         <v>147</v>
@@ -9546,7 +9546,7 @@
         <v>220</v>
       </c>
       <c r="O121">
-        <v>17311986</v>
+        <v>17756726</v>
       </c>
       <c r="P121" t="s">
         <v>224</v>
@@ -9555,7 +9555,7 @@
         <v>237</v>
       </c>
       <c r="R121" s="1">
-        <v>46267.65903065972</v>
+        <v>46267.65903172454</v>
       </c>
       <c r="S121">
         <v>28</v>
@@ -9578,10 +9578,10 @@
     </row>
     <row r="122" spans="1:33">
       <c r="A122">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B122" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C122" t="s">
         <v>141</v>
@@ -9590,7 +9590,7 @@
         <v>144</v>
       </c>
       <c r="E122" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F122" t="s">
         <v>147</v>
@@ -9614,7 +9614,7 @@
         <v>220</v>
       </c>
       <c r="O122">
-        <v>17756726</v>
+        <v>17221940</v>
       </c>
       <c r="P122" t="s">
         <v>224</v>
@@ -9623,7 +9623,7 @@
         <v>237</v>
       </c>
       <c r="R122" s="1">
-        <v>46267.65903172454</v>
+        <v>46267.65903244213</v>
       </c>
       <c r="S122">
         <v>28</v>
@@ -9646,10 +9646,10 @@
     </row>
     <row r="123" spans="1:33">
       <c r="A123">
-        <v>4063</v>
+        <v>4535</v>
       </c>
       <c r="B123" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C123" t="s">
         <v>141</v>
@@ -9658,7 +9658,7 @@
         <v>144</v>
       </c>
       <c r="E123" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F123" t="s">
         <v>147</v>
@@ -9682,7 +9682,7 @@
         <v>220</v>
       </c>
       <c r="O123">
-        <v>17221940</v>
+        <v>17260716</v>
       </c>
       <c r="P123" t="s">
         <v>224</v>
@@ -9691,7 +9691,7 @@
         <v>237</v>
       </c>
       <c r="R123" s="1">
-        <v>46267.65903244213</v>
+        <v>46267.65903319445</v>
       </c>
       <c r="S123">
         <v>28</v>
@@ -9714,16 +9714,16 @@
     </row>
     <row r="124" spans="1:33">
       <c r="A124">
-        <v>4535</v>
+        <v>4815</v>
       </c>
       <c r="B124" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C124" t="s">
         <v>141</v>
       </c>
       <c r="D124" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E124" t="s">
         <v>147</v>
@@ -9750,7 +9750,7 @@
         <v>220</v>
       </c>
       <c r="O124">
-        <v>17260716</v>
+        <v>17728429</v>
       </c>
       <c r="P124" t="s">
         <v>224</v>
@@ -9759,7 +9759,7 @@
         <v>237</v>
       </c>
       <c r="R124" s="1">
-        <v>46267.65903319445</v>
+        <v>46267.65903408565</v>
       </c>
       <c r="S124">
         <v>28</v>
@@ -9782,16 +9782,16 @@
     </row>
     <row r="125" spans="1:33">
       <c r="A125">
-        <v>4815</v>
+        <v>4059</v>
       </c>
       <c r="B125" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C125" t="s">
         <v>141</v>
       </c>
       <c r="D125" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E125" t="s">
         <v>147</v>
@@ -9800,7 +9800,7 @@
         <v>147</v>
       </c>
       <c r="G125">
-        <v>11293</v>
+        <v>9570</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -9809,16 +9809,16 @@
         <v>160</v>
       </c>
       <c r="J125" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L125" s="1">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="N125" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O125">
-        <v>17728429</v>
+        <v>17311907</v>
       </c>
       <c r="P125" t="s">
         <v>224</v>
@@ -9827,10 +9827,10 @@
         <v>237</v>
       </c>
       <c r="R125" s="1">
-        <v>46267.65903408565</v>
+        <v>46266.65725641204</v>
       </c>
       <c r="S125">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T125" t="s">
         <v>238</v>
@@ -9845,15 +9845,15 @@
         <v>224</v>
       </c>
       <c r="AG125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="126" spans="1:33">
       <c r="A126">
-        <v>4059</v>
+        <v>4061</v>
       </c>
       <c r="B126" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C126" t="s">
         <v>141</v>
@@ -9862,7 +9862,7 @@
         <v>144</v>
       </c>
       <c r="E126" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F126" t="s">
         <v>147</v>
@@ -9886,7 +9886,7 @@
         <v>221</v>
       </c>
       <c r="O126">
-        <v>17311907</v>
+        <v>17311957</v>
       </c>
       <c r="P126" t="s">
         <v>224</v>
@@ -9895,7 +9895,7 @@
         <v>237</v>
       </c>
       <c r="R126" s="1">
-        <v>46266.65725641204</v>
+        <v>46266.65725738426</v>
       </c>
       <c r="S126">
         <v>29</v>
@@ -9918,10 +9918,10 @@
     </row>
     <row r="127" spans="1:33">
       <c r="A127">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B127" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C127" t="s">
         <v>141</v>
@@ -9930,7 +9930,7 @@
         <v>144</v>
       </c>
       <c r="E127" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F127" t="s">
         <v>147</v>
@@ -9954,7 +9954,7 @@
         <v>221</v>
       </c>
       <c r="O127">
-        <v>17311957</v>
+        <v>17756697</v>
       </c>
       <c r="P127" t="s">
         <v>224</v>
@@ -9963,7 +9963,7 @@
         <v>237</v>
       </c>
       <c r="R127" s="1">
-        <v>46266.65725738426</v>
+        <v>46266.65725806713</v>
       </c>
       <c r="S127">
         <v>29</v>
@@ -9986,10 +9986,10 @@
     </row>
     <row r="128" spans="1:33">
       <c r="A128">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B128" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C128" t="s">
         <v>141</v>
@@ -9998,7 +9998,7 @@
         <v>144</v>
       </c>
       <c r="E128" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F128" t="s">
         <v>147</v>
@@ -10022,7 +10022,7 @@
         <v>221</v>
       </c>
       <c r="O128">
-        <v>17756697</v>
+        <v>17221863</v>
       </c>
       <c r="P128" t="s">
         <v>224</v>
@@ -10031,7 +10031,7 @@
         <v>237</v>
       </c>
       <c r="R128" s="1">
-        <v>46266.65725806713</v>
+        <v>46266.65725861111</v>
       </c>
       <c r="S128">
         <v>29</v>
@@ -10054,10 +10054,10 @@
     </row>
     <row r="129" spans="1:33">
       <c r="A129">
-        <v>4063</v>
+        <v>4535</v>
       </c>
       <c r="B129" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C129" t="s">
         <v>141</v>
@@ -10066,7 +10066,7 @@
         <v>144</v>
       </c>
       <c r="E129" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F129" t="s">
         <v>147</v>
@@ -10090,7 +10090,7 @@
         <v>221</v>
       </c>
       <c r="O129">
-        <v>17221863</v>
+        <v>17260687</v>
       </c>
       <c r="P129" t="s">
         <v>224</v>
@@ -10099,7 +10099,7 @@
         <v>237</v>
       </c>
       <c r="R129" s="1">
-        <v>46266.65725861111</v>
+        <v>46266.65725960648</v>
       </c>
       <c r="S129">
         <v>29</v>
@@ -10122,16 +10122,16 @@
     </row>
     <row r="130" spans="1:33">
       <c r="A130">
-        <v>4535</v>
+        <v>4917</v>
       </c>
       <c r="B130" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="C130" t="s">
         <v>141</v>
       </c>
       <c r="D130" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E130" t="s">
         <v>147</v>
@@ -10140,25 +10140,28 @@
         <v>147</v>
       </c>
       <c r="G130">
-        <v>9570</v>
+        <v>9277</v>
       </c>
       <c r="H130">
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J130" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L130" s="1">
-        <v>46266</v>
+        <v>46295</v>
+      </c>
+      <c r="M130" t="s">
+        <v>211</v>
       </c>
       <c r="N130" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O130">
-        <v>17260687</v>
+        <v>17629821</v>
       </c>
       <c r="P130" t="s">
         <v>224</v>
@@ -10167,10 +10170,10 @@
         <v>237</v>
       </c>
       <c r="R130" s="1">
-        <v>46266.65725960648</v>
+        <v>46295.40261266204</v>
       </c>
       <c r="S130">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="T130" t="s">
         <v>238</v>
@@ -10178,6 +10181,9 @@
       <c r="U130" t="s">
         <v>243</v>
       </c>
+      <c r="W130" t="s">
+        <v>254</v>
+      </c>
       <c r="AA130">
         <v>0</v>
       </c>
@@ -10190,16 +10196,16 @@
     </row>
     <row r="131" spans="1:33">
       <c r="A131">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B131" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C131" t="s">
         <v>141</v>
       </c>
       <c r="D131" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E131" t="s">
         <v>147</v>
@@ -10208,7 +10214,7 @@
         <v>147</v>
       </c>
       <c r="G131">
-        <v>9277</v>
+        <v>9309</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -10217,19 +10223,19 @@
         <v>153</v>
       </c>
       <c r="J131" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="L131" s="1">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="M131" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N131" t="s">
         <v>220</v>
       </c>
       <c r="O131">
-        <v>17629821</v>
+        <v>17311875</v>
       </c>
       <c r="P131" t="s">
         <v>224</v>
@@ -10238,10 +10244,10 @@
         <v>237</v>
       </c>
       <c r="R131" s="1">
-        <v>46295.40261266204</v>
+        <v>46293.34178662037</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T131" t="s">
         <v>238</v>
@@ -10250,7 +10256,7 @@
         <v>243</v>
       </c>
       <c r="W131" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AA131">
         <v>0</v>
@@ -10259,24 +10265,24 @@
         <v>224</v>
       </c>
       <c r="AG131" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="132" spans="1:33">
       <c r="A132">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="B132" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C132" t="s">
         <v>141</v>
       </c>
       <c r="D132" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E132" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F132" t="s">
         <v>147</v>
@@ -10303,7 +10309,7 @@
         <v>220</v>
       </c>
       <c r="O132">
-        <v>17311875</v>
+        <v>17841014</v>
       </c>
       <c r="P132" t="s">
         <v>224</v>
@@ -10312,7 +10318,7 @@
         <v>237</v>
       </c>
       <c r="R132" s="1">
-        <v>46293.34178662037</v>
+        <v>46293.34178696759</v>
       </c>
       <c r="S132">
         <v>5</v>
@@ -10338,16 +10344,16 @@
     </row>
     <row r="133" spans="1:33">
       <c r="A133">
-        <v>4064</v>
+        <v>4066</v>
       </c>
       <c r="B133" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C133" t="s">
         <v>141</v>
       </c>
       <c r="D133" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E133" t="s">
         <v>149</v>
@@ -10377,7 +10383,7 @@
         <v>220</v>
       </c>
       <c r="O133">
-        <v>17841014</v>
+        <v>17424440</v>
       </c>
       <c r="P133" t="s">
         <v>224</v>
@@ -10386,7 +10392,7 @@
         <v>237</v>
       </c>
       <c r="R133" s="1">
-        <v>46293.34178696759</v>
+        <v>46293.34178755787</v>
       </c>
       <c r="S133">
         <v>5</v>
@@ -10412,7 +10418,7 @@
     </row>
     <row r="134" spans="1:33">
       <c r="A134">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B134" t="s">
         <v>79</v>
@@ -10424,7 +10430,7 @@
         <v>142</v>
       </c>
       <c r="E134" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F134" t="s">
         <v>147</v>
@@ -10451,7 +10457,7 @@
         <v>220</v>
       </c>
       <c r="O134">
-        <v>17424440</v>
+        <v>17493433</v>
       </c>
       <c r="P134" t="s">
         <v>224</v>
@@ -10460,7 +10466,7 @@
         <v>237</v>
       </c>
       <c r="R134" s="1">
-        <v>46293.34178755787</v>
+        <v>46293.34178815972</v>
       </c>
       <c r="S134">
         <v>5</v>
@@ -10486,7 +10492,7 @@
     </row>
     <row r="135" spans="1:33">
       <c r="A135">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="B135" t="s">
         <v>80</v>
@@ -10525,7 +10531,7 @@
         <v>220</v>
       </c>
       <c r="O135">
-        <v>17493433</v>
+        <v>17424480</v>
       </c>
       <c r="P135" t="s">
         <v>224</v>
@@ -10534,7 +10540,7 @@
         <v>237</v>
       </c>
       <c r="R135" s="1">
-        <v>46293.34178815972</v>
+        <v>46293.34178859954</v>
       </c>
       <c r="S135">
         <v>5</v>
@@ -10560,10 +10566,10 @@
     </row>
     <row r="136" spans="1:33">
       <c r="A136">
-        <v>4068</v>
+        <v>4815</v>
       </c>
       <c r="B136" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C136" t="s">
         <v>141</v>
@@ -10599,7 +10605,7 @@
         <v>220</v>
       </c>
       <c r="O136">
-        <v>17424480</v>
+        <v>17728378</v>
       </c>
       <c r="P136" t="s">
         <v>224</v>
@@ -10608,7 +10614,7 @@
         <v>237</v>
       </c>
       <c r="R136" s="1">
-        <v>46293.34178859954</v>
+        <v>46295.45179462963</v>
       </c>
       <c r="S136">
         <v>5</v>
@@ -10637,7 +10643,7 @@
         <v>4059</v>
       </c>
       <c r="B137" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C137" t="s">
         <v>141</v>
@@ -10705,7 +10711,7 @@
         <v>4066</v>
       </c>
       <c r="B138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C138" t="s">
         <v>141</v>
@@ -10773,7 +10779,7 @@
         <v>4064</v>
       </c>
       <c r="B139" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C139" t="s">
         <v>141</v>
@@ -10847,7 +10853,7 @@
         <v>4917</v>
       </c>
       <c r="B140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C140" t="s">
         <v>141</v>
@@ -10921,7 +10927,7 @@
         <v>4059</v>
       </c>
       <c r="B141" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C141" t="s">
         <v>141</v>
@@ -11069,7 +11075,7 @@
         <v>4066</v>
       </c>
       <c r="B143" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C143" t="s">
         <v>141</v>
@@ -11143,7 +11149,7 @@
         <v>4067</v>
       </c>
       <c r="B144" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C144" t="s">
         <v>141</v>
@@ -11217,7 +11223,7 @@
         <v>4068</v>
       </c>
       <c r="B145" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C145" t="s">
         <v>141</v>
@@ -11291,7 +11297,7 @@
         <v>4602</v>
       </c>
       <c r="B146" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C146" t="s">
         <v>141</v>
@@ -11365,7 +11371,7 @@
         <v>4815</v>
       </c>
       <c r="B147" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C147" t="s">
         <v>141</v>
@@ -11587,7 +11593,7 @@
         <v>4059</v>
       </c>
       <c r="B150" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C150" t="s">
         <v>141</v>
@@ -11661,7 +11667,7 @@
         <v>4064</v>
       </c>
       <c r="B151" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C151" t="s">
         <v>141</v>
@@ -11735,7 +11741,7 @@
         <v>4917</v>
       </c>
       <c r="B152" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C152" t="s">
         <v>141</v>
@@ -11809,7 +11815,7 @@
         <v>4059</v>
       </c>
       <c r="B153" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C153" t="s">
         <v>141</v>
@@ -11883,7 +11889,7 @@
         <v>4064</v>
       </c>
       <c r="B154" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C154" t="s">
         <v>141</v>
@@ -11951,7 +11957,7 @@
         <v>4917</v>
       </c>
       <c r="B155" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C155" t="s">
         <v>141</v>
@@ -12019,7 +12025,7 @@
         <v>4602</v>
       </c>
       <c r="B156" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C156" t="s">
         <v>141</v>
@@ -12093,7 +12099,7 @@
         <v>4815</v>
       </c>
       <c r="B157" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C157" t="s">
         <v>141</v>
@@ -12167,7 +12173,7 @@
         <v>4059</v>
       </c>
       <c r="B158" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C158" t="s">
         <v>141</v>
@@ -12241,7 +12247,7 @@
         <v>4059</v>
       </c>
       <c r="B159" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C159" t="s">
         <v>141</v>
@@ -12309,7 +12315,7 @@
         <v>4064</v>
       </c>
       <c r="B160" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C160" t="s">
         <v>141</v>
@@ -12377,7 +12383,7 @@
         <v>4917</v>
       </c>
       <c r="B161" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C161" t="s">
         <v>141</v>
@@ -12445,7 +12451,7 @@
         <v>4059</v>
       </c>
       <c r="B162" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C162" t="s">
         <v>141</v>
@@ -12513,7 +12519,7 @@
         <v>4059</v>
       </c>
       <c r="B163" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C163" t="s">
         <v>141</v>
@@ -12581,7 +12587,7 @@
         <v>2371</v>
       </c>
       <c r="B164" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C164" t="s">
         <v>141</v>
@@ -12652,7 +12658,7 @@
         <v>3366</v>
       </c>
       <c r="B165" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C165" t="s">
         <v>141</v>
@@ -12723,7 +12729,7 @@
         <v>2371</v>
       </c>
       <c r="B166" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C166" t="s">
         <v>141</v>
@@ -12794,7 +12800,7 @@
         <v>2372</v>
       </c>
       <c r="B167" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C167" t="s">
         <v>141</v>
@@ -12865,7 +12871,7 @@
         <v>2373</v>
       </c>
       <c r="B168" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C168" t="s">
         <v>141</v>
@@ -12936,7 +12942,7 @@
         <v>2374</v>
       </c>
       <c r="B169" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C169" t="s">
         <v>141</v>
@@ -13007,7 +13013,7 @@
         <v>2395</v>
       </c>
       <c r="B170" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C170" t="s">
         <v>141</v>
@@ -13078,7 +13084,7 @@
         <v>2426</v>
       </c>
       <c r="B171" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C171" t="s">
         <v>141</v>
@@ -13149,7 +13155,7 @@
         <v>2994</v>
       </c>
       <c r="B172" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C172" t="s">
         <v>141</v>
@@ -13220,7 +13226,7 @@
         <v>3278</v>
       </c>
       <c r="B173" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C173" t="s">
         <v>141</v>
@@ -13291,7 +13297,7 @@
         <v>3279</v>
       </c>
       <c r="B174" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C174" t="s">
         <v>141</v>
@@ -13362,7 +13368,7 @@
         <v>3497</v>
       </c>
       <c r="B175" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C175" t="s">
         <v>141</v>
@@ -13433,7 +13439,7 @@
         <v>3862</v>
       </c>
       <c r="B176" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C176" t="s">
         <v>141</v>
@@ -13504,7 +13510,7 @@
         <v>4423</v>
       </c>
       <c r="B177" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C177" t="s">
         <v>141</v>
@@ -13575,7 +13581,7 @@
         <v>4424</v>
       </c>
       <c r="B178" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C178" t="s">
         <v>141</v>
@@ -13646,7 +13652,7 @@
         <v>4633</v>
       </c>
       <c r="B179" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C179" t="s">
         <v>141</v>
@@ -13717,7 +13723,7 @@
         <v>4990</v>
       </c>
       <c r="B180" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C180" t="s">
         <v>141</v>
@@ -13788,7 +13794,7 @@
         <v>5070</v>
       </c>
       <c r="B181" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C181" t="s">
         <v>141</v>
@@ -28242,7 +28248,7 @@
         <v>3216</v>
       </c>
       <c r="B388" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C388" t="s">
         <v>141</v>
@@ -28316,7 +28322,7 @@
         <v>3218</v>
       </c>
       <c r="B389" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C389" t="s">
         <v>141</v>
@@ -28390,7 +28396,7 @@
         <v>3219</v>
       </c>
       <c r="B390" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C390" t="s">
         <v>141</v>
@@ -28464,7 +28470,7 @@
         <v>3220</v>
       </c>
       <c r="B391" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C391" t="s">
         <v>141</v>
@@ -28606,7 +28612,7 @@
         <v>3666</v>
       </c>
       <c r="B393" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C393" t="s">
         <v>141</v>
@@ -28680,7 +28686,7 @@
         <v>3667</v>
       </c>
       <c r="B394" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C394" t="s">
         <v>141</v>
@@ -28748,7 +28754,7 @@
         <v>3668</v>
       </c>
       <c r="B395" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C395" t="s">
         <v>141</v>
@@ -28816,7 +28822,7 @@
         <v>3670</v>
       </c>
       <c r="B396" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C396" t="s">
         <v>141</v>
@@ -28884,7 +28890,7 @@
         <v>3671</v>
       </c>
       <c r="B397" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C397" t="s">
         <v>141</v>
@@ -29094,7 +29100,7 @@
         <v>3216</v>
       </c>
       <c r="B400" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C400" t="s">
         <v>141</v>
@@ -29242,7 +29248,7 @@
         <v>3218</v>
       </c>
       <c r="B402" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C402" t="s">
         <v>141</v>
@@ -29316,7 +29322,7 @@
         <v>3219</v>
       </c>
       <c r="B403" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C403" t="s">
         <v>141</v>
@@ -29384,7 +29390,7 @@
         <v>3220</v>
       </c>
       <c r="B404" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C404" t="s">
         <v>141</v>
@@ -29458,7 +29464,7 @@
         <v>3666</v>
       </c>
       <c r="B405" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C405" t="s">
         <v>141</v>
@@ -29526,7 +29532,7 @@
         <v>3667</v>
       </c>
       <c r="B406" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C406" t="s">
         <v>141</v>
@@ -29594,7 +29600,7 @@
         <v>3668</v>
       </c>
       <c r="B407" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C407" t="s">
         <v>141</v>
@@ -29662,7 +29668,7 @@
         <v>3669</v>
       </c>
       <c r="B408" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C408" t="s">
         <v>141</v>
@@ -29730,7 +29736,7 @@
         <v>3671</v>
       </c>
       <c r="B409" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C409" t="s">
         <v>141</v>
@@ -29798,7 +29804,7 @@
         <v>4614</v>
       </c>
       <c r="B410" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C410" t="s">
         <v>141</v>
@@ -29940,7 +29946,7 @@
         <v>3218</v>
       </c>
       <c r="B412" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C412" t="s">
         <v>141</v>
@@ -30014,7 +30020,7 @@
         <v>3220</v>
       </c>
       <c r="B413" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C413" t="s">
         <v>141</v>
@@ -30088,7 +30094,7 @@
         <v>3666</v>
       </c>
       <c r="B414" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C414" t="s">
         <v>141</v>
@@ -30162,7 +30168,7 @@
         <v>3667</v>
       </c>
       <c r="B415" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C415" t="s">
         <v>141</v>
@@ -30236,7 +30242,7 @@
         <v>3668</v>
       </c>
       <c r="B416" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C416" t="s">
         <v>141</v>
@@ -30310,7 +30316,7 @@
         <v>3669</v>
       </c>
       <c r="B417" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C417" t="s">
         <v>141</v>
@@ -30384,7 +30390,7 @@
         <v>3670</v>
       </c>
       <c r="B418" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C418" t="s">
         <v>141</v>
@@ -30458,7 +30464,7 @@
         <v>3671</v>
       </c>
       <c r="B419" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C419" t="s">
         <v>141</v>
@@ -30532,7 +30538,7 @@
         <v>3667</v>
       </c>
       <c r="B420" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C420" t="s">
         <v>141</v>
@@ -30600,7 +30606,7 @@
         <v>3670</v>
       </c>
       <c r="B421" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C421" t="s">
         <v>141</v>
@@ -30668,7 +30674,7 @@
         <v>3671</v>
       </c>
       <c r="B422" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C422" t="s">
         <v>141</v>
@@ -30736,7 +30742,7 @@
         <v>3216</v>
       </c>
       <c r="B423" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C423" t="s">
         <v>141</v>
@@ -30804,7 +30810,7 @@
         <v>3218</v>
       </c>
       <c r="B424" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C424" t="s">
         <v>141</v>
@@ -30872,7 +30878,7 @@
         <v>3220</v>
       </c>
       <c r="B425" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C425" t="s">
         <v>141</v>
@@ -31014,7 +31020,7 @@
         <v>3216</v>
       </c>
       <c r="B427" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C427" t="s">
         <v>141</v>
@@ -31162,7 +31168,7 @@
         <v>3218</v>
       </c>
       <c r="B429" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C429" t="s">
         <v>141</v>
@@ -31236,7 +31242,7 @@
         <v>3220</v>
       </c>
       <c r="B430" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C430" t="s">
         <v>141</v>
@@ -31310,7 +31316,7 @@
         <v>3666</v>
       </c>
       <c r="B431" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C431" t="s">
         <v>141</v>
@@ -31384,7 +31390,7 @@
         <v>3667</v>
       </c>
       <c r="B432" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C432" t="s">
         <v>141</v>
@@ -31452,7 +31458,7 @@
         <v>3668</v>
       </c>
       <c r="B433" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C433" t="s">
         <v>141</v>
@@ -31520,7 +31526,7 @@
         <v>3669</v>
       </c>
       <c r="B434" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C434" t="s">
         <v>141</v>
@@ -31588,7 +31594,7 @@
         <v>3670</v>
       </c>
       <c r="B435" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C435" t="s">
         <v>141</v>
@@ -31662,7 +31668,7 @@
         <v>3671</v>
       </c>
       <c r="B436" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C436" t="s">
         <v>141</v>
@@ -31730,7 +31736,7 @@
         <v>4614</v>
       </c>
       <c r="B437" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C437" t="s">
         <v>141</v>
@@ -31798,7 +31804,7 @@
         <v>3219</v>
       </c>
       <c r="B438" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C438" t="s">
         <v>141</v>
@@ -32070,7 +32076,7 @@
         <v>3219</v>
       </c>
       <c r="B442" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C442" t="s">
         <v>141</v>
@@ -32614,7 +32620,7 @@
         <v>3218</v>
       </c>
       <c r="B450" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C450" t="s">
         <v>141</v>
@@ -32682,7 +32688,7 @@
         <v>3220</v>
       </c>
       <c r="B451" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C451" t="s">
         <v>141</v>
@@ -32818,7 +32824,7 @@
         <v>3666</v>
       </c>
       <c r="B453" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C453" t="s">
         <v>141</v>
@@ -32886,7 +32892,7 @@
         <v>3667</v>
       </c>
       <c r="B454" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C454" t="s">
         <v>141</v>
@@ -32954,7 +32960,7 @@
         <v>3668</v>
       </c>
       <c r="B455" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C455" t="s">
         <v>141</v>
@@ -33022,7 +33028,7 @@
         <v>3669</v>
       </c>
       <c r="B456" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C456" t="s">
         <v>141</v>
@@ -33090,7 +33096,7 @@
         <v>3670</v>
       </c>
       <c r="B457" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C457" t="s">
         <v>141</v>
@@ -33158,7 +33164,7 @@
         <v>3671</v>
       </c>
       <c r="B458" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C458" t="s">
         <v>141</v>
@@ -33226,7 +33232,7 @@
         <v>4614</v>
       </c>
       <c r="B459" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C459" t="s">
         <v>141</v>
@@ -33634,7 +33640,7 @@
         <v>3218</v>
       </c>
       <c r="B465" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C465" t="s">
         <v>141</v>
@@ -33770,7 +33776,7 @@
         <v>3666</v>
       </c>
       <c r="B467" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C467" t="s">
         <v>141</v>
@@ -33838,7 +33844,7 @@
         <v>3667</v>
       </c>
       <c r="B468" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C468" t="s">
         <v>141</v>
@@ -33906,7 +33912,7 @@
         <v>3668</v>
       </c>
       <c r="B469" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C469" t="s">
         <v>141</v>
@@ -33974,7 +33980,7 @@
         <v>3669</v>
       </c>
       <c r="B470" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C470" t="s">
         <v>141</v>
@@ -34042,7 +34048,7 @@
         <v>3670</v>
       </c>
       <c r="B471" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C471" t="s">
         <v>141</v>
@@ -34110,7 +34116,7 @@
         <v>3671</v>
       </c>
       <c r="B472" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C472" t="s">
         <v>141</v>
@@ -34178,7 +34184,7 @@
         <v>4614</v>
       </c>
       <c r="B473" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C473" t="s">
         <v>141</v>
@@ -34586,7 +34592,7 @@
         <v>3218</v>
       </c>
       <c r="B479" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C479" t="s">
         <v>141</v>
@@ -34654,7 +34660,7 @@
         <v>3220</v>
       </c>
       <c r="B480" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C480" t="s">
         <v>141</v>
@@ -34790,7 +34796,7 @@
         <v>3666</v>
       </c>
       <c r="B482" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C482" t="s">
         <v>141</v>
@@ -34858,7 +34864,7 @@
         <v>3667</v>
       </c>
       <c r="B483" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C483" t="s">
         <v>141</v>
@@ -34926,7 +34932,7 @@
         <v>3668</v>
       </c>
       <c r="B484" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C484" t="s">
         <v>141</v>
@@ -34994,7 +35000,7 @@
         <v>3669</v>
       </c>
       <c r="B485" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C485" t="s">
         <v>141</v>
@@ -35062,7 +35068,7 @@
         <v>3670</v>
       </c>
       <c r="B486" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C486" t="s">
         <v>141</v>
@@ -35130,7 +35136,7 @@
         <v>3671</v>
       </c>
       <c r="B487" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C487" t="s">
         <v>141</v>
@@ -35198,7 +35204,7 @@
         <v>4614</v>
       </c>
       <c r="B488" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C488" t="s">
         <v>141</v>
@@ -35266,7 +35272,7 @@
         <v>3218</v>
       </c>
       <c r="B489" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C489" t="s">
         <v>141</v>
@@ -35340,7 +35346,7 @@
         <v>3220</v>
       </c>
       <c r="B490" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C490" t="s">
         <v>141</v>
@@ -35828,7 +35834,7 @@
         <v>3216</v>
       </c>
       <c r="B497" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C497" t="s">
         <v>141</v>
@@ -35896,7 +35902,7 @@
         <v>3220</v>
       </c>
       <c r="B498" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C498" t="s">
         <v>141</v>
@@ -36032,7 +36038,7 @@
         <v>3666</v>
       </c>
       <c r="B500" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C500" t="s">
         <v>141</v>
@@ -36100,7 +36106,7 @@
         <v>3667</v>
       </c>
       <c r="B501" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C501" t="s">
         <v>141</v>
@@ -36168,7 +36174,7 @@
         <v>3668</v>
       </c>
       <c r="B502" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C502" t="s">
         <v>141</v>
@@ -36236,7 +36242,7 @@
         <v>3669</v>
       </c>
       <c r="B503" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C503" t="s">
         <v>141</v>
@@ -36304,7 +36310,7 @@
         <v>3670</v>
       </c>
       <c r="B504" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C504" t="s">
         <v>141</v>
@@ -36372,7 +36378,7 @@
         <v>3671</v>
       </c>
       <c r="B505" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C505" t="s">
         <v>141</v>
@@ -36440,7 +36446,7 @@
         <v>4614</v>
       </c>
       <c r="B506" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C506" t="s">
         <v>141</v>
@@ -36576,7 +36582,7 @@
         <v>3666</v>
       </c>
       <c r="B508" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C508" t="s">
         <v>141</v>
@@ -36644,7 +36650,7 @@
         <v>3667</v>
       </c>
       <c r="B509" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C509" t="s">
         <v>141</v>
@@ -36712,7 +36718,7 @@
         <v>3668</v>
       </c>
       <c r="B510" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C510" t="s">
         <v>141</v>
@@ -36780,7 +36786,7 @@
         <v>3669</v>
       </c>
       <c r="B511" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C511" t="s">
         <v>141</v>
@@ -36848,7 +36854,7 @@
         <v>3670</v>
       </c>
       <c r="B512" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C512" t="s">
         <v>141</v>
@@ -36916,7 +36922,7 @@
         <v>3671</v>
       </c>
       <c r="B513" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C513" t="s">
         <v>141</v>
@@ -37324,7 +37330,7 @@
         <v>3216</v>
       </c>
       <c r="B519" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C519" t="s">
         <v>141</v>
@@ -37392,7 +37398,7 @@
         <v>3218</v>
       </c>
       <c r="B520" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C520" t="s">
         <v>141</v>
@@ -37460,7 +37466,7 @@
         <v>3220</v>
       </c>
       <c r="B521" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C521" t="s">
         <v>141</v>
@@ -37596,7 +37602,7 @@
         <v>3666</v>
       </c>
       <c r="B523" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C523" t="s">
         <v>141</v>
@@ -37664,7 +37670,7 @@
         <v>3667</v>
       </c>
       <c r="B524" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C524" t="s">
         <v>141</v>
@@ -37732,7 +37738,7 @@
         <v>3668</v>
       </c>
       <c r="B525" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C525" t="s">
         <v>141</v>
@@ -37800,7 +37806,7 @@
         <v>3669</v>
       </c>
       <c r="B526" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C526" t="s">
         <v>141</v>
@@ -37868,7 +37874,7 @@
         <v>3670</v>
       </c>
       <c r="B527" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C527" t="s">
         <v>141</v>
@@ -37936,7 +37942,7 @@
         <v>3671</v>
       </c>
       <c r="B528" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C528" t="s">
         <v>141</v>
@@ -38560,7 +38566,7 @@
         <v>3216</v>
       </c>
       <c r="B537" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C537" t="s">
         <v>141</v>
@@ -38634,7 +38640,7 @@
         <v>3218</v>
       </c>
       <c r="B538" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C538" t="s">
         <v>141</v>
@@ -38708,7 +38714,7 @@
         <v>3219</v>
       </c>
       <c r="B539" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C539" t="s">
         <v>141</v>
@@ -38782,7 +38788,7 @@
         <v>3220</v>
       </c>
       <c r="B540" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C540" t="s">
         <v>141</v>
@@ -38930,7 +38936,7 @@
         <v>3666</v>
       </c>
       <c r="B542" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C542" t="s">
         <v>141</v>
@@ -39004,7 +39010,7 @@
         <v>3667</v>
       </c>
       <c r="B543" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C543" t="s">
         <v>141</v>
@@ -39078,7 +39084,7 @@
         <v>3668</v>
       </c>
       <c r="B544" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C544" t="s">
         <v>141</v>
@@ -39152,7 +39158,7 @@
         <v>3669</v>
       </c>
       <c r="B545" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C545" t="s">
         <v>141</v>
@@ -39226,7 +39232,7 @@
         <v>3670</v>
       </c>
       <c r="B546" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C546" t="s">
         <v>141</v>
@@ -39300,7 +39306,7 @@
         <v>3671</v>
       </c>
       <c r="B547" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C547" t="s">
         <v>141</v>
@@ -39374,7 +39380,7 @@
         <v>4614</v>
       </c>
       <c r="B548" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C548" t="s">
         <v>141</v>
@@ -39652,7 +39658,7 @@
         <v>3218</v>
       </c>
       <c r="B552" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C552" t="s">
         <v>141</v>
@@ -39720,7 +39726,7 @@
         <v>3220</v>
       </c>
       <c r="B553" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C553" t="s">
         <v>141</v>
@@ -39856,7 +39862,7 @@
         <v>3666</v>
       </c>
       <c r="B555" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C555" t="s">
         <v>141</v>
@@ -39924,7 +39930,7 @@
         <v>3668</v>
       </c>
       <c r="B556" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C556" t="s">
         <v>141</v>
@@ -39992,7 +39998,7 @@
         <v>3670</v>
       </c>
       <c r="B557" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C557" t="s">
         <v>141</v>
@@ -40060,7 +40066,7 @@
         <v>3671</v>
       </c>
       <c r="B558" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C558" t="s">
         <v>141</v>
@@ -40196,7 +40202,7 @@
         <v>4614</v>
       </c>
       <c r="B560" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C560" t="s">
         <v>141</v>
@@ -40412,7 +40418,7 @@
         <v>3216</v>
       </c>
       <c r="B563" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C563" t="s">
         <v>141</v>
@@ -40560,7 +40566,7 @@
         <v>3218</v>
       </c>
       <c r="B565" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C565" t="s">
         <v>141</v>
@@ -40634,7 +40640,7 @@
         <v>3219</v>
       </c>
       <c r="B566" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C566" t="s">
         <v>141</v>
@@ -40708,7 +40714,7 @@
         <v>3220</v>
       </c>
       <c r="B567" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C567" t="s">
         <v>141</v>
@@ -40856,7 +40862,7 @@
         <v>3666</v>
       </c>
       <c r="B569" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C569" t="s">
         <v>141</v>
@@ -40930,7 +40936,7 @@
         <v>3667</v>
       </c>
       <c r="B570" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C570" t="s">
         <v>141</v>
@@ -41004,7 +41010,7 @@
         <v>3668</v>
       </c>
       <c r="B571" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C571" t="s">
         <v>141</v>
@@ -41078,7 +41084,7 @@
         <v>3669</v>
       </c>
       <c r="B572" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C572" t="s">
         <v>141</v>
@@ -41152,7 +41158,7 @@
         <v>3670</v>
       </c>
       <c r="B573" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C573" t="s">
         <v>141</v>
@@ -41226,7 +41232,7 @@
         <v>3671</v>
       </c>
       <c r="B574" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C574" t="s">
         <v>141</v>
@@ -41374,7 +41380,7 @@
         <v>4614</v>
       </c>
       <c r="B576" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C576" t="s">
         <v>141</v>
@@ -42536,7 +42542,7 @@
         <v>2804</v>
       </c>
       <c r="B593" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C593" t="s">
         <v>141</v>
@@ -42610,7 +42616,7 @@
         <v>2835</v>
       </c>
       <c r="B594" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C594" t="s">
         <v>141</v>
@@ -42684,7 +42690,7 @@
         <v>2837</v>
       </c>
       <c r="B595" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C595" t="s">
         <v>141</v>
@@ -42758,7 +42764,7 @@
         <v>2838</v>
       </c>
       <c r="B596" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C596" t="s">
         <v>141</v>
@@ -42832,7 +42838,7 @@
         <v>2842</v>
       </c>
       <c r="B597" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C597" t="s">
         <v>141</v>
@@ -42906,7 +42912,7 @@
         <v>3004</v>
       </c>
       <c r="B598" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C598" t="s">
         <v>141</v>
@@ -42980,7 +42986,7 @@
         <v>3005</v>
       </c>
       <c r="B599" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C599" t="s">
         <v>141</v>
@@ -43054,7 +43060,7 @@
         <v>3039</v>
       </c>
       <c r="B600" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C600" t="s">
         <v>141</v>
@@ -43128,7 +43134,7 @@
         <v>3053</v>
       </c>
       <c r="B601" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C601" t="s">
         <v>141</v>
@@ -43202,7 +43208,7 @@
         <v>3209</v>
       </c>
       <c r="B602" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C602" t="s">
         <v>141</v>
@@ -43276,7 +43282,7 @@
         <v>3480</v>
       </c>
       <c r="B603" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C603" t="s">
         <v>141</v>
@@ -43350,7 +43356,7 @@
         <v>3481</v>
       </c>
       <c r="B604" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C604" t="s">
         <v>141</v>
@@ -43424,7 +43430,7 @@
         <v>2804</v>
       </c>
       <c r="B605" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C605" t="s">
         <v>141</v>
@@ -43498,7 +43504,7 @@
         <v>2835</v>
       </c>
       <c r="B606" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C606" t="s">
         <v>141</v>
@@ -43572,7 +43578,7 @@
         <v>2837</v>
       </c>
       <c r="B607" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C607" t="s">
         <v>141</v>
@@ -43646,7 +43652,7 @@
         <v>2838</v>
       </c>
       <c r="B608" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C608" t="s">
         <v>141</v>
@@ -43720,7 +43726,7 @@
         <v>3004</v>
       </c>
       <c r="B609" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C609" t="s">
         <v>141</v>
@@ -43794,7 +43800,7 @@
         <v>3005</v>
       </c>
       <c r="B610" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C610" t="s">
         <v>141</v>
@@ -43868,7 +43874,7 @@
         <v>3039</v>
       </c>
       <c r="B611" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C611" t="s">
         <v>141</v>
@@ -43942,7 +43948,7 @@
         <v>3209</v>
       </c>
       <c r="B612" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C612" t="s">
         <v>141</v>
@@ -44016,7 +44022,7 @@
         <v>3480</v>
       </c>
       <c r="B613" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C613" t="s">
         <v>141</v>
@@ -44090,7 +44096,7 @@
         <v>3481</v>
       </c>
       <c r="B614" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C614" t="s">
         <v>141</v>
@@ -44164,7 +44170,7 @@
         <v>2835</v>
       </c>
       <c r="B615" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C615" t="s">
         <v>141</v>
@@ -44232,7 +44238,7 @@
         <v>2835</v>
       </c>
       <c r="B616" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C616" t="s">
         <v>141</v>
@@ -44306,7 +44312,7 @@
         <v>2837</v>
       </c>
       <c r="B617" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C617" t="s">
         <v>141</v>
@@ -44380,7 +44386,7 @@
         <v>2838</v>
       </c>
       <c r="B618" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C618" t="s">
         <v>141</v>
@@ -44454,7 +44460,7 @@
         <v>2842</v>
       </c>
       <c r="B619" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C619" t="s">
         <v>141</v>
@@ -44528,7 +44534,7 @@
         <v>3004</v>
       </c>
       <c r="B620" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C620" t="s">
         <v>141</v>
@@ -44602,7 +44608,7 @@
         <v>3005</v>
       </c>
       <c r="B621" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C621" t="s">
         <v>141</v>
@@ -44676,7 +44682,7 @@
         <v>3039</v>
       </c>
       <c r="B622" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C622" t="s">
         <v>141</v>
@@ -44750,7 +44756,7 @@
         <v>3209</v>
       </c>
       <c r="B623" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C623" t="s">
         <v>141</v>
@@ -44824,7 +44830,7 @@
         <v>3480</v>
       </c>
       <c r="B624" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C624" t="s">
         <v>141</v>
@@ -44898,7 +44904,7 @@
         <v>3481</v>
       </c>
       <c r="B625" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C625" t="s">
         <v>141</v>
@@ -44972,7 +44978,7 @@
         <v>2804</v>
       </c>
       <c r="B626" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C626" t="s">
         <v>141</v>
@@ -45564,7 +45570,7 @@
         <v>2804</v>
       </c>
       <c r="B634" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C634" t="s">
         <v>141</v>
@@ -45638,7 +45644,7 @@
         <v>3053</v>
       </c>
       <c r="B635" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C635" t="s">
         <v>141</v>
@@ -45712,7 +45718,7 @@
         <v>2842</v>
       </c>
       <c r="B636" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C636" t="s">
         <v>141</v>
@@ -45786,7 +45792,7 @@
         <v>3053</v>
       </c>
       <c r="B637" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C637" t="s">
         <v>141</v>
@@ -45854,7 +45860,7 @@
         <v>2835</v>
       </c>
       <c r="B638" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C638" t="s">
         <v>141</v>
@@ -45928,7 +45934,7 @@
         <v>2837</v>
       </c>
       <c r="B639" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C639" t="s">
         <v>141</v>
@@ -46002,7 +46008,7 @@
         <v>2838</v>
       </c>
       <c r="B640" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C640" t="s">
         <v>141</v>
@@ -46076,7 +46082,7 @@
         <v>2842</v>
       </c>
       <c r="B641" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C641" t="s">
         <v>141</v>
@@ -46150,7 +46156,7 @@
         <v>3004</v>
       </c>
       <c r="B642" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C642" t="s">
         <v>141</v>
@@ -46224,7 +46230,7 @@
         <v>3005</v>
       </c>
       <c r="B643" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C643" t="s">
         <v>141</v>
@@ -46298,7 +46304,7 @@
         <v>3039</v>
       </c>
       <c r="B644" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C644" t="s">
         <v>141</v>
@@ -46372,7 +46378,7 @@
         <v>3209</v>
       </c>
       <c r="B645" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C645" t="s">
         <v>141</v>
@@ -46446,7 +46452,7 @@
         <v>3480</v>
       </c>
       <c r="B646" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C646" t="s">
         <v>141</v>
@@ -46520,7 +46526,7 @@
         <v>3481</v>
       </c>
       <c r="B647" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C647" t="s">
         <v>141</v>
@@ -46594,7 +46600,7 @@
         <v>2804</v>
       </c>
       <c r="B648" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C648" t="s">
         <v>141</v>
@@ -46665,7 +46671,7 @@
         <v>2835</v>
       </c>
       <c r="B649" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C649" t="s">
         <v>141</v>
@@ -46736,7 +46742,7 @@
         <v>2837</v>
       </c>
       <c r="B650" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C650" t="s">
         <v>141</v>
@@ -46807,7 +46813,7 @@
         <v>2838</v>
       </c>
       <c r="B651" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C651" t="s">
         <v>141</v>
@@ -46878,7 +46884,7 @@
         <v>2842</v>
       </c>
       <c r="B652" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C652" t="s">
         <v>141</v>
@@ -46949,7 +46955,7 @@
         <v>3004</v>
       </c>
       <c r="B653" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C653" t="s">
         <v>141</v>
@@ -47020,7 +47026,7 @@
         <v>3005</v>
       </c>
       <c r="B654" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C654" t="s">
         <v>141</v>
@@ -47091,7 +47097,7 @@
         <v>3039</v>
       </c>
       <c r="B655" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C655" t="s">
         <v>141</v>
@@ -47162,7 +47168,7 @@
         <v>3209</v>
       </c>
       <c r="B656" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C656" t="s">
         <v>141</v>
@@ -47233,7 +47239,7 @@
         <v>3480</v>
       </c>
       <c r="B657" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C657" t="s">
         <v>141</v>
@@ -47304,7 +47310,7 @@
         <v>3481</v>
       </c>
       <c r="B658" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C658" t="s">
         <v>141</v>
@@ -47375,7 +47381,7 @@
         <v>2804</v>
       </c>
       <c r="B659" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C659" t="s">
         <v>141</v>
@@ -47893,7 +47899,7 @@
         <v>2835</v>
       </c>
       <c r="B666" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C666" t="s">
         <v>141</v>
@@ -47967,7 +47973,7 @@
         <v>2837</v>
       </c>
       <c r="B667" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C667" t="s">
         <v>141</v>
@@ -48041,7 +48047,7 @@
         <v>2838</v>
       </c>
       <c r="B668" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C668" t="s">
         <v>141</v>
@@ -48115,7 +48121,7 @@
         <v>2842</v>
       </c>
       <c r="B669" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C669" t="s">
         <v>141</v>
@@ -48189,7 +48195,7 @@
         <v>3005</v>
       </c>
       <c r="B670" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C670" t="s">
         <v>141</v>
@@ -48263,7 +48269,7 @@
         <v>3039</v>
       </c>
       <c r="B671" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C671" t="s">
         <v>141</v>
@@ -48337,7 +48343,7 @@
         <v>3053</v>
       </c>
       <c r="B672" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C672" t="s">
         <v>141</v>
@@ -48411,7 +48417,7 @@
         <v>3209</v>
       </c>
       <c r="B673" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C673" t="s">
         <v>141</v>
@@ -48485,7 +48491,7 @@
         <v>3480</v>
       </c>
       <c r="B674" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C674" t="s">
         <v>141</v>
@@ -48559,7 +48565,7 @@
         <v>3481</v>
       </c>
       <c r="B675" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C675" t="s">
         <v>141</v>
@@ -48633,7 +48639,7 @@
         <v>3480</v>
       </c>
       <c r="B676" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C676" t="s">
         <v>141</v>
@@ -48707,7 +48713,7 @@
         <v>3481</v>
       </c>
       <c r="B677" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C677" t="s">
         <v>141</v>
@@ -48781,7 +48787,7 @@
         <v>2804</v>
       </c>
       <c r="B678" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C678" t="s">
         <v>141</v>
@@ -48855,7 +48861,7 @@
         <v>2804</v>
       </c>
       <c r="B679" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C679" t="s">
         <v>141</v>
@@ -48929,7 +48935,7 @@
         <v>2835</v>
       </c>
       <c r="B680" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C680" t="s">
         <v>141</v>
@@ -49003,7 +49009,7 @@
         <v>2837</v>
       </c>
       <c r="B681" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C681" t="s">
         <v>141</v>
@@ -49077,7 +49083,7 @@
         <v>2838</v>
       </c>
       <c r="B682" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C682" t="s">
         <v>141</v>
@@ -49151,7 +49157,7 @@
         <v>2842</v>
       </c>
       <c r="B683" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C683" t="s">
         <v>141</v>
@@ -49225,7 +49231,7 @@
         <v>3004</v>
       </c>
       <c r="B684" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C684" t="s">
         <v>141</v>
@@ -49299,7 +49305,7 @@
         <v>3005</v>
       </c>
       <c r="B685" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C685" t="s">
         <v>141</v>
@@ -49373,7 +49379,7 @@
         <v>3039</v>
       </c>
       <c r="B686" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C686" t="s">
         <v>141</v>
@@ -49447,7 +49453,7 @@
         <v>3053</v>
       </c>
       <c r="B687" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C687" t="s">
         <v>141</v>
@@ -49521,7 +49527,7 @@
         <v>3209</v>
       </c>
       <c r="B688" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C688" t="s">
         <v>141</v>
@@ -49595,7 +49601,7 @@
         <v>3480</v>
       </c>
       <c r="B689" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C689" t="s">
         <v>141</v>
@@ -49669,7 +49675,7 @@
         <v>3481</v>
       </c>
       <c r="B690" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C690" t="s">
         <v>141</v>
@@ -49743,7 +49749,7 @@
         <v>2835</v>
       </c>
       <c r="B691" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C691" t="s">
         <v>141</v>
@@ -49817,7 +49823,7 @@
         <v>2837</v>
       </c>
       <c r="B692" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C692" t="s">
         <v>141</v>
@@ -49891,7 +49897,7 @@
         <v>2838</v>
       </c>
       <c r="B693" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C693" t="s">
         <v>141</v>
@@ -49965,7 +49971,7 @@
         <v>3004</v>
       </c>
       <c r="B694" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C694" t="s">
         <v>141</v>
@@ -50039,7 +50045,7 @@
         <v>3005</v>
       </c>
       <c r="B695" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C695" t="s">
         <v>141</v>
@@ -50113,7 +50119,7 @@
         <v>3039</v>
       </c>
       <c r="B696" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C696" t="s">
         <v>141</v>
@@ -50187,7 +50193,7 @@
         <v>3209</v>
       </c>
       <c r="B697" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C697" t="s">
         <v>141</v>
@@ -50261,7 +50267,7 @@
         <v>3480</v>
       </c>
       <c r="B698" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C698" t="s">
         <v>141</v>
@@ -50335,7 +50341,7 @@
         <v>3481</v>
       </c>
       <c r="B699" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C699" t="s">
         <v>141</v>
@@ -50409,7 +50415,7 @@
         <v>2804</v>
       </c>
       <c r="B700" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C700" t="s">
         <v>141</v>
@@ -50483,7 +50489,7 @@
         <v>2835</v>
       </c>
       <c r="B701" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C701" t="s">
         <v>141</v>
@@ -50557,7 +50563,7 @@
         <v>2837</v>
       </c>
       <c r="B702" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C702" t="s">
         <v>141</v>
@@ -50631,7 +50637,7 @@
         <v>2838</v>
       </c>
       <c r="B703" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C703" t="s">
         <v>141</v>
@@ -50705,7 +50711,7 @@
         <v>2842</v>
       </c>
       <c r="B704" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C704" t="s">
         <v>141</v>
@@ -50779,7 +50785,7 @@
         <v>3005</v>
       </c>
       <c r="B705" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C705" t="s">
         <v>141</v>
@@ -50853,7 +50859,7 @@
         <v>3039</v>
       </c>
       <c r="B706" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C706" t="s">
         <v>141</v>
@@ -50927,7 +50933,7 @@
         <v>3053</v>
       </c>
       <c r="B707" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C707" t="s">
         <v>141</v>
@@ -51001,7 +51007,7 @@
         <v>3209</v>
       </c>
       <c r="B708" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C708" t="s">
         <v>141</v>
@@ -51075,7 +51081,7 @@
         <v>3480</v>
       </c>
       <c r="B709" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C709" t="s">
         <v>141</v>
@@ -51149,7 +51155,7 @@
         <v>3481</v>
       </c>
       <c r="B710" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C710" t="s">
         <v>141</v>
@@ -51223,7 +51229,7 @@
         <v>2835</v>
       </c>
       <c r="B711" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C711" t="s">
         <v>141</v>
@@ -51291,7 +51297,7 @@
         <v>2837</v>
       </c>
       <c r="B712" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C712" t="s">
         <v>141</v>
@@ -51365,7 +51371,7 @@
         <v>2838</v>
       </c>
       <c r="B713" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C713" t="s">
         <v>141</v>
@@ -51439,7 +51445,7 @@
         <v>2842</v>
       </c>
       <c r="B714" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C714" t="s">
         <v>141</v>
@@ -51507,7 +51513,7 @@
         <v>3004</v>
       </c>
       <c r="B715" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C715" t="s">
         <v>141</v>
@@ -51581,7 +51587,7 @@
         <v>3005</v>
       </c>
       <c r="B716" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C716" t="s">
         <v>141</v>
@@ -51655,7 +51661,7 @@
         <v>3039</v>
       </c>
       <c r="B717" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C717" t="s">
         <v>141</v>
@@ -51729,7 +51735,7 @@
         <v>3209</v>
       </c>
       <c r="B718" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C718" t="s">
         <v>141</v>
@@ -51797,7 +51803,7 @@
         <v>3480</v>
       </c>
       <c r="B719" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C719" t="s">
         <v>141</v>
@@ -51865,7 +51871,7 @@
         <v>3481</v>
       </c>
       <c r="B720" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C720" t="s">
         <v>141</v>
@@ -52229,7 +52235,7 @@
         <v>2804</v>
       </c>
       <c r="B725" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C725" t="s">
         <v>141</v>
@@ -52729,7 +52735,7 @@
         <v>2835</v>
       </c>
       <c r="B732" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C732" t="s">
         <v>141</v>
@@ -52797,7 +52803,7 @@
         <v>2837</v>
       </c>
       <c r="B733" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C733" t="s">
         <v>141</v>
@@ -52871,7 +52877,7 @@
         <v>2838</v>
       </c>
       <c r="B734" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C734" t="s">
         <v>141</v>
@@ -52945,7 +52951,7 @@
         <v>2842</v>
       </c>
       <c r="B735" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C735" t="s">
         <v>141</v>
@@ -53013,7 +53019,7 @@
         <v>3004</v>
       </c>
       <c r="B736" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C736" t="s">
         <v>141</v>
@@ -53087,7 +53093,7 @@
         <v>3005</v>
       </c>
       <c r="B737" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C737" t="s">
         <v>141</v>
@@ -53161,7 +53167,7 @@
         <v>3039</v>
       </c>
       <c r="B738" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C738" t="s">
         <v>141</v>
@@ -53235,7 +53241,7 @@
         <v>3053</v>
       </c>
       <c r="B739" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C739" t="s">
         <v>141</v>
@@ -53309,7 +53315,7 @@
         <v>3209</v>
       </c>
       <c r="B740" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C740" t="s">
         <v>141</v>
@@ -53457,7 +53463,7 @@
         <v>3480</v>
       </c>
       <c r="B742" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C742" t="s">
         <v>141</v>
@@ -53531,7 +53537,7 @@
         <v>3481</v>
       </c>
       <c r="B743" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C743" t="s">
         <v>141</v>
@@ -54105,7 +54111,7 @@
         <v>2804</v>
       </c>
       <c r="B751" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C751" t="s">
         <v>141</v>
@@ -54581,7 +54587,7 @@
         <v>3053</v>
       </c>
       <c r="B758" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C758" t="s">
         <v>141</v>
@@ -55057,7 +55063,7 @@
         <v>2371</v>
       </c>
       <c r="B765" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C765" t="s">
         <v>141</v>
@@ -55131,7 +55137,7 @@
         <v>3366</v>
       </c>
       <c r="B766" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C766" t="s">
         <v>141</v>
@@ -55205,7 +55211,7 @@
         <v>2371</v>
       </c>
       <c r="B767" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C767" t="s">
         <v>141</v>
@@ -55279,7 +55285,7 @@
         <v>2371</v>
       </c>
       <c r="B768" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C768" t="s">
         <v>141</v>
@@ -55353,7 +55359,7 @@
         <v>2371</v>
       </c>
       <c r="B769" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C769" t="s">
         <v>141</v>
@@ -55427,7 +55433,7 @@
         <v>2371</v>
       </c>
       <c r="B770" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C770" t="s">
         <v>141</v>
@@ -55501,7 +55507,7 @@
         <v>3366</v>
       </c>
       <c r="B771" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C771" t="s">
         <v>141</v>
@@ -55575,7 +55581,7 @@
         <v>2371</v>
       </c>
       <c r="B772" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C772" t="s">
         <v>141</v>
@@ -55649,7 +55655,7 @@
         <v>2371</v>
       </c>
       <c r="B773" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C773" t="s">
         <v>141</v>
@@ -55723,7 +55729,7 @@
         <v>3366</v>
       </c>
       <c r="B774" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C774" t="s">
         <v>141</v>
@@ -55797,7 +55803,7 @@
         <v>2371</v>
       </c>
       <c r="B775" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C775" t="s">
         <v>141</v>
@@ -55871,7 +55877,7 @@
         <v>3366</v>
       </c>
       <c r="B776" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C776" t="s">
         <v>141</v>
@@ -55945,7 +55951,7 @@
         <v>2371</v>
       </c>
       <c r="B777" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C777" t="s">
         <v>141</v>
@@ -56019,7 +56025,7 @@
         <v>3366</v>
       </c>
       <c r="B778" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C778" t="s">
         <v>141</v>
@@ -56093,7 +56099,7 @@
         <v>2371</v>
       </c>
       <c r="B779" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C779" t="s">
         <v>141</v>
@@ -56167,7 +56173,7 @@
         <v>3366</v>
       </c>
       <c r="B780" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C780" t="s">
         <v>141</v>
@@ -56241,7 +56247,7 @@
         <v>2371</v>
       </c>
       <c r="B781" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C781" t="s">
         <v>141</v>
@@ -56312,7 +56318,7 @@
         <v>2371</v>
       </c>
       <c r="B782" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C782" t="s">
         <v>141</v>
@@ -56386,7 +56392,7 @@
         <v>3366</v>
       </c>
       <c r="B783" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C783" t="s">
         <v>141</v>
@@ -56460,7 +56466,7 @@
         <v>2371</v>
       </c>
       <c r="B784" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C784" t="s">
         <v>141</v>
@@ -56528,7 +56534,7 @@
         <v>2373</v>
       </c>
       <c r="B785" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C785" t="s">
         <v>141</v>
@@ -56596,7 +56602,7 @@
         <v>2374</v>
       </c>
       <c r="B786" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C786" t="s">
         <v>141</v>
@@ -56664,7 +56670,7 @@
         <v>2395</v>
       </c>
       <c r="B787" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C787" t="s">
         <v>141</v>
@@ -56732,7 +56738,7 @@
         <v>2426</v>
       </c>
       <c r="B788" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C788" t="s">
         <v>141</v>
@@ -56800,7 +56806,7 @@
         <v>2994</v>
       </c>
       <c r="B789" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C789" t="s">
         <v>141</v>
@@ -56868,7 +56874,7 @@
         <v>2371</v>
       </c>
       <c r="B790" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C790" t="s">
         <v>141</v>
@@ -56936,7 +56942,7 @@
         <v>2373</v>
       </c>
       <c r="B791" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C791" t="s">
         <v>141</v>
@@ -57004,7 +57010,7 @@
         <v>2374</v>
       </c>
       <c r="B792" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C792" t="s">
         <v>141</v>
@@ -57072,7 +57078,7 @@
         <v>2395</v>
       </c>
       <c r="B793" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C793" t="s">
         <v>141</v>
@@ -57140,7 +57146,7 @@
         <v>2426</v>
       </c>
       <c r="B794" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C794" t="s">
         <v>141</v>
@@ -57208,7 +57214,7 @@
         <v>2994</v>
       </c>
       <c r="B795" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C795" t="s">
         <v>141</v>
@@ -57276,7 +57282,7 @@
         <v>3278</v>
       </c>
       <c r="B796" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C796" t="s">
         <v>141</v>
@@ -57344,7 +57350,7 @@
         <v>3279</v>
       </c>
       <c r="B797" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C797" t="s">
         <v>141</v>
@@ -57412,7 +57418,7 @@
         <v>3366</v>
       </c>
       <c r="B798" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C798" t="s">
         <v>141</v>
@@ -57480,7 +57486,7 @@
         <v>3497</v>
       </c>
       <c r="B799" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C799" t="s">
         <v>141</v>
@@ -57548,7 +57554,7 @@
         <v>3862</v>
       </c>
       <c r="B800" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C800" t="s">
         <v>141</v>
@@ -57616,7 +57622,7 @@
         <v>4423</v>
       </c>
       <c r="B801" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C801" t="s">
         <v>141</v>
@@ -57684,7 +57690,7 @@
         <v>4633</v>
       </c>
       <c r="B802" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C802" t="s">
         <v>141</v>
@@ -57752,7 +57758,7 @@
         <v>5070</v>
       </c>
       <c r="B803" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C803" t="s">
         <v>141</v>
@@ -57888,7 +57894,7 @@
         <v>2371</v>
       </c>
       <c r="B805" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C805" t="s">
         <v>141</v>
@@ -57962,7 +57968,7 @@
         <v>3366</v>
       </c>
       <c r="B806" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C806" t="s">
         <v>141</v>
@@ -58036,7 +58042,7 @@
         <v>2371</v>
       </c>
       <c r="B807" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C807" t="s">
         <v>141</v>
@@ -58110,7 +58116,7 @@
         <v>2371</v>
       </c>
       <c r="B808" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C808" t="s">
         <v>141</v>
@@ -58178,7 +58184,7 @@
         <v>3278</v>
       </c>
       <c r="B809" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C809" t="s">
         <v>141</v>
@@ -58246,7 +58252,7 @@
         <v>3279</v>
       </c>
       <c r="B810" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C810" t="s">
         <v>141</v>
@@ -58314,7 +58320,7 @@
         <v>3497</v>
       </c>
       <c r="B811" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C811" t="s">
         <v>141</v>
@@ -58382,7 +58388,7 @@
         <v>3862</v>
       </c>
       <c r="B812" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C812" t="s">
         <v>141</v>
@@ -58450,7 +58456,7 @@
         <v>4423</v>
       </c>
       <c r="B813" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C813" t="s">
         <v>141</v>
@@ -58518,7 +58524,7 @@
         <v>4633</v>
       </c>
       <c r="B814" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C814" t="s">
         <v>141</v>
@@ -58586,7 +58592,7 @@
         <v>4990</v>
       </c>
       <c r="B815" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C815" t="s">
         <v>141</v>
@@ -58654,7 +58660,7 @@
         <v>2371</v>
       </c>
       <c r="B816" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C816" t="s">
         <v>141</v>
@@ -58722,7 +58728,7 @@
         <v>2372</v>
       </c>
       <c r="B817" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C817" t="s">
         <v>141</v>
@@ -58790,7 +58796,7 @@
         <v>2373</v>
       </c>
       <c r="B818" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C818" t="s">
         <v>141</v>
@@ -58858,7 +58864,7 @@
         <v>2374</v>
       </c>
       <c r="B819" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C819" t="s">
         <v>141</v>
@@ -58926,7 +58932,7 @@
         <v>2426</v>
       </c>
       <c r="B820" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C820" t="s">
         <v>141</v>
@@ -58994,7 +59000,7 @@
         <v>2994</v>
       </c>
       <c r="B821" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C821" t="s">
         <v>141</v>

--- a/dados/base/bpo.xlsx
+++ b/dados/base/bpo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11789" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11790" uniqueCount="265">
   <si>
     <t>CodCliente</t>
   </si>
@@ -661,9 +661,6 @@
     <t>13/10/2026</t>
   </si>
   <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
     <t>05/10/2026</t>
   </si>
   <si>
@@ -674,6 +671,9 @@
   </si>
   <si>
     <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
   </si>
   <si>
     <t>09/2026</t>
@@ -766,10 +766,6 @@
     <t>Comentário Padrão   Previsão para conclusão dia 13/10/2026 - Data Comentário: 09/10/2026 15:38</t>
   </si>
   <si>
-    <t>Controladoria, Erro de baixa, Chamado Nº  Previsão para conclusão dia 15/10/2026 
-Não aceita o arquivo para Baixa. - Data Comentário: 14/10/2026 11:32</t>
-  </si>
-  <si>
     <t>Comentário Colaborador + Previsão de conclusão, Previsto para: 05/10/2026 - Data Comentário: 21/09/2026 09:20</t>
   </si>
   <si>
@@ -786,6 +782,10 @@
   </si>
   <si>
     <t>Comentário Padrão  Previsão para conclusão dia 17/09/2026 - Data Comentário: 17/09/2026 07:44</t>
+  </si>
+  <si>
+    <t>Controladoria, Erro de baixa, Chamado Nº  Previsão para conclusão dia 15/10/2026 
+Não aceita o arquivo para Baixa. - Data Comentário: 14/10/2026 11:32</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 09/10/2026 
@@ -38741,7 +38741,7 @@
         <v>147</v>
       </c>
       <c r="G604">
-        <v>6788</v>
+        <v>2144</v>
       </c>
       <c r="H604">
         <v>0</v>
@@ -38750,19 +38750,16 @@
         <v>165</v>
       </c>
       <c r="J604" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="L604" s="1">
-        <v>46309</v>
-      </c>
-      <c r="M604" t="s">
-        <v>215</v>
+        <v>46322</v>
       </c>
       <c r="N604" t="s">
         <v>220</v>
       </c>
       <c r="O604">
-        <v>17540563</v>
+        <v>17540404</v>
       </c>
       <c r="P604" t="s">
         <v>234</v>
@@ -38771,7 +38768,7 @@
         <v>237</v>
       </c>
       <c r="S604">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="T604" t="s">
         <v>240</v>
@@ -38779,28 +38776,25 @@
       <c r="U604" t="s">
         <v>245</v>
       </c>
-      <c r="W604" t="s">
-        <v>250</v>
-      </c>
       <c r="AA604">
         <v>0</v>
       </c>
       <c r="AG604" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="605" spans="1:33">
       <c r="A605">
-        <v>2371</v>
+        <v>3366</v>
       </c>
       <c r="B605" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C605" t="s">
         <v>141</v>
       </c>
       <c r="D605" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E605" t="s">
         <v>147</v>
@@ -38827,7 +38821,7 @@
         <v>220</v>
       </c>
       <c r="O605">
-        <v>17540404</v>
+        <v>17448589</v>
       </c>
       <c r="P605" t="s">
         <v>234</v>
@@ -38871,7 +38865,7 @@
         <v>147</v>
       </c>
       <c r="G606">
-        <v>2144</v>
+        <v>9132</v>
       </c>
       <c r="H606">
         <v>0</v>
@@ -38880,16 +38874,16 @@
         <v>165</v>
       </c>
       <c r="J606" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L606" s="1">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="N606" t="s">
         <v>220</v>
       </c>
       <c r="O606">
-        <v>17448589</v>
+        <v>17448693</v>
       </c>
       <c r="P606" t="s">
         <v>234</v>
@@ -38898,7 +38892,7 @@
         <v>237</v>
       </c>
       <c r="S606">
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="T606" t="s">
         <v>240</v>
@@ -38910,21 +38904,21 @@
         <v>0</v>
       </c>
       <c r="AG606" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="607" spans="1:33">
       <c r="A607">
-        <v>3366</v>
+        <v>2371</v>
       </c>
       <c r="B607" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C607" t="s">
         <v>141</v>
       </c>
       <c r="D607" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E607" t="s">
         <v>147</v>
@@ -38933,7 +38927,7 @@
         <v>147</v>
       </c>
       <c r="G607">
-        <v>9132</v>
+        <v>11522</v>
       </c>
       <c r="H607">
         <v>0</v>
@@ -38942,16 +38936,16 @@
         <v>165</v>
       </c>
       <c r="J607" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="L607" s="1">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="N607" t="s">
         <v>220</v>
       </c>
       <c r="O607">
-        <v>17448693</v>
+        <v>17540634</v>
       </c>
       <c r="P607" t="s">
         <v>234</v>
@@ -38960,7 +38954,7 @@
         <v>237</v>
       </c>
       <c r="S607">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="T607" t="s">
         <v>240</v>
@@ -38972,21 +38966,21 @@
         <v>0</v>
       </c>
       <c r="AG607" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="608" spans="1:33">
       <c r="A608">
-        <v>2371</v>
+        <v>3366</v>
       </c>
       <c r="B608" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C608" t="s">
         <v>141</v>
       </c>
       <c r="D608" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E608" t="s">
         <v>147</v>
@@ -39013,7 +39007,7 @@
         <v>220</v>
       </c>
       <c r="O608">
-        <v>17540634</v>
+        <v>17448711</v>
       </c>
       <c r="P608" t="s">
         <v>234</v>
@@ -39039,16 +39033,16 @@
     </row>
     <row r="609" spans="1:33">
       <c r="A609">
-        <v>3366</v>
+        <v>2371</v>
       </c>
       <c r="B609" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C609" t="s">
         <v>141</v>
       </c>
       <c r="D609" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E609" t="s">
         <v>147</v>
@@ -39057,25 +39051,25 @@
         <v>147</v>
       </c>
       <c r="G609">
-        <v>11522</v>
+        <v>2190</v>
       </c>
       <c r="H609">
-        <v>0</v>
+        <v>2143</v>
       </c>
       <c r="I609" t="s">
         <v>165</v>
       </c>
       <c r="J609" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="L609" s="1">
-        <v>46321</v>
+        <v>46315</v>
       </c>
       <c r="N609" t="s">
         <v>220</v>
       </c>
       <c r="O609">
-        <v>17448711</v>
+        <v>17540493</v>
       </c>
       <c r="P609" t="s">
         <v>234</v>
@@ -39084,7 +39078,7 @@
         <v>237</v>
       </c>
       <c r="S609">
-        <v>-12</v>
+        <v>-6</v>
       </c>
       <c r="T609" t="s">
         <v>240</v>
@@ -39096,21 +39090,21 @@
         <v>0</v>
       </c>
       <c r="AG609" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="610" spans="1:33">
       <c r="A610">
-        <v>2371</v>
+        <v>3366</v>
       </c>
       <c r="B610" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C610" t="s">
         <v>141</v>
       </c>
       <c r="D610" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E610" t="s">
         <v>147</v>
@@ -39119,34 +39113,34 @@
         <v>147</v>
       </c>
       <c r="G610">
-        <v>2190</v>
+        <v>2921</v>
       </c>
       <c r="H610">
-        <v>2143</v>
+        <v>0</v>
       </c>
       <c r="I610" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J610" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="L610" s="1">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="N610" t="s">
         <v>220</v>
       </c>
       <c r="O610">
-        <v>17540493</v>
+        <v>17448647</v>
       </c>
       <c r="P610" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q610" t="s">
         <v>237</v>
       </c>
       <c r="S610">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="T610" t="s">
         <v>240</v>
@@ -39158,21 +39152,21 @@
         <v>0</v>
       </c>
       <c r="AG610" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="611" spans="1:33">
       <c r="A611">
-        <v>3366</v>
+        <v>2371</v>
       </c>
       <c r="B611" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C611" t="s">
         <v>141</v>
       </c>
       <c r="D611" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E611" t="s">
         <v>147</v>
@@ -39181,7 +39175,7 @@
         <v>147</v>
       </c>
       <c r="G611">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="H611">
         <v>0</v>
@@ -39190,7 +39184,7 @@
         <v>166</v>
       </c>
       <c r="J611" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L611" s="1">
         <v>46317</v>
@@ -39199,7 +39193,7 @@
         <v>220</v>
       </c>
       <c r="O611">
-        <v>17448647</v>
+        <v>17540503</v>
       </c>
       <c r="P611" t="s">
         <v>235</v>
@@ -39225,10 +39219,10 @@
     </row>
     <row r="612" spans="1:33">
       <c r="A612">
-        <v>2371</v>
+        <v>4059</v>
       </c>
       <c r="B612" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C612" t="s">
         <v>141</v>
@@ -39243,63 +39237,75 @@
         <v>147</v>
       </c>
       <c r="G612">
-        <v>2922</v>
+        <v>9328</v>
       </c>
       <c r="H612">
         <v>0</v>
       </c>
       <c r="I612" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J612" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="L612" s="1">
-        <v>46317</v>
+        <v>46296</v>
+      </c>
+      <c r="M612" t="s">
+        <v>211</v>
       </c>
       <c r="N612" t="s">
         <v>220</v>
       </c>
       <c r="O612">
-        <v>17540503</v>
+        <v>17311897</v>
       </c>
       <c r="P612" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="Q612" t="s">
-        <v>237</v>
+        <v>238</v>
+      </c>
+      <c r="R612" s="1">
+        <v>46297.64184394676</v>
       </c>
       <c r="S612">
-        <v>-8</v>
+        <v>13</v>
       </c>
       <c r="T612" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="U612" t="s">
-        <v>245</v>
+        <v>244</v>
+      </c>
+      <c r="W612" t="s">
+        <v>246</v>
       </c>
       <c r="AA612">
         <v>0</v>
       </c>
+      <c r="AB612" t="s">
+        <v>259</v>
+      </c>
       <c r="AG612" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="613" spans="1:33">
       <c r="A613">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="B613" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C613" t="s">
         <v>141</v>
       </c>
       <c r="D613" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E613" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F613" t="s">
         <v>147</v>
@@ -39326,7 +39332,7 @@
         <v>220</v>
       </c>
       <c r="O613">
-        <v>17311897</v>
+        <v>17841046</v>
       </c>
       <c r="P613" t="s">
         <v>224</v>
@@ -39335,7 +39341,7 @@
         <v>238</v>
       </c>
       <c r="R613" s="1">
-        <v>46297.64184394676</v>
+        <v>46297.64184417824</v>
       </c>
       <c r="S613">
         <v>13</v>
@@ -39361,19 +39367,19 @@
     </row>
     <row r="614" spans="1:33">
       <c r="A614">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B614" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C614" t="s">
         <v>141</v>
       </c>
       <c r="D614" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E614" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F614" t="s">
         <v>147</v>
@@ -39400,7 +39406,7 @@
         <v>220</v>
       </c>
       <c r="O614">
-        <v>17841046</v>
+        <v>17222032</v>
       </c>
       <c r="P614" t="s">
         <v>224</v>
@@ -39409,7 +39415,7 @@
         <v>238</v>
       </c>
       <c r="R614" s="1">
-        <v>46297.64184417824</v>
+        <v>46297.64184452546</v>
       </c>
       <c r="S614">
         <v>13</v>
@@ -39435,10 +39441,10 @@
     </row>
     <row r="615" spans="1:33">
       <c r="A615">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="B615" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="C615" t="s">
         <v>141</v>
@@ -39447,7 +39453,7 @@
         <v>143</v>
       </c>
       <c r="E615" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F615" t="s">
         <v>147</v>
@@ -39474,7 +39480,7 @@
         <v>220</v>
       </c>
       <c r="O615">
-        <v>17222032</v>
+        <v>17424461</v>
       </c>
       <c r="P615" t="s">
         <v>224</v>
@@ -39483,7 +39489,7 @@
         <v>238</v>
       </c>
       <c r="R615" s="1">
-        <v>46297.64184452546</v>
+        <v>46297.6418449074</v>
       </c>
       <c r="S615">
         <v>13</v>
@@ -39509,10 +39515,10 @@
     </row>
     <row r="616" spans="1:33">
       <c r="A616">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B616" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="C616" t="s">
         <v>141</v>
@@ -39521,7 +39527,7 @@
         <v>143</v>
       </c>
       <c r="E616" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F616" t="s">
         <v>147</v>
@@ -39548,7 +39554,7 @@
         <v>220</v>
       </c>
       <c r="O616">
-        <v>17424461</v>
+        <v>17493454</v>
       </c>
       <c r="P616" t="s">
         <v>224</v>
@@ -39557,7 +39563,7 @@
         <v>238</v>
       </c>
       <c r="R616" s="1">
-        <v>46297.6418449074</v>
+        <v>46297.64184525463</v>
       </c>
       <c r="S616">
         <v>13</v>
@@ -39583,10 +39589,10 @@
     </row>
     <row r="617" spans="1:33">
       <c r="A617">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="B617" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C617" t="s">
         <v>141</v>
@@ -39622,7 +39628,7 @@
         <v>220</v>
       </c>
       <c r="O617">
-        <v>17493454</v>
+        <v>17424501</v>
       </c>
       <c r="P617" t="s">
         <v>224</v>
@@ -39631,7 +39637,7 @@
         <v>238</v>
       </c>
       <c r="R617" s="1">
-        <v>46297.64184525463</v>
+        <v>46297.64184560185</v>
       </c>
       <c r="S617">
         <v>13</v>
@@ -39657,10 +39663,10 @@
     </row>
     <row r="618" spans="1:33">
       <c r="A618">
-        <v>4068</v>
+        <v>4602</v>
       </c>
       <c r="B618" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C618" t="s">
         <v>141</v>
@@ -39696,7 +39702,7 @@
         <v>220</v>
       </c>
       <c r="O618">
-        <v>17424501</v>
+        <v>17719870</v>
       </c>
       <c r="P618" t="s">
         <v>224</v>
@@ -39705,7 +39711,7 @@
         <v>238</v>
       </c>
       <c r="R618" s="1">
-        <v>46297.64184560185</v>
+        <v>46297.64184603009</v>
       </c>
       <c r="S618">
         <v>13</v>
@@ -39731,10 +39737,10 @@
     </row>
     <row r="619" spans="1:33">
       <c r="A619">
-        <v>4602</v>
+        <v>4815</v>
       </c>
       <c r="B619" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C619" t="s">
         <v>141</v>
@@ -39770,7 +39776,7 @@
         <v>220</v>
       </c>
       <c r="O619">
-        <v>17719870</v>
+        <v>17728400</v>
       </c>
       <c r="P619" t="s">
         <v>224</v>
@@ -39779,7 +39785,7 @@
         <v>238</v>
       </c>
       <c r="R619" s="1">
-        <v>46297.64184603009</v>
+        <v>46297.64184633102</v>
       </c>
       <c r="S619">
         <v>13</v>
@@ -39805,16 +39811,16 @@
     </row>
     <row r="620" spans="1:33">
       <c r="A620">
-        <v>4815</v>
+        <v>4917</v>
       </c>
       <c r="B620" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C620" t="s">
         <v>141</v>
       </c>
       <c r="D620" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E620" t="s">
         <v>147</v>
@@ -39844,7 +39850,7 @@
         <v>220</v>
       </c>
       <c r="O620">
-        <v>17728400</v>
+        <v>17629862</v>
       </c>
       <c r="P620" t="s">
         <v>224</v>
@@ -39853,7 +39859,7 @@
         <v>238</v>
       </c>
       <c r="R620" s="1">
-        <v>46297.64184633102</v>
+        <v>46297.64184679398</v>
       </c>
       <c r="S620">
         <v>13</v>
@@ -39879,16 +39885,16 @@
     </row>
     <row r="621" spans="1:33">
       <c r="A621">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B621" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C621" t="s">
         <v>141</v>
       </c>
       <c r="D621" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E621" t="s">
         <v>147</v>
@@ -39897,7 +39903,7 @@
         <v>147</v>
       </c>
       <c r="G621">
-        <v>9328</v>
+        <v>9570</v>
       </c>
       <c r="H621">
         <v>0</v>
@@ -39906,7 +39912,7 @@
         <v>159</v>
       </c>
       <c r="J621" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="L621" s="1">
         <v>46296</v>
@@ -39915,10 +39921,10 @@
         <v>211</v>
       </c>
       <c r="N621" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O621">
-        <v>17629862</v>
+        <v>17311908</v>
       </c>
       <c r="P621" t="s">
         <v>224</v>
@@ -39927,7 +39933,7 @@
         <v>238</v>
       </c>
       <c r="R621" s="1">
-        <v>46297.64184679398</v>
+        <v>46296.74303420139</v>
       </c>
       <c r="S621">
         <v>13</v>
@@ -39945,7 +39951,7 @@
         <v>0</v>
       </c>
       <c r="AB621" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="AG621" t="s">
         <v>263</v>
@@ -39953,10 +39959,10 @@
     </row>
     <row r="622" spans="1:33">
       <c r="A622">
-        <v>4059</v>
+        <v>4061</v>
       </c>
       <c r="B622" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C622" t="s">
         <v>141</v>
@@ -39965,7 +39971,7 @@
         <v>142</v>
       </c>
       <c r="E622" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F622" t="s">
         <v>147</v>
@@ -39992,7 +39998,7 @@
         <v>221</v>
       </c>
       <c r="O622">
-        <v>17311908</v>
+        <v>17311958</v>
       </c>
       <c r="P622" t="s">
         <v>224</v>
@@ -40001,7 +40007,7 @@
         <v>238</v>
       </c>
       <c r="R622" s="1">
-        <v>46296.74303420139</v>
+        <v>46296.74303458333</v>
       </c>
       <c r="S622">
         <v>13</v>
@@ -40027,10 +40033,10 @@
     </row>
     <row r="623" spans="1:33">
       <c r="A623">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B623" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C623" t="s">
         <v>141</v>
@@ -40039,7 +40045,7 @@
         <v>142</v>
       </c>
       <c r="E623" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F623" t="s">
         <v>147</v>
@@ -40066,7 +40072,7 @@
         <v>221</v>
       </c>
       <c r="O623">
-        <v>17311958</v>
+        <v>17756698</v>
       </c>
       <c r="P623" t="s">
         <v>224</v>
@@ -40075,7 +40081,7 @@
         <v>238</v>
       </c>
       <c r="R623" s="1">
-        <v>46296.74303458333</v>
+        <v>46296.7430350463</v>
       </c>
       <c r="S623">
         <v>13</v>
@@ -40101,10 +40107,10 @@
     </row>
     <row r="624" spans="1:33">
       <c r="A624">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B624" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C624" t="s">
         <v>141</v>
@@ -40113,7 +40119,7 @@
         <v>142</v>
       </c>
       <c r="E624" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F624" t="s">
         <v>147</v>
@@ -40140,7 +40146,7 @@
         <v>221</v>
       </c>
       <c r="O624">
-        <v>17756698</v>
+        <v>17221865</v>
       </c>
       <c r="P624" t="s">
         <v>224</v>
@@ -40149,7 +40155,7 @@
         <v>238</v>
       </c>
       <c r="R624" s="1">
-        <v>46296.7430350463</v>
+        <v>46296.74303538194</v>
       </c>
       <c r="S624">
         <v>13</v>
@@ -40175,10 +40181,10 @@
     </row>
     <row r="625" spans="1:33">
       <c r="A625">
-        <v>4063</v>
+        <v>4535</v>
       </c>
       <c r="B625" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C625" t="s">
         <v>141</v>
@@ -40187,7 +40193,7 @@
         <v>142</v>
       </c>
       <c r="E625" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F625" t="s">
         <v>147</v>
@@ -40214,7 +40220,7 @@
         <v>221</v>
       </c>
       <c r="O625">
-        <v>17221865</v>
+        <v>17260688</v>
       </c>
       <c r="P625" t="s">
         <v>224</v>
@@ -40223,7 +40229,7 @@
         <v>238</v>
       </c>
       <c r="R625" s="1">
-        <v>46296.74303538194</v>
+        <v>46296.74303584491</v>
       </c>
       <c r="S625">
         <v>13</v>
@@ -40249,10 +40255,10 @@
     </row>
     <row r="626" spans="1:33">
       <c r="A626">
-        <v>4535</v>
+        <v>4059</v>
       </c>
       <c r="B626" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="C626" t="s">
         <v>141</v>
@@ -40267,28 +40273,25 @@
         <v>147</v>
       </c>
       <c r="G626">
-        <v>9570</v>
+        <v>9196</v>
       </c>
       <c r="H626">
         <v>0</v>
       </c>
       <c r="I626" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J626" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="L626" s="1">
-        <v>46296</v>
-      </c>
-      <c r="M626" t="s">
-        <v>211</v>
+        <v>46304</v>
       </c>
       <c r="N626" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O626">
-        <v>17260688</v>
+        <v>17311821</v>
       </c>
       <c r="P626" t="s">
         <v>224</v>
@@ -40297,10 +40300,10 @@
         <v>238</v>
       </c>
       <c r="R626" s="1">
-        <v>46296.74303584491</v>
+        <v>46304.44261545139</v>
       </c>
       <c r="S626">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T626" t="s">
         <v>239</v>
@@ -40308,9 +40311,6 @@
       <c r="U626" t="s">
         <v>244</v>
       </c>
-      <c r="W626" t="s">
-        <v>246</v>
-      </c>
       <c r="AA626">
         <v>0</v>
       </c>
@@ -40318,24 +40318,24 @@
         <v>224</v>
       </c>
       <c r="AG626" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="627" spans="1:33">
       <c r="A627">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="B627" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C627" t="s">
         <v>141</v>
       </c>
       <c r="D627" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E627" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F627" t="s">
         <v>147</v>
@@ -40359,7 +40359,7 @@
         <v>220</v>
       </c>
       <c r="O627">
-        <v>17311821</v>
+        <v>17840983</v>
       </c>
       <c r="P627" t="s">
         <v>224</v>
@@ -40368,7 +40368,7 @@
         <v>238</v>
       </c>
       <c r="R627" s="1">
-        <v>46304.44261545139</v>
+        <v>46304.44261584491</v>
       </c>
       <c r="S627">
         <v>5</v>
@@ -40391,10 +40391,10 @@
     </row>
     <row r="628" spans="1:33">
       <c r="A628">
-        <v>4064</v>
+        <v>4917</v>
       </c>
       <c r="B628" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C628" t="s">
         <v>141</v>
@@ -40403,7 +40403,7 @@
         <v>144</v>
       </c>
       <c r="E628" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F628" t="s">
         <v>147</v>
@@ -40427,7 +40427,7 @@
         <v>220</v>
       </c>
       <c r="O628">
-        <v>17840983</v>
+        <v>17629790</v>
       </c>
       <c r="P628" t="s">
         <v>224</v>
@@ -40436,7 +40436,7 @@
         <v>238</v>
       </c>
       <c r="R628" s="1">
-        <v>46304.44261584491</v>
+        <v>46304.44261625</v>
       </c>
       <c r="S628">
         <v>5</v>
@@ -40459,16 +40459,16 @@
     </row>
     <row r="629" spans="1:33">
       <c r="A629">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B629" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C629" t="s">
         <v>141</v>
       </c>
       <c r="D629" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E629" t="s">
         <v>147</v>
@@ -40477,7 +40477,7 @@
         <v>147</v>
       </c>
       <c r="G629">
-        <v>9196</v>
+        <v>9197</v>
       </c>
       <c r="H629">
         <v>0</v>
@@ -40486,7 +40486,7 @@
         <v>160</v>
       </c>
       <c r="J629" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="L629" s="1">
         <v>46304</v>
@@ -40495,7 +40495,7 @@
         <v>220</v>
       </c>
       <c r="O629">
-        <v>17629790</v>
+        <v>17311831</v>
       </c>
       <c r="P629" t="s">
         <v>224</v>
@@ -40504,7 +40504,7 @@
         <v>238</v>
       </c>
       <c r="R629" s="1">
-        <v>46304.44261625</v>
+        <v>46304.44295746527</v>
       </c>
       <c r="S629">
         <v>5</v>
@@ -40527,19 +40527,19 @@
     </row>
     <row r="630" spans="1:33">
       <c r="A630">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="B630" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C630" t="s">
         <v>141</v>
       </c>
       <c r="D630" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E630" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F630" t="s">
         <v>147</v>
@@ -40563,7 +40563,7 @@
         <v>220</v>
       </c>
       <c r="O630">
-        <v>17311831</v>
+        <v>17840993</v>
       </c>
       <c r="P630" t="s">
         <v>224</v>
@@ -40572,7 +40572,7 @@
         <v>238</v>
       </c>
       <c r="R630" s="1">
-        <v>46304.44295746527</v>
+        <v>46304.44295855324</v>
       </c>
       <c r="S630">
         <v>5</v>
@@ -40595,10 +40595,10 @@
     </row>
     <row r="631" spans="1:33">
       <c r="A631">
-        <v>4064</v>
+        <v>4917</v>
       </c>
       <c r="B631" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C631" t="s">
         <v>141</v>
@@ -40607,7 +40607,7 @@
         <v>144</v>
       </c>
       <c r="E631" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F631" t="s">
         <v>147</v>
@@ -40631,7 +40631,7 @@
         <v>220</v>
       </c>
       <c r="O631">
-        <v>17840993</v>
+        <v>17629800</v>
       </c>
       <c r="P631" t="s">
         <v>224</v>
@@ -40640,7 +40640,7 @@
         <v>238</v>
       </c>
       <c r="R631" s="1">
-        <v>46304.44295855324</v>
+        <v>46304.4429590162</v>
       </c>
       <c r="S631">
         <v>5</v>
@@ -40663,16 +40663,16 @@
     </row>
     <row r="632" spans="1:33">
       <c r="A632">
-        <v>4917</v>
+        <v>4059</v>
       </c>
       <c r="B632" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C632" t="s">
         <v>141</v>
       </c>
       <c r="D632" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E632" t="s">
         <v>147</v>
@@ -40681,7 +40681,7 @@
         <v>147</v>
       </c>
       <c r="G632">
-        <v>9197</v>
+        <v>9191</v>
       </c>
       <c r="H632">
         <v>0</v>
@@ -40690,7 +40690,7 @@
         <v>160</v>
       </c>
       <c r="J632" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="L632" s="1">
         <v>46304</v>
@@ -40699,7 +40699,7 @@
         <v>220</v>
       </c>
       <c r="O632">
-        <v>17629800</v>
+        <v>17311801</v>
       </c>
       <c r="P632" t="s">
         <v>224</v>
@@ -40708,7 +40708,7 @@
         <v>238</v>
       </c>
       <c r="R632" s="1">
-        <v>46304.4429590162</v>
+        <v>46304.45204290509</v>
       </c>
       <c r="S632">
         <v>5</v>
@@ -40749,7 +40749,7 @@
         <v>147</v>
       </c>
       <c r="G633">
-        <v>9191</v>
+        <v>9192</v>
       </c>
       <c r="H633">
         <v>0</v>
@@ -40758,7 +40758,7 @@
         <v>160</v>
       </c>
       <c r="J633" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L633" s="1">
         <v>46304</v>
@@ -40767,7 +40767,7 @@
         <v>220</v>
       </c>
       <c r="O633">
-        <v>17311801</v>
+        <v>17311811</v>
       </c>
       <c r="P633" t="s">
         <v>224</v>
@@ -40776,7 +40776,7 @@
         <v>238</v>
       </c>
       <c r="R633" s="1">
-        <v>46304.45204290509</v>
+        <v>46304.45233193287</v>
       </c>
       <c r="S633">
         <v>5</v>
@@ -40799,84 +40799,90 @@
     </row>
     <row r="634" spans="1:33">
       <c r="A634">
-        <v>4059</v>
+        <v>3080</v>
       </c>
       <c r="B634" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C634" t="s">
         <v>141</v>
       </c>
       <c r="D634" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E634" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F634" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G634">
-        <v>9192</v>
+        <v>10252</v>
       </c>
       <c r="H634">
-        <v>0</v>
+        <v>10236</v>
       </c>
       <c r="I634" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J634" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="L634" s="1">
-        <v>46304</v>
+        <v>46300</v>
+      </c>
+      <c r="M634" t="s">
+        <v>215</v>
       </c>
       <c r="N634" t="s">
         <v>220</v>
       </c>
       <c r="O634">
-        <v>17311811</v>
+        <v>16989327</v>
       </c>
       <c r="P634" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="Q634" t="s">
         <v>238</v>
       </c>
       <c r="R634" s="1">
-        <v>46304.45233193287</v>
+        <v>46300.36809652777</v>
       </c>
       <c r="S634">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T634" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="U634" t="s">
         <v>244</v>
       </c>
+      <c r="W634" t="s">
+        <v>250</v>
+      </c>
       <c r="AA634">
         <v>0</v>
       </c>
       <c r="AB634" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="AG634" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="635" spans="1:33">
       <c r="A635">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="B635" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C635" t="s">
         <v>141</v>
       </c>
       <c r="D635" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E635" t="s">
         <v>149</v>
@@ -40900,13 +40906,13 @@
         <v>46300</v>
       </c>
       <c r="M635" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N635" t="s">
         <v>220</v>
       </c>
       <c r="O635">
-        <v>16989327</v>
+        <v>16989851</v>
       </c>
       <c r="P635" t="s">
         <v>231</v>
@@ -40915,7 +40921,7 @@
         <v>238</v>
       </c>
       <c r="R635" s="1">
-        <v>46300.36809652777</v>
+        <v>46300.36809695602</v>
       </c>
       <c r="S635">
         <v>9</v>
@@ -40927,7 +40933,7 @@
         <v>244</v>
       </c>
       <c r="W635" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA635">
         <v>0</v>
@@ -40941,10 +40947,10 @@
     </row>
     <row r="636" spans="1:33">
       <c r="A636">
-        <v>3081</v>
+        <v>3155</v>
       </c>
       <c r="B636" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="C636" t="s">
         <v>141</v>
@@ -40974,13 +40980,13 @@
         <v>46300</v>
       </c>
       <c r="M636" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N636" t="s">
         <v>220</v>
       </c>
       <c r="O636">
-        <v>16989851</v>
+        <v>17234324</v>
       </c>
       <c r="P636" t="s">
         <v>231</v>
@@ -40989,7 +40995,7 @@
         <v>238</v>
       </c>
       <c r="R636" s="1">
-        <v>46300.36809695602</v>
+        <v>46300.36809767361</v>
       </c>
       <c r="S636">
         <v>9</v>
@@ -41001,7 +41007,7 @@
         <v>244</v>
       </c>
       <c r="W636" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA636">
         <v>0</v>
@@ -41015,16 +41021,16 @@
     </row>
     <row r="637" spans="1:33">
       <c r="A637">
-        <v>3155</v>
+        <v>3192</v>
       </c>
       <c r="B637" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C637" t="s">
         <v>141</v>
       </c>
       <c r="D637" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E637" t="s">
         <v>149</v>
@@ -41048,22 +41054,22 @@
         <v>46300</v>
       </c>
       <c r="M637" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N637" t="s">
         <v>220</v>
       </c>
       <c r="O637">
-        <v>17234324</v>
+        <v>17392714</v>
       </c>
       <c r="P637" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q637" t="s">
         <v>238</v>
       </c>
       <c r="R637" s="1">
-        <v>46300.36809767361</v>
+        <v>46300.368098125</v>
       </c>
       <c r="S637">
         <v>9</v>
@@ -41075,7 +41081,7 @@
         <v>244</v>
       </c>
       <c r="W637" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA637">
         <v>0</v>
@@ -41089,16 +41095,16 @@
     </row>
     <row r="638" spans="1:33">
       <c r="A638">
-        <v>3192</v>
+        <v>3332</v>
       </c>
       <c r="B638" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="C638" t="s">
         <v>141</v>
       </c>
       <c r="D638" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E638" t="s">
         <v>149</v>
@@ -41122,13 +41128,13 @@
         <v>46300</v>
       </c>
       <c r="M638" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N638" t="s">
         <v>220</v>
       </c>
       <c r="O638">
-        <v>17392714</v>
+        <v>17073172</v>
       </c>
       <c r="P638" t="s">
         <v>232</v>
@@ -41137,7 +41143,7 @@
         <v>238</v>
       </c>
       <c r="R638" s="1">
-        <v>46300.368098125</v>
+        <v>46300.36809855324</v>
       </c>
       <c r="S638">
         <v>9</v>
@@ -41149,7 +41155,7 @@
         <v>244</v>
       </c>
       <c r="W638" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA638">
         <v>0</v>
@@ -41163,10 +41169,10 @@
     </row>
     <row r="639" spans="1:33">
       <c r="A639">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="B639" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C639" t="s">
         <v>141</v>
@@ -41196,13 +41202,13 @@
         <v>46300</v>
       </c>
       <c r="M639" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N639" t="s">
         <v>220</v>
       </c>
       <c r="O639">
-        <v>17073172</v>
+        <v>17685193</v>
       </c>
       <c r="P639" t="s">
         <v>232</v>
@@ -41211,7 +41217,7 @@
         <v>238</v>
       </c>
       <c r="R639" s="1">
-        <v>46300.36809855324</v>
+        <v>46300.36809900463</v>
       </c>
       <c r="S639">
         <v>9</v>
@@ -41223,7 +41229,7 @@
         <v>244</v>
       </c>
       <c r="W639" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA639">
         <v>0</v>
@@ -41237,10 +41243,10 @@
     </row>
     <row r="640" spans="1:33">
       <c r="A640">
-        <v>3333</v>
+        <v>3453</v>
       </c>
       <c r="B640" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C640" t="s">
         <v>141</v>
@@ -41270,22 +41276,22 @@
         <v>46300</v>
       </c>
       <c r="M640" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N640" t="s">
         <v>220</v>
       </c>
       <c r="O640">
-        <v>17685193</v>
+        <v>17668118</v>
       </c>
       <c r="P640" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q640" t="s">
         <v>238</v>
       </c>
       <c r="R640" s="1">
-        <v>46300.36809900463</v>
+        <v>46300.3680994676</v>
       </c>
       <c r="S640">
         <v>9</v>
@@ -41297,7 +41303,7 @@
         <v>244</v>
       </c>
       <c r="W640" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA640">
         <v>0</v>
@@ -41311,10 +41317,10 @@
     </row>
     <row r="641" spans="1:33">
       <c r="A641">
-        <v>3453</v>
+        <v>3637</v>
       </c>
       <c r="B641" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C641" t="s">
         <v>141</v>
@@ -41344,13 +41350,13 @@
         <v>46300</v>
       </c>
       <c r="M641" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N641" t="s">
         <v>220</v>
       </c>
       <c r="O641">
-        <v>17668118</v>
+        <v>17890048</v>
       </c>
       <c r="P641" t="s">
         <v>231</v>
@@ -41359,7 +41365,7 @@
         <v>238</v>
       </c>
       <c r="R641" s="1">
-        <v>46300.3680994676</v>
+        <v>46300.3681</v>
       </c>
       <c r="S641">
         <v>9</v>
@@ -41371,7 +41377,7 @@
         <v>244</v>
       </c>
       <c r="W641" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA641">
         <v>0</v>
@@ -41385,10 +41391,10 @@
     </row>
     <row r="642" spans="1:33">
       <c r="A642">
-        <v>3637</v>
+        <v>3698</v>
       </c>
       <c r="B642" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C642" t="s">
         <v>141</v>
@@ -41418,13 +41424,13 @@
         <v>46300</v>
       </c>
       <c r="M642" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N642" t="s">
         <v>220</v>
       </c>
       <c r="O642">
-        <v>17890048</v>
+        <v>17448771</v>
       </c>
       <c r="P642" t="s">
         <v>231</v>
@@ -41433,7 +41439,7 @@
         <v>238</v>
       </c>
       <c r="R642" s="1">
-        <v>46300.3681</v>
+        <v>46300.36810055556</v>
       </c>
       <c r="S642">
         <v>9</v>
@@ -41445,7 +41451,7 @@
         <v>244</v>
       </c>
       <c r="W642" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA642">
         <v>0</v>
@@ -41459,16 +41465,16 @@
     </row>
     <row r="643" spans="1:33">
       <c r="A643">
-        <v>3698</v>
+        <v>4378</v>
       </c>
       <c r="B643" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C643" t="s">
         <v>141</v>
       </c>
       <c r="D643" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E643" t="s">
         <v>149</v>
@@ -41492,22 +41498,22 @@
         <v>46300</v>
       </c>
       <c r="M643" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N643" t="s">
         <v>220</v>
       </c>
       <c r="O643">
-        <v>17448771</v>
+        <v>17865435</v>
       </c>
       <c r="P643" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q643" t="s">
         <v>238</v>
       </c>
       <c r="R643" s="1">
-        <v>46300.36810055556</v>
+        <v>46300.36935405093</v>
       </c>
       <c r="S643">
         <v>9</v>
@@ -41519,7 +41525,7 @@
         <v>244</v>
       </c>
       <c r="W643" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA643">
         <v>0</v>
@@ -41533,10 +41539,10 @@
     </row>
     <row r="644" spans="1:33">
       <c r="A644">
-        <v>4378</v>
+        <v>4449</v>
       </c>
       <c r="B644" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C644" t="s">
         <v>141</v>
@@ -41566,22 +41572,22 @@
         <v>46300</v>
       </c>
       <c r="M644" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N644" t="s">
         <v>220</v>
       </c>
       <c r="O644">
-        <v>17865435</v>
+        <v>17223578</v>
       </c>
       <c r="P644" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q644" t="s">
         <v>238</v>
       </c>
       <c r="R644" s="1">
-        <v>46300.36935405093</v>
+        <v>46300.36935451389</v>
       </c>
       <c r="S644">
         <v>9</v>
@@ -41593,7 +41599,7 @@
         <v>244</v>
       </c>
       <c r="W644" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA644">
         <v>0</v>
@@ -41607,16 +41613,16 @@
     </row>
     <row r="645" spans="1:33">
       <c r="A645">
-        <v>4449</v>
+        <v>4475</v>
       </c>
       <c r="B645" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C645" t="s">
         <v>141</v>
       </c>
       <c r="D645" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E645" t="s">
         <v>149</v>
@@ -41640,22 +41646,22 @@
         <v>46300</v>
       </c>
       <c r="M645" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N645" t="s">
         <v>220</v>
       </c>
       <c r="O645">
-        <v>17223578</v>
+        <v>17293186</v>
       </c>
       <c r="P645" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q645" t="s">
         <v>238</v>
       </c>
       <c r="R645" s="1">
-        <v>46300.36935451389</v>
+        <v>46300.369355</v>
       </c>
       <c r="S645">
         <v>9</v>
@@ -41667,7 +41673,7 @@
         <v>244</v>
       </c>
       <c r="W645" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA645">
         <v>0</v>
@@ -41681,10 +41687,10 @@
     </row>
     <row r="646" spans="1:33">
       <c r="A646">
-        <v>4475</v>
+        <v>4661</v>
       </c>
       <c r="B646" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="C646" t="s">
         <v>141</v>
@@ -41714,13 +41720,13 @@
         <v>46300</v>
       </c>
       <c r="M646" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N646" t="s">
         <v>220</v>
       </c>
       <c r="O646">
-        <v>17293186</v>
+        <v>17710377</v>
       </c>
       <c r="P646" t="s">
         <v>232</v>
@@ -41729,7 +41735,7 @@
         <v>238</v>
       </c>
       <c r="R646" s="1">
-        <v>46300.369355</v>
+        <v>46300.3693555787</v>
       </c>
       <c r="S646">
         <v>9</v>
@@ -41741,7 +41747,7 @@
         <v>244</v>
       </c>
       <c r="W646" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA646">
         <v>0</v>
@@ -41755,16 +41761,16 @@
     </row>
     <row r="647" spans="1:33">
       <c r="A647">
-        <v>4661</v>
+        <v>5005</v>
       </c>
       <c r="B647" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C647" t="s">
         <v>141</v>
       </c>
       <c r="D647" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E647" t="s">
         <v>149</v>
@@ -41788,13 +41794,13 @@
         <v>46300</v>
       </c>
       <c r="M647" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N647" t="s">
         <v>220</v>
       </c>
       <c r="O647">
-        <v>17710377</v>
+        <v>17381507</v>
       </c>
       <c r="P647" t="s">
         <v>232</v>
@@ -41803,7 +41809,7 @@
         <v>238</v>
       </c>
       <c r="R647" s="1">
-        <v>46300.3693555787</v>
+        <v>46300.36935664352</v>
       </c>
       <c r="S647">
         <v>9</v>
@@ -41815,7 +41821,7 @@
         <v>244</v>
       </c>
       <c r="W647" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA647">
         <v>0</v>
@@ -41829,10 +41835,10 @@
     </row>
     <row r="648" spans="1:33">
       <c r="A648">
-        <v>5005</v>
+        <v>5006</v>
       </c>
       <c r="B648" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="C648" t="s">
         <v>141</v>
@@ -41844,7 +41850,7 @@
         <v>149</v>
       </c>
       <c r="F648" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G648">
         <v>10252</v>
@@ -41862,13 +41868,13 @@
         <v>46300</v>
       </c>
       <c r="M648" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N648" t="s">
         <v>220</v>
       </c>
       <c r="O648">
-        <v>17381507</v>
+        <v>17229281</v>
       </c>
       <c r="P648" t="s">
         <v>232</v>
@@ -41877,7 +41883,7 @@
         <v>238</v>
       </c>
       <c r="R648" s="1">
-        <v>46300.36935664352</v>
+        <v>46300.36936003473</v>
       </c>
       <c r="S648">
         <v>9</v>
@@ -41889,7 +41895,7 @@
         <v>244</v>
       </c>
       <c r="W648" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA648">
         <v>0</v>
@@ -41903,10 +41909,10 @@
     </row>
     <row r="649" spans="1:33">
       <c r="A649">
-        <v>5006</v>
+        <v>5007</v>
       </c>
       <c r="B649" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C649" t="s">
         <v>141</v>
@@ -41918,7 +41924,7 @@
         <v>149</v>
       </c>
       <c r="F649" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G649">
         <v>10252</v>
@@ -41936,13 +41942,13 @@
         <v>46300</v>
       </c>
       <c r="M649" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N649" t="s">
         <v>220</v>
       </c>
       <c r="O649">
-        <v>17229281</v>
+        <v>17479382</v>
       </c>
       <c r="P649" t="s">
         <v>232</v>
@@ -41951,7 +41957,7 @@
         <v>238</v>
       </c>
       <c r="R649" s="1">
-        <v>46300.36936003473</v>
+        <v>46300.36936210648</v>
       </c>
       <c r="S649">
         <v>9</v>
@@ -41963,7 +41969,7 @@
         <v>244</v>
       </c>
       <c r="W649" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA649">
         <v>0</v>
@@ -41977,16 +41983,16 @@
     </row>
     <row r="650" spans="1:33">
       <c r="A650">
-        <v>5007</v>
+        <v>3080</v>
       </c>
       <c r="B650" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C650" t="s">
         <v>141</v>
       </c>
       <c r="D650" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E650" t="s">
         <v>149</v>
@@ -41995,40 +42001,37 @@
         <v>151</v>
       </c>
       <c r="G650">
-        <v>10252</v>
+        <v>10293</v>
       </c>
       <c r="H650">
-        <v>10236</v>
+        <v>0</v>
       </c>
       <c r="I650" t="s">
         <v>161</v>
       </c>
       <c r="J650" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="L650" s="1">
-        <v>46300</v>
-      </c>
-      <c r="M650" t="s">
-        <v>216</v>
+        <v>46309</v>
       </c>
       <c r="N650" t="s">
         <v>220</v>
       </c>
       <c r="O650">
-        <v>17479382</v>
+        <v>16989358</v>
       </c>
       <c r="P650" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q650" t="s">
         <v>238</v>
       </c>
       <c r="R650" s="1">
-        <v>46300.36936210648</v>
+        <v>46309.4709946875</v>
       </c>
       <c r="S650">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T650" t="s">
         <v>241</v>
@@ -42036,25 +42039,22 @@
       <c r="U650" t="s">
         <v>244</v>
       </c>
-      <c r="W650" t="s">
-        <v>251</v>
-      </c>
       <c r="AA650">
         <v>0</v>
       </c>
       <c r="AB650" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="AG650" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="651" spans="1:33">
       <c r="A651">
-        <v>3080</v>
+        <v>3192</v>
       </c>
       <c r="B651" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C651" t="s">
         <v>141</v>
@@ -42087,16 +42087,16 @@
         <v>220</v>
       </c>
       <c r="O651">
-        <v>16989358</v>
+        <v>17392726</v>
       </c>
       <c r="P651" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q651" t="s">
         <v>238</v>
       </c>
       <c r="R651" s="1">
-        <v>46309.4709946875</v>
+        <v>46309.3839881713</v>
       </c>
       <c r="S651">
         <v>0</v>
@@ -42111,7 +42111,7 @@
         <v>0</v>
       </c>
       <c r="AB651" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG651" t="s">
         <v>262</v>
@@ -42119,10 +42119,10 @@
     </row>
     <row r="652" spans="1:33">
       <c r="A652">
-        <v>3192</v>
+        <v>3864</v>
       </c>
       <c r="B652" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C652" t="s">
         <v>141</v>
@@ -42155,16 +42155,16 @@
         <v>220</v>
       </c>
       <c r="O652">
-        <v>17392726</v>
+        <v>17363476</v>
       </c>
       <c r="P652" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q652" t="s">
         <v>238</v>
       </c>
       <c r="R652" s="1">
-        <v>46309.3839881713</v>
+        <v>46309.50643565972</v>
       </c>
       <c r="S652">
         <v>0</v>
@@ -42179,7 +42179,7 @@
         <v>0</v>
       </c>
       <c r="AB652" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="AG652" t="s">
         <v>262</v>
@@ -42187,10 +42187,10 @@
     </row>
     <row r="653" spans="1:33">
       <c r="A653">
-        <v>3864</v>
+        <v>4378</v>
       </c>
       <c r="B653" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C653" t="s">
         <v>141</v>
@@ -42223,16 +42223,16 @@
         <v>220</v>
       </c>
       <c r="O653">
-        <v>17363476</v>
+        <v>17865447</v>
       </c>
       <c r="P653" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q653" t="s">
         <v>238</v>
       </c>
       <c r="R653" s="1">
-        <v>46309.50643565972</v>
+        <v>46309.38398854167</v>
       </c>
       <c r="S653">
         <v>0</v>
@@ -42247,7 +42247,7 @@
         <v>0</v>
       </c>
       <c r="AB653" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="AG653" t="s">
         <v>262</v>
@@ -42255,10 +42255,10 @@
     </row>
     <row r="654" spans="1:33">
       <c r="A654">
-        <v>4378</v>
+        <v>4449</v>
       </c>
       <c r="B654" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C654" t="s">
         <v>141</v>
@@ -42291,16 +42291,16 @@
         <v>220</v>
       </c>
       <c r="O654">
-        <v>17865447</v>
+        <v>17223608</v>
       </c>
       <c r="P654" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q654" t="s">
         <v>238</v>
       </c>
       <c r="R654" s="1">
-        <v>46309.38398854167</v>
+        <v>46309.47099496528</v>
       </c>
       <c r="S654">
         <v>0</v>
@@ -42315,7 +42315,7 @@
         <v>0</v>
       </c>
       <c r="AB654" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG654" t="s">
         <v>262</v>
@@ -42323,16 +42323,16 @@
     </row>
     <row r="655" spans="1:33">
       <c r="A655">
-        <v>4449</v>
+        <v>4661</v>
       </c>
       <c r="B655" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C655" t="s">
         <v>141</v>
       </c>
       <c r="D655" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E655" t="s">
         <v>149</v>
@@ -42359,16 +42359,16 @@
         <v>220</v>
       </c>
       <c r="O655">
-        <v>17223608</v>
+        <v>17710387</v>
       </c>
       <c r="P655" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q655" t="s">
         <v>238</v>
       </c>
       <c r="R655" s="1">
-        <v>46309.47099496528</v>
+        <v>46309.38398908565</v>
       </c>
       <c r="S655">
         <v>0</v>
@@ -42383,7 +42383,7 @@
         <v>0</v>
       </c>
       <c r="AB655" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG655" t="s">
         <v>262</v>
@@ -42391,10 +42391,10 @@
     </row>
     <row r="656" spans="1:33">
       <c r="A656">
-        <v>4661</v>
+        <v>4786</v>
       </c>
       <c r="B656" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C656" t="s">
         <v>141</v>
@@ -42427,16 +42427,16 @@
         <v>220</v>
       </c>
       <c r="O656">
-        <v>17710387</v>
+        <v>17559737</v>
       </c>
       <c r="P656" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q656" t="s">
         <v>238</v>
       </c>
       <c r="R656" s="1">
-        <v>46309.38398908565</v>
+        <v>46309.47849606482</v>
       </c>
       <c r="S656">
         <v>0</v>
@@ -42451,7 +42451,7 @@
         <v>0</v>
       </c>
       <c r="AB656" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG656" t="s">
         <v>262</v>
@@ -42459,10 +42459,10 @@
     </row>
     <row r="657" spans="1:33">
       <c r="A657">
-        <v>4786</v>
+        <v>4787</v>
       </c>
       <c r="B657" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C657" t="s">
         <v>141</v>
@@ -42495,7 +42495,7 @@
         <v>220</v>
       </c>
       <c r="O657">
-        <v>17559737</v>
+        <v>17468461</v>
       </c>
       <c r="P657" t="s">
         <v>231</v>
@@ -42504,7 +42504,7 @@
         <v>238</v>
       </c>
       <c r="R657" s="1">
-        <v>46309.47849606482</v>
+        <v>46309.47849643519</v>
       </c>
       <c r="S657">
         <v>0</v>
@@ -42527,10 +42527,10 @@
     </row>
     <row r="658" spans="1:33">
       <c r="A658">
-        <v>4787</v>
+        <v>4862</v>
       </c>
       <c r="B658" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C658" t="s">
         <v>141</v>
@@ -42563,7 +42563,7 @@
         <v>220</v>
       </c>
       <c r="O658">
-        <v>17468461</v>
+        <v>17503979</v>
       </c>
       <c r="P658" t="s">
         <v>231</v>
@@ -42572,7 +42572,7 @@
         <v>238</v>
       </c>
       <c r="R658" s="1">
-        <v>46309.47849643519</v>
+        <v>46309.47849680555</v>
       </c>
       <c r="S658">
         <v>0</v>
@@ -42595,10 +42595,10 @@
     </row>
     <row r="659" spans="1:33">
       <c r="A659">
-        <v>4862</v>
+        <v>4926</v>
       </c>
       <c r="B659" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C659" t="s">
         <v>141</v>
@@ -42631,16 +42631,16 @@
         <v>220</v>
       </c>
       <c r="O659">
-        <v>17503979</v>
+        <v>17328268</v>
       </c>
       <c r="P659" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q659" t="s">
         <v>238</v>
       </c>
       <c r="R659" s="1">
-        <v>46309.47849680555</v>
+        <v>46309.38398954861</v>
       </c>
       <c r="S659">
         <v>0</v>
@@ -42655,7 +42655,7 @@
         <v>0</v>
       </c>
       <c r="AB659" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG659" t="s">
         <v>262</v>
@@ -42663,10 +42663,10 @@
     </row>
     <row r="660" spans="1:33">
       <c r="A660">
-        <v>4926</v>
+        <v>5008</v>
       </c>
       <c r="B660" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C660" t="s">
         <v>141</v>
@@ -42699,7 +42699,7 @@
         <v>220</v>
       </c>
       <c r="O660">
-        <v>17328268</v>
+        <v>17345977</v>
       </c>
       <c r="P660" t="s">
         <v>232</v>
@@ -42708,7 +42708,7 @@
         <v>238</v>
       </c>
       <c r="R660" s="1">
-        <v>46309.38398954861</v>
+        <v>46309.38398988426</v>
       </c>
       <c r="S660">
         <v>0</v>
@@ -42731,10 +42731,10 @@
     </row>
     <row r="661" spans="1:33">
       <c r="A661">
-        <v>5008</v>
+        <v>5021</v>
       </c>
       <c r="B661" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C661" t="s">
         <v>141</v>
@@ -42767,16 +42767,16 @@
         <v>220</v>
       </c>
       <c r="O661">
-        <v>17345977</v>
+        <v>17381713</v>
       </c>
       <c r="P661" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q661" t="s">
         <v>238</v>
       </c>
       <c r="R661" s="1">
-        <v>46309.38398988426</v>
+        <v>46309.47849715278</v>
       </c>
       <c r="S661">
         <v>0</v>
@@ -42791,7 +42791,7 @@
         <v>0</v>
       </c>
       <c r="AB661" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG661" t="s">
         <v>262</v>
@@ -42799,22 +42799,22 @@
     </row>
     <row r="662" spans="1:33">
       <c r="A662">
-        <v>5021</v>
+        <v>5064</v>
       </c>
       <c r="B662" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C662" t="s">
         <v>141</v>
       </c>
       <c r="D662" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E662" t="s">
         <v>149</v>
       </c>
       <c r="F662" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G662">
         <v>10293</v>
@@ -42835,16 +42835,16 @@
         <v>220</v>
       </c>
       <c r="O662">
-        <v>17381713</v>
+        <v>17097477</v>
       </c>
       <c r="P662" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q662" t="s">
         <v>238</v>
       </c>
       <c r="R662" s="1">
-        <v>46309.47849715278</v>
+        <v>46309.38399024306</v>
       </c>
       <c r="S662">
         <v>0</v>
@@ -42859,7 +42859,7 @@
         <v>0</v>
       </c>
       <c r="AB662" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG662" t="s">
         <v>262</v>
@@ -42867,16 +42867,16 @@
     </row>
     <row r="663" spans="1:33">
       <c r="A663">
-        <v>5064</v>
+        <v>5217</v>
       </c>
       <c r="B663" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C663" t="s">
         <v>141</v>
       </c>
       <c r="D663" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E663" t="s">
         <v>149</v>
@@ -42903,16 +42903,16 @@
         <v>220</v>
       </c>
       <c r="O663">
-        <v>17097477</v>
+        <v>17683382</v>
       </c>
       <c r="P663" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q663" t="s">
         <v>238</v>
       </c>
       <c r="R663" s="1">
-        <v>46309.38399024306</v>
+        <v>46309.47849747686</v>
       </c>
       <c r="S663">
         <v>0</v>
@@ -42927,7 +42927,7 @@
         <v>0</v>
       </c>
       <c r="AB663" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG663" t="s">
         <v>262</v>
@@ -42935,10 +42935,10 @@
     </row>
     <row r="664" spans="1:33">
       <c r="A664">
-        <v>5217</v>
+        <v>5384</v>
       </c>
       <c r="B664" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C664" t="s">
         <v>141</v>
@@ -42950,7 +42950,7 @@
         <v>149</v>
       </c>
       <c r="F664" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G664">
         <v>10293</v>
@@ -42971,16 +42971,16 @@
         <v>220</v>
       </c>
       <c r="O664">
-        <v>17683382</v>
+        <v>17765233</v>
       </c>
       <c r="P664" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q664" t="s">
         <v>238</v>
       </c>
       <c r="R664" s="1">
-        <v>46309.47849747686</v>
+        <v>46309.38399096065</v>
       </c>
       <c r="S664">
         <v>0</v>
@@ -42995,7 +42995,7 @@
         <v>0</v>
       </c>
       <c r="AB664" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG664" t="s">
         <v>262</v>
@@ -43003,16 +43003,16 @@
     </row>
     <row r="665" spans="1:33">
       <c r="A665">
-        <v>5384</v>
+        <v>5763</v>
       </c>
       <c r="B665" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C665" t="s">
         <v>141</v>
       </c>
       <c r="D665" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E665" t="s">
         <v>149</v>
@@ -43039,7 +43039,7 @@
         <v>220</v>
       </c>
       <c r="O665">
-        <v>17765233</v>
+        <v>17796808</v>
       </c>
       <c r="P665" t="s">
         <v>232</v>
@@ -43048,7 +43048,7 @@
         <v>238</v>
       </c>
       <c r="R665" s="1">
-        <v>46309.38399096065</v>
+        <v>46309.38399150463</v>
       </c>
       <c r="S665">
         <v>0</v>
@@ -43071,10 +43071,10 @@
     </row>
     <row r="666" spans="1:33">
       <c r="A666">
-        <v>5763</v>
+        <v>6565</v>
       </c>
       <c r="B666" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C666" t="s">
         <v>141</v>
@@ -43107,16 +43107,16 @@
         <v>220</v>
       </c>
       <c r="O666">
-        <v>17796808</v>
+        <v>17167493</v>
       </c>
       <c r="P666" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q666" t="s">
         <v>238</v>
       </c>
       <c r="R666" s="1">
-        <v>46309.38399150463</v>
+        <v>46309.47099542824</v>
       </c>
       <c r="S666">
         <v>0</v>
@@ -43131,7 +43131,7 @@
         <v>0</v>
       </c>
       <c r="AB666" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG666" t="s">
         <v>262</v>
@@ -43139,10 +43139,10 @@
     </row>
     <row r="667" spans="1:33">
       <c r="A667">
-        <v>6565</v>
+        <v>6982</v>
       </c>
       <c r="B667" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C667" t="s">
         <v>141</v>
@@ -43175,16 +43175,16 @@
         <v>220</v>
       </c>
       <c r="O667">
-        <v>17167493</v>
+        <v>18203766</v>
       </c>
       <c r="P667" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q667" t="s">
         <v>238</v>
       </c>
       <c r="R667" s="1">
-        <v>46309.47099542824</v>
+        <v>46309.38399181713</v>
       </c>
       <c r="S667">
         <v>0</v>
@@ -43199,7 +43199,7 @@
         <v>0</v>
       </c>
       <c r="AB667" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG667" t="s">
         <v>262</v>
@@ -43207,16 +43207,16 @@
     </row>
     <row r="668" spans="1:33">
       <c r="A668">
-        <v>6982</v>
+        <v>5005</v>
       </c>
       <c r="B668" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="C668" t="s">
         <v>141</v>
       </c>
       <c r="D668" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E668" t="s">
         <v>149</v>
@@ -43225,37 +43225,40 @@
         <v>151</v>
       </c>
       <c r="G668">
-        <v>10293</v>
+        <v>10322</v>
       </c>
       <c r="H668">
-        <v>0</v>
+        <v>10307</v>
       </c>
       <c r="I668" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="J668" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="L668" s="1">
-        <v>46309</v>
+        <v>46296</v>
+      </c>
+      <c r="M668" t="s">
+        <v>211</v>
       </c>
       <c r="N668" t="s">
         <v>220</v>
       </c>
       <c r="O668">
-        <v>18203766</v>
+        <v>17381562</v>
       </c>
       <c r="P668" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="Q668" t="s">
         <v>238</v>
       </c>
       <c r="R668" s="1">
-        <v>46309.38399181713</v>
+        <v>46296.44241663194</v>
       </c>
       <c r="S668">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T668" t="s">
         <v>241</v>
@@ -43263,28 +43266,31 @@
       <c r="U668" t="s">
         <v>244</v>
       </c>
+      <c r="W668" t="s">
+        <v>251</v>
+      </c>
       <c r="AA668">
         <v>0</v>
       </c>
       <c r="AB668" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="AG668" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="669" spans="1:33">
       <c r="A669">
-        <v>5005</v>
+        <v>3080</v>
       </c>
       <c r="B669" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="C669" t="s">
         <v>141</v>
       </c>
       <c r="D669" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E669" t="s">
         <v>149</v>
@@ -43293,7 +43299,7 @@
         <v>151</v>
       </c>
       <c r="G669">
-        <v>10322</v>
+        <v>10325</v>
       </c>
       <c r="H669">
         <v>10307</v>
@@ -43302,31 +43308,31 @@
         <v>155</v>
       </c>
       <c r="J669" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L669" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="M669" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="N669" t="s">
         <v>220</v>
       </c>
       <c r="O669">
-        <v>17381562</v>
+        <v>16989434</v>
       </c>
       <c r="P669" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q669" t="s">
         <v>238</v>
       </c>
       <c r="R669" s="1">
-        <v>46296.44241663194</v>
+        <v>46301.33944819444</v>
       </c>
       <c r="S669">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T669" t="s">
         <v>241</v>
@@ -43349,16 +43355,16 @@
     </row>
     <row r="670" spans="1:33">
       <c r="A670">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="B670" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C670" t="s">
         <v>141</v>
       </c>
       <c r="D670" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E670" t="s">
         <v>149</v>
@@ -43382,22 +43388,22 @@
         <v>46301</v>
       </c>
       <c r="M670" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N670" t="s">
         <v>220</v>
       </c>
       <c r="O670">
-        <v>16989434</v>
+        <v>16989980</v>
       </c>
       <c r="P670" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q670" t="s">
         <v>238</v>
       </c>
       <c r="R670" s="1">
-        <v>46301.33944819444</v>
+        <v>46301.33945127315</v>
       </c>
       <c r="S670">
         <v>8</v>
@@ -43409,7 +43415,7 @@
         <v>244</v>
       </c>
       <c r="W670" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA670">
         <v>0</v>
@@ -43423,10 +43429,10 @@
     </row>
     <row r="671" spans="1:33">
       <c r="A671">
-        <v>3081</v>
+        <v>3155</v>
       </c>
       <c r="B671" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="C671" t="s">
         <v>141</v>
@@ -43456,13 +43462,13 @@
         <v>46301</v>
       </c>
       <c r="M671" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N671" t="s">
         <v>220</v>
       </c>
       <c r="O671">
-        <v>16989980</v>
+        <v>17234334</v>
       </c>
       <c r="P671" t="s">
         <v>226</v>
@@ -43471,7 +43477,7 @@
         <v>238</v>
       </c>
       <c r="R671" s="1">
-        <v>46301.33945127315</v>
+        <v>46301.33945334491</v>
       </c>
       <c r="S671">
         <v>8</v>
@@ -43483,7 +43489,7 @@
         <v>244</v>
       </c>
       <c r="W671" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA671">
         <v>0</v>
@@ -43497,16 +43503,16 @@
     </row>
     <row r="672" spans="1:33">
       <c r="A672">
-        <v>3155</v>
+        <v>3192</v>
       </c>
       <c r="B672" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C672" t="s">
         <v>141</v>
       </c>
       <c r="D672" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E672" t="s">
         <v>149</v>
@@ -43530,22 +43536,22 @@
         <v>46301</v>
       </c>
       <c r="M672" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N672" t="s">
         <v>220</v>
       </c>
       <c r="O672">
-        <v>17234334</v>
+        <v>17392758</v>
       </c>
       <c r="P672" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q672" t="s">
         <v>238</v>
       </c>
       <c r="R672" s="1">
-        <v>46301.33945334491</v>
+        <v>46301.3394547338</v>
       </c>
       <c r="S672">
         <v>8</v>
@@ -43557,7 +43563,7 @@
         <v>244</v>
       </c>
       <c r="W672" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA672">
         <v>0</v>
@@ -43571,16 +43577,16 @@
     </row>
     <row r="673" spans="1:33">
       <c r="A673">
-        <v>3192</v>
+        <v>3332</v>
       </c>
       <c r="B673" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="C673" t="s">
         <v>141</v>
       </c>
       <c r="D673" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E673" t="s">
         <v>149</v>
@@ -43604,13 +43610,13 @@
         <v>46301</v>
       </c>
       <c r="M673" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N673" t="s">
         <v>220</v>
       </c>
       <c r="O673">
-        <v>17392758</v>
+        <v>17073282</v>
       </c>
       <c r="P673" t="s">
         <v>227</v>
@@ -43619,7 +43625,7 @@
         <v>238</v>
       </c>
       <c r="R673" s="1">
-        <v>46301.3394547338</v>
+        <v>46301.33945626157</v>
       </c>
       <c r="S673">
         <v>8</v>
@@ -43631,7 +43637,7 @@
         <v>244</v>
       </c>
       <c r="W673" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA673">
         <v>0</v>
@@ -43645,10 +43651,10 @@
     </row>
     <row r="674" spans="1:33">
       <c r="A674">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="B674" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C674" t="s">
         <v>141</v>
@@ -43678,13 +43684,13 @@
         <v>46301</v>
       </c>
       <c r="M674" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N674" t="s">
         <v>220</v>
       </c>
       <c r="O674">
-        <v>17073282</v>
+        <v>17685239</v>
       </c>
       <c r="P674" t="s">
         <v>227</v>
@@ -43693,7 +43699,7 @@
         <v>238</v>
       </c>
       <c r="R674" s="1">
-        <v>46301.33945626157</v>
+        <v>46301.33945729167</v>
       </c>
       <c r="S674">
         <v>8</v>
@@ -43705,7 +43711,7 @@
         <v>244</v>
       </c>
       <c r="W674" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA674">
         <v>0</v>
@@ -43719,10 +43725,10 @@
     </row>
     <row r="675" spans="1:33">
       <c r="A675">
-        <v>3333</v>
+        <v>3453</v>
       </c>
       <c r="B675" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C675" t="s">
         <v>141</v>
@@ -43752,22 +43758,22 @@
         <v>46301</v>
       </c>
       <c r="M675" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N675" t="s">
         <v>220</v>
       </c>
       <c r="O675">
-        <v>17685239</v>
+        <v>17668128</v>
       </c>
       <c r="P675" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q675" t="s">
         <v>238</v>
       </c>
       <c r="R675" s="1">
-        <v>46301.33945729167</v>
+        <v>46301.33945819444</v>
       </c>
       <c r="S675">
         <v>8</v>
@@ -43779,7 +43785,7 @@
         <v>244</v>
       </c>
       <c r="W675" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA675">
         <v>0</v>
@@ -43793,10 +43799,10 @@
     </row>
     <row r="676" spans="1:33">
       <c r="A676">
-        <v>3453</v>
+        <v>3637</v>
       </c>
       <c r="B676" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C676" t="s">
         <v>141</v>
@@ -43826,13 +43832,13 @@
         <v>46301</v>
       </c>
       <c r="M676" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N676" t="s">
         <v>220</v>
       </c>
       <c r="O676">
-        <v>17668128</v>
+        <v>17890058</v>
       </c>
       <c r="P676" t="s">
         <v>226</v>
@@ -43841,7 +43847,7 @@
         <v>238</v>
       </c>
       <c r="R676" s="1">
-        <v>46301.33945819444</v>
+        <v>46301.33945935185</v>
       </c>
       <c r="S676">
         <v>8</v>
@@ -43853,7 +43859,7 @@
         <v>244</v>
       </c>
       <c r="W676" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA676">
         <v>0</v>
@@ -43867,10 +43873,10 @@
     </row>
     <row r="677" spans="1:33">
       <c r="A677">
-        <v>3637</v>
+        <v>3698</v>
       </c>
       <c r="B677" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C677" t="s">
         <v>141</v>
@@ -43900,13 +43906,13 @@
         <v>46301</v>
       </c>
       <c r="M677" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N677" t="s">
         <v>220</v>
       </c>
       <c r="O677">
-        <v>17890058</v>
+        <v>17448781</v>
       </c>
       <c r="P677" t="s">
         <v>226</v>
@@ -43915,7 +43921,7 @@
         <v>238</v>
       </c>
       <c r="R677" s="1">
-        <v>46301.33945935185</v>
+        <v>46301.33946129629</v>
       </c>
       <c r="S677">
         <v>8</v>
@@ -43927,7 +43933,7 @@
         <v>244</v>
       </c>
       <c r="W677" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA677">
         <v>0</v>
@@ -43941,16 +43947,16 @@
     </row>
     <row r="678" spans="1:33">
       <c r="A678">
-        <v>3698</v>
+        <v>4378</v>
       </c>
       <c r="B678" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C678" t="s">
         <v>141</v>
       </c>
       <c r="D678" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E678" t="s">
         <v>149</v>
@@ -43974,22 +43980,22 @@
         <v>46301</v>
       </c>
       <c r="M678" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N678" t="s">
         <v>220</v>
       </c>
       <c r="O678">
-        <v>17448781</v>
+        <v>17865479</v>
       </c>
       <c r="P678" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q678" t="s">
         <v>238</v>
       </c>
       <c r="R678" s="1">
-        <v>46301.33946129629</v>
+        <v>46301.33946422454</v>
       </c>
       <c r="S678">
         <v>8</v>
@@ -44001,7 +44007,7 @@
         <v>244</v>
       </c>
       <c r="W678" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA678">
         <v>0</v>
@@ -44015,10 +44021,10 @@
     </row>
     <row r="679" spans="1:33">
       <c r="A679">
-        <v>4378</v>
+        <v>4449</v>
       </c>
       <c r="B679" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C679" t="s">
         <v>141</v>
@@ -44048,13 +44054,13 @@
         <v>46301</v>
       </c>
       <c r="M679" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N679" t="s">
         <v>220</v>
       </c>
       <c r="O679">
-        <v>17865479</v>
+        <v>17223694</v>
       </c>
       <c r="P679" t="s">
         <v>227</v>
@@ -44063,7 +44069,7 @@
         <v>238</v>
       </c>
       <c r="R679" s="1">
-        <v>46301.33946422454</v>
+        <v>46301.33946770833</v>
       </c>
       <c r="S679">
         <v>8</v>
@@ -44075,7 +44081,7 @@
         <v>244</v>
       </c>
       <c r="W679" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA679">
         <v>0</v>
@@ -44089,16 +44095,16 @@
     </row>
     <row r="680" spans="1:33">
       <c r="A680">
-        <v>4449</v>
+        <v>4475</v>
       </c>
       <c r="B680" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C680" t="s">
         <v>141</v>
       </c>
       <c r="D680" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E680" t="s">
         <v>149</v>
@@ -44122,13 +44128,13 @@
         <v>46301</v>
       </c>
       <c r="M680" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N680" t="s">
         <v>220</v>
       </c>
       <c r="O680">
-        <v>17223694</v>
+        <v>17293228</v>
       </c>
       <c r="P680" t="s">
         <v>227</v>
@@ -44137,7 +44143,7 @@
         <v>238</v>
       </c>
       <c r="R680" s="1">
-        <v>46301.33946770833</v>
+        <v>46301.33947332176</v>
       </c>
       <c r="S680">
         <v>8</v>
@@ -44149,7 +44155,7 @@
         <v>244</v>
       </c>
       <c r="W680" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA680">
         <v>0</v>
@@ -44163,10 +44169,10 @@
     </row>
     <row r="681" spans="1:33">
       <c r="A681">
-        <v>4475</v>
+        <v>4661</v>
       </c>
       <c r="B681" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="C681" t="s">
         <v>141</v>
@@ -44196,13 +44202,13 @@
         <v>46301</v>
       </c>
       <c r="M681" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N681" t="s">
         <v>220</v>
       </c>
       <c r="O681">
-        <v>17293228</v>
+        <v>17710417</v>
       </c>
       <c r="P681" t="s">
         <v>227</v>
@@ -44211,7 +44217,7 @@
         <v>238</v>
       </c>
       <c r="R681" s="1">
-        <v>46301.33947332176</v>
+        <v>46301.33947644676</v>
       </c>
       <c r="S681">
         <v>8</v>
@@ -44223,7 +44229,7 @@
         <v>244</v>
       </c>
       <c r="W681" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA681">
         <v>0</v>
@@ -44237,16 +44243,16 @@
     </row>
     <row r="682" spans="1:33">
       <c r="A682">
-        <v>4661</v>
+        <v>5005</v>
       </c>
       <c r="B682" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C682" t="s">
         <v>141</v>
       </c>
       <c r="D682" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E682" t="s">
         <v>149</v>
@@ -44270,22 +44276,22 @@
         <v>46301</v>
       </c>
       <c r="M682" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N682" t="s">
         <v>220</v>
       </c>
       <c r="O682">
-        <v>17710417</v>
+        <v>17381572</v>
       </c>
       <c r="P682" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q682" t="s">
         <v>238</v>
       </c>
       <c r="R682" s="1">
-        <v>46301.33947644676</v>
+        <v>46301.33947908565</v>
       </c>
       <c r="S682">
         <v>8</v>
@@ -44297,7 +44303,7 @@
         <v>244</v>
       </c>
       <c r="W682" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA682">
         <v>0</v>
@@ -44311,10 +44317,10 @@
     </row>
     <row r="683" spans="1:33">
       <c r="A683">
-        <v>5005</v>
+        <v>3081</v>
       </c>
       <c r="B683" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C683" t="s">
         <v>141</v>
@@ -44329,19 +44335,19 @@
         <v>151</v>
       </c>
       <c r="G683">
-        <v>10325</v>
+        <v>10372</v>
       </c>
       <c r="H683">
-        <v>10307</v>
+        <v>0</v>
       </c>
       <c r="I683" t="s">
         <v>155</v>
       </c>
       <c r="J683" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="L683" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="M683" t="s">
         <v>217</v>
@@ -44350,7 +44356,7 @@
         <v>220</v>
       </c>
       <c r="O683">
-        <v>17381572</v>
+        <v>16990030</v>
       </c>
       <c r="P683" t="s">
         <v>226</v>
@@ -44359,10 +44365,10 @@
         <v>238</v>
       </c>
       <c r="R683" s="1">
-        <v>46301.33947908565</v>
+        <v>46308.55870003472</v>
       </c>
       <c r="S683">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T683" t="s">
         <v>241</v>
@@ -44380,15 +44386,15 @@
         <v>260</v>
       </c>
       <c r="AG683" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="684" spans="1:33">
       <c r="A684">
-        <v>3081</v>
+        <v>3155</v>
       </c>
       <c r="B684" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="C684" t="s">
         <v>141</v>
@@ -44418,13 +44424,13 @@
         <v>46303</v>
       </c>
       <c r="M684" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N684" t="s">
         <v>220</v>
       </c>
       <c r="O684">
-        <v>16990030</v>
+        <v>17234354</v>
       </c>
       <c r="P684" t="s">
         <v>226</v>
@@ -44433,7 +44439,7 @@
         <v>238</v>
       </c>
       <c r="R684" s="1">
-        <v>46308.55870003472</v>
+        <v>46308.55870027778</v>
       </c>
       <c r="S684">
         <v>6</v>
@@ -44445,7 +44451,7 @@
         <v>244</v>
       </c>
       <c r="W684" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA684">
         <v>0</v>
@@ -44459,10 +44465,10 @@
     </row>
     <row r="685" spans="1:33">
       <c r="A685">
-        <v>3155</v>
+        <v>3332</v>
       </c>
       <c r="B685" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C685" t="s">
         <v>141</v>
@@ -44492,22 +44498,22 @@
         <v>46303</v>
       </c>
       <c r="M685" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N685" t="s">
         <v>220</v>
       </c>
       <c r="O685">
-        <v>17234354</v>
+        <v>17073309</v>
       </c>
       <c r="P685" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q685" t="s">
         <v>238</v>
       </c>
       <c r="R685" s="1">
-        <v>46308.55870027778</v>
+        <v>46308.47171083334</v>
       </c>
       <c r="S685">
         <v>6</v>
@@ -44519,7 +44525,7 @@
         <v>244</v>
       </c>
       <c r="W685" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA685">
         <v>0</v>
@@ -44533,10 +44539,10 @@
     </row>
     <row r="686" spans="1:33">
       <c r="A686">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="B686" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C686" t="s">
         <v>141</v>
@@ -44566,13 +44572,13 @@
         <v>46303</v>
       </c>
       <c r="M686" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N686" t="s">
         <v>220</v>
       </c>
       <c r="O686">
-        <v>17073309</v>
+        <v>17685259</v>
       </c>
       <c r="P686" t="s">
         <v>227</v>
@@ -44581,7 +44587,7 @@
         <v>238</v>
       </c>
       <c r="R686" s="1">
-        <v>46308.47171083334</v>
+        <v>46308.55993447917</v>
       </c>
       <c r="S686">
         <v>6</v>
@@ -44593,7 +44599,7 @@
         <v>244</v>
       </c>
       <c r="W686" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA686">
         <v>0</v>
@@ -44607,10 +44613,10 @@
     </row>
     <row r="687" spans="1:33">
       <c r="A687">
-        <v>3333</v>
+        <v>3453</v>
       </c>
       <c r="B687" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C687" t="s">
         <v>141</v>
@@ -44640,22 +44646,22 @@
         <v>46303</v>
       </c>
       <c r="M687" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N687" t="s">
         <v>220</v>
       </c>
       <c r="O687">
-        <v>17685259</v>
+        <v>17668148</v>
       </c>
       <c r="P687" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q687" t="s">
         <v>238</v>
       </c>
       <c r="R687" s="1">
-        <v>46308.55993447917</v>
+        <v>46308.57203359954</v>
       </c>
       <c r="S687">
         <v>6</v>
@@ -44667,7 +44673,7 @@
         <v>244</v>
       </c>
       <c r="W687" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA687">
         <v>0</v>
@@ -44681,10 +44687,10 @@
     </row>
     <row r="688" spans="1:33">
       <c r="A688">
-        <v>3453</v>
+        <v>3637</v>
       </c>
       <c r="B688" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C688" t="s">
         <v>141</v>
@@ -44714,13 +44720,13 @@
         <v>46303</v>
       </c>
       <c r="M688" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N688" t="s">
         <v>220</v>
       </c>
       <c r="O688">
-        <v>17668148</v>
+        <v>17890078</v>
       </c>
       <c r="P688" t="s">
         <v>226</v>
@@ -44729,7 +44735,7 @@
         <v>238</v>
       </c>
       <c r="R688" s="1">
-        <v>46308.57203359954</v>
+        <v>46308.55870060185</v>
       </c>
       <c r="S688">
         <v>6</v>
@@ -44741,7 +44747,7 @@
         <v>244</v>
       </c>
       <c r="W688" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA688">
         <v>0</v>
@@ -44755,10 +44761,10 @@
     </row>
     <row r="689" spans="1:33">
       <c r="A689">
-        <v>3637</v>
+        <v>3698</v>
       </c>
       <c r="B689" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C689" t="s">
         <v>141</v>
@@ -44788,13 +44794,13 @@
         <v>46303</v>
       </c>
       <c r="M689" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N689" t="s">
         <v>220</v>
       </c>
       <c r="O689">
-        <v>17890078</v>
+        <v>17448801</v>
       </c>
       <c r="P689" t="s">
         <v>226</v>
@@ -44803,7 +44809,7 @@
         <v>238</v>
       </c>
       <c r="R689" s="1">
-        <v>46308.55870060185</v>
+        <v>46308.55870101852</v>
       </c>
       <c r="S689">
         <v>6</v>
@@ -44815,7 +44821,7 @@
         <v>244</v>
       </c>
       <c r="W689" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA689">
         <v>0</v>
@@ -44829,16 +44835,16 @@
     </row>
     <row r="690" spans="1:33">
       <c r="A690">
-        <v>3698</v>
+        <v>4475</v>
       </c>
       <c r="B690" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C690" t="s">
         <v>141</v>
       </c>
       <c r="D690" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E690" t="s">
         <v>149</v>
@@ -44862,22 +44868,22 @@
         <v>46303</v>
       </c>
       <c r="M690" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N690" t="s">
         <v>220</v>
       </c>
       <c r="O690">
-        <v>17448801</v>
+        <v>17293248</v>
       </c>
       <c r="P690" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q690" t="s">
         <v>238</v>
       </c>
       <c r="R690" s="1">
-        <v>46308.55870101852</v>
+        <v>46308.38688019676</v>
       </c>
       <c r="S690">
         <v>6</v>
@@ -44889,7 +44895,7 @@
         <v>244</v>
       </c>
       <c r="W690" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA690">
         <v>0</v>
@@ -44903,16 +44909,16 @@
     </row>
     <row r="691" spans="1:33">
       <c r="A691">
-        <v>4475</v>
+        <v>5005</v>
       </c>
       <c r="B691" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C691" t="s">
         <v>141</v>
       </c>
       <c r="D691" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E691" t="s">
         <v>149</v>
@@ -44936,22 +44942,22 @@
         <v>46303</v>
       </c>
       <c r="M691" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N691" t="s">
         <v>220</v>
       </c>
       <c r="O691">
-        <v>17293248</v>
+        <v>17381592</v>
       </c>
       <c r="P691" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q691" t="s">
         <v>238</v>
       </c>
       <c r="R691" s="1">
-        <v>46308.38688019676</v>
+        <v>46308.47232888889</v>
       </c>
       <c r="S691">
         <v>6</v>
@@ -44963,7 +44969,7 @@
         <v>244</v>
       </c>
       <c r="W691" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA691">
         <v>0</v>
@@ -44977,10 +44983,10 @@
     </row>
     <row r="692" spans="1:33">
       <c r="A692">
-        <v>5005</v>
+        <v>5006</v>
       </c>
       <c r="B692" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="C692" t="s">
         <v>141</v>
@@ -44992,7 +44998,7 @@
         <v>149</v>
       </c>
       <c r="F692" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G692">
         <v>10372</v>
@@ -45010,13 +45016,13 @@
         <v>46303</v>
       </c>
       <c r="M692" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N692" t="s">
         <v>220</v>
       </c>
       <c r="O692">
-        <v>17381592</v>
+        <v>17229301</v>
       </c>
       <c r="P692" t="s">
         <v>226</v>
@@ -45025,7 +45031,7 @@
         <v>238</v>
       </c>
       <c r="R692" s="1">
-        <v>46308.47232888889</v>
+        <v>46308.47232934028</v>
       </c>
       <c r="S692">
         <v>6</v>
@@ -45037,7 +45043,7 @@
         <v>244</v>
       </c>
       <c r="W692" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA692">
         <v>0</v>
@@ -45051,10 +45057,10 @@
     </row>
     <row r="693" spans="1:33">
       <c r="A693">
-        <v>5006</v>
+        <v>5007</v>
       </c>
       <c r="B693" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C693" t="s">
         <v>141</v>
@@ -45066,7 +45072,7 @@
         <v>149</v>
       </c>
       <c r="F693" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G693">
         <v>10372</v>
@@ -45084,13 +45090,13 @@
         <v>46303</v>
       </c>
       <c r="M693" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N693" t="s">
         <v>220</v>
       </c>
       <c r="O693">
-        <v>17229301</v>
+        <v>17479402</v>
       </c>
       <c r="P693" t="s">
         <v>226</v>
@@ -45099,7 +45105,7 @@
         <v>238</v>
       </c>
       <c r="R693" s="1">
-        <v>46308.47232934028</v>
+        <v>46308.47232962963</v>
       </c>
       <c r="S693">
         <v>6</v>
@@ -45111,7 +45117,7 @@
         <v>244</v>
       </c>
       <c r="W693" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA693">
         <v>0</v>
@@ -45125,10 +45131,10 @@
     </row>
     <row r="694" spans="1:33">
       <c r="A694">
-        <v>5007</v>
+        <v>3081</v>
       </c>
       <c r="B694" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="C694" t="s">
         <v>141</v>
@@ -45143,7 +45149,7 @@
         <v>151</v>
       </c>
       <c r="G694">
-        <v>10372</v>
+        <v>10385</v>
       </c>
       <c r="H694">
         <v>0</v>
@@ -45152,19 +45158,16 @@
         <v>155</v>
       </c>
       <c r="J694" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="L694" s="1">
-        <v>46303</v>
-      </c>
-      <c r="M694" t="s">
-        <v>218</v>
+        <v>46308</v>
       </c>
       <c r="N694" t="s">
         <v>220</v>
       </c>
       <c r="O694">
-        <v>17479402</v>
+        <v>16990092</v>
       </c>
       <c r="P694" t="s">
         <v>226</v>
@@ -45173,10 +45176,10 @@
         <v>238</v>
       </c>
       <c r="R694" s="1">
-        <v>46308.47232962963</v>
+        <v>46308.33992331019</v>
       </c>
       <c r="S694">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T694" t="s">
         <v>241</v>
@@ -45184,9 +45187,6 @@
       <c r="U694" t="s">
         <v>244</v>
       </c>
-      <c r="W694" t="s">
-        <v>254</v>
-      </c>
       <c r="AA694">
         <v>0</v>
       </c>
@@ -45194,15 +45194,15 @@
         <v>260</v>
       </c>
       <c r="AG694" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="695" spans="1:33">
       <c r="A695">
-        <v>3081</v>
+        <v>3155</v>
       </c>
       <c r="B695" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="C695" t="s">
         <v>141</v>
@@ -45235,7 +45235,7 @@
         <v>220</v>
       </c>
       <c r="O695">
-        <v>16990092</v>
+        <v>17234360</v>
       </c>
       <c r="P695" t="s">
         <v>226</v>
@@ -45244,7 +45244,7 @@
         <v>238</v>
       </c>
       <c r="R695" s="1">
-        <v>46308.33992331019</v>
+        <v>46308.33992403935</v>
       </c>
       <c r="S695">
         <v>1</v>
@@ -45267,10 +45267,10 @@
     </row>
     <row r="696" spans="1:33">
       <c r="A696">
-        <v>3155</v>
+        <v>3332</v>
       </c>
       <c r="B696" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C696" t="s">
         <v>141</v>
@@ -45303,16 +45303,16 @@
         <v>220</v>
       </c>
       <c r="O696">
-        <v>17234360</v>
+        <v>17073336</v>
       </c>
       <c r="P696" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q696" t="s">
         <v>238</v>
       </c>
       <c r="R696" s="1">
-        <v>46308.33992403935</v>
+        <v>46308.33992453704</v>
       </c>
       <c r="S696">
         <v>1</v>
@@ -45335,10 +45335,10 @@
     </row>
     <row r="697" spans="1:33">
       <c r="A697">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="B697" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C697" t="s">
         <v>141</v>
@@ -45371,7 +45371,7 @@
         <v>220</v>
       </c>
       <c r="O697">
-        <v>17073336</v>
+        <v>17685275</v>
       </c>
       <c r="P697" t="s">
         <v>227</v>
@@ -45380,7 +45380,7 @@
         <v>238</v>
       </c>
       <c r="R697" s="1">
-        <v>46308.33992453704</v>
+        <v>46308.33992481481</v>
       </c>
       <c r="S697">
         <v>1</v>
@@ -45403,10 +45403,10 @@
     </row>
     <row r="698" spans="1:33">
       <c r="A698">
-        <v>3333</v>
+        <v>3453</v>
       </c>
       <c r="B698" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C698" t="s">
         <v>141</v>
@@ -45439,16 +45439,16 @@
         <v>220</v>
       </c>
       <c r="O698">
-        <v>17685275</v>
+        <v>17668154</v>
       </c>
       <c r="P698" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q698" t="s">
         <v>238</v>
       </c>
       <c r="R698" s="1">
-        <v>46308.33992481481</v>
+        <v>46308.33992521991</v>
       </c>
       <c r="S698">
         <v>1</v>
@@ -45471,10 +45471,10 @@
     </row>
     <row r="699" spans="1:33">
       <c r="A699">
-        <v>3453</v>
+        <v>3637</v>
       </c>
       <c r="B699" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C699" t="s">
         <v>141</v>
@@ -45507,7 +45507,7 @@
         <v>220</v>
       </c>
       <c r="O699">
-        <v>17668154</v>
+        <v>17890084</v>
       </c>
       <c r="P699" t="s">
         <v>226</v>
@@ -45516,7 +45516,7 @@
         <v>238</v>
       </c>
       <c r="R699" s="1">
-        <v>46308.33992521991</v>
+        <v>46308.33992607639</v>
       </c>
       <c r="S699">
         <v>1</v>
@@ -45539,10 +45539,10 @@
     </row>
     <row r="700" spans="1:33">
       <c r="A700">
-        <v>3637</v>
+        <v>3698</v>
       </c>
       <c r="B700" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C700" t="s">
         <v>141</v>
@@ -45575,7 +45575,7 @@
         <v>220</v>
       </c>
       <c r="O700">
-        <v>17890084</v>
+        <v>17448807</v>
       </c>
       <c r="P700" t="s">
         <v>226</v>
@@ -45584,7 +45584,7 @@
         <v>238</v>
       </c>
       <c r="R700" s="1">
-        <v>46308.33992607639</v>
+        <v>46308.33992636574</v>
       </c>
       <c r="S700">
         <v>1</v>
@@ -45607,16 +45607,16 @@
     </row>
     <row r="701" spans="1:33">
       <c r="A701">
-        <v>3698</v>
+        <v>4475</v>
       </c>
       <c r="B701" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C701" t="s">
         <v>141</v>
       </c>
       <c r="D701" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E701" t="s">
         <v>149</v>
@@ -45643,16 +45643,16 @@
         <v>220</v>
       </c>
       <c r="O701">
-        <v>17448807</v>
+        <v>17293272</v>
       </c>
       <c r="P701" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q701" t="s">
         <v>238</v>
       </c>
       <c r="R701" s="1">
-        <v>46308.33992636574</v>
+        <v>46308.33992673611</v>
       </c>
       <c r="S701">
         <v>1</v>
@@ -45675,10 +45675,10 @@
     </row>
     <row r="702" spans="1:33">
       <c r="A702">
-        <v>4475</v>
+        <v>4661</v>
       </c>
       <c r="B702" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="C702" t="s">
         <v>141</v>
@@ -45711,7 +45711,7 @@
         <v>220</v>
       </c>
       <c r="O702">
-        <v>17293272</v>
+        <v>17710447</v>
       </c>
       <c r="P702" t="s">
         <v>227</v>
@@ -45720,7 +45720,7 @@
         <v>238</v>
       </c>
       <c r="R702" s="1">
-        <v>46308.33992673611</v>
+        <v>46308.3399272801</v>
       </c>
       <c r="S702">
         <v>1</v>
@@ -45743,22 +45743,22 @@
     </row>
     <row r="703" spans="1:33">
       <c r="A703">
-        <v>4661</v>
+        <v>5006</v>
       </c>
       <c r="B703" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C703" t="s">
         <v>141</v>
       </c>
       <c r="D703" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E703" t="s">
         <v>149</v>
       </c>
       <c r="F703" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G703">
         <v>10385</v>
@@ -45779,16 +45779,16 @@
         <v>220</v>
       </c>
       <c r="O703">
-        <v>17710447</v>
+        <v>17229307</v>
       </c>
       <c r="P703" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q703" t="s">
         <v>238</v>
       </c>
       <c r="R703" s="1">
-        <v>46308.3399272801</v>
+        <v>46308.33992822916</v>
       </c>
       <c r="S703">
         <v>1</v>
@@ -45811,10 +45811,10 @@
     </row>
     <row r="704" spans="1:33">
       <c r="A704">
-        <v>5006</v>
+        <v>5007</v>
       </c>
       <c r="B704" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C704" t="s">
         <v>141</v>
@@ -45826,7 +45826,7 @@
         <v>149</v>
       </c>
       <c r="F704" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G704">
         <v>10385</v>
@@ -45847,7 +45847,7 @@
         <v>220</v>
       </c>
       <c r="O704">
-        <v>17229307</v>
+        <v>17479408</v>
       </c>
       <c r="P704" t="s">
         <v>226</v>
@@ -45856,7 +45856,7 @@
         <v>238</v>
       </c>
       <c r="R704" s="1">
-        <v>46308.33992822916</v>
+        <v>46308.33992873842</v>
       </c>
       <c r="S704">
         <v>1</v>
@@ -45879,16 +45879,16 @@
     </row>
     <row r="705" spans="1:33">
       <c r="A705">
-        <v>5007</v>
+        <v>3080</v>
       </c>
       <c r="B705" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C705" t="s">
         <v>141</v>
       </c>
       <c r="D705" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E705" t="s">
         <v>149</v>
@@ -45897,7 +45897,7 @@
         <v>151</v>
       </c>
       <c r="G705">
-        <v>10385</v>
+        <v>10399</v>
       </c>
       <c r="H705">
         <v>0</v>
@@ -45906,25 +45906,28 @@
         <v>155</v>
       </c>
       <c r="J705" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="L705" s="1">
         <v>46308</v>
       </c>
+      <c r="M705" t="s">
+        <v>213</v>
+      </c>
       <c r="N705" t="s">
         <v>220</v>
       </c>
       <c r="O705">
-        <v>17479408</v>
+        <v>16989489</v>
       </c>
       <c r="P705" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q705" t="s">
         <v>238</v>
       </c>
       <c r="R705" s="1">
-        <v>46308.33992873842</v>
+        <v>46309.49307806713</v>
       </c>
       <c r="S705">
         <v>1</v>
@@ -45935,6 +45938,9 @@
       <c r="U705" t="s">
         <v>244</v>
       </c>
+      <c r="W705" t="s">
+        <v>248</v>
+      </c>
       <c r="AA705">
         <v>0</v>
       </c>
@@ -45942,15 +45948,15 @@
         <v>260</v>
       </c>
       <c r="AG705" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="706" spans="1:33">
       <c r="A706">
-        <v>3080</v>
+        <v>3192</v>
       </c>
       <c r="B706" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C706" t="s">
         <v>141</v>
@@ -45986,7 +45992,7 @@
         <v>220</v>
       </c>
       <c r="O706">
-        <v>16989489</v>
+        <v>17392780</v>
       </c>
       <c r="P706" t="s">
         <v>227</v>
@@ -45995,7 +46001,7 @@
         <v>238</v>
       </c>
       <c r="R706" s="1">
-        <v>46309.49307806713</v>
+        <v>46309.49308027777</v>
       </c>
       <c r="S706">
         <v>1</v>
@@ -46021,10 +46027,10 @@
     </row>
     <row r="707" spans="1:33">
       <c r="A707">
-        <v>3192</v>
+        <v>3864</v>
       </c>
       <c r="B707" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C707" t="s">
         <v>141</v>
@@ -46060,7 +46066,7 @@
         <v>220</v>
       </c>
       <c r="O707">
-        <v>17392780</v>
+        <v>17363508</v>
       </c>
       <c r="P707" t="s">
         <v>227</v>
@@ -46069,7 +46075,7 @@
         <v>238</v>
       </c>
       <c r="R707" s="1">
-        <v>46309.49308027777</v>
+        <v>46309.50619553241</v>
       </c>
       <c r="S707">
         <v>1</v>
@@ -46095,10 +46101,10 @@
     </row>
     <row r="708" spans="1:33">
       <c r="A708">
-        <v>3864</v>
+        <v>4378</v>
       </c>
       <c r="B708" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C708" t="s">
         <v>141</v>
@@ -46134,7 +46140,7 @@
         <v>220</v>
       </c>
       <c r="O708">
-        <v>17363508</v>
+        <v>17865501</v>
       </c>
       <c r="P708" t="s">
         <v>227</v>
@@ -46143,7 +46149,7 @@
         <v>238</v>
       </c>
       <c r="R708" s="1">
-        <v>46309.50619553241</v>
+        <v>46309.49308068287</v>
       </c>
       <c r="S708">
         <v>1</v>
@@ -46169,10 +46175,10 @@
     </row>
     <row r="709" spans="1:33">
       <c r="A709">
-        <v>4378</v>
+        <v>4449</v>
       </c>
       <c r="B709" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C709" t="s">
         <v>141</v>
@@ -46208,7 +46214,7 @@
         <v>220</v>
       </c>
       <c r="O709">
-        <v>17865501</v>
+        <v>17223746</v>
       </c>
       <c r="P709" t="s">
         <v>227</v>
@@ -46217,7 +46223,7 @@
         <v>238</v>
       </c>
       <c r="R709" s="1">
-        <v>46309.49308068287</v>
+        <v>46309.49308114583</v>
       </c>
       <c r="S709">
         <v>1</v>
@@ -46243,16 +46249,16 @@
     </row>
     <row r="710" spans="1:33">
       <c r="A710">
-        <v>4449</v>
+        <v>4661</v>
       </c>
       <c r="B710" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C710" t="s">
         <v>141</v>
       </c>
       <c r="D710" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E710" t="s">
         <v>149</v>
@@ -46282,7 +46288,7 @@
         <v>220</v>
       </c>
       <c r="O710">
-        <v>17223746</v>
+        <v>17710465</v>
       </c>
       <c r="P710" t="s">
         <v>227</v>
@@ -46291,7 +46297,7 @@
         <v>238</v>
       </c>
       <c r="R710" s="1">
-        <v>46309.49308114583</v>
+        <v>46309.49309138889</v>
       </c>
       <c r="S710">
         <v>1</v>
@@ -46317,10 +46323,10 @@
     </row>
     <row r="711" spans="1:33">
       <c r="A711">
-        <v>4661</v>
+        <v>4786</v>
       </c>
       <c r="B711" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C711" t="s">
         <v>141</v>
@@ -46356,7 +46362,7 @@
         <v>220</v>
       </c>
       <c r="O711">
-        <v>17710465</v>
+        <v>17559757</v>
       </c>
       <c r="P711" t="s">
         <v>227</v>
@@ -46365,7 +46371,7 @@
         <v>238</v>
       </c>
       <c r="R711" s="1">
-        <v>46309.49309138889</v>
+        <v>46309.49406915509</v>
       </c>
       <c r="S711">
         <v>1</v>
@@ -46391,10 +46397,10 @@
     </row>
     <row r="712" spans="1:33">
       <c r="A712">
-        <v>4786</v>
+        <v>4787</v>
       </c>
       <c r="B712" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C712" t="s">
         <v>141</v>
@@ -46430,7 +46436,7 @@
         <v>220</v>
       </c>
       <c r="O712">
-        <v>17559757</v>
+        <v>17468481</v>
       </c>
       <c r="P712" t="s">
         <v>227</v>
@@ -46439,7 +46445,7 @@
         <v>238</v>
       </c>
       <c r="R712" s="1">
-        <v>46309.49406915509</v>
+        <v>46309.49411724537</v>
       </c>
       <c r="S712">
         <v>1</v>
@@ -46465,10 +46471,10 @@
     </row>
     <row r="713" spans="1:33">
       <c r="A713">
-        <v>4787</v>
+        <v>4862</v>
       </c>
       <c r="B713" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C713" t="s">
         <v>141</v>
@@ -46504,7 +46510,7 @@
         <v>220</v>
       </c>
       <c r="O713">
-        <v>17468481</v>
+        <v>17503999</v>
       </c>
       <c r="P713" t="s">
         <v>227</v>
@@ -46513,7 +46519,7 @@
         <v>238</v>
       </c>
       <c r="R713" s="1">
-        <v>46309.49411724537</v>
+        <v>46309.49412034722</v>
       </c>
       <c r="S713">
         <v>1</v>
@@ -46539,10 +46545,10 @@
     </row>
     <row r="714" spans="1:33">
       <c r="A714">
-        <v>4862</v>
+        <v>4926</v>
       </c>
       <c r="B714" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C714" t="s">
         <v>141</v>
@@ -46578,7 +46584,7 @@
         <v>220</v>
       </c>
       <c r="O714">
-        <v>17503999</v>
+        <v>17328288</v>
       </c>
       <c r="P714" t="s">
         <v>227</v>
@@ -46587,7 +46593,7 @@
         <v>238</v>
       </c>
       <c r="R714" s="1">
-        <v>46309.49412034722</v>
+        <v>46309.49417806713</v>
       </c>
       <c r="S714">
         <v>1</v>
@@ -46613,10 +46619,10 @@
     </row>
     <row r="715" spans="1:33">
       <c r="A715">
-        <v>4926</v>
+        <v>5008</v>
       </c>
       <c r="B715" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C715" t="s">
         <v>141</v>
@@ -46652,16 +46658,16 @@
         <v>220</v>
       </c>
       <c r="O715">
-        <v>17328288</v>
+        <v>17346021</v>
       </c>
       <c r="P715" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q715" t="s">
         <v>238</v>
       </c>
       <c r="R715" s="1">
-        <v>46309.49417806713</v>
+        <v>46309.49553943287</v>
       </c>
       <c r="S715">
         <v>1</v>
@@ -46687,10 +46693,10 @@
     </row>
     <row r="716" spans="1:33">
       <c r="A716">
-        <v>5008</v>
+        <v>5021</v>
       </c>
       <c r="B716" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C716" t="s">
         <v>141</v>
@@ -46726,16 +46732,16 @@
         <v>220</v>
       </c>
       <c r="O716">
-        <v>17346021</v>
+        <v>17381733</v>
       </c>
       <c r="P716" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q716" t="s">
         <v>238</v>
       </c>
       <c r="R716" s="1">
-        <v>46309.49553943287</v>
+        <v>46309.49554005787</v>
       </c>
       <c r="S716">
         <v>1</v>
@@ -46761,22 +46767,22 @@
     </row>
     <row r="717" spans="1:33">
       <c r="A717">
-        <v>5021</v>
+        <v>5064</v>
       </c>
       <c r="B717" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C717" t="s">
         <v>141</v>
       </c>
       <c r="D717" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E717" t="s">
         <v>149</v>
       </c>
       <c r="F717" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G717">
         <v>10399</v>
@@ -46800,7 +46806,7 @@
         <v>220</v>
       </c>
       <c r="O717">
-        <v>17381733</v>
+        <v>17097617</v>
       </c>
       <c r="P717" t="s">
         <v>227</v>
@@ -46809,7 +46815,7 @@
         <v>238</v>
       </c>
       <c r="R717" s="1">
-        <v>46309.49554005787</v>
+        <v>46309.49554141203</v>
       </c>
       <c r="S717">
         <v>1</v>
@@ -46835,16 +46841,16 @@
     </row>
     <row r="718" spans="1:33">
       <c r="A718">
-        <v>5064</v>
+        <v>5217</v>
       </c>
       <c r="B718" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C718" t="s">
         <v>141</v>
       </c>
       <c r="D718" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E718" t="s">
         <v>149</v>
@@ -46874,7 +46880,7 @@
         <v>220</v>
       </c>
       <c r="O718">
-        <v>17097617</v>
+        <v>17683402</v>
       </c>
       <c r="P718" t="s">
         <v>227</v>
@@ -46883,7 +46889,7 @@
         <v>238</v>
       </c>
       <c r="R718" s="1">
-        <v>46309.49554141203</v>
+        <v>46309.49554200232</v>
       </c>
       <c r="S718">
         <v>1</v>
@@ -46909,10 +46915,10 @@
     </row>
     <row r="719" spans="1:33">
       <c r="A719">
-        <v>5217</v>
+        <v>5384</v>
       </c>
       <c r="B719" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C719" t="s">
         <v>141</v>
@@ -46924,7 +46930,7 @@
         <v>149</v>
       </c>
       <c r="F719" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G719">
         <v>10399</v>
@@ -46948,7 +46954,7 @@
         <v>220</v>
       </c>
       <c r="O719">
-        <v>17683402</v>
+        <v>17765253</v>
       </c>
       <c r="P719" t="s">
         <v>227</v>
@@ -46957,7 +46963,7 @@
         <v>238</v>
       </c>
       <c r="R719" s="1">
-        <v>46309.49554200232</v>
+        <v>46309.49554241898</v>
       </c>
       <c r="S719">
         <v>1</v>
@@ -46983,16 +46989,16 @@
     </row>
     <row r="720" spans="1:33">
       <c r="A720">
-        <v>5384</v>
+        <v>5763</v>
       </c>
       <c r="B720" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C720" t="s">
         <v>141</v>
       </c>
       <c r="D720" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E720" t="s">
         <v>149</v>
@@ -47022,7 +47028,7 @@
         <v>220</v>
       </c>
       <c r="O720">
-        <v>17765253</v>
+        <v>17796853</v>
       </c>
       <c r="P720" t="s">
         <v>227</v>
@@ -47031,7 +47037,7 @@
         <v>238</v>
       </c>
       <c r="R720" s="1">
-        <v>46309.49554241898</v>
+        <v>46309.49554274305</v>
       </c>
       <c r="S720">
         <v>1</v>
@@ -47057,10 +47063,10 @@
     </row>
     <row r="721" spans="1:33">
       <c r="A721">
-        <v>5763</v>
+        <v>6565</v>
       </c>
       <c r="B721" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C721" t="s">
         <v>141</v>
@@ -47096,7 +47102,7 @@
         <v>220</v>
       </c>
       <c r="O721">
-        <v>17796853</v>
+        <v>17167537</v>
       </c>
       <c r="P721" t="s">
         <v>227</v>
@@ -47105,7 +47111,7 @@
         <v>238</v>
       </c>
       <c r="R721" s="1">
-        <v>46309.49554274305</v>
+        <v>46309.50592586806</v>
       </c>
       <c r="S721">
         <v>1</v>
@@ -47131,10 +47137,10 @@
     </row>
     <row r="722" spans="1:33">
       <c r="A722">
-        <v>6565</v>
+        <v>6982</v>
       </c>
       <c r="B722" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C722" t="s">
         <v>141</v>
@@ -47170,7 +47176,7 @@
         <v>220</v>
       </c>
       <c r="O722">
-        <v>17167537</v>
+        <v>18203794</v>
       </c>
       <c r="P722" t="s">
         <v>227</v>
@@ -47179,7 +47185,7 @@
         <v>238</v>
       </c>
       <c r="R722" s="1">
-        <v>46309.50592586806</v>
+        <v>46309.49554407407</v>
       </c>
       <c r="S722">
         <v>1</v>
@@ -47205,16 +47211,16 @@
     </row>
     <row r="723" spans="1:33">
       <c r="A723">
-        <v>6982</v>
+        <v>3081</v>
       </c>
       <c r="B723" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C723" t="s">
         <v>141</v>
       </c>
       <c r="D723" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E723" t="s">
         <v>149</v>
@@ -47223,7 +47229,7 @@
         <v>151</v>
       </c>
       <c r="G723">
-        <v>10399</v>
+        <v>10397</v>
       </c>
       <c r="H723">
         <v>0</v>
@@ -47232,31 +47238,28 @@
         <v>155</v>
       </c>
       <c r="J723" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L723" s="1">
-        <v>46308</v>
-      </c>
-      <c r="M723" t="s">
-        <v>213</v>
+        <v>46304</v>
       </c>
       <c r="N723" t="s">
         <v>220</v>
       </c>
       <c r="O723">
-        <v>18203794</v>
+        <v>16990142</v>
       </c>
       <c r="P723" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q723" t="s">
         <v>238</v>
       </c>
       <c r="R723" s="1">
-        <v>46309.49554407407</v>
+        <v>46304.559438125</v>
       </c>
       <c r="S723">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T723" t="s">
         <v>241</v>
@@ -47264,9 +47267,6 @@
       <c r="U723" t="s">
         <v>244</v>
       </c>
-      <c r="W723" t="s">
-        <v>248</v>
-      </c>
       <c r="AA723">
         <v>0</v>
       </c>
@@ -47274,15 +47274,15 @@
         <v>260</v>
       </c>
       <c r="AG723" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="724" spans="1:33">
       <c r="A724">
-        <v>3081</v>
+        <v>5005</v>
       </c>
       <c r="B724" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C724" t="s">
         <v>141</v>
@@ -47315,7 +47315,7 @@
         <v>220</v>
       </c>
       <c r="O724">
-        <v>16990142</v>
+        <v>17381613</v>
       </c>
       <c r="P724" t="s">
         <v>226</v>
@@ -47324,7 +47324,7 @@
         <v>238</v>
       </c>
       <c r="R724" s="1">
-        <v>46304.559438125</v>
+        <v>46304.56028420139</v>
       </c>
       <c r="S724">
         <v>5</v>
@@ -47347,10 +47347,10 @@
     </row>
     <row r="725" spans="1:33">
       <c r="A725">
-        <v>5005</v>
+        <v>3081</v>
       </c>
       <c r="B725" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C725" t="s">
         <v>141</v>
@@ -47365,7 +47365,7 @@
         <v>151</v>
       </c>
       <c r="G725">
-        <v>10397</v>
+        <v>10405</v>
       </c>
       <c r="H725">
         <v>0</v>
@@ -47374,7 +47374,7 @@
         <v>155</v>
       </c>
       <c r="J725" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="L725" s="1">
         <v>46304</v>
@@ -47383,7 +47383,7 @@
         <v>220</v>
       </c>
       <c r="O725">
-        <v>17381613</v>
+        <v>16990220</v>
       </c>
       <c r="P725" t="s">
         <v>226</v>
@@ -47392,7 +47392,7 @@
         <v>238</v>
       </c>
       <c r="R725" s="1">
-        <v>46304.56028420139</v>
+        <v>46304.55781960648</v>
       </c>
       <c r="S725">
         <v>5</v>
@@ -47415,10 +47415,10 @@
     </row>
     <row r="726" spans="1:33">
       <c r="A726">
-        <v>3081</v>
+        <v>3155</v>
       </c>
       <c r="B726" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="C726" t="s">
         <v>141</v>
@@ -47451,7 +47451,7 @@
         <v>220</v>
       </c>
       <c r="O726">
-        <v>16990220</v>
+        <v>17234389</v>
       </c>
       <c r="P726" t="s">
         <v>226</v>
@@ -47460,7 +47460,7 @@
         <v>238</v>
       </c>
       <c r="R726" s="1">
-        <v>46304.55781960648</v>
+        <v>46304.55782019676</v>
       </c>
       <c r="S726">
         <v>5</v>
@@ -47483,10 +47483,10 @@
     </row>
     <row r="727" spans="1:33">
       <c r="A727">
-        <v>3155</v>
+        <v>3332</v>
       </c>
       <c r="B727" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C727" t="s">
         <v>141</v>
@@ -47519,16 +47519,16 @@
         <v>220</v>
       </c>
       <c r="O727">
-        <v>17234389</v>
+        <v>17073420</v>
       </c>
       <c r="P727" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q727" t="s">
         <v>238</v>
       </c>
       <c r="R727" s="1">
-        <v>46304.55782019676</v>
+        <v>46304.55782097222</v>
       </c>
       <c r="S727">
         <v>5</v>
@@ -47551,10 +47551,10 @@
     </row>
     <row r="728" spans="1:33">
       <c r="A728">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="B728" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C728" t="s">
         <v>141</v>
@@ -47587,7 +47587,7 @@
         <v>220</v>
       </c>
       <c r="O728">
-        <v>17073420</v>
+        <v>17685324</v>
       </c>
       <c r="P728" t="s">
         <v>227</v>
@@ -47596,7 +47596,7 @@
         <v>238</v>
       </c>
       <c r="R728" s="1">
-        <v>46304.55782097222</v>
+        <v>46304.55782189815</v>
       </c>
       <c r="S728">
         <v>5</v>
@@ -47619,10 +47619,10 @@
     </row>
     <row r="729" spans="1:33">
       <c r="A729">
-        <v>3333</v>
+        <v>3453</v>
       </c>
       <c r="B729" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C729" t="s">
         <v>141</v>
@@ -47655,16 +47655,16 @@
         <v>220</v>
       </c>
       <c r="O729">
-        <v>17685324</v>
+        <v>17668183</v>
       </c>
       <c r="P729" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q729" t="s">
         <v>238</v>
       </c>
       <c r="R729" s="1">
-        <v>46304.55782189815</v>
+        <v>46304.55782240741</v>
       </c>
       <c r="S729">
         <v>5</v>
@@ -47687,10 +47687,10 @@
     </row>
     <row r="730" spans="1:33">
       <c r="A730">
-        <v>3453</v>
+        <v>3637</v>
       </c>
       <c r="B730" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C730" t="s">
         <v>141</v>
@@ -47723,7 +47723,7 @@
         <v>220</v>
       </c>
       <c r="O730">
-        <v>17668183</v>
+        <v>17890113</v>
       </c>
       <c r="P730" t="s">
         <v>226</v>
@@ -47732,7 +47732,7 @@
         <v>238</v>
       </c>
       <c r="R730" s="1">
-        <v>46304.55782240741</v>
+        <v>46304.55782303241</v>
       </c>
       <c r="S730">
         <v>5</v>
@@ -47755,10 +47755,10 @@
     </row>
     <row r="731" spans="1:33">
       <c r="A731">
-        <v>3637</v>
+        <v>3698</v>
       </c>
       <c r="B731" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C731" t="s">
         <v>141</v>
@@ -47791,7 +47791,7 @@
         <v>220</v>
       </c>
       <c r="O731">
-        <v>17890113</v>
+        <v>17448836</v>
       </c>
       <c r="P731" t="s">
         <v>226</v>
@@ -47800,7 +47800,7 @@
         <v>238</v>
       </c>
       <c r="R731" s="1">
-        <v>46304.55782303241</v>
+        <v>46304.55782371528</v>
       </c>
       <c r="S731">
         <v>5</v>
@@ -47823,10 +47823,10 @@
     </row>
     <row r="732" spans="1:33">
       <c r="A732">
-        <v>3698</v>
+        <v>5005</v>
       </c>
       <c r="B732" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="C732" t="s">
         <v>141</v>
@@ -47859,7 +47859,7 @@
         <v>220</v>
       </c>
       <c r="O732">
-        <v>17448836</v>
+        <v>17381643</v>
       </c>
       <c r="P732" t="s">
         <v>226</v>
@@ -47868,7 +47868,7 @@
         <v>238</v>
       </c>
       <c r="R732" s="1">
-        <v>46304.55782371528</v>
+        <v>46304.55841929398</v>
       </c>
       <c r="S732">
         <v>5</v>
@@ -47891,10 +47891,10 @@
     </row>
     <row r="733" spans="1:33">
       <c r="A733">
-        <v>5005</v>
+        <v>5006</v>
       </c>
       <c r="B733" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="C733" t="s">
         <v>141</v>
@@ -47906,7 +47906,7 @@
         <v>149</v>
       </c>
       <c r="F733" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G733">
         <v>10405</v>
@@ -47927,7 +47927,7 @@
         <v>220</v>
       </c>
       <c r="O733">
-        <v>17381643</v>
+        <v>17229336</v>
       </c>
       <c r="P733" t="s">
         <v>226</v>
@@ -47936,7 +47936,7 @@
         <v>238</v>
       </c>
       <c r="R733" s="1">
-        <v>46304.55841929398</v>
+        <v>46304.55841981481</v>
       </c>
       <c r="S733">
         <v>5</v>
@@ -47959,10 +47959,10 @@
     </row>
     <row r="734" spans="1:33">
       <c r="A734">
-        <v>5006</v>
+        <v>5007</v>
       </c>
       <c r="B734" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C734" t="s">
         <v>141</v>
@@ -47974,7 +47974,7 @@
         <v>149</v>
       </c>
       <c r="F734" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G734">
         <v>10405</v>
@@ -47995,7 +47995,7 @@
         <v>220</v>
       </c>
       <c r="O734">
-        <v>17229336</v>
+        <v>17479437</v>
       </c>
       <c r="P734" t="s">
         <v>226</v>
@@ -48004,7 +48004,7 @@
         <v>238</v>
       </c>
       <c r="R734" s="1">
-        <v>46304.55841981481</v>
+        <v>46304.55842033565</v>
       </c>
       <c r="S734">
         <v>5</v>
@@ -48027,10 +48027,10 @@
     </row>
     <row r="735" spans="1:33">
       <c r="A735">
-        <v>5007</v>
+        <v>3081</v>
       </c>
       <c r="B735" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="C735" t="s">
         <v>141</v>
@@ -48045,7 +48045,7 @@
         <v>151</v>
       </c>
       <c r="G735">
-        <v>10405</v>
+        <v>10367</v>
       </c>
       <c r="H735">
         <v>0</v>
@@ -48054,16 +48054,16 @@
         <v>155</v>
       </c>
       <c r="J735" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="L735" s="1">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="N735" t="s">
         <v>220</v>
       </c>
       <c r="O735">
-        <v>17479437</v>
+        <v>16990009</v>
       </c>
       <c r="P735" t="s">
         <v>226</v>
@@ -48072,10 +48072,10 @@
         <v>238</v>
       </c>
       <c r="R735" s="1">
-        <v>46304.55842033565</v>
+        <v>46302.50750034722</v>
       </c>
       <c r="S735">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T735" t="s">
         <v>241</v>
@@ -48095,10 +48095,10 @@
     </row>
     <row r="736" spans="1:33">
       <c r="A736">
-        <v>3081</v>
+        <v>3155</v>
       </c>
       <c r="B736" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="C736" t="s">
         <v>141</v>
@@ -48131,7 +48131,7 @@
         <v>220</v>
       </c>
       <c r="O736">
-        <v>16990009</v>
+        <v>17234344</v>
       </c>
       <c r="P736" t="s">
         <v>226</v>
@@ -48140,7 +48140,7 @@
         <v>238</v>
       </c>
       <c r="R736" s="1">
-        <v>46302.50750034722</v>
+        <v>46302.50750078704</v>
       </c>
       <c r="S736">
         <v>7</v>
@@ -48163,10 +48163,10 @@
     </row>
     <row r="737" spans="1:33">
       <c r="A737">
-        <v>3155</v>
+        <v>3332</v>
       </c>
       <c r="B737" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C737" t="s">
         <v>141</v>
@@ -48199,16 +48199,16 @@
         <v>220</v>
       </c>
       <c r="O737">
-        <v>17234344</v>
+        <v>17073295</v>
       </c>
       <c r="P737" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q737" t="s">
         <v>238</v>
       </c>
       <c r="R737" s="1">
-        <v>46302.50750078704</v>
+        <v>46302.51116497685</v>
       </c>
       <c r="S737">
         <v>7</v>
@@ -48231,10 +48231,10 @@
     </row>
     <row r="738" spans="1:33">
       <c r="A738">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="B738" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C738" t="s">
         <v>141</v>
@@ -48267,7 +48267,7 @@
         <v>220</v>
       </c>
       <c r="O738">
-        <v>17073295</v>
+        <v>17685249</v>
       </c>
       <c r="P738" t="s">
         <v>227</v>
@@ -48276,7 +48276,7 @@
         <v>238</v>
       </c>
       <c r="R738" s="1">
-        <v>46302.51116497685</v>
+        <v>46302.50750148148</v>
       </c>
       <c r="S738">
         <v>7</v>
@@ -48299,10 +48299,10 @@
     </row>
     <row r="739" spans="1:33">
       <c r="A739">
-        <v>3333</v>
+        <v>3453</v>
       </c>
       <c r="B739" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C739" t="s">
         <v>141</v>
@@ -48335,16 +48335,16 @@
         <v>220</v>
       </c>
       <c r="O739">
-        <v>17685249</v>
+        <v>17668138</v>
       </c>
       <c r="P739" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q739" t="s">
         <v>238</v>
       </c>
       <c r="R739" s="1">
-        <v>46302.50750148148</v>
+        <v>46302.50850604167</v>
       </c>
       <c r="S739">
         <v>7</v>
@@ -48367,10 +48367,10 @@
     </row>
     <row r="740" spans="1:33">
       <c r="A740">
-        <v>3453</v>
+        <v>3637</v>
       </c>
       <c r="B740" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C740" t="s">
         <v>141</v>
@@ -48403,7 +48403,7 @@
         <v>220</v>
       </c>
       <c r="O740">
-        <v>17668138</v>
+        <v>17890068</v>
       </c>
       <c r="P740" t="s">
         <v>226</v>
@@ -48412,7 +48412,7 @@
         <v>238</v>
       </c>
       <c r="R740" s="1">
-        <v>46302.50850604167</v>
+        <v>46302.507501875</v>
       </c>
       <c r="S740">
         <v>7</v>
@@ -48435,10 +48435,10 @@
     </row>
     <row r="741" spans="1:33">
       <c r="A741">
-        <v>3637</v>
+        <v>3698</v>
       </c>
       <c r="B741" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C741" t="s">
         <v>141</v>
@@ -48471,7 +48471,7 @@
         <v>220</v>
       </c>
       <c r="O741">
-        <v>17890068</v>
+        <v>17448791</v>
       </c>
       <c r="P741" t="s">
         <v>226</v>
@@ -48480,7 +48480,7 @@
         <v>238</v>
       </c>
       <c r="R741" s="1">
-        <v>46302.507501875</v>
+        <v>46302.50750232639</v>
       </c>
       <c r="S741">
         <v>7</v>
@@ -48503,16 +48503,16 @@
     </row>
     <row r="742" spans="1:33">
       <c r="A742">
-        <v>3698</v>
+        <v>4475</v>
       </c>
       <c r="B742" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="C742" t="s">
         <v>141</v>
       </c>
       <c r="D742" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E742" t="s">
         <v>149</v>
@@ -48539,16 +48539,16 @@
         <v>220</v>
       </c>
       <c r="O742">
-        <v>17448791</v>
+        <v>17293238</v>
       </c>
       <c r="P742" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q742" t="s">
         <v>238</v>
       </c>
       <c r="R742" s="1">
-        <v>46302.50750232639</v>
+        <v>46302.50917300926</v>
       </c>
       <c r="S742">
         <v>7</v>
@@ -48571,10 +48571,10 @@
     </row>
     <row r="743" spans="1:33">
       <c r="A743">
-        <v>4475</v>
+        <v>4661</v>
       </c>
       <c r="B743" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="C743" t="s">
         <v>141</v>
@@ -48607,7 +48607,7 @@
         <v>220</v>
       </c>
       <c r="O743">
-        <v>17293238</v>
+        <v>17710427</v>
       </c>
       <c r="P743" t="s">
         <v>227</v>
@@ -48616,7 +48616,7 @@
         <v>238</v>
       </c>
       <c r="R743" s="1">
-        <v>46302.50917300926</v>
+        <v>46302.51183856482</v>
       </c>
       <c r="S743">
         <v>7</v>
@@ -48639,10 +48639,10 @@
     </row>
     <row r="744" spans="1:33">
       <c r="A744">
-        <v>4661</v>
+        <v>3667</v>
       </c>
       <c r="B744" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="C744" t="s">
         <v>141</v>
@@ -48651,46 +48651,46 @@
         <v>143</v>
       </c>
       <c r="E744" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F744" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G744">
-        <v>10367</v>
+        <v>6193</v>
       </c>
       <c r="H744">
         <v>0</v>
       </c>
       <c r="I744" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J744" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="L744" s="1">
-        <v>46302</v>
+        <v>46311</v>
       </c>
       <c r="N744" t="s">
         <v>220</v>
       </c>
       <c r="O744">
-        <v>17710427</v>
+        <v>17314178</v>
       </c>
       <c r="P744" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q744" t="s">
         <v>238</v>
       </c>
       <c r="R744" s="1">
-        <v>46302.51183856482</v>
+        <v>46295.38656690972</v>
       </c>
       <c r="S744">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="T744" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="U744" t="s">
         <v>244</v>
@@ -48699,7 +48699,7 @@
         <v>0</v>
       </c>
       <c r="AB744" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="AG744" t="s">
         <v>264</v>
@@ -48707,10 +48707,10 @@
     </row>
     <row r="745" spans="1:33">
       <c r="A745">
-        <v>3667</v>
+        <v>3670</v>
       </c>
       <c r="B745" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C745" t="s">
         <v>141</v>
@@ -48743,7 +48743,7 @@
         <v>220</v>
       </c>
       <c r="O745">
-        <v>17314178</v>
+        <v>17035369</v>
       </c>
       <c r="P745" t="s">
         <v>233</v>
@@ -48752,7 +48752,7 @@
         <v>238</v>
       </c>
       <c r="R745" s="1">
-        <v>46295.38656690972</v>
+        <v>46295.38656856481</v>
       </c>
       <c r="S745">
         <v>-2</v>
@@ -48775,10 +48775,10 @@
     </row>
     <row r="746" spans="1:33">
       <c r="A746">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="B746" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C746" t="s">
         <v>141</v>
@@ -48811,7 +48811,7 @@
         <v>220</v>
       </c>
       <c r="O746">
-        <v>17035369</v>
+        <v>17772526</v>
       </c>
       <c r="P746" t="s">
         <v>233</v>
@@ -48820,7 +48820,7 @@
         <v>238</v>
       </c>
       <c r="R746" s="1">
-        <v>46295.38656856481</v>
+        <v>46295.38657111111</v>
       </c>
       <c r="S746">
         <v>-2</v>
@@ -48843,10 +48843,10 @@
     </row>
     <row r="747" spans="1:33">
       <c r="A747">
-        <v>3671</v>
+        <v>3216</v>
       </c>
       <c r="B747" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C747" t="s">
         <v>141</v>
@@ -48861,7 +48861,7 @@
         <v>147</v>
       </c>
       <c r="G747">
-        <v>6193</v>
+        <v>6195</v>
       </c>
       <c r="H747">
         <v>0</v>
@@ -48870,16 +48870,16 @@
         <v>162</v>
       </c>
       <c r="J747" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="L747" s="1">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="N747" t="s">
         <v>220</v>
       </c>
       <c r="O747">
-        <v>17772526</v>
+        <v>17758790</v>
       </c>
       <c r="P747" t="s">
         <v>233</v>
@@ -48888,10 +48888,10 @@
         <v>238</v>
       </c>
       <c r="R747" s="1">
-        <v>46295.38657111111</v>
+        <v>46303.50233027778</v>
       </c>
       <c r="S747">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="T747" t="s">
         <v>242</v>
@@ -48911,10 +48911,10 @@
     </row>
     <row r="748" spans="1:33">
       <c r="A748">
-        <v>3216</v>
+        <v>3218</v>
       </c>
       <c r="B748" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C748" t="s">
         <v>141</v>
@@ -48947,7 +48947,7 @@
         <v>220</v>
       </c>
       <c r="O748">
-        <v>17758790</v>
+        <v>17135281</v>
       </c>
       <c r="P748" t="s">
         <v>233</v>
@@ -48956,7 +48956,7 @@
         <v>238</v>
       </c>
       <c r="R748" s="1">
-        <v>46303.50233027778</v>
+        <v>46303.50233253472</v>
       </c>
       <c r="S748">
         <v>5</v>
@@ -48979,10 +48979,10 @@
     </row>
     <row r="749" spans="1:33">
       <c r="A749">
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="B749" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C749" t="s">
         <v>141</v>
@@ -49015,7 +49015,7 @@
         <v>220</v>
       </c>
       <c r="O749">
-        <v>17135281</v>
+        <v>17726231</v>
       </c>
       <c r="P749" t="s">
         <v>233</v>
@@ -49024,7 +49024,7 @@
         <v>238</v>
       </c>
       <c r="R749" s="1">
-        <v>46303.50233253472</v>
+        <v>46303.50233501157</v>
       </c>
       <c r="S749">
         <v>5</v>
@@ -49047,10 +49047,10 @@
     </row>
     <row r="750" spans="1:33">
       <c r="A750">
-        <v>3220</v>
+        <v>3217</v>
       </c>
       <c r="B750" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="C750" t="s">
         <v>141</v>
@@ -49059,13 +49059,13 @@
         <v>143</v>
       </c>
       <c r="E750" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F750" t="s">
         <v>147</v>
       </c>
       <c r="G750">
-        <v>6195</v>
+        <v>9134</v>
       </c>
       <c r="H750">
         <v>0</v>
@@ -49074,16 +49074,16 @@
         <v>162</v>
       </c>
       <c r="J750" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="L750" s="1">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="N750" t="s">
         <v>220</v>
       </c>
       <c r="O750">
-        <v>17726231</v>
+        <v>17259178</v>
       </c>
       <c r="P750" t="s">
         <v>233</v>
@@ -49092,10 +49092,10 @@
         <v>238</v>
       </c>
       <c r="R750" s="1">
-        <v>46303.50233501157</v>
+        <v>46295.38674228009</v>
       </c>
       <c r="S750">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="T750" t="s">
         <v>242</v>
@@ -49110,15 +49110,15 @@
         <v>233</v>
       </c>
       <c r="AG750" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="751" spans="1:33">
       <c r="A751">
-        <v>3217</v>
+        <v>3210</v>
       </c>
       <c r="B751" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="C751" t="s">
         <v>141</v>
@@ -49127,43 +49127,43 @@
         <v>143</v>
       </c>
       <c r="E751" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F751" t="s">
         <v>147</v>
       </c>
       <c r="G751">
-        <v>9134</v>
+        <v>6120</v>
       </c>
       <c r="H751">
         <v>0</v>
       </c>
       <c r="I751" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J751" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="L751" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="N751" t="s">
         <v>220</v>
       </c>
       <c r="O751">
-        <v>17259178</v>
+        <v>17409021</v>
       </c>
       <c r="P751" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="Q751" t="s">
         <v>238</v>
       </c>
       <c r="R751" s="1">
-        <v>46295.38674228009</v>
+        <v>46297.50044318287</v>
       </c>
       <c r="S751">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="T751" t="s">
         <v>242</v>
@@ -49175,24 +49175,24 @@
         <v>0</v>
       </c>
       <c r="AB751" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG751" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="752" spans="1:33">
       <c r="A752">
-        <v>3210</v>
+        <v>3213</v>
       </c>
       <c r="B752" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C752" t="s">
         <v>141</v>
       </c>
       <c r="D752" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E752" t="s">
         <v>150</v>
@@ -49219,7 +49219,7 @@
         <v>220</v>
       </c>
       <c r="O752">
-        <v>17409021</v>
+        <v>17618714</v>
       </c>
       <c r="P752" t="s">
         <v>228</v>
@@ -49228,7 +49228,7 @@
         <v>238</v>
       </c>
       <c r="R752" s="1">
-        <v>46297.50044318287</v>
+        <v>46297.50044424769</v>
       </c>
       <c r="S752">
         <v>-2</v>
@@ -49251,10 +49251,10 @@
     </row>
     <row r="753" spans="1:33">
       <c r="A753">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="B753" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C753" t="s">
         <v>141</v>
@@ -49287,7 +49287,7 @@
         <v>220</v>
       </c>
       <c r="O753">
-        <v>17618714</v>
+        <v>17259072</v>
       </c>
       <c r="P753" t="s">
         <v>228</v>
@@ -49296,7 +49296,7 @@
         <v>238</v>
       </c>
       <c r="R753" s="1">
-        <v>46297.50044424769</v>
+        <v>46297.50044479167</v>
       </c>
       <c r="S753">
         <v>-2</v>
@@ -49319,10 +49319,10 @@
     </row>
     <row r="754" spans="1:33">
       <c r="A754">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="B754" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C754" t="s">
         <v>141</v>
@@ -49331,7 +49331,7 @@
         <v>142</v>
       </c>
       <c r="E754" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F754" t="s">
         <v>147</v>
@@ -49355,7 +49355,7 @@
         <v>220</v>
       </c>
       <c r="O754">
-        <v>17259072</v>
+        <v>17618794</v>
       </c>
       <c r="P754" t="s">
         <v>228</v>
@@ -49364,7 +49364,7 @@
         <v>238</v>
       </c>
       <c r="R754" s="1">
-        <v>46297.50044479167</v>
+        <v>46297.50044525463</v>
       </c>
       <c r="S754">
         <v>-2</v>
@@ -49387,19 +49387,19 @@
     </row>
     <row r="755" spans="1:33">
       <c r="A755">
-        <v>3215</v>
+        <v>3218</v>
       </c>
       <c r="B755" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C755" t="s">
         <v>141</v>
       </c>
       <c r="D755" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E755" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F755" t="s">
         <v>147</v>
@@ -49423,7 +49423,7 @@
         <v>220</v>
       </c>
       <c r="O755">
-        <v>17618794</v>
+        <v>17135167</v>
       </c>
       <c r="P755" t="s">
         <v>228</v>
@@ -49432,7 +49432,7 @@
         <v>238</v>
       </c>
       <c r="R755" s="1">
-        <v>46297.50044525463</v>
+        <v>46297.50044622686</v>
       </c>
       <c r="S755">
         <v>-2</v>
@@ -49455,10 +49455,10 @@
     </row>
     <row r="756" spans="1:33">
       <c r="A756">
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="B756" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C756" t="s">
         <v>141</v>
@@ -49491,7 +49491,7 @@
         <v>220</v>
       </c>
       <c r="O756">
-        <v>17135167</v>
+        <v>17726183</v>
       </c>
       <c r="P756" t="s">
         <v>228</v>
@@ -49500,7 +49500,7 @@
         <v>238</v>
       </c>
       <c r="R756" s="1">
-        <v>46297.50044622686</v>
+        <v>46297.50044667824</v>
       </c>
       <c r="S756">
         <v>-2</v>
@@ -49523,16 +49523,16 @@
     </row>
     <row r="757" spans="1:33">
       <c r="A757">
-        <v>3220</v>
+        <v>3419</v>
       </c>
       <c r="B757" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C757" t="s">
         <v>141</v>
       </c>
       <c r="D757" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E757" t="s">
         <v>150</v>
@@ -49559,16 +49559,16 @@
         <v>220</v>
       </c>
       <c r="O757">
-        <v>17726183</v>
+        <v>17839441</v>
       </c>
       <c r="P757" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q757" t="s">
         <v>238</v>
       </c>
       <c r="R757" s="1">
-        <v>46297.50044667824</v>
+        <v>46297.50017836806</v>
       </c>
       <c r="S757">
         <v>-2</v>
@@ -49591,16 +49591,16 @@
     </row>
     <row r="758" spans="1:33">
       <c r="A758">
-        <v>3419</v>
+        <v>3666</v>
       </c>
       <c r="B758" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C758" t="s">
         <v>141</v>
       </c>
       <c r="D758" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E758" t="s">
         <v>150</v>
@@ -49627,16 +49627,16 @@
         <v>220</v>
       </c>
       <c r="O758">
-        <v>17839441</v>
+        <v>17722579</v>
       </c>
       <c r="P758" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q758" t="s">
         <v>238</v>
       </c>
       <c r="R758" s="1">
-        <v>46297.50017836806</v>
+        <v>46297.50044712963</v>
       </c>
       <c r="S758">
         <v>-2</v>
@@ -49659,10 +49659,10 @@
     </row>
     <row r="759" spans="1:33">
       <c r="A759">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="B759" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C759" t="s">
         <v>141</v>
@@ -49695,7 +49695,7 @@
         <v>220</v>
       </c>
       <c r="O759">
-        <v>17722579</v>
+        <v>17314123</v>
       </c>
       <c r="P759" t="s">
         <v>228</v>
@@ -49704,7 +49704,7 @@
         <v>238</v>
       </c>
       <c r="R759" s="1">
-        <v>46297.50044712963</v>
+        <v>46297.50044756944</v>
       </c>
       <c r="S759">
         <v>-2</v>
@@ -49727,10 +49727,10 @@
     </row>
     <row r="760" spans="1:33">
       <c r="A760">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="B760" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C760" t="s">
         <v>141</v>
@@ -49763,7 +49763,7 @@
         <v>220</v>
       </c>
       <c r="O760">
-        <v>17314123</v>
+        <v>17314278</v>
       </c>
       <c r="P760" t="s">
         <v>228</v>
@@ -49772,7 +49772,7 @@
         <v>238</v>
       </c>
       <c r="R760" s="1">
-        <v>46297.50044756944</v>
+        <v>46297.50044806713</v>
       </c>
       <c r="S760">
         <v>-2</v>
@@ -49795,10 +49795,10 @@
     </row>
     <row r="761" spans="1:33">
       <c r="A761">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="B761" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C761" t="s">
         <v>141</v>
@@ -49831,7 +49831,7 @@
         <v>220</v>
       </c>
       <c r="O761">
-        <v>17314278</v>
+        <v>17772336</v>
       </c>
       <c r="P761" t="s">
         <v>228</v>
@@ -49840,7 +49840,7 @@
         <v>238</v>
       </c>
       <c r="R761" s="1">
-        <v>46297.50044806713</v>
+        <v>46297.50044849537</v>
       </c>
       <c r="S761">
         <v>-2</v>
@@ -49863,10 +49863,10 @@
     </row>
     <row r="762" spans="1:33">
       <c r="A762">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="B762" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C762" t="s">
         <v>141</v>
@@ -49899,7 +49899,7 @@
         <v>220</v>
       </c>
       <c r="O762">
-        <v>17772336</v>
+        <v>17035228</v>
       </c>
       <c r="P762" t="s">
         <v>228</v>
@@ -49908,7 +49908,7 @@
         <v>238</v>
       </c>
       <c r="R762" s="1">
-        <v>46297.50044849537</v>
+        <v>46297.50044895833</v>
       </c>
       <c r="S762">
         <v>-2</v>
@@ -49931,10 +49931,10 @@
     </row>
     <row r="763" spans="1:33">
       <c r="A763">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="B763" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C763" t="s">
         <v>141</v>
@@ -49967,7 +49967,7 @@
         <v>220</v>
       </c>
       <c r="O763">
-        <v>17035228</v>
+        <v>17772471</v>
       </c>
       <c r="P763" t="s">
         <v>228</v>
@@ -49976,7 +49976,7 @@
         <v>238</v>
       </c>
       <c r="R763" s="1">
-        <v>46297.50044895833</v>
+        <v>46297.50044939815</v>
       </c>
       <c r="S763">
         <v>-2</v>
@@ -49999,10 +49999,10 @@
     </row>
     <row r="764" spans="1:33">
       <c r="A764">
-        <v>3671</v>
+        <v>4614</v>
       </c>
       <c r="B764" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C764" t="s">
         <v>141</v>
@@ -50035,7 +50035,7 @@
         <v>220</v>
       </c>
       <c r="O764">
-        <v>17772471</v>
+        <v>17880068</v>
       </c>
       <c r="P764" t="s">
         <v>228</v>
@@ -50044,7 +50044,7 @@
         <v>238</v>
       </c>
       <c r="R764" s="1">
-        <v>46297.50044939815</v>
+        <v>46297.50044983796</v>
       </c>
       <c r="S764">
         <v>-2</v>
@@ -50067,10 +50067,10 @@
     </row>
     <row r="765" spans="1:33">
       <c r="A765">
-        <v>4614</v>
+        <v>3210</v>
       </c>
       <c r="B765" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C765" t="s">
         <v>141</v>
@@ -50085,7 +50085,7 @@
         <v>147</v>
       </c>
       <c r="G765">
-        <v>6120</v>
+        <v>6121</v>
       </c>
       <c r="H765">
         <v>0</v>
@@ -50094,16 +50094,16 @@
         <v>156</v>
       </c>
       <c r="J765" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="L765" s="1">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="N765" t="s">
         <v>220</v>
       </c>
       <c r="O765">
-        <v>17880068</v>
+        <v>17409031</v>
       </c>
       <c r="P765" t="s">
         <v>228</v>
@@ -50112,10 +50112,10 @@
         <v>238</v>
       </c>
       <c r="R765" s="1">
-        <v>46297.50044983796</v>
+        <v>46294.47617453703</v>
       </c>
       <c r="S765">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="T765" t="s">
         <v>242</v>
@@ -50135,16 +50135,16 @@
     </row>
     <row r="766" spans="1:33">
       <c r="A766">
-        <v>3210</v>
+        <v>3212</v>
       </c>
       <c r="B766" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C766" t="s">
         <v>141</v>
       </c>
       <c r="D766" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E766" t="s">
         <v>150</v>
@@ -50171,7 +50171,7 @@
         <v>220</v>
       </c>
       <c r="O766">
-        <v>17409031</v>
+        <v>17515182</v>
       </c>
       <c r="P766" t="s">
         <v>228</v>
@@ -50180,7 +50180,7 @@
         <v>238</v>
       </c>
       <c r="R766" s="1">
-        <v>46294.47617453703</v>
+        <v>46294.47617489583</v>
       </c>
       <c r="S766">
         <v>5</v>
@@ -50203,10 +50203,10 @@
     </row>
     <row r="767" spans="1:33">
       <c r="A767">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="B767" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C767" t="s">
         <v>141</v>
@@ -50239,7 +50239,7 @@
         <v>220</v>
       </c>
       <c r="O767">
-        <v>17515182</v>
+        <v>17618724</v>
       </c>
       <c r="P767" t="s">
         <v>228</v>
@@ -50248,7 +50248,7 @@
         <v>238</v>
       </c>
       <c r="R767" s="1">
-        <v>46294.47617489583</v>
+        <v>46294.47617527778</v>
       </c>
       <c r="S767">
         <v>5</v>
@@ -50271,10 +50271,10 @@
     </row>
     <row r="768" spans="1:33">
       <c r="A768">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="B768" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C768" t="s">
         <v>141</v>
@@ -50307,7 +50307,7 @@
         <v>220</v>
       </c>
       <c r="O768">
-        <v>17618724</v>
+        <v>17259082</v>
       </c>
       <c r="P768" t="s">
         <v>228</v>
@@ -50316,7 +50316,7 @@
         <v>238</v>
       </c>
       <c r="R768" s="1">
-        <v>46294.47617527778</v>
+        <v>46294.4761756713</v>
       </c>
       <c r="S768">
         <v>5</v>
@@ -50339,10 +50339,10 @@
     </row>
     <row r="769" spans="1:33">
       <c r="A769">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="B769" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C769" t="s">
         <v>141</v>
@@ -50351,7 +50351,7 @@
         <v>142</v>
       </c>
       <c r="E769" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F769" t="s">
         <v>147</v>
@@ -50375,7 +50375,7 @@
         <v>220</v>
       </c>
       <c r="O769">
-        <v>17259082</v>
+        <v>17618804</v>
       </c>
       <c r="P769" t="s">
         <v>228</v>
@@ -50384,7 +50384,7 @@
         <v>238</v>
       </c>
       <c r="R769" s="1">
-        <v>46294.4761756713</v>
+        <v>46294.47617598379</v>
       </c>
       <c r="S769">
         <v>5</v>
@@ -50407,19 +50407,19 @@
     </row>
     <row r="770" spans="1:33">
       <c r="A770">
-        <v>3215</v>
+        <v>3218</v>
       </c>
       <c r="B770" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C770" t="s">
         <v>141</v>
       </c>
       <c r="D770" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E770" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F770" t="s">
         <v>147</v>
@@ -50443,7 +50443,7 @@
         <v>220</v>
       </c>
       <c r="O770">
-        <v>17618804</v>
+        <v>17135188</v>
       </c>
       <c r="P770" t="s">
         <v>228</v>
@@ -50452,7 +50452,7 @@
         <v>238</v>
       </c>
       <c r="R770" s="1">
-        <v>46294.47617598379</v>
+        <v>46294.47617638889</v>
       </c>
       <c r="S770">
         <v>5</v>
@@ -50475,16 +50475,16 @@
     </row>
     <row r="771" spans="1:33">
       <c r="A771">
-        <v>3218</v>
+        <v>3419</v>
       </c>
       <c r="B771" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C771" t="s">
         <v>141</v>
       </c>
       <c r="D771" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E771" t="s">
         <v>150</v>
@@ -50511,16 +50511,16 @@
         <v>220</v>
       </c>
       <c r="O771">
-        <v>17135188</v>
+        <v>17839451</v>
       </c>
       <c r="P771" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q771" t="s">
         <v>238</v>
       </c>
       <c r="R771" s="1">
-        <v>46294.47617638889</v>
+        <v>46294.47562336805</v>
       </c>
       <c r="S771">
         <v>5</v>
@@ -50543,16 +50543,16 @@
     </row>
     <row r="772" spans="1:33">
       <c r="A772">
-        <v>3419</v>
+        <v>3666</v>
       </c>
       <c r="B772" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C772" t="s">
         <v>141</v>
       </c>
       <c r="D772" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E772" t="s">
         <v>150</v>
@@ -50579,16 +50579,16 @@
         <v>220</v>
       </c>
       <c r="O772">
-        <v>17839451</v>
+        <v>17722589</v>
       </c>
       <c r="P772" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q772" t="s">
         <v>238</v>
       </c>
       <c r="R772" s="1">
-        <v>46294.47562336805</v>
+        <v>46294.47617682871</v>
       </c>
       <c r="S772">
         <v>5</v>
@@ -50611,10 +50611,10 @@
     </row>
     <row r="773" spans="1:33">
       <c r="A773">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="B773" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C773" t="s">
         <v>141</v>
@@ -50647,7 +50647,7 @@
         <v>220</v>
       </c>
       <c r="O773">
-        <v>17722589</v>
+        <v>17314133</v>
       </c>
       <c r="P773" t="s">
         <v>228</v>
@@ -50656,7 +50656,7 @@
         <v>238</v>
       </c>
       <c r="R773" s="1">
-        <v>46294.47617682871</v>
+        <v>46294.47617710648</v>
       </c>
       <c r="S773">
         <v>5</v>
@@ -50679,10 +50679,10 @@
     </row>
     <row r="774" spans="1:33">
       <c r="A774">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="B774" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C774" t="s">
         <v>141</v>
@@ -50715,7 +50715,7 @@
         <v>220</v>
       </c>
       <c r="O774">
-        <v>17314133</v>
+        <v>17314288</v>
       </c>
       <c r="P774" t="s">
         <v>228</v>
@@ -50724,7 +50724,7 @@
         <v>238</v>
       </c>
       <c r="R774" s="1">
-        <v>46294.47617710648</v>
+        <v>46294.4761774537</v>
       </c>
       <c r="S774">
         <v>5</v>
@@ -50747,10 +50747,10 @@
     </row>
     <row r="775" spans="1:33">
       <c r="A775">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="B775" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C775" t="s">
         <v>141</v>
@@ -50783,7 +50783,7 @@
         <v>220</v>
       </c>
       <c r="O775">
-        <v>17314288</v>
+        <v>17772346</v>
       </c>
       <c r="P775" t="s">
         <v>228</v>
@@ -50792,7 +50792,7 @@
         <v>238</v>
       </c>
       <c r="R775" s="1">
-        <v>46294.4761774537</v>
+        <v>46294.47617782407</v>
       </c>
       <c r="S775">
         <v>5</v>
@@ -50815,10 +50815,10 @@
     </row>
     <row r="776" spans="1:33">
       <c r="A776">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="B776" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C776" t="s">
         <v>141</v>
@@ -50851,7 +50851,7 @@
         <v>220</v>
       </c>
       <c r="O776">
-        <v>17772346</v>
+        <v>17035252</v>
       </c>
       <c r="P776" t="s">
         <v>228</v>
@@ -50860,7 +50860,7 @@
         <v>238</v>
       </c>
       <c r="R776" s="1">
-        <v>46294.47617782407</v>
+        <v>46294.4761781713</v>
       </c>
       <c r="S776">
         <v>5</v>
@@ -50883,10 +50883,10 @@
     </row>
     <row r="777" spans="1:33">
       <c r="A777">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="B777" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C777" t="s">
         <v>141</v>
@@ -50919,7 +50919,7 @@
         <v>220</v>
       </c>
       <c r="O777">
-        <v>17035252</v>
+        <v>17772481</v>
       </c>
       <c r="P777" t="s">
         <v>228</v>
@@ -50928,7 +50928,7 @@
         <v>238</v>
       </c>
       <c r="R777" s="1">
-        <v>46294.4761781713</v>
+        <v>46294.47617857639</v>
       </c>
       <c r="S777">
         <v>5</v>
@@ -50951,10 +50951,10 @@
     </row>
     <row r="778" spans="1:33">
       <c r="A778">
-        <v>3671</v>
+        <v>4614</v>
       </c>
       <c r="B778" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C778" t="s">
         <v>141</v>
@@ -50987,7 +50987,7 @@
         <v>220</v>
       </c>
       <c r="O778">
-        <v>17772481</v>
+        <v>17880078</v>
       </c>
       <c r="P778" t="s">
         <v>228</v>
@@ -50996,7 +50996,7 @@
         <v>238</v>
       </c>
       <c r="R778" s="1">
-        <v>46294.47617857639</v>
+        <v>46294.47617891204</v>
       </c>
       <c r="S778">
         <v>5</v>
@@ -51019,10 +51019,10 @@
     </row>
     <row r="779" spans="1:33">
       <c r="A779">
-        <v>4614</v>
+        <v>3210</v>
       </c>
       <c r="B779" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C779" t="s">
         <v>141</v>
@@ -51037,7 +51037,7 @@
         <v>147</v>
       </c>
       <c r="G779">
-        <v>6121</v>
+        <v>6122</v>
       </c>
       <c r="H779">
         <v>0</v>
@@ -51046,16 +51046,16 @@
         <v>156</v>
       </c>
       <c r="J779" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="L779" s="1">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="N779" t="s">
         <v>220</v>
       </c>
       <c r="O779">
-        <v>17880078</v>
+        <v>17409041</v>
       </c>
       <c r="P779" t="s">
         <v>228</v>
@@ -51064,10 +51064,10 @@
         <v>238</v>
       </c>
       <c r="R779" s="1">
-        <v>46294.47617891204</v>
+        <v>46294.47609409722</v>
       </c>
       <c r="S779">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="T779" t="s">
         <v>242</v>
@@ -51087,16 +51087,16 @@
     </row>
     <row r="780" spans="1:33">
       <c r="A780">
-        <v>3210</v>
+        <v>3213</v>
       </c>
       <c r="B780" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C780" t="s">
         <v>141</v>
       </c>
       <c r="D780" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E780" t="s">
         <v>150</v>
@@ -51123,7 +51123,7 @@
         <v>220</v>
       </c>
       <c r="O780">
-        <v>17409041</v>
+        <v>17618734</v>
       </c>
       <c r="P780" t="s">
         <v>228</v>
@@ -51132,7 +51132,7 @@
         <v>238</v>
       </c>
       <c r="R780" s="1">
-        <v>46294.47609409722</v>
+        <v>46294.47609446759</v>
       </c>
       <c r="S780">
         <v>-2</v>
@@ -51155,10 +51155,10 @@
     </row>
     <row r="781" spans="1:33">
       <c r="A781">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="B781" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C781" t="s">
         <v>141</v>
@@ -51191,7 +51191,7 @@
         <v>220</v>
       </c>
       <c r="O781">
-        <v>17618734</v>
+        <v>17259092</v>
       </c>
       <c r="P781" t="s">
         <v>228</v>
@@ -51200,7 +51200,7 @@
         <v>238</v>
       </c>
       <c r="R781" s="1">
-        <v>46294.47609446759</v>
+        <v>46294.47609488426</v>
       </c>
       <c r="S781">
         <v>-2</v>
@@ -51223,10 +51223,10 @@
     </row>
     <row r="782" spans="1:33">
       <c r="A782">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="B782" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C782" t="s">
         <v>141</v>
@@ -51235,7 +51235,7 @@
         <v>142</v>
       </c>
       <c r="E782" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F782" t="s">
         <v>147</v>
@@ -51259,7 +51259,7 @@
         <v>220</v>
       </c>
       <c r="O782">
-        <v>17259092</v>
+        <v>17618814</v>
       </c>
       <c r="P782" t="s">
         <v>228</v>
@@ -51268,7 +51268,7 @@
         <v>238</v>
       </c>
       <c r="R782" s="1">
-        <v>46294.47609488426</v>
+        <v>46294.47609523148</v>
       </c>
       <c r="S782">
         <v>-2</v>
@@ -51291,19 +51291,19 @@
     </row>
     <row r="783" spans="1:33">
       <c r="A783">
-        <v>3215</v>
+        <v>3419</v>
       </c>
       <c r="B783" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C783" t="s">
         <v>141</v>
       </c>
       <c r="D783" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E783" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F783" t="s">
         <v>147</v>
@@ -51327,16 +51327,16 @@
         <v>220</v>
       </c>
       <c r="O783">
-        <v>17618814</v>
+        <v>17839461</v>
       </c>
       <c r="P783" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q783" t="s">
         <v>238</v>
       </c>
       <c r="R783" s="1">
-        <v>46294.47609523148</v>
+        <v>46294.4755502662</v>
       </c>
       <c r="S783">
         <v>-2</v>
@@ -51359,16 +51359,16 @@
     </row>
     <row r="784" spans="1:33">
       <c r="A784">
-        <v>3419</v>
+        <v>3666</v>
       </c>
       <c r="B784" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C784" t="s">
         <v>141</v>
       </c>
       <c r="D784" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E784" t="s">
         <v>150</v>
@@ -51395,16 +51395,16 @@
         <v>220</v>
       </c>
       <c r="O784">
-        <v>17839461</v>
+        <v>17722599</v>
       </c>
       <c r="P784" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q784" t="s">
         <v>238</v>
       </c>
       <c r="R784" s="1">
-        <v>46294.4755502662</v>
+        <v>46294.47609559027</v>
       </c>
       <c r="S784">
         <v>-2</v>
@@ -51427,10 +51427,10 @@
     </row>
     <row r="785" spans="1:33">
       <c r="A785">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="B785" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C785" t="s">
         <v>141</v>
@@ -51463,7 +51463,7 @@
         <v>220</v>
       </c>
       <c r="O785">
-        <v>17722599</v>
+        <v>17314143</v>
       </c>
       <c r="P785" t="s">
         <v>228</v>
@@ -51472,7 +51472,7 @@
         <v>238</v>
       </c>
       <c r="R785" s="1">
-        <v>46294.47609559027</v>
+        <v>46294.47609604167</v>
       </c>
       <c r="S785">
         <v>-2</v>
@@ -51495,10 +51495,10 @@
     </row>
     <row r="786" spans="1:33">
       <c r="A786">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="B786" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C786" t="s">
         <v>141</v>
@@ -51531,7 +51531,7 @@
         <v>220</v>
       </c>
       <c r="O786">
-        <v>17314143</v>
+        <v>17314298</v>
       </c>
       <c r="P786" t="s">
         <v>228</v>
@@ -51540,7 +51540,7 @@
         <v>238</v>
       </c>
       <c r="R786" s="1">
-        <v>46294.47609604167</v>
+        <v>46294.47609636574</v>
       </c>
       <c r="S786">
         <v>-2</v>
@@ -51563,10 +51563,10 @@
     </row>
     <row r="787" spans="1:33">
       <c r="A787">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="B787" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C787" t="s">
         <v>141</v>
@@ -51599,7 +51599,7 @@
         <v>220</v>
       </c>
       <c r="O787">
-        <v>17314298</v>
+        <v>17772356</v>
       </c>
       <c r="P787" t="s">
         <v>228</v>
@@ -51608,7 +51608,7 @@
         <v>238</v>
       </c>
       <c r="R787" s="1">
-        <v>46294.47609636574</v>
+        <v>46294.47609671296</v>
       </c>
       <c r="S787">
         <v>-2</v>
@@ -51631,10 +51631,10 @@
     </row>
     <row r="788" spans="1:33">
       <c r="A788">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="B788" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C788" t="s">
         <v>141</v>
@@ -51667,7 +51667,7 @@
         <v>220</v>
       </c>
       <c r="O788">
-        <v>17772356</v>
+        <v>17035275</v>
       </c>
       <c r="P788" t="s">
         <v>228</v>
@@ -51676,7 +51676,7 @@
         <v>238</v>
       </c>
       <c r="R788" s="1">
-        <v>46294.47609671296</v>
+        <v>46294.47609734954</v>
       </c>
       <c r="S788">
         <v>-2</v>
@@ -51699,10 +51699,10 @@
     </row>
     <row r="789" spans="1:33">
       <c r="A789">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="B789" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C789" t="s">
         <v>141</v>
@@ -51735,7 +51735,7 @@
         <v>220</v>
       </c>
       <c r="O789">
-        <v>17035275</v>
+        <v>17772491</v>
       </c>
       <c r="P789" t="s">
         <v>228</v>
@@ -51744,7 +51744,7 @@
         <v>238</v>
       </c>
       <c r="R789" s="1">
-        <v>46294.47609734954</v>
+        <v>46294.47609777778</v>
       </c>
       <c r="S789">
         <v>-2</v>
@@ -51767,10 +51767,10 @@
     </row>
     <row r="790" spans="1:33">
       <c r="A790">
-        <v>3671</v>
+        <v>4614</v>
       </c>
       <c r="B790" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C790" t="s">
         <v>141</v>
@@ -51803,7 +51803,7 @@
         <v>220</v>
       </c>
       <c r="O790">
-        <v>17772491</v>
+        <v>17880088</v>
       </c>
       <c r="P790" t="s">
         <v>228</v>
@@ -51812,7 +51812,7 @@
         <v>238</v>
       </c>
       <c r="R790" s="1">
-        <v>46294.47609777778</v>
+        <v>46294.47609811342</v>
       </c>
       <c r="S790">
         <v>-2</v>
@@ -51835,10 +51835,10 @@
     </row>
     <row r="791" spans="1:33">
       <c r="A791">
-        <v>4614</v>
+        <v>3210</v>
       </c>
       <c r="B791" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C791" t="s">
         <v>141</v>
@@ -51853,7 +51853,7 @@
         <v>147</v>
       </c>
       <c r="G791">
-        <v>6122</v>
+        <v>6123</v>
       </c>
       <c r="H791">
         <v>0</v>
@@ -51862,16 +51862,16 @@
         <v>156</v>
       </c>
       <c r="J791" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="L791" s="1">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="N791" t="s">
         <v>220</v>
       </c>
       <c r="O791">
-        <v>17880088</v>
+        <v>17409051</v>
       </c>
       <c r="P791" t="s">
         <v>228</v>
@@ -51880,10 +51880,10 @@
         <v>238</v>
       </c>
       <c r="R791" s="1">
-        <v>46294.47609811342</v>
+        <v>46294.47598342592</v>
       </c>
       <c r="S791">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="T791" t="s">
         <v>242</v>
@@ -51903,16 +51903,16 @@
     </row>
     <row r="792" spans="1:33">
       <c r="A792">
-        <v>3210</v>
+        <v>3212</v>
       </c>
       <c r="B792" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C792" t="s">
         <v>141</v>
       </c>
       <c r="D792" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E792" t="s">
         <v>150</v>
@@ -51939,7 +51939,7 @@
         <v>220</v>
       </c>
       <c r="O792">
-        <v>17409051</v>
+        <v>17515202</v>
       </c>
       <c r="P792" t="s">
         <v>228</v>
@@ -51948,7 +51948,7 @@
         <v>238</v>
       </c>
       <c r="R792" s="1">
-        <v>46294.47598342592</v>
+        <v>46303.50172873843</v>
       </c>
       <c r="S792">
         <v>5</v>
@@ -51963,7 +51963,7 @@
         <v>0</v>
       </c>
       <c r="AB792" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG792" t="s">
         <v>264</v>
@@ -51971,10 +51971,10 @@
     </row>
     <row r="793" spans="1:33">
       <c r="A793">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="B793" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C793" t="s">
         <v>141</v>
@@ -52007,7 +52007,7 @@
         <v>220</v>
       </c>
       <c r="O793">
-        <v>17515202</v>
+        <v>17618744</v>
       </c>
       <c r="P793" t="s">
         <v>228</v>
@@ -52016,7 +52016,7 @@
         <v>238</v>
       </c>
       <c r="R793" s="1">
-        <v>46303.50172873843</v>
+        <v>46294.47598378472</v>
       </c>
       <c r="S793">
         <v>5</v>
@@ -52031,7 +52031,7 @@
         <v>0</v>
       </c>
       <c r="AB793" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG793" t="s">
         <v>264</v>
@@ -52039,10 +52039,10 @@
     </row>
     <row r="794" spans="1:33">
       <c r="A794">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="B794" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C794" t="s">
         <v>141</v>
@@ -52075,7 +52075,7 @@
         <v>220</v>
       </c>
       <c r="O794">
-        <v>17618744</v>
+        <v>17259102</v>
       </c>
       <c r="P794" t="s">
         <v>228</v>
@@ -52084,7 +52084,7 @@
         <v>238</v>
       </c>
       <c r="R794" s="1">
-        <v>46294.47598378472</v>
+        <v>46294.47598421296</v>
       </c>
       <c r="S794">
         <v>5</v>
@@ -52107,10 +52107,10 @@
     </row>
     <row r="795" spans="1:33">
       <c r="A795">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="B795" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C795" t="s">
         <v>141</v>
@@ -52119,7 +52119,7 @@
         <v>142</v>
       </c>
       <c r="E795" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F795" t="s">
         <v>147</v>
@@ -52143,7 +52143,7 @@
         <v>220</v>
       </c>
       <c r="O795">
-        <v>17259102</v>
+        <v>17618824</v>
       </c>
       <c r="P795" t="s">
         <v>228</v>
@@ -52152,7 +52152,7 @@
         <v>238</v>
       </c>
       <c r="R795" s="1">
-        <v>46294.47598421296</v>
+        <v>46294.47598456019</v>
       </c>
       <c r="S795">
         <v>5</v>
@@ -52175,19 +52175,19 @@
     </row>
     <row r="796" spans="1:33">
       <c r="A796">
-        <v>3215</v>
+        <v>3216</v>
       </c>
       <c r="B796" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C796" t="s">
         <v>141</v>
       </c>
       <c r="D796" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E796" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F796" t="s">
         <v>147</v>
@@ -52211,7 +52211,7 @@
         <v>220</v>
       </c>
       <c r="O796">
-        <v>17618824</v>
+        <v>17758766</v>
       </c>
       <c r="P796" t="s">
         <v>228</v>
@@ -52220,7 +52220,7 @@
         <v>238</v>
       </c>
       <c r="R796" s="1">
-        <v>46294.47598456019</v>
+        <v>46303.5017292824</v>
       </c>
       <c r="S796">
         <v>5</v>
@@ -52235,7 +52235,7 @@
         <v>0</v>
       </c>
       <c r="AB796" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG796" t="s">
         <v>264</v>
@@ -52243,10 +52243,10 @@
     </row>
     <row r="797" spans="1:33">
       <c r="A797">
-        <v>3216</v>
+        <v>3220</v>
       </c>
       <c r="B797" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C797" t="s">
         <v>141</v>
@@ -52279,7 +52279,7 @@
         <v>220</v>
       </c>
       <c r="O797">
-        <v>17758766</v>
+        <v>17726203</v>
       </c>
       <c r="P797" t="s">
         <v>228</v>
@@ -52288,7 +52288,7 @@
         <v>238</v>
       </c>
       <c r="R797" s="1">
-        <v>46303.5017292824</v>
+        <v>46303.5017297801</v>
       </c>
       <c r="S797">
         <v>5</v>
@@ -52311,16 +52311,16 @@
     </row>
     <row r="798" spans="1:33">
       <c r="A798">
-        <v>3220</v>
+        <v>3419</v>
       </c>
       <c r="B798" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C798" t="s">
         <v>141</v>
       </c>
       <c r="D798" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E798" t="s">
         <v>150</v>
@@ -52347,16 +52347,16 @@
         <v>220</v>
       </c>
       <c r="O798">
-        <v>17726203</v>
+        <v>17839471</v>
       </c>
       <c r="P798" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q798" t="s">
         <v>238</v>
       </c>
       <c r="R798" s="1">
-        <v>46303.5017297801</v>
+        <v>46294.47548111111</v>
       </c>
       <c r="S798">
         <v>5</v>
@@ -52371,7 +52371,7 @@
         <v>0</v>
       </c>
       <c r="AB798" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG798" t="s">
         <v>264</v>
@@ -52379,16 +52379,16 @@
     </row>
     <row r="799" spans="1:33">
       <c r="A799">
-        <v>3419</v>
+        <v>3666</v>
       </c>
       <c r="B799" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C799" t="s">
         <v>141</v>
       </c>
       <c r="D799" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E799" t="s">
         <v>150</v>
@@ -52415,16 +52415,16 @@
         <v>220</v>
       </c>
       <c r="O799">
-        <v>17839471</v>
+        <v>17722609</v>
       </c>
       <c r="P799" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q799" t="s">
         <v>238</v>
       </c>
       <c r="R799" s="1">
-        <v>46294.47548111111</v>
+        <v>46294.47598489583</v>
       </c>
       <c r="S799">
         <v>5</v>
@@ -52447,10 +52447,10 @@
     </row>
     <row r="800" spans="1:33">
       <c r="A800">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="B800" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C800" t="s">
         <v>141</v>
@@ -52483,7 +52483,7 @@
         <v>220</v>
       </c>
       <c r="O800">
-        <v>17722609</v>
+        <v>17314153</v>
       </c>
       <c r="P800" t="s">
         <v>228</v>
@@ -52492,7 +52492,7 @@
         <v>238</v>
       </c>
       <c r="R800" s="1">
-        <v>46294.47598489583</v>
+        <v>46294.47598528935</v>
       </c>
       <c r="S800">
         <v>5</v>
@@ -52515,10 +52515,10 @@
     </row>
     <row r="801" spans="1:33">
       <c r="A801">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="B801" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C801" t="s">
         <v>141</v>
@@ -52551,7 +52551,7 @@
         <v>220</v>
       </c>
       <c r="O801">
-        <v>17314153</v>
+        <v>17314308</v>
       </c>
       <c r="P801" t="s">
         <v>228</v>
@@ -52560,7 +52560,7 @@
         <v>238</v>
       </c>
       <c r="R801" s="1">
-        <v>46294.47598528935</v>
+        <v>46294.47598581018</v>
       </c>
       <c r="S801">
         <v>5</v>
@@ -52583,10 +52583,10 @@
     </row>
     <row r="802" spans="1:33">
       <c r="A802">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="B802" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C802" t="s">
         <v>141</v>
@@ -52619,7 +52619,7 @@
         <v>220</v>
       </c>
       <c r="O802">
-        <v>17314308</v>
+        <v>17772366</v>
       </c>
       <c r="P802" t="s">
         <v>228</v>
@@ -52628,7 +52628,7 @@
         <v>238</v>
       </c>
       <c r="R802" s="1">
-        <v>46294.47598581018</v>
+        <v>46294.47598618056</v>
       </c>
       <c r="S802">
         <v>5</v>
@@ -52651,10 +52651,10 @@
     </row>
     <row r="803" spans="1:33">
       <c r="A803">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="B803" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C803" t="s">
         <v>141</v>
@@ -52687,7 +52687,7 @@
         <v>220</v>
       </c>
       <c r="O803">
-        <v>17772366</v>
+        <v>17035300</v>
       </c>
       <c r="P803" t="s">
         <v>228</v>
@@ -52696,7 +52696,7 @@
         <v>238</v>
       </c>
       <c r="R803" s="1">
-        <v>46294.47598618056</v>
+        <v>46294.47598663194</v>
       </c>
       <c r="S803">
         <v>5</v>
@@ -52719,10 +52719,10 @@
     </row>
     <row r="804" spans="1:33">
       <c r="A804">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="B804" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C804" t="s">
         <v>141</v>
@@ -52755,7 +52755,7 @@
         <v>220</v>
       </c>
       <c r="O804">
-        <v>17035300</v>
+        <v>17772501</v>
       </c>
       <c r="P804" t="s">
         <v>228</v>
@@ -52764,7 +52764,7 @@
         <v>238</v>
       </c>
       <c r="R804" s="1">
-        <v>46294.47598663194</v>
+        <v>46294.47598710648</v>
       </c>
       <c r="S804">
         <v>5</v>
@@ -52787,10 +52787,10 @@
     </row>
     <row r="805" spans="1:33">
       <c r="A805">
-        <v>3671</v>
+        <v>4614</v>
       </c>
       <c r="B805" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C805" t="s">
         <v>141</v>
@@ -52823,7 +52823,7 @@
         <v>220</v>
       </c>
       <c r="O805">
-        <v>17772501</v>
+        <v>17880098</v>
       </c>
       <c r="P805" t="s">
         <v>228</v>
@@ -52832,7 +52832,7 @@
         <v>238</v>
       </c>
       <c r="R805" s="1">
-        <v>46294.47598710648</v>
+        <v>46294.47598746528</v>
       </c>
       <c r="S805">
         <v>5</v>
@@ -52855,10 +52855,10 @@
     </row>
     <row r="806" spans="1:33">
       <c r="A806">
-        <v>4614</v>
+        <v>3210</v>
       </c>
       <c r="B806" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C806" t="s">
         <v>141</v>
@@ -52873,7 +52873,7 @@
         <v>147</v>
       </c>
       <c r="G806">
-        <v>6123</v>
+        <v>6098</v>
       </c>
       <c r="H806">
         <v>0</v>
@@ -52882,16 +52882,19 @@
         <v>156</v>
       </c>
       <c r="J806" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="L806" s="1">
-        <v>46304</v>
+        <v>46300</v>
+      </c>
+      <c r="M806" t="s">
+        <v>215</v>
       </c>
       <c r="N806" t="s">
         <v>220</v>
       </c>
       <c r="O806">
-        <v>17880098</v>
+        <v>17409001</v>
       </c>
       <c r="P806" t="s">
         <v>228</v>
@@ -52900,10 +52903,10 @@
         <v>238</v>
       </c>
       <c r="R806" s="1">
-        <v>46294.47598746528</v>
+        <v>46287.46396708333</v>
       </c>
       <c r="S806">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T806" t="s">
         <v>242</v>
@@ -52911,6 +52914,9 @@
       <c r="U806" t="s">
         <v>244</v>
       </c>
+      <c r="W806" t="s">
+        <v>254</v>
+      </c>
       <c r="AA806">
         <v>0</v>
       </c>
@@ -52918,21 +52924,21 @@
         <v>229</v>
       </c>
       <c r="AG806" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="807" spans="1:33">
       <c r="A807">
-        <v>3210</v>
+        <v>3212</v>
       </c>
       <c r="B807" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C807" t="s">
         <v>141</v>
       </c>
       <c r="D807" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E807" t="s">
         <v>150</v>
@@ -52941,7 +52947,7 @@
         <v>147</v>
       </c>
       <c r="G807">
-        <v>6098</v>
+        <v>6142</v>
       </c>
       <c r="H807">
         <v>0</v>
@@ -52950,19 +52956,19 @@
         <v>156</v>
       </c>
       <c r="J807" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L807" s="1">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="M807" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N807" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O807">
-        <v>17409001</v>
+        <v>17515233</v>
       </c>
       <c r="P807" t="s">
         <v>228</v>
@@ -52971,10 +52977,10 @@
         <v>238</v>
       </c>
       <c r="R807" s="1">
-        <v>46287.46396708333</v>
+        <v>46282.3269916088</v>
       </c>
       <c r="S807">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T807" t="s">
         <v>242</v>
@@ -52997,10 +53003,10 @@
     </row>
     <row r="808" spans="1:33">
       <c r="A808">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="B808" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C808" t="s">
         <v>141</v>
@@ -53030,13 +53036,13 @@
         <v>46296</v>
       </c>
       <c r="M808" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N808" t="s">
         <v>221</v>
       </c>
       <c r="O808">
-        <v>17515233</v>
+        <v>17618755</v>
       </c>
       <c r="P808" t="s">
         <v>228</v>
@@ -53045,7 +53051,7 @@
         <v>238</v>
       </c>
       <c r="R808" s="1">
-        <v>46282.3269916088</v>
+        <v>46282.32699195602</v>
       </c>
       <c r="S808">
         <v>13</v>
@@ -53057,7 +53063,7 @@
         <v>244</v>
       </c>
       <c r="W808" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AA808">
         <v>0</v>
@@ -53071,10 +53077,10 @@
     </row>
     <row r="809" spans="1:33">
       <c r="A809">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="B809" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C809" t="s">
         <v>141</v>
@@ -53104,13 +53110,13 @@
         <v>46296</v>
       </c>
       <c r="M809" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N809" t="s">
         <v>221</v>
       </c>
       <c r="O809">
-        <v>17618755</v>
+        <v>17259113</v>
       </c>
       <c r="P809" t="s">
         <v>228</v>
@@ -53119,7 +53125,7 @@
         <v>238</v>
       </c>
       <c r="R809" s="1">
-        <v>46282.32699195602</v>
+        <v>46282.32699233796</v>
       </c>
       <c r="S809">
         <v>13</v>
@@ -53131,7 +53137,7 @@
         <v>244</v>
       </c>
       <c r="W809" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AA809">
         <v>0</v>
@@ -53145,10 +53151,10 @@
     </row>
     <row r="810" spans="1:33">
       <c r="A810">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="B810" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C810" t="s">
         <v>141</v>
@@ -53157,7 +53163,7 @@
         <v>142</v>
       </c>
       <c r="E810" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F810" t="s">
         <v>147</v>
@@ -53178,13 +53184,13 @@
         <v>46296</v>
       </c>
       <c r="M810" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N810" t="s">
         <v>221</v>
       </c>
       <c r="O810">
-        <v>17259113</v>
+        <v>17618835</v>
       </c>
       <c r="P810" t="s">
         <v>228</v>
@@ -53193,7 +53199,7 @@
         <v>238</v>
       </c>
       <c r="R810" s="1">
-        <v>46282.32699233796</v>
+        <v>46282.32699266203</v>
       </c>
       <c r="S810">
         <v>13</v>
@@ -53205,7 +53211,7 @@
         <v>244</v>
       </c>
       <c r="W810" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AA810">
         <v>0</v>
@@ -53219,10 +53225,10 @@
     </row>
     <row r="811" spans="1:33">
       <c r="A811">
-        <v>3215</v>
+        <v>3792</v>
       </c>
       <c r="B811" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="C811" t="s">
         <v>141</v>
@@ -53231,7 +53237,7 @@
         <v>142</v>
       </c>
       <c r="E811" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F811" t="s">
         <v>147</v>
@@ -53252,13 +53258,13 @@
         <v>46296</v>
       </c>
       <c r="M811" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N811" t="s">
         <v>221</v>
       </c>
       <c r="O811">
-        <v>17618835</v>
+        <v>17207208</v>
       </c>
       <c r="P811" t="s">
         <v>228</v>
@@ -53267,7 +53273,7 @@
         <v>238</v>
       </c>
       <c r="R811" s="1">
-        <v>46282.32699266203</v>
+        <v>46282.32699290509</v>
       </c>
       <c r="S811">
         <v>13</v>
@@ -53279,7 +53285,7 @@
         <v>244</v>
       </c>
       <c r="W811" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AA811">
         <v>0</v>
@@ -53293,16 +53299,16 @@
     </row>
     <row r="812" spans="1:33">
       <c r="A812">
-        <v>3792</v>
+        <v>4613</v>
       </c>
       <c r="B812" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C812" t="s">
         <v>141</v>
       </c>
       <c r="D812" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E812" t="s">
         <v>150</v>
@@ -53326,13 +53332,13 @@
         <v>46296</v>
       </c>
       <c r="M812" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N812" t="s">
         <v>221</v>
       </c>
       <c r="O812">
-        <v>17207208</v>
+        <v>17606826</v>
       </c>
       <c r="P812" t="s">
         <v>228</v>
@@ -53341,7 +53347,7 @@
         <v>238</v>
       </c>
       <c r="R812" s="1">
-        <v>46282.32699290509</v>
+        <v>46282.32699324074</v>
       </c>
       <c r="S812">
         <v>13</v>
@@ -53353,7 +53359,7 @@
         <v>244</v>
       </c>
       <c r="W812" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AA812">
         <v>0</v>
@@ -53367,16 +53373,16 @@
     </row>
     <row r="813" spans="1:33">
       <c r="A813">
-        <v>4613</v>
+        <v>2835</v>
       </c>
       <c r="B813" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C813" t="s">
         <v>141</v>
       </c>
       <c r="D813" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E813" t="s">
         <v>150</v>
@@ -53385,55 +53391,49 @@
         <v>147</v>
       </c>
       <c r="G813">
-        <v>6142</v>
+        <v>2811</v>
       </c>
       <c r="H813">
-        <v>0</v>
+        <v>2764</v>
       </c>
       <c r="I813" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="J813" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L813" s="1">
-        <v>46296</v>
-      </c>
-      <c r="M813" t="s">
-        <v>219</v>
+        <v>46315</v>
       </c>
       <c r="N813" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O813">
-        <v>17606826</v>
+        <v>17089769</v>
       </c>
       <c r="P813" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q813" t="s">
         <v>238</v>
       </c>
       <c r="R813" s="1">
-        <v>46282.32699324074</v>
+        <v>46296.72939065972</v>
       </c>
       <c r="S813">
-        <v>13</v>
+        <v>-6</v>
       </c>
       <c r="T813" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U813" t="s">
         <v>244</v>
       </c>
-      <c r="W813" t="s">
-        <v>256</v>
-      </c>
       <c r="AA813">
         <v>0</v>
       </c>
       <c r="AB813" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG813" t="s">
         <v>263</v>
@@ -53441,10 +53441,10 @@
     </row>
     <row r="814" spans="1:33">
       <c r="A814">
-        <v>2835</v>
+        <v>3209</v>
       </c>
       <c r="B814" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C814" t="s">
         <v>141</v>
@@ -53453,31 +53453,31 @@
         <v>143</v>
       </c>
       <c r="E814" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F814" t="s">
         <v>147</v>
       </c>
       <c r="G814">
-        <v>2811</v>
+        <v>5636</v>
       </c>
       <c r="H814">
-        <v>2764</v>
+        <v>0</v>
       </c>
       <c r="I814" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="J814" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="L814" s="1">
-        <v>46315</v>
+        <v>46302</v>
       </c>
       <c r="N814" t="s">
         <v>220</v>
       </c>
       <c r="O814">
-        <v>17089769</v>
+        <v>17134958</v>
       </c>
       <c r="P814" t="s">
         <v>230</v>
@@ -53486,10 +53486,10 @@
         <v>238</v>
       </c>
       <c r="R814" s="1">
-        <v>46296.72939065972</v>
+        <v>46302.6853569213</v>
       </c>
       <c r="S814">
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="T814" t="s">
         <v>243</v>
@@ -53501,18 +53501,18 @@
         <v>0</v>
       </c>
       <c r="AB814" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="AG814" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="815" spans="1:33">
       <c r="A815">
-        <v>3209</v>
+        <v>3480</v>
       </c>
       <c r="B815" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C815" t="s">
         <v>141</v>
@@ -53521,7 +53521,7 @@
         <v>143</v>
       </c>
       <c r="E815" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F815" t="s">
         <v>147</v>
@@ -53545,7 +53545,7 @@
         <v>220</v>
       </c>
       <c r="O815">
-        <v>17134958</v>
+        <v>17821430</v>
       </c>
       <c r="P815" t="s">
         <v>230</v>
@@ -53554,7 +53554,7 @@
         <v>238</v>
       </c>
       <c r="R815" s="1">
-        <v>46302.6853569213</v>
+        <v>46302.68535739584</v>
       </c>
       <c r="S815">
         <v>7</v>
@@ -53577,16 +53577,16 @@
     </row>
     <row r="816" spans="1:33">
       <c r="A816">
-        <v>3480</v>
+        <v>2804</v>
       </c>
       <c r="B816" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C816" t="s">
         <v>141</v>
       </c>
       <c r="D816" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E816" t="s">
         <v>150</v>
@@ -53595,7 +53595,7 @@
         <v>147</v>
       </c>
       <c r="G816">
-        <v>5636</v>
+        <v>5731</v>
       </c>
       <c r="H816">
         <v>0</v>
@@ -53604,16 +53604,19 @@
         <v>157</v>
       </c>
       <c r="J816" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="L816" s="1">
-        <v>46302</v>
+        <v>46296</v>
+      </c>
+      <c r="M816" t="s">
+        <v>211</v>
       </c>
       <c r="N816" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O816">
-        <v>17821430</v>
+        <v>17326583</v>
       </c>
       <c r="P816" t="s">
         <v>230</v>
@@ -53622,10 +53625,10 @@
         <v>238</v>
       </c>
       <c r="R816" s="1">
-        <v>46302.68535739584</v>
+        <v>46301.66652939815</v>
       </c>
       <c r="S816">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T816" t="s">
         <v>243</v>
@@ -53633,22 +53636,25 @@
       <c r="U816" t="s">
         <v>244</v>
       </c>
+      <c r="W816" t="s">
+        <v>246</v>
+      </c>
       <c r="AA816">
         <v>0</v>
       </c>
       <c r="AB816" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG816" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="817" spans="1:33">
       <c r="A817">
-        <v>2804</v>
+        <v>2829</v>
       </c>
       <c r="B817" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C817" t="s">
         <v>141</v>
@@ -53684,7 +53690,7 @@
         <v>221</v>
       </c>
       <c r="O817">
-        <v>17326583</v>
+        <v>17730846</v>
       </c>
       <c r="P817" t="s">
         <v>230</v>
@@ -53693,7 +53699,7 @@
         <v>238</v>
       </c>
       <c r="R817" s="1">
-        <v>46301.66652939815</v>
+        <v>46301.66652954861</v>
       </c>
       <c r="S817">
         <v>13</v>
@@ -53719,10 +53725,10 @@
     </row>
     <row r="818" spans="1:33">
       <c r="A818">
-        <v>2829</v>
+        <v>2830</v>
       </c>
       <c r="B818" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C818" t="s">
         <v>141</v>
@@ -53731,7 +53737,7 @@
         <v>145</v>
       </c>
       <c r="E818" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F818" t="s">
         <v>147</v>
@@ -53758,7 +53764,7 @@
         <v>221</v>
       </c>
       <c r="O818">
-        <v>17730846</v>
+        <v>17332660</v>
       </c>
       <c r="P818" t="s">
         <v>230</v>
@@ -53767,7 +53773,7 @@
         <v>238</v>
       </c>
       <c r="R818" s="1">
-        <v>46301.66652954861</v>
+        <v>46301.66652971064</v>
       </c>
       <c r="S818">
         <v>13</v>
@@ -53793,10 +53799,10 @@
     </row>
     <row r="819" spans="1:33">
       <c r="A819">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="B819" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C819" t="s">
         <v>141</v>
@@ -53805,7 +53811,7 @@
         <v>145</v>
       </c>
       <c r="E819" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F819" t="s">
         <v>147</v>
@@ -53832,7 +53838,7 @@
         <v>221</v>
       </c>
       <c r="O819">
-        <v>17332660</v>
+        <v>17743480</v>
       </c>
       <c r="P819" t="s">
         <v>230</v>
@@ -53841,7 +53847,7 @@
         <v>238</v>
       </c>
       <c r="R819" s="1">
-        <v>46301.66652971064</v>
+        <v>46301.66652986111</v>
       </c>
       <c r="S819">
         <v>13</v>
@@ -53867,10 +53873,10 @@
     </row>
     <row r="820" spans="1:33">
       <c r="A820">
-        <v>2831</v>
+        <v>2832</v>
       </c>
       <c r="B820" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C820" t="s">
         <v>141</v>
@@ -53879,7 +53885,7 @@
         <v>145</v>
       </c>
       <c r="E820" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F820" t="s">
         <v>147</v>
@@ -53906,7 +53912,7 @@
         <v>221</v>
       </c>
       <c r="O820">
-        <v>17743480</v>
+        <v>17743530</v>
       </c>
       <c r="P820" t="s">
         <v>230</v>
@@ -53915,7 +53921,7 @@
         <v>238</v>
       </c>
       <c r="R820" s="1">
-        <v>46301.66652986111</v>
+        <v>46301.66653001157</v>
       </c>
       <c r="S820">
         <v>13</v>
@@ -53941,10 +53947,10 @@
     </row>
     <row r="821" spans="1:33">
       <c r="A821">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="B821" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C821" t="s">
         <v>141</v>
@@ -53953,7 +53959,7 @@
         <v>145</v>
       </c>
       <c r="E821" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F821" t="s">
         <v>147</v>
@@ -53980,7 +53986,7 @@
         <v>221</v>
       </c>
       <c r="O821">
-        <v>17743530</v>
+        <v>17820062</v>
       </c>
       <c r="P821" t="s">
         <v>230</v>
@@ -53989,7 +53995,7 @@
         <v>238</v>
       </c>
       <c r="R821" s="1">
-        <v>46301.66653001157</v>
+        <v>46301.66653012732</v>
       </c>
       <c r="S821">
         <v>13</v>
@@ -54015,10 +54021,10 @@
     </row>
     <row r="822" spans="1:33">
       <c r="A822">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="B822" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C822" t="s">
         <v>141</v>
@@ -54054,7 +54060,7 @@
         <v>221</v>
       </c>
       <c r="O822">
-        <v>17820062</v>
+        <v>17385204</v>
       </c>
       <c r="P822" t="s">
         <v>230</v>
@@ -54063,7 +54069,7 @@
         <v>238</v>
       </c>
       <c r="R822" s="1">
-        <v>46301.66653012732</v>
+        <v>46301.66653040509</v>
       </c>
       <c r="S822">
         <v>13</v>
@@ -54089,16 +54095,16 @@
     </row>
     <row r="823" spans="1:33">
       <c r="A823">
-        <v>2834</v>
+        <v>3053</v>
       </c>
       <c r="B823" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="C823" t="s">
         <v>141</v>
       </c>
       <c r="D823" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E823" t="s">
         <v>150</v>
@@ -54128,7 +54134,7 @@
         <v>221</v>
       </c>
       <c r="O823">
-        <v>17385204</v>
+        <v>17194063</v>
       </c>
       <c r="P823" t="s">
         <v>230</v>
@@ -54163,16 +54169,16 @@
     </row>
     <row r="824" spans="1:33">
       <c r="A824">
-        <v>3053</v>
+        <v>3325</v>
       </c>
       <c r="B824" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="C824" t="s">
         <v>141</v>
       </c>
       <c r="D824" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E824" t="s">
         <v>150</v>
@@ -54202,7 +54208,7 @@
         <v>221</v>
       </c>
       <c r="O824">
-        <v>17194063</v>
+        <v>17863924</v>
       </c>
       <c r="P824" t="s">
         <v>230</v>
@@ -54211,7 +54217,7 @@
         <v>238</v>
       </c>
       <c r="R824" s="1">
-        <v>46301.66653040509</v>
+        <v>46301.66653059028</v>
       </c>
       <c r="S824">
         <v>13</v>
@@ -54237,10 +54243,10 @@
     </row>
     <row r="825" spans="1:33">
       <c r="A825">
-        <v>3325</v>
+        <v>3840</v>
       </c>
       <c r="B825" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C825" t="s">
         <v>141</v>
@@ -54276,7 +54282,7 @@
         <v>221</v>
       </c>
       <c r="O825">
-        <v>17863924</v>
+        <v>17462572</v>
       </c>
       <c r="P825" t="s">
         <v>230</v>
@@ -54285,7 +54291,7 @@
         <v>238</v>
       </c>
       <c r="R825" s="1">
-        <v>46301.66653059028</v>
+        <v>46301.66653078704</v>
       </c>
       <c r="S825">
         <v>13</v>
@@ -54311,10 +54317,10 @@
     </row>
     <row r="826" spans="1:33">
       <c r="A826">
-        <v>3840</v>
+        <v>3842</v>
       </c>
       <c r="B826" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C826" t="s">
         <v>141</v>
@@ -54323,7 +54329,7 @@
         <v>145</v>
       </c>
       <c r="E826" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F826" t="s">
         <v>147</v>
@@ -54350,7 +54356,7 @@
         <v>221</v>
       </c>
       <c r="O826">
-        <v>17462572</v>
+        <v>17462602</v>
       </c>
       <c r="P826" t="s">
         <v>230</v>
@@ -54359,7 +54365,7 @@
         <v>238</v>
       </c>
       <c r="R826" s="1">
-        <v>46301.66653078704</v>
+        <v>46301.6665309838</v>
       </c>
       <c r="S826">
         <v>13</v>
@@ -54385,10 +54391,10 @@
     </row>
     <row r="827" spans="1:33">
       <c r="A827">
-        <v>3842</v>
+        <v>4758</v>
       </c>
       <c r="B827" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C827" t="s">
         <v>141</v>
@@ -54397,7 +54403,7 @@
         <v>145</v>
       </c>
       <c r="E827" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F827" t="s">
         <v>147</v>
@@ -54424,7 +54430,7 @@
         <v>221</v>
       </c>
       <c r="O827">
-        <v>17462602</v>
+        <v>17386966</v>
       </c>
       <c r="P827" t="s">
         <v>230</v>
@@ -54433,7 +54439,7 @@
         <v>238</v>
       </c>
       <c r="R827" s="1">
-        <v>46301.6665309838</v>
+        <v>46301.66653113426</v>
       </c>
       <c r="S827">
         <v>13</v>
@@ -54459,10 +54465,10 @@
     </row>
     <row r="828" spans="1:33">
       <c r="A828">
-        <v>4758</v>
+        <v>4759</v>
       </c>
       <c r="B828" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C828" t="s">
         <v>141</v>
@@ -54498,7 +54504,7 @@
         <v>221</v>
       </c>
       <c r="O828">
-        <v>17386966</v>
+        <v>17293731</v>
       </c>
       <c r="P828" t="s">
         <v>230</v>
@@ -54507,7 +54513,7 @@
         <v>238</v>
       </c>
       <c r="R828" s="1">
-        <v>46301.66653113426</v>
+        <v>46301.66653133101</v>
       </c>
       <c r="S828">
         <v>13</v>
@@ -54533,10 +54539,10 @@
     </row>
     <row r="829" spans="1:33">
       <c r="A829">
-        <v>4759</v>
+        <v>4760</v>
       </c>
       <c r="B829" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C829" t="s">
         <v>141</v>
@@ -54548,7 +54554,7 @@
         <v>150</v>
       </c>
       <c r="F829" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G829">
         <v>5731</v>
@@ -54572,7 +54578,7 @@
         <v>221</v>
       </c>
       <c r="O829">
-        <v>17293731</v>
+        <v>17293771</v>
       </c>
       <c r="P829" t="s">
         <v>230</v>
@@ -54581,7 +54587,7 @@
         <v>238</v>
       </c>
       <c r="R829" s="1">
-        <v>46301.66653133101</v>
+        <v>46301.6665315162</v>
       </c>
       <c r="S829">
         <v>13</v>
@@ -54607,67 +54613,67 @@
     </row>
     <row r="830" spans="1:33">
       <c r="A830">
-        <v>4760</v>
+        <v>2371</v>
       </c>
       <c r="B830" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="C830" t="s">
         <v>141</v>
       </c>
       <c r="D830" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E830" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F830" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G830">
-        <v>5731</v>
+        <v>6788</v>
       </c>
       <c r="H830">
         <v>0</v>
       </c>
       <c r="I830" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="J830" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="L830" s="1">
-        <v>46296</v>
+        <v>46309</v>
       </c>
       <c r="M830" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N830" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O830">
-        <v>17293771</v>
+        <v>17540563</v>
       </c>
       <c r="P830" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q830" t="s">
         <v>238</v>
       </c>
       <c r="R830" s="1">
-        <v>46301.6665315162</v>
+        <v>46309.75407569444</v>
       </c>
       <c r="S830">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="T830" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="U830" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="W830" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="AA830">
         <v>0</v>
@@ -54676,7 +54682,7 @@
         <v>259</v>
       </c>
       <c r="AG830" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="831" spans="1:33">
@@ -55666,7 +55672,7 @@
         <v>46302</v>
       </c>
       <c r="M845" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N845" t="s">
         <v>220</v>

--- a/dados/base/bpo.xlsx
+++ b/dados/base/bpo.xlsx
@@ -5322,7 +5322,7 @@
         <v>142</v>
       </c>
       <c r="E64" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F64" t="s">
         <v>147</v>
@@ -5446,7 +5446,7 @@
         <v>142</v>
       </c>
       <c r="E66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F66" t="s">
         <v>147</v>
@@ -10902,7 +10902,7 @@
         <v>142</v>
       </c>
       <c r="E154" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F154" t="s">
         <v>147</v>
@@ -15724,7 +15724,7 @@
         <v>142</v>
       </c>
       <c r="E222" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F222" t="s">
         <v>147</v>
@@ -15872,7 +15872,7 @@
         <v>142</v>
       </c>
       <c r="E224" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F224" t="s">
         <v>147</v>
@@ -16020,7 +16020,7 @@
         <v>142</v>
       </c>
       <c r="E226" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F226" t="s">
         <v>147</v>
@@ -56567,7 +56567,7 @@
         <v>142</v>
       </c>
       <c r="E806" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F806" t="s">
         <v>147</v>
@@ -56703,7 +56703,7 @@
         <v>142</v>
       </c>
       <c r="E808" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F808" t="s">
         <v>147</v>
@@ -56771,7 +56771,7 @@
         <v>142</v>
       </c>
       <c r="E809" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F809" t="s">
         <v>147</v>
@@ -56839,7 +56839,7 @@
         <v>142</v>
       </c>
       <c r="E810" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F810" t="s">
         <v>147</v>
@@ -56907,7 +56907,7 @@
         <v>142</v>
       </c>
       <c r="E811" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F811" t="s">
         <v>147</v>
@@ -57043,7 +57043,7 @@
         <v>142</v>
       </c>
       <c r="E813" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F813" t="s">
         <v>147</v>
@@ -57111,7 +57111,7 @@
         <v>142</v>
       </c>
       <c r="E814" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F814" t="s">
         <v>147</v>
@@ -57247,7 +57247,7 @@
         <v>142</v>
       </c>
       <c r="E816" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F816" t="s">
         <v>147</v>
@@ -57383,7 +57383,7 @@
         <v>142</v>
       </c>
       <c r="E818" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F818" t="s">
         <v>147</v>
@@ -57531,7 +57531,7 @@
         <v>142</v>
       </c>
       <c r="E820" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F820" t="s">
         <v>147</v>
@@ -57679,7 +57679,7 @@
         <v>142</v>
       </c>
       <c r="E822" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F822" t="s">
         <v>147</v>
@@ -57753,7 +57753,7 @@
         <v>142</v>
       </c>
       <c r="E823" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F823" t="s">
         <v>147</v>
@@ -57969,7 +57969,7 @@
         <v>142</v>
       </c>
       <c r="E826" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F826" t="s">
         <v>147</v>
@@ -58117,7 +58117,7 @@
         <v>142</v>
       </c>
       <c r="E828" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F828" t="s">
         <v>147</v>
@@ -58525,7 +58525,7 @@
         <v>142</v>
       </c>
       <c r="E834" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F834" t="s">
         <v>147</v>
@@ -59551,7 +59551,7 @@
         <v>142</v>
       </c>
       <c r="E849" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F849" t="s">
         <v>147</v>
@@ -59687,7 +59687,7 @@
         <v>142</v>
       </c>
       <c r="E851" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F851" t="s">
         <v>147</v>
@@ -59755,7 +59755,7 @@
         <v>142</v>
       </c>
       <c r="E852" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F852" t="s">
         <v>147</v>
@@ -60347,7 +60347,7 @@
         <v>142</v>
       </c>
       <c r="E860" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F860" t="s">
         <v>147</v>
